--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 17.07.2026 15:59</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 03:47</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -61,31 +61,34 @@
     <t>M4A4 | Desolate Space (Factory New)</t>
   </si>
   <si>
+    <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
+  </si>
+  <si>
     <t>AK-47 | Point Disarray (Factory New)</t>
   </si>
   <si>
-    <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
-  </si>
-  <si>
     <t>AWP | Containment Breach (Field-Tested)</t>
   </si>
   <si>
     <t>AK-47 | Legion of Anubis (Factory New)</t>
   </si>
   <si>
+    <t>MAC-10 | Fade (Factory New)</t>
+  </si>
+  <si>
+    <t>AWP | Neo-Noir (Factory New)</t>
+  </si>
+  <si>
     <t>USP-S | Orion (Minimal Wear)</t>
   </si>
   <si>
-    <t>MAC-10 | Fade (Factory New)</t>
-  </si>
-  <si>
-    <t>AWP | Neo-Noir (Factory New)</t>
+    <t>AWP | Containment Breach (Well-Worn)</t>
   </si>
   <si>
     <t>M4A1-S | Vaporwave (Field-Tested)</t>
   </si>
   <si>
-    <t>AWP | Containment Breach (Well-Worn)</t>
+    <t>P250 | Apep's Curse (Field-Tested)</t>
   </si>
   <si>
     <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
@@ -94,9 +97,6 @@
     <t>Desert Eagle | Starcade (Field-Tested)</t>
   </si>
   <si>
-    <t>P250 | Apep's Curse (Field-Tested)</t>
-  </si>
-  <si>
     <t>Dual Berettas | Emerald (Factory New)</t>
   </si>
   <si>
@@ -124,18 +124,18 @@
     <t>FAMAS | Styx (Minimal Wear)</t>
   </si>
   <si>
+    <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
+  </si>
+  <si>
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
-    <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
+    <t>MP9 | Music Box (Factory New)</t>
   </si>
   <si>
     <t>Tec-9 | Brass (Minimal Wear)</t>
   </si>
   <si>
-    <t>MP9 | Music Box (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -145,18 +145,18 @@
     <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
   </si>
   <si>
+    <t>Michael Syfers  | FBI Sniper</t>
+  </si>
+  <si>
     <t>Sticker | Great Wave (Foil)</t>
   </si>
   <si>
-    <t>Michael Syfers  | FBI Sniper</t>
+    <t>M4A4 | Evil Daimyo (Factory New)</t>
   </si>
   <si>
     <t>SG 553 | Candy Apple (Factory New)</t>
   </si>
   <si>
-    <t>M4A4 | Evil Daimyo (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
@@ -193,57 +193,57 @@
     <t>Markus Delrow | FBI HRT</t>
   </si>
   <si>
+    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | Great Wave (Holo)</t>
   </si>
   <si>
-    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
+    <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>SG 553 | Integrale (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Rezan The Ready | Sabre</t>
+  </si>
+  <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
+    <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Slingshot | Phoenix</t>
   </si>
   <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>SG 553 | Integrale (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Rezan The Ready | Sabre</t>
-  </si>
-  <si>
     <t>Rezan the Redshirt | Sabre</t>
   </si>
   <si>
-    <t>Blackwolf | Sabre</t>
-  </si>
-  <si>
-    <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
+    <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Liquid Fire</t>
   </si>
   <si>
     <t>Prof. Shahmat | Elite Crew</t>
   </si>
   <si>
-    <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Liquid Fire</t>
+    <t>AK-47 | Crossfade (Factory New)</t>
   </si>
   <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>AK-47 | Crossfade (Factory New)</t>
-  </si>
-  <si>
     <t>AK-47 | Slate (Minimal Wear)</t>
   </si>
   <si>
+    <t>Maximus | Sabre</t>
+  </si>
+  <si>
     <t>Tec-9 | Brass (Field-Tested)</t>
   </si>
   <si>
-    <t>Maximus | Sabre</t>
-  </si>
-  <si>
     <t>Dragomir | Sabre</t>
   </si>
   <si>
@@ -256,105 +256,105 @@
     <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
   </si>
   <si>
     <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
     <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+    <t>AWP | Black Nile (Minimal Wear)</t>
   </si>
   <si>
     <t>MAC-10 | Strats (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>R8 Revolver | Blaze (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>AWP | Black Nile (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>R8 Revolver | Blaze (Factory New)</t>
+    <t>P250 | Epicenter (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
     <t>Sticker | Stone Scales (Foil)</t>
   </si>
   <si>
-    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Gold Web (Foil)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
+    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
     <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>AK-47 | Slate (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>AK-47 | Slate (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | Team Liquid (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>M4A4 | Turbine (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Perfect World (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>M4A4 | Turbine (Minimal Wear)</t>
+    <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Galil AR | Tuxedo (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>XM1014 | Seasons (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
+    <t>Five-SeveN | Retrobution (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Five-SeveN | Retrobution (Minimal Wear)</t>
-  </si>
-  <si>
     <t>P2000 | Amber Fade (Factory New)</t>
   </si>
   <si>
@@ -388,13 +388,13 @@
     <t>Sticker | Coiled Strike (Holo)</t>
   </si>
   <si>
+    <t>Sticker | Enemy Spotted (Holo)</t>
+  </si>
+  <si>
+    <t>FAMAS | Teardown (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Mastermind (Holo)</t>
-  </si>
-  <si>
-    <t>FAMAS | Teardown (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Enemy Spotted (Holo)</t>
   </si>
   <si>
     <t>Sticker | Web Stuck (Holo)</t>
@@ -816,7 +816,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.35</v>
+        <v>81.58</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -825,7 +825,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>11.4548</v>
+        <v>11.534</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -865,22 +865,22 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C6">
-        <v>94.1</v>
+        <v>91.76</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>10573.81</v>
+        <v>10643.81</v>
       </c>
       <c r="F6">
-        <v>7193.61</v>
+        <v>7231.59</v>
       </c>
       <c r="G6">
-        <v>7050.43</v>
+        <v>7145.31</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -897,22 +897,22 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="C7">
-        <v>86.31</v>
+        <v>84.8</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>9094.08</v>
+        <v>9065.61</v>
       </c>
       <c r="F7">
-        <v>6408.85</v>
+        <v>6222.36</v>
       </c>
       <c r="G7">
-        <v>6271.5</v>
+        <v>6228.36</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -929,22 +929,22 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>198</v>
       </c>
       <c r="C8">
-        <v>84.66</v>
+        <v>81.48</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>9003.36</v>
+        <v>8905.52</v>
       </c>
       <c r="F8">
-        <v>6179.64</v>
+        <v>6343.7</v>
       </c>
       <c r="G8">
-        <v>6185.59</v>
+        <v>6314.87</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -961,22 +961,22 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C9">
-        <v>79.38</v>
+        <v>80.34</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>8468.53</v>
+        <v>8524.78</v>
       </c>
       <c r="F9">
-        <v>5883.19</v>
+        <v>5882.34</v>
       </c>
       <c r="G9">
-        <v>5853.4</v>
+        <v>5824.67</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -993,22 +993,22 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C10">
-        <v>60.25</v>
+        <v>59.89</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>6398.65</v>
+        <v>6620.17</v>
       </c>
       <c r="F10">
-        <v>4417.09</v>
+        <v>4447.51</v>
       </c>
       <c r="G10">
-        <v>4444.46</v>
+        <v>4498.26</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1025,22 +1025,22 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="C11">
-        <v>58.87</v>
+        <v>58.25</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>6455.01</v>
+        <v>6669.88</v>
       </c>
       <c r="F11">
-        <v>4421.55</v>
+        <v>4380.61</v>
       </c>
       <c r="G11">
-        <v>4352.71</v>
+        <v>4302.18</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1057,22 +1057,22 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C12">
-        <v>58.55</v>
+        <v>57.38</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>6185.59</v>
+        <v>6665.96</v>
       </c>
       <c r="F12">
-        <v>4348.24</v>
+        <v>4256.05</v>
       </c>
       <c r="G12">
-        <v>4255.23</v>
+        <v>4186.73</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1089,22 +1089,22 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="C13">
-        <v>56.79</v>
+        <v>56.59</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>6547.33</v>
+        <v>6483.03</v>
       </c>
       <c r="F13">
-        <v>4238.16</v>
+        <v>4452.12</v>
       </c>
       <c r="G13">
-        <v>4169.55</v>
+        <v>4382.69</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1121,22 +1121,22 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="C14">
-        <v>54.6</v>
+        <v>52</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>5938.28</v>
+        <v>6024.21</v>
       </c>
       <c r="F14">
-        <v>4061.76</v>
+        <v>4016.83</v>
       </c>
       <c r="G14">
-        <v>4066.34</v>
+        <v>3967.7</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1153,22 +1153,22 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>86</v>
+        <v>266</v>
       </c>
       <c r="C15">
-        <v>52.03</v>
+        <v>51.19</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>5878.72</v>
+        <v>5951.66</v>
       </c>
       <c r="F15">
-        <v>3989.82</v>
+        <v>4036.9</v>
       </c>
       <c r="G15">
-        <v>3946.18</v>
+        <v>4087.42</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1185,22 +1185,22 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C16">
-        <v>48.6</v>
+        <v>49.48</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>5399.56</v>
+        <v>5863.42</v>
       </c>
       <c r="F16">
-        <v>3659.69</v>
+        <v>3667.81</v>
       </c>
       <c r="G16">
-        <v>3625.33</v>
+        <v>3748.55</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1217,22 +1217,22 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="C17">
-        <v>48.15</v>
+        <v>48.6</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>5126.37</v>
+        <v>5425.13</v>
       </c>
       <c r="F17">
-        <v>3688.45</v>
+        <v>3684.77</v>
       </c>
       <c r="G17">
-        <v>3545.26</v>
+        <v>3638.63</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1249,22 +1249,22 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>62</v>
+        <v>181</v>
       </c>
       <c r="C18">
-        <v>47.28</v>
+        <v>48.15</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>6316.41</v>
+        <v>5214.64</v>
       </c>
       <c r="F18">
-        <v>3642.63</v>
+        <v>3713.95</v>
       </c>
       <c r="G18">
-        <v>3665.54</v>
+        <v>3564.01</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1281,7 +1281,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19">
         <v>37.68</v>
@@ -1290,13 +1290,13 @@
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>4465.65</v>
+        <v>4496.53</v>
       </c>
       <c r="F19">
-        <v>2695.2</v>
+        <v>2708.18</v>
       </c>
       <c r="G19">
-        <v>2958.77</v>
+        <v>2960.78</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1316,19 +1316,19 @@
         <v>67</v>
       </c>
       <c r="C20">
-        <v>37.15</v>
+        <v>37.46</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>4120.41</v>
+        <v>4139.44</v>
       </c>
       <c r="F20">
-        <v>2856.48</v>
+        <v>2876.23</v>
       </c>
       <c r="G20">
-        <v>2588.78</v>
+        <v>2743.94</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1345,7 +1345,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21">
         <v>35.45</v>
@@ -1354,13 +1354,13 @@
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>4384.21</v>
+        <v>4414.52</v>
       </c>
       <c r="F21">
-        <v>2662.1</v>
+        <v>2680.5</v>
       </c>
       <c r="G21">
-        <v>3081.23</v>
+        <v>3021.91</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1377,22 +1377,22 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C22">
-        <v>33.07</v>
+        <v>32.96</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>3524.53</v>
+        <v>3529.98</v>
       </c>
       <c r="F22">
-        <v>2382.6</v>
+        <v>2429.52</v>
       </c>
       <c r="G22">
-        <v>2438.38</v>
+        <v>2422.14</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1409,22 +1409,22 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C23">
-        <v>32.37</v>
+        <v>32.25</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>3513.65</v>
+        <v>3530.79</v>
       </c>
       <c r="F23">
-        <v>2519.94</v>
+        <v>2537.36</v>
       </c>
       <c r="G23">
-        <v>2376.87</v>
+        <v>2399.07</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1441,22 +1441,22 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C24">
-        <v>28.76</v>
+        <v>28.47</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>3129.22</v>
+        <v>3152.36</v>
       </c>
       <c r="F24">
-        <v>2170.68</v>
+        <v>2191.46</v>
       </c>
       <c r="G24">
-        <v>2107.68</v>
+        <v>2104.96</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1473,22 +1473,22 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C25">
-        <v>25.82</v>
+        <v>25.78</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>2677.44</v>
+        <v>2811.07</v>
       </c>
       <c r="F25">
-        <v>1904.7</v>
+        <v>1923.64</v>
       </c>
       <c r="G25">
-        <v>1901.5</v>
+        <v>1914.64</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1505,22 +1505,22 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C26">
-        <v>21.17</v>
+        <v>21.18</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>2361.98</v>
+        <v>2368.85</v>
       </c>
       <c r="F26">
-        <v>1586.38</v>
+        <v>1597.34</v>
       </c>
       <c r="G26">
-        <v>1555.45</v>
+        <v>1568.62</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1537,7 +1537,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C27">
         <v>19.93</v>
@@ -1546,13 +1546,13 @@
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>2347.89</v>
+        <v>2307.38</v>
       </c>
       <c r="F27">
-        <v>1464.27</v>
+        <v>1474.16</v>
       </c>
       <c r="G27">
-        <v>1492.56</v>
+        <v>1497.11</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1569,22 +1569,22 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="C28">
-        <v>19.63</v>
+        <v>19.53</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>2166.22</v>
+        <v>2267.12</v>
       </c>
       <c r="F28">
-        <v>1424.98</v>
+        <v>1487.89</v>
       </c>
       <c r="G28">
-        <v>1407.79</v>
+        <v>1430.1</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1601,22 +1601,22 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C29">
-        <v>19.16</v>
+        <v>19.5</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>2129.45</v>
+        <v>2125.25</v>
       </c>
       <c r="F29">
-        <v>1466.21</v>
+        <v>1384.08</v>
       </c>
       <c r="G29">
-        <v>1420.4</v>
+        <v>1417.53</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1633,22 +1633,22 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C30">
-        <v>15.81</v>
+        <v>16.26</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>1956.37</v>
+        <v>1917.07</v>
       </c>
       <c r="F30">
-        <v>1241.7</v>
+        <v>1265.16</v>
       </c>
       <c r="G30">
-        <v>1269.08</v>
+        <v>1239.91</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1665,22 +1665,22 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C31">
-        <v>15.31</v>
+        <v>15.64</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>1942.28</v>
+        <v>1760.2</v>
       </c>
       <c r="F31">
-        <v>1281.56</v>
+        <v>1250.29</v>
       </c>
       <c r="G31">
-        <v>1271.48</v>
+        <v>1261.7</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1706,13 +1706,13 @@
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>1495.31</v>
+        <v>1499.3</v>
       </c>
       <c r="F32">
-        <v>993.13</v>
+        <v>1000</v>
       </c>
       <c r="G32">
-        <v>947.08</v>
+        <v>947.86</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -1729,7 +1729,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>1696</v>
+        <v>1746</v>
       </c>
       <c r="C33">
         <v>13.48</v>
@@ -1738,13 +1738,13 @@
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>1453.84</v>
+        <v>1511.88</v>
       </c>
       <c r="F33">
-        <v>1008.02</v>
+        <v>1009.11</v>
       </c>
       <c r="G33">
-        <v>1006.65</v>
+        <v>1017.3</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -1764,19 +1764,19 @@
         <v>62</v>
       </c>
       <c r="C34">
-        <v>13.19</v>
+        <v>13.26</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>1495.31</v>
+        <v>1441.75</v>
       </c>
       <c r="F34">
-        <v>969.08</v>
+        <v>975.78</v>
       </c>
       <c r="G34">
-        <v>1041.13</v>
+        <v>1037.94</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -1793,22 +1793,22 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>1420</v>
       </c>
       <c r="C35">
-        <v>13.16</v>
+        <v>13.03</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>1408.37</v>
+        <v>1564.7</v>
       </c>
       <c r="F35">
-        <v>1027.15</v>
+        <v>957.32</v>
       </c>
       <c r="G35">
-        <v>970.68</v>
+        <v>945.79</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -1825,22 +1825,22 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>1390</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>13.05</v>
+        <v>12.62</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>1524.29</v>
+        <v>1418.11</v>
       </c>
       <c r="F36">
-        <v>972.51</v>
+        <v>1033.45</v>
       </c>
       <c r="G36">
-        <v>974.8</v>
+        <v>977.39</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -1857,22 +1857,22 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="C37">
-        <v>12.57</v>
+        <v>12.6</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>1406.08</v>
+        <v>1417.3</v>
       </c>
       <c r="F37">
-        <v>900.35</v>
+        <v>945.79</v>
       </c>
       <c r="G37">
-        <v>942.62</v>
+        <v>966.55</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -1889,22 +1889,22 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>361</v>
+        <v>86</v>
       </c>
       <c r="C38">
-        <v>12.35</v>
+        <v>12.52</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1407.57</v>
+        <v>1414.99</v>
       </c>
       <c r="F38">
-        <v>961.06</v>
+        <v>906.57</v>
       </c>
       <c r="G38">
-        <v>962.2</v>
+        <v>944.52</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1921,22 +1921,22 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C39">
-        <v>11.64</v>
+        <v>10.91</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1244.79</v>
+        <v>1253.4</v>
       </c>
       <c r="F39">
-        <v>859.11</v>
+        <v>862.74</v>
       </c>
       <c r="G39">
-        <v>852.01</v>
+        <v>857.9</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -1953,22 +1953,22 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="C40">
-        <v>10.97</v>
+        <v>10.82</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1288.55</v>
+        <v>1262.05</v>
       </c>
       <c r="F40">
-        <v>813.29</v>
+        <v>825.6</v>
       </c>
       <c r="G40">
-        <v>813.06</v>
+        <v>807.38</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -1985,22 +1985,22 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C41">
-        <v>10.75</v>
+        <v>10.71</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1184.43</v>
+        <v>1180.85</v>
       </c>
       <c r="F41">
-        <v>822.23</v>
+        <v>823.07</v>
       </c>
       <c r="G41">
-        <v>823.6</v>
+        <v>823.53</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2017,7 +2017,7 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42">
         <v>10.46</v>
@@ -2026,13 +2026,13 @@
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1091.3</v>
+        <v>1097.23</v>
       </c>
       <c r="F42">
-        <v>743.42</v>
+        <v>748.56</v>
       </c>
       <c r="G42">
-        <v>787.98</v>
+        <v>793.42</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2052,19 +2052,19 @@
         <v>202</v>
       </c>
       <c r="C43">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1236.89</v>
+        <v>1239.91</v>
       </c>
       <c r="F43">
-        <v>767.47</v>
+        <v>772.78</v>
       </c>
       <c r="G43">
-        <v>734.83</v>
+        <v>741.06</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2090,13 +2090,13 @@
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1171.94</v>
+        <v>1153.28</v>
       </c>
       <c r="F44">
-        <v>753.61</v>
+        <v>758.71</v>
       </c>
       <c r="G44">
-        <v>813.29</v>
+        <v>818.91</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2113,22 +2113,22 @@
         <v>54</v>
       </c>
       <c r="B45">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C45">
-        <v>10.19</v>
+        <v>10.2</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1124.98</v>
+        <v>1129.64</v>
       </c>
       <c r="F45">
-        <v>710.08</v>
+        <v>736.91</v>
       </c>
       <c r="G45">
-        <v>720.39</v>
+        <v>723.07</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2145,22 +2145,22 @@
         <v>55</v>
       </c>
       <c r="B46">
-        <v>1261</v>
+        <v>1302</v>
       </c>
       <c r="C46">
-        <v>10.14</v>
+        <v>9.92</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1124.98</v>
+        <v>1114.65</v>
       </c>
       <c r="F46">
-        <v>775.95</v>
+        <v>761.24</v>
       </c>
       <c r="G46">
-        <v>760.6</v>
+        <v>760.09</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2180,19 +2180,19 @@
         <v>92</v>
       </c>
       <c r="C47">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1009.86</v>
+        <v>1016.84</v>
       </c>
       <c r="F47">
-        <v>731.96</v>
+        <v>713.95</v>
       </c>
       <c r="G47">
-        <v>751.43</v>
+        <v>748.56</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2209,7 +2209,7 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="C48">
         <v>9.69</v>
@@ -2218,13 +2218,13 @@
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1141.36</v>
+        <v>1178.43</v>
       </c>
       <c r="F48">
-        <v>748.91</v>
+        <v>747.4</v>
       </c>
       <c r="G48">
-        <v>719.36</v>
+        <v>715.11</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2241,22 +2241,22 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C49">
-        <v>9.31</v>
+        <v>9.28</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>944.91</v>
+        <v>943.6</v>
       </c>
       <c r="F49">
-        <v>658.42</v>
+        <v>661.36</v>
       </c>
       <c r="G49">
-        <v>672.17</v>
+        <v>677.97</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2273,22 +2273,22 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="C50">
-        <v>8.75</v>
+        <v>8.63</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>927.72</v>
+        <v>972.78</v>
       </c>
       <c r="F50">
-        <v>652.69</v>
+        <v>640.14</v>
       </c>
       <c r="G50">
-        <v>640.32</v>
+        <v>653.98</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2305,22 +2305,22 @@
         <v>60</v>
       </c>
       <c r="B51">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C51">
-        <v>8.58</v>
+        <v>8.28</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>932.42</v>
+        <v>935.64</v>
       </c>
       <c r="F51">
-        <v>605.96</v>
+        <v>678.2</v>
       </c>
       <c r="G51">
-        <v>628.87</v>
+        <v>632.06</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2337,22 +2337,22 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C52">
-        <v>8.28</v>
+        <v>8.25</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>994.28</v>
+        <v>938.87</v>
       </c>
       <c r="F52">
-        <v>673.54</v>
+        <v>609</v>
       </c>
       <c r="G52">
-        <v>627.72</v>
+        <v>690.66</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2369,22 +2369,22 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>835</v>
+        <v>261</v>
       </c>
       <c r="C53">
-        <v>8.26</v>
+        <v>8.23</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>976.98</v>
+        <v>852.13</v>
       </c>
       <c r="F53">
-        <v>599.43</v>
+        <v>681.08</v>
       </c>
       <c r="G53">
-        <v>585.34</v>
+        <v>665.51</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2401,22 +2401,22 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="C54">
-        <v>8.22</v>
+        <v>8.09</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>886.95</v>
+        <v>822.14</v>
       </c>
       <c r="F54">
-        <v>676.41</v>
+        <v>576.7</v>
       </c>
       <c r="G54">
-        <v>662.09</v>
+        <v>584.77</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2433,22 +2433,22 @@
         <v>64</v>
       </c>
       <c r="B55">
-        <v>135</v>
+        <v>1424</v>
       </c>
       <c r="C55">
-        <v>8.08</v>
+        <v>7.99</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>810.2</v>
+        <v>902.54</v>
       </c>
       <c r="F55">
-        <v>572.74</v>
+        <v>598.61</v>
       </c>
       <c r="G55">
-        <v>581.9</v>
+        <v>578.78</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2465,22 +2465,22 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>1392</v>
+        <v>834</v>
       </c>
       <c r="C56">
-        <v>7.96</v>
+        <v>7.81</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>944.91</v>
+        <v>906.46</v>
       </c>
       <c r="F56">
-        <v>595.65</v>
+        <v>599.77</v>
       </c>
       <c r="G56">
-        <v>572.74</v>
+        <v>583.51</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2497,22 +2497,22 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>740</v>
+        <v>143</v>
       </c>
       <c r="C57">
-        <v>7.96</v>
+        <v>7.67</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>882.25</v>
+        <v>842.67</v>
       </c>
       <c r="F57">
-        <v>581.9</v>
+        <v>553.86</v>
       </c>
       <c r="G57">
-        <v>572.63</v>
+        <v>571.51</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2529,22 +2529,22 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C58">
-        <v>7.91</v>
+        <v>7.62</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>889.35</v>
+        <v>981.43</v>
       </c>
       <c r="F58">
-        <v>595.65</v>
+        <v>600.11</v>
       </c>
       <c r="G58">
-        <v>578.24</v>
+        <v>589.39</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2561,22 +2561,22 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>144</v>
+        <v>745</v>
       </c>
       <c r="C59">
-        <v>7.68</v>
+        <v>7.36</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>836.89</v>
+        <v>834.02</v>
       </c>
       <c r="F59">
-        <v>550.17</v>
+        <v>582.47</v>
       </c>
       <c r="G59">
-        <v>568.16</v>
+        <v>575.55</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2593,22 +2593,22 @@
         <v>69</v>
       </c>
       <c r="B60">
-        <v>1151</v>
+        <v>209</v>
       </c>
       <c r="C60">
-        <v>7.63</v>
+        <v>7.1</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>828.98</v>
+        <v>755.13</v>
       </c>
       <c r="F60">
-        <v>565.87</v>
+        <v>551.21</v>
       </c>
       <c r="G60">
-        <v>542.96</v>
+        <v>546.71</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -2625,22 +2625,22 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>208</v>
+        <v>8</v>
       </c>
       <c r="C61">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>769.53</v>
+        <v>848.9</v>
       </c>
       <c r="F61">
-        <v>549.6</v>
+        <v>521.57</v>
       </c>
       <c r="G61">
-        <v>542.96</v>
+        <v>516.49</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -2657,7 +2657,7 @@
         <v>71</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>1147</v>
       </c>
       <c r="C62">
         <v>7.07</v>
@@ -2666,13 +2666,13 @@
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>847.77</v>
+        <v>906.46</v>
       </c>
       <c r="F62">
-        <v>520.39</v>
+        <v>547.87</v>
       </c>
       <c r="G62">
-        <v>513.98</v>
+        <v>546.71</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -2689,22 +2689,22 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>56</v>
+        <v>388</v>
       </c>
       <c r="C63">
-        <v>6.9</v>
+        <v>6.78</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>726.46</v>
+        <v>782.7</v>
       </c>
       <c r="F63">
-        <v>512.03</v>
+        <v>489.04</v>
       </c>
       <c r="G63">
-        <v>458.19</v>
+        <v>484.43</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -2721,22 +2721,22 @@
         <v>73</v>
       </c>
       <c r="B64">
-        <v>393</v>
+        <v>57</v>
       </c>
       <c r="C64">
-        <v>6.85</v>
+        <v>6.57</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>769.53</v>
+        <v>731.49</v>
       </c>
       <c r="F64">
-        <v>486.83</v>
+        <v>510.84</v>
       </c>
       <c r="G64">
-        <v>486.83</v>
+        <v>461.36</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -2753,22 +2753,22 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>1295</v>
+        <v>1310</v>
       </c>
       <c r="C65">
-        <v>6.82</v>
+        <v>6.55</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>738.95</v>
+        <v>748.79</v>
       </c>
       <c r="F65">
-        <v>511.92</v>
+        <v>515.45</v>
       </c>
       <c r="G65">
-        <v>501.72</v>
+        <v>519.03</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -2785,22 +2785,22 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>76</v>
+        <v>1184</v>
       </c>
       <c r="C66">
-        <v>6.71</v>
+        <v>6.51</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>782.82</v>
+        <v>783.5</v>
       </c>
       <c r="F66">
-        <v>475.95</v>
+        <v>472.89</v>
       </c>
       <c r="G66">
-        <v>576.86</v>
+        <v>471.74</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -2817,22 +2817,22 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>1144</v>
+        <v>77</v>
       </c>
       <c r="C67">
-        <v>6.55</v>
+        <v>6.49</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>728.87</v>
+        <v>786.73</v>
       </c>
       <c r="F67">
-        <v>469.65</v>
+        <v>479.01</v>
       </c>
       <c r="G67">
-        <v>477.67</v>
+        <v>579.58</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -2849,22 +2849,22 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>873</v>
+        <v>935</v>
       </c>
       <c r="C68">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>782.82</v>
+        <v>709.46</v>
       </c>
       <c r="F68">
-        <v>479.96</v>
+        <v>471.74</v>
       </c>
       <c r="G68">
-        <v>470.68</v>
+        <v>475.09</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -2890,13 +2890,13 @@
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>552.69</v>
+        <v>554.9</v>
       </c>
       <c r="F69">
-        <v>418.1</v>
+        <v>420.88</v>
       </c>
       <c r="G69">
-        <v>395.19</v>
+        <v>397.35</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -2922,13 +2922,13 @@
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>679.5</v>
+        <v>684.2</v>
       </c>
       <c r="F70">
-        <v>462.2</v>
+        <v>463.9</v>
       </c>
       <c r="G70">
-        <v>456.82</v>
+        <v>459.17</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -2948,19 +2948,19 @@
         <v>279</v>
       </c>
       <c r="C71">
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>633.34</v>
+        <v>627.45</v>
       </c>
       <c r="F71">
-        <v>507.45</v>
+        <v>509.8</v>
       </c>
       <c r="G71">
-        <v>481.1</v>
+        <v>482.12</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -2977,22 +2977,22 @@
         <v>81</v>
       </c>
       <c r="B72">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C72">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>600.46</v>
+        <v>689.73</v>
       </c>
       <c r="F72">
-        <v>524.63</v>
+        <v>417.3</v>
       </c>
       <c r="G72">
-        <v>451.66</v>
+        <v>435.75</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3009,22 +3009,22 @@
         <v>82</v>
       </c>
       <c r="B73">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C73">
-        <v>5.83</v>
+        <v>5.78</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>693.59</v>
+        <v>604.61</v>
       </c>
       <c r="F73">
-        <v>413.29</v>
+        <v>524.8</v>
       </c>
       <c r="G73">
-        <v>432.76</v>
+        <v>459.63</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3041,22 +3041,22 @@
         <v>83</v>
       </c>
       <c r="B74">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="C74">
-        <v>5.76</v>
+        <v>5.61</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>680.3</v>
+        <v>622.72</v>
       </c>
       <c r="F74">
-        <v>431.16</v>
+        <v>458.94</v>
       </c>
       <c r="G74">
-        <v>454.76</v>
+        <v>400.23</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3073,22 +3073,22 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="C75">
-        <v>5.67</v>
+        <v>5.49</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>620.74</v>
+        <v>685.81</v>
       </c>
       <c r="F75">
-        <v>457.05</v>
+        <v>434.14</v>
       </c>
       <c r="G75">
-        <v>399.77</v>
+        <v>457.78</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3105,22 +3105,22 @@
         <v>85</v>
       </c>
       <c r="B76">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C76">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>578.47</v>
+        <v>590.43</v>
       </c>
       <c r="F76">
-        <v>420.28</v>
+        <v>423.07</v>
       </c>
       <c r="G76">
-        <v>426.12</v>
+        <v>426.76</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3137,22 +3137,22 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>888</v>
+        <v>511</v>
       </c>
       <c r="C77">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>597.25</v>
+        <v>568.28</v>
       </c>
       <c r="F77">
-        <v>423.83</v>
+        <v>397.92</v>
       </c>
       <c r="G77">
-        <v>420.39</v>
+        <v>386.39</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3169,7 +3169,7 @@
         <v>87</v>
       </c>
       <c r="B78">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C78">
         <v>5.37</v>
@@ -3178,13 +3178,13 @@
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>618.44</v>
+        <v>601.38</v>
       </c>
       <c r="F78">
-        <v>422.68</v>
+        <v>424.45</v>
       </c>
       <c r="G78">
-        <v>403.78</v>
+        <v>405.07</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3201,22 +3201,22 @@
         <v>88</v>
       </c>
       <c r="B79">
-        <v>512</v>
+        <v>889</v>
       </c>
       <c r="C79">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>573.77</v>
+        <v>603</v>
       </c>
       <c r="F79">
-        <v>395.19</v>
+        <v>422.14</v>
       </c>
       <c r="G79">
-        <v>383.51</v>
+        <v>430.22</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3233,22 +3233,22 @@
         <v>89</v>
       </c>
       <c r="B80">
-        <v>28</v>
+        <v>497</v>
       </c>
       <c r="C80">
-        <v>5.21</v>
+        <v>5.08</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>578.47</v>
+        <v>613.26</v>
       </c>
       <c r="F80">
-        <v>365.41</v>
+        <v>362.17</v>
       </c>
       <c r="G80">
-        <v>395.19</v>
+        <v>392.16</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3265,22 +3265,22 @@
         <v>90</v>
       </c>
       <c r="B81">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="C81">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>586.37</v>
+        <v>567.47</v>
       </c>
       <c r="F81">
-        <v>408.82</v>
+        <v>412.23</v>
       </c>
       <c r="G81">
-        <v>378.01</v>
+        <v>396.77</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3297,22 +3297,22 @@
         <v>91</v>
       </c>
       <c r="B82">
-        <v>498</v>
+        <v>73</v>
       </c>
       <c r="C82">
-        <v>5.02</v>
+        <v>4.92</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>566.78</v>
+        <v>580.16</v>
       </c>
       <c r="F82">
-        <v>360.83</v>
+        <v>386.5</v>
       </c>
       <c r="G82">
-        <v>389.46</v>
+        <v>369.09</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3329,22 +3329,22 @@
         <v>92</v>
       </c>
       <c r="B83">
-        <v>68</v>
+        <v>580</v>
       </c>
       <c r="C83">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>573.77</v>
+        <v>510.03</v>
       </c>
       <c r="F83">
-        <v>385.57</v>
+        <v>362.86</v>
       </c>
       <c r="G83">
-        <v>367.7</v>
+        <v>344.87</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3361,22 +3361,22 @@
         <v>93</v>
       </c>
       <c r="B84">
-        <v>578</v>
+        <v>121</v>
       </c>
       <c r="C84">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>507.22</v>
+        <v>588.81</v>
       </c>
       <c r="F84">
-        <v>361.74</v>
+        <v>411.42</v>
       </c>
       <c r="G84">
-        <v>342.38</v>
+        <v>379.24</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3393,22 +3393,22 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C85">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>562.89</v>
+        <v>550.98</v>
       </c>
       <c r="F85">
-        <v>371.82</v>
+        <v>344.87</v>
       </c>
       <c r="G85">
-        <v>378.01</v>
+        <v>375.89</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -3428,19 +3428,19 @@
         <v>53</v>
       </c>
       <c r="C86">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>525.32</v>
+        <v>521.8</v>
       </c>
       <c r="F86">
-        <v>356.7</v>
+        <v>357.55</v>
       </c>
       <c r="G86">
-        <v>350.52</v>
+        <v>352.94</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -3457,7 +3457,7 @@
         <v>96</v>
       </c>
       <c r="B87">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C87">
         <v>4.66</v>
@@ -3466,13 +3466,13 @@
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>493.13</v>
+        <v>539.91</v>
       </c>
       <c r="F87">
-        <v>364.38</v>
+        <v>356.4</v>
       </c>
       <c r="G87">
-        <v>320.73</v>
+        <v>322.95</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -3489,22 +3489,22 @@
         <v>97</v>
       </c>
       <c r="B88">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C88">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>558.88</v>
+        <v>566.78</v>
       </c>
       <c r="F88">
-        <v>320.73</v>
+        <v>363.32</v>
       </c>
       <c r="G88">
-        <v>373.2</v>
+        <v>380.62</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -3521,22 +3521,22 @@
         <v>98</v>
       </c>
       <c r="B89">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C89">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>472.05</v>
+        <v>468.17</v>
       </c>
       <c r="F89">
-        <v>337.46</v>
+        <v>342.21</v>
       </c>
       <c r="G89">
-        <v>340.21</v>
+        <v>329.87</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -3553,22 +3553,22 @@
         <v>99</v>
       </c>
       <c r="B90">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="C90">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>482.25</v>
+        <v>435.87</v>
       </c>
       <c r="F90">
-        <v>320.28</v>
+        <v>339.56</v>
       </c>
       <c r="G90">
-        <v>289.58</v>
+        <v>334.49</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -3585,7 +3585,7 @@
         <v>100</v>
       </c>
       <c r="B91">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="C91">
         <v>4.45</v>
@@ -3594,13 +3594,13 @@
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>443.87</v>
+        <v>446.94</v>
       </c>
       <c r="F91">
-        <v>338.72</v>
+        <v>355.13</v>
       </c>
       <c r="G91">
-        <v>337.92</v>
+        <v>311.42</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -3617,22 +3617,22 @@
         <v>101</v>
       </c>
       <c r="B92">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="C92">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>446.16</v>
+        <v>475.32</v>
       </c>
       <c r="F92">
-        <v>352.69</v>
+        <v>339.79</v>
       </c>
       <c r="G92">
-        <v>309.28</v>
+        <v>342.56</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -3649,7 +3649,7 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>2394</v>
+        <v>2425</v>
       </c>
       <c r="C93">
         <v>4.43</v>
@@ -3658,13 +3658,13 @@
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>463.46</v>
+        <v>481.66</v>
       </c>
       <c r="F93">
-        <v>321.88</v>
+        <v>332.18</v>
       </c>
       <c r="G93">
-        <v>329.9</v>
+        <v>330.68</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -3681,22 +3681,22 @@
         <v>103</v>
       </c>
       <c r="B94">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="C94">
-        <v>4.38</v>
+        <v>4.09</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>468.84</v>
+        <v>485.58</v>
       </c>
       <c r="F94">
-        <v>341.01</v>
+        <v>322.84</v>
       </c>
       <c r="G94">
-        <v>328.75</v>
+        <v>291.58</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -3713,7 +3713,7 @@
         <v>104</v>
       </c>
       <c r="B95">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C95">
         <v>4.09</v>
@@ -3722,13 +3722,13 @@
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>465.75</v>
+        <v>472.89</v>
       </c>
       <c r="F95">
-        <v>303.55</v>
+        <v>303.34</v>
       </c>
       <c r="G95">
-        <v>306.99</v>
+        <v>309.11</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -3745,22 +3745,22 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C96">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>427.38</v>
+        <v>429.53</v>
       </c>
       <c r="F96">
-        <v>309.17</v>
+        <v>311.3</v>
       </c>
       <c r="G96">
-        <v>308.13</v>
+        <v>310.26</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -3777,22 +3777,22 @@
         <v>106</v>
       </c>
       <c r="B97">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="C97">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>402.41</v>
+        <v>417.76</v>
       </c>
       <c r="F97">
-        <v>297.71</v>
+        <v>299.65</v>
       </c>
       <c r="G97">
-        <v>290.95</v>
+        <v>295.27</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -3809,22 +3809,22 @@
         <v>107</v>
       </c>
       <c r="B98">
-        <v>245</v>
+        <v>360</v>
       </c>
       <c r="C98">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>411.8</v>
+        <v>402.77</v>
       </c>
       <c r="F98">
-        <v>293.24</v>
+        <v>299.65</v>
       </c>
       <c r="G98">
-        <v>289.58</v>
+        <v>288.35</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -3841,22 +3841,22 @@
         <v>108</v>
       </c>
       <c r="B99">
-        <v>363</v>
+        <v>128</v>
       </c>
       <c r="C99">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>402.41</v>
+        <v>377.51</v>
       </c>
       <c r="F99">
-        <v>265.75</v>
+        <v>285.81</v>
       </c>
       <c r="G99">
-        <v>265.64</v>
+        <v>275.66</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -3873,22 +3873,22 @@
         <v>109</v>
       </c>
       <c r="B100">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="C100">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>375.72</v>
+        <v>400.46</v>
       </c>
       <c r="F100">
-        <v>283.85</v>
+        <v>270.82</v>
       </c>
       <c r="G100">
-        <v>274.92</v>
+        <v>294.12</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -3905,22 +3905,22 @@
         <v>110</v>
       </c>
       <c r="B101">
-        <v>46</v>
+        <v>374</v>
       </c>
       <c r="C101">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>421.19</v>
+        <v>403.57</v>
       </c>
       <c r="F101">
-        <v>263.35</v>
+        <v>290.77</v>
       </c>
       <c r="G101">
-        <v>272.62</v>
+        <v>277.62</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -3937,22 +3937,22 @@
         <v>111</v>
       </c>
       <c r="B102">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C102">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>397.71</v>
+        <v>401.96</v>
       </c>
       <c r="F102">
-        <v>270.1</v>
+        <v>265.17</v>
       </c>
       <c r="G102">
-        <v>262.31</v>
+        <v>264.13</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -3969,22 +3969,22 @@
         <v>112</v>
       </c>
       <c r="B103">
-        <v>243</v>
+        <v>71</v>
       </c>
       <c r="C103">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>381.22</v>
+        <v>360.21</v>
       </c>
       <c r="F103">
-        <v>249.6</v>
+        <v>246.71</v>
       </c>
       <c r="G103">
-        <v>249.71</v>
+        <v>238.29</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4001,22 +4001,22 @@
         <v>113</v>
       </c>
       <c r="B104">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="C104">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>374.92</v>
+        <v>383.04</v>
       </c>
       <c r="F104">
-        <v>243.87</v>
+        <v>252.48</v>
       </c>
       <c r="G104">
-        <v>233.33</v>
+        <v>251.44</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4033,22 +4033,22 @@
         <v>114</v>
       </c>
       <c r="B105">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C105">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>338.95</v>
+        <v>340.48</v>
       </c>
       <c r="F105">
-        <v>232.88</v>
+        <v>239.79</v>
       </c>
       <c r="G105">
-        <v>233.56</v>
+        <v>235.06</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4065,22 +4065,22 @@
         <v>115</v>
       </c>
       <c r="B106">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C106">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>348.34</v>
+        <v>336.56</v>
       </c>
       <c r="F106">
-        <v>244.9</v>
+        <v>245.67</v>
       </c>
       <c r="G106">
-        <v>239.29</v>
+        <v>246.6</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4097,7 +4097,7 @@
         <v>116</v>
       </c>
       <c r="B107">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C107">
         <v>2.97</v>
@@ -4106,13 +4106,13 @@
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>343.64</v>
+        <v>353.06</v>
       </c>
       <c r="F107">
-        <v>220.28</v>
+        <v>218.34</v>
       </c>
       <c r="G107">
-        <v>219.93</v>
+        <v>223.76</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4129,7 +4129,7 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C108">
         <v>2.97</v>
@@ -4138,13 +4138,13 @@
         <f>C108*$B$3</f>
       </c>
       <c r="E108">
-        <v>325.66</v>
+        <v>327.1</v>
       </c>
       <c r="F108">
-        <v>216.5</v>
+        <v>217.99</v>
       </c>
       <c r="G108">
-        <v>209.28</v>
+        <v>210.61</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4161,22 +4161,22 @@
         <v>118</v>
       </c>
       <c r="B109">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C109">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>296.68</v>
+        <v>301.04</v>
       </c>
       <c r="F109">
-        <v>218.33</v>
+        <v>215.57</v>
       </c>
       <c r="G109">
-        <v>210.42</v>
+        <v>213.15</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4193,22 +4193,22 @@
         <v>119</v>
       </c>
       <c r="B110">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C110">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>239.52</v>
+        <v>250.63</v>
       </c>
       <c r="F110">
-        <v>176.29</v>
+        <v>178.55</v>
       </c>
       <c r="G110">
-        <v>169.53</v>
+        <v>169.55</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4234,13 +4234,13 @@
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>248.11</v>
+        <v>249.83</v>
       </c>
       <c r="F111">
-        <v>170.45</v>
+        <v>171.05</v>
       </c>
       <c r="G111">
-        <v>187.86</v>
+        <v>188</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -4257,7 +4257,7 @@
         <v>121</v>
       </c>
       <c r="B112">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C112">
         <v>2.24</v>
@@ -4266,13 +4266,13 @@
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>293.59</v>
+        <v>297.12</v>
       </c>
       <c r="F112">
-        <v>171.82</v>
+        <v>175.2</v>
       </c>
       <c r="G112">
-        <v>178.69</v>
+        <v>179.93</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -4289,7 +4289,7 @@
         <v>122</v>
       </c>
       <c r="B113">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C113">
         <v>2.13</v>
@@ -4298,13 +4298,13 @@
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>227.72</v>
+        <v>230.91</v>
       </c>
       <c r="F113">
-        <v>181.44</v>
+        <v>180.74</v>
       </c>
       <c r="G113">
-        <v>175.26</v>
+        <v>175.32</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -4330,13 +4330,13 @@
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>208.25</v>
+        <v>211.99</v>
       </c>
       <c r="F114">
-        <v>145.13</v>
+        <v>146.14</v>
       </c>
       <c r="G114">
-        <v>153.49</v>
+        <v>153.4</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -4353,22 +4353,22 @@
         <v>124</v>
       </c>
       <c r="B115">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C115">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>213.63</v>
+        <v>255.36</v>
       </c>
       <c r="F115">
-        <v>132.53</v>
+        <v>131.14</v>
       </c>
       <c r="G115">
-        <v>144.33</v>
+        <v>145.33</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -4385,22 +4385,22 @@
         <v>125</v>
       </c>
       <c r="B116">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="C116">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>177.66</v>
+        <v>163.09</v>
       </c>
       <c r="F116">
-        <v>128.98</v>
+        <v>123.07</v>
       </c>
       <c r="G116">
-        <v>147.77</v>
+        <v>125.61</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -4420,19 +4420,19 @@
         <v>60</v>
       </c>
       <c r="C117">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>169.07</v>
+        <v>171.74</v>
       </c>
       <c r="F117">
-        <v>122.34</v>
+        <v>123.07</v>
       </c>
       <c r="G117">
-        <v>123.71</v>
+        <v>123.41</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -4449,22 +4449,22 @@
         <v>127</v>
       </c>
       <c r="B118">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="C118">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>162.77</v>
+        <v>178.89</v>
       </c>
       <c r="F118">
-        <v>119.7</v>
+        <v>127.45</v>
       </c>
       <c r="G118">
-        <v>125.43</v>
+        <v>146.25</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -4490,13 +4490,13 @@
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>154.18</v>
+        <v>149.71</v>
       </c>
       <c r="F119">
-        <v>106.53</v>
+        <v>106.92</v>
       </c>
       <c r="G119">
-        <v>102.98</v>
+        <v>103.69</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -4513,7 +4513,7 @@
         <v>129</v>
       </c>
       <c r="B120">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C120">
         <v>1.03</v>
@@ -4522,13 +4522,13 @@
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>120.5</v>
+        <v>121.34</v>
       </c>
       <c r="F120">
-        <v>74.11</v>
+        <v>78.43</v>
       </c>
       <c r="G120">
-        <v>78.92</v>
+        <v>78.66</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -4545,22 +4545,22 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C121">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>98.63</v>
+        <v>93.77</v>
       </c>
       <c r="F121">
-        <v>67.35</v>
+        <v>67.36</v>
       </c>
       <c r="G121">
-        <v>65.41</v>
+        <v>63.21</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -4577,22 +4577,22 @@
         <v>131</v>
       </c>
       <c r="B122">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C122">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>82.13</v>
+        <v>81.89</v>
       </c>
       <c r="F122">
-        <v>50.97</v>
+        <v>50.98</v>
       </c>
       <c r="G122">
-        <v>49.26</v>
+        <v>50.63</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -4609,22 +4609,22 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C123">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>64.15</v>
+        <v>65.4</v>
       </c>
       <c r="F123">
-        <v>36.31</v>
+        <v>36.45</v>
       </c>
       <c r="G123">
-        <v>35.51</v>
+        <v>35.52</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 03:47</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 04:02</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -223,10 +223,10 @@
     <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Prof. Shahmat | Elite Crew</t>
+  </si>
+  <si>
     <t>Sticker | Liquid Fire</t>
-  </si>
-  <si>
-    <t>Prof. Shahmat | Elite Crew</t>
   </si>
   <si>
     <t>AK-47 | Crossfade (Factory New)</t>
@@ -865,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6">
-        <v>91.76</v>
+        <v>93.5</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
@@ -897,7 +897,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>84.8</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8">
         <v>81.48</v>
@@ -961,7 +961,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C9">
         <v>80.34</v>
@@ -1057,7 +1057,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C12">
         <v>57.38</v>
@@ -1153,7 +1153,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C15">
         <v>51.19</v>
@@ -1377,10 +1377,10 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C22">
-        <v>32.96</v>
+        <v>32.66</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
@@ -1409,7 +1409,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23">
         <v>32.25</v>
@@ -1633,7 +1633,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30">
         <v>16.26</v>
@@ -1729,10 +1729,10 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C33">
-        <v>13.48</v>
+        <v>13.47</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
@@ -1793,7 +1793,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="C35">
         <v>13.03</v>
@@ -1857,7 +1857,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C37">
         <v>12.6</v>
@@ -1889,7 +1889,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38">
         <v>12.52</v>
@@ -1921,10 +1921,10 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C39">
-        <v>10.91</v>
+        <v>11.64</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
@@ -1953,7 +1953,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C40">
         <v>10.82</v>
@@ -2209,7 +2209,7 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C48">
         <v>9.69</v>
@@ -2273,7 +2273,7 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C50">
         <v>8.63</v>
@@ -2369,7 +2369,7 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C53">
         <v>8.23</v>
@@ -2433,7 +2433,7 @@
         <v>64</v>
       </c>
       <c r="B55">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="C55">
         <v>7.99</v>
@@ -2561,7 +2561,7 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C59">
         <v>7.36</v>
@@ -2625,7 +2625,7 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>8</v>
+        <v>1147</v>
       </c>
       <c r="C61">
         <v>7.07</v>
@@ -2634,13 +2634,13 @@
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>848.9</v>
+        <v>906.46</v>
       </c>
       <c r="F61">
-        <v>521.57</v>
+        <v>547.87</v>
       </c>
       <c r="G61">
-        <v>516.49</v>
+        <v>546.71</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -2657,7 +2657,7 @@
         <v>71</v>
       </c>
       <c r="B62">
-        <v>1147</v>
+        <v>8</v>
       </c>
       <c r="C62">
         <v>7.07</v>
@@ -2666,13 +2666,13 @@
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>906.46</v>
+        <v>848.9</v>
       </c>
       <c r="F62">
-        <v>547.87</v>
+        <v>521.57</v>
       </c>
       <c r="G62">
-        <v>546.71</v>
+        <v>516.49</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -2753,7 +2753,7 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C65">
         <v>6.55</v>
@@ -2785,7 +2785,7 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C66">
         <v>6.51</v>
@@ -2849,7 +2849,7 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C68">
         <v>6.3</v>
@@ -2977,7 +2977,7 @@
         <v>81</v>
       </c>
       <c r="B72">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C72">
         <v>5.81</v>
@@ -3073,7 +3073,7 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>5.49</v>
@@ -3137,7 +3137,7 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C77">
         <v>5.41</v>
@@ -3201,7 +3201,7 @@
         <v>88</v>
       </c>
       <c r="B79">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C79">
         <v>5.31</v>
@@ -3329,7 +3329,7 @@
         <v>92</v>
       </c>
       <c r="B83">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C83">
         <v>4.87</v>
@@ -3393,7 +3393,7 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C85">
         <v>4.73</v>
@@ -3536,7 +3536,7 @@
         <v>342.21</v>
       </c>
       <c r="G89">
-        <v>329.87</v>
+        <v>328.72</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -3649,7 +3649,7 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="C93">
         <v>4.43</v>
@@ -3661,7 +3661,7 @@
         <v>481.66</v>
       </c>
       <c r="F93">
-        <v>332.18</v>
+        <v>339.1</v>
       </c>
       <c r="G93">
         <v>330.68</v>
@@ -3882,7 +3882,7 @@
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>400.46</v>
+        <v>507.61</v>
       </c>
       <c r="F100">
         <v>270.82</v>
@@ -3905,7 +3905,7 @@
         <v>110</v>
       </c>
       <c r="B101">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C101">
         <v>3.56</v>
@@ -3914,13 +3914,13 @@
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>403.57</v>
+        <v>405.19</v>
       </c>
       <c r="F101">
         <v>290.77</v>
       </c>
       <c r="G101">
-        <v>277.62</v>
+        <v>276.59</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4045,10 +4045,10 @@
         <v>340.48</v>
       </c>
       <c r="F105">
-        <v>239.79</v>
+        <v>240.95</v>
       </c>
       <c r="G105">
-        <v>235.06</v>
+        <v>234.95</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4141,7 +4141,7 @@
         <v>327.1</v>
       </c>
       <c r="F108">
-        <v>217.99</v>
+        <v>216.84</v>
       </c>
       <c r="G108">
         <v>210.61</v>
@@ -4205,7 +4205,7 @@
         <v>250.63</v>
       </c>
       <c r="F110">
-        <v>178.55</v>
+        <v>177.39</v>
       </c>
       <c r="G110">
         <v>169.55</v>
@@ -4461,7 +4461,7 @@
         <v>178.89</v>
       </c>
       <c r="F118">
-        <v>127.45</v>
+        <v>126.3</v>
       </c>
       <c r="G118">
         <v>146.25</v>
@@ -4493,10 +4493,10 @@
         <v>149.71</v>
       </c>
       <c r="F119">
-        <v>106.92</v>
+        <v>106.8</v>
       </c>
       <c r="G119">
-        <v>103.69</v>
+        <v>101.5</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -4525,7 +4525,7 @@
         <v>121.34</v>
       </c>
       <c r="F120">
-        <v>78.43</v>
+        <v>78.32</v>
       </c>
       <c r="G120">
         <v>78.66</v>
@@ -4545,7 +4545,7 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="C121">
         <v>0.87</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 04:02</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 15:10</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -61,12 +61,12 @@
     <t>M4A4 | Desolate Space (Factory New)</t>
   </si>
   <si>
+    <t>AK-47 | Point Disarray (Factory New)</t>
+  </si>
+  <si>
     <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
   </si>
   <si>
-    <t>AK-47 | Point Disarray (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Containment Breach (Field-Tested)</t>
   </si>
   <si>
@@ -76,24 +76,24 @@
     <t>MAC-10 | Fade (Factory New)</t>
   </si>
   <si>
+    <t>USP-S | Orion (Minimal Wear)</t>
+  </si>
+  <si>
     <t>AWP | Neo-Noir (Factory New)</t>
   </si>
   <si>
-    <t>USP-S | Orion (Minimal Wear)</t>
+    <t>M4A1-S | Vaporwave (Field-Tested)</t>
   </si>
   <si>
     <t>AWP | Containment Breach (Well-Worn)</t>
   </si>
   <si>
-    <t>M4A1-S | Vaporwave (Field-Tested)</t>
+    <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
   </si>
   <si>
     <t>P250 | Apep's Curse (Field-Tested)</t>
   </si>
   <si>
-    <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
-  </si>
-  <si>
     <t>Desert Eagle | Starcade (Field-Tested)</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
+    <t>Tec-9 | Brass (Minimal Wear)</t>
+  </si>
+  <si>
     <t>MP9 | Music Box (Factory New)</t>
   </si>
   <si>
-    <t>Tec-9 | Brass (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -151,30 +151,30 @@
     <t>Sticker | Great Wave (Foil)</t>
   </si>
   <si>
+    <t>SG 553 | Candy Apple (Factory New)</t>
+  </si>
+  <si>
     <t>M4A4 | Evil Daimyo (Factory New)</t>
   </si>
   <si>
-    <t>SG 553 | Candy Apple (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
     <t>The Elite Mr. Muhlik | Elite Crew</t>
   </si>
   <si>
+    <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>USP-S | Guardian (Factory New)</t>
   </si>
   <si>
+    <t>FAMAS | Styx (Field-Tested)</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>FAMAS | Styx (Field-Tested)</t>
-  </si>
-  <si>
     <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
   </si>
   <si>
@@ -187,6 +187,9 @@
     <t>B Squadron Officer | SAS</t>
   </si>
   <si>
+    <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>SSG 08 | Rapid Transit (Factory New)</t>
   </si>
   <si>
@@ -202,57 +205,57 @@
     <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Slingshot | Phoenix</t>
+  </si>
+  <si>
+    <t>Rezan The Ready | Sabre</t>
+  </si>
+  <si>
+    <t>Rezan the Redshirt | Sabre</t>
+  </si>
+  <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
     <t>SG 553 | Integrale (Field-Tested)</t>
   </si>
   <si>
-    <t>Rezan The Ready | Sabre</t>
-  </si>
-  <si>
-    <t>Blackwolf | Sabre</t>
-  </si>
-  <si>
     <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Slingshot | Phoenix</t>
-  </si>
-  <si>
-    <t>Rezan the Redshirt | Sabre</t>
+    <t>Prof. Shahmat | Elite Crew</t>
   </si>
   <si>
     <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Prof. Shahmat | Elite Crew</t>
-  </si>
-  <si>
     <t>Sticker | Liquid Fire</t>
   </si>
   <si>
     <t>AK-47 | Crossfade (Factory New)</t>
   </si>
   <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Maximus | Sabre</t>
   </si>
   <si>
+    <t>Dragomir | Sabre</t>
+  </si>
+  <si>
     <t>Tec-9 | Brass (Field-Tested)</t>
   </si>
   <si>
-    <t>Dragomir | Sabre</t>
+    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -265,27 +268,27 @@
     <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>CZ75-Auto | Tacticat (Factory New)</t>
+  </si>
+  <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>CZ75-Auto | Tacticat (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+    <t>MAC-10 | Strats (Factory New)</t>
   </si>
   <si>
     <t>AWP | Black Nile (Minimal Wear)</t>
   </si>
   <si>
-    <t>MAC-10 | Strats (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -295,36 +298,33 @@
     <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Stone Scales (Foil)</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
-    <t>Sticker | Stone Scales (Foil)</t>
-  </si>
-  <si>
-    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>AK-47 | Slate (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -337,18 +337,18 @@
     <t>Sticker | Perfect World (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Galil AR | Tuxedo (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>XM1014 | Seasons (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Galil AR | Tuxedo (Factory New)</t>
-  </si>
-  <si>
-    <t>XM1014 | Seasons (Factory New)</t>
-  </si>
-  <si>
     <t>Five-SeveN | Retrobution (Minimal Wear)</t>
   </si>
   <si>
@@ -370,6 +370,9 @@
     <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | BIG (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
   </si>
   <si>
@@ -379,22 +382,19 @@
     <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
-    <t>Sticker | BIG (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Ancient Beast (Foil)</t>
   </si>
   <si>
     <t>Sticker | Coiled Strike (Holo)</t>
   </si>
   <si>
+    <t>Sticker | Mastermind (Holo)</t>
+  </si>
+  <si>
     <t>Sticker | Enemy Spotted (Holo)</t>
   </si>
   <si>
     <t>FAMAS | Teardown (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Mastermind (Holo)</t>
   </si>
   <si>
     <t>Sticker | Web Stuck (Holo)</t>
@@ -816,7 +816,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.58</v>
+        <v>81.7</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -865,22 +865,22 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C6">
-        <v>93.5</v>
+        <v>97.61</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>10643.81</v>
+        <v>10640.58</v>
       </c>
       <c r="F6">
-        <v>7231.59</v>
+        <v>7484.18</v>
       </c>
       <c r="G6">
-        <v>7145.31</v>
+        <v>7468.27</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -897,22 +897,22 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="C7">
-        <v>84.8</v>
+        <v>87.23</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>9065.61</v>
+        <v>9160.99</v>
       </c>
       <c r="F7">
-        <v>6222.36</v>
+        <v>6580.15</v>
       </c>
       <c r="G7">
-        <v>6228.36</v>
+        <v>6574.38</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -929,22 +929,22 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>81.48</v>
+        <v>84.7</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>8905.52</v>
+        <v>8653.27</v>
       </c>
       <c r="F8">
-        <v>6343.7</v>
+        <v>6222.25</v>
       </c>
       <c r="G8">
-        <v>6314.87</v>
+        <v>6435.97</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -961,10 +961,10 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C9">
-        <v>80.34</v>
+        <v>81.05</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
@@ -973,10 +973,10 @@
         <v>8524.78</v>
       </c>
       <c r="F9">
-        <v>5882.34</v>
+        <v>5920.4</v>
       </c>
       <c r="G9">
-        <v>5824.67</v>
+        <v>5876.57</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -993,10 +993,10 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C10">
-        <v>59.89</v>
+        <v>59.06</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1005,10 +1005,10 @@
         <v>6620.17</v>
       </c>
       <c r="F10">
-        <v>4447.51</v>
+        <v>4515.56</v>
       </c>
       <c r="G10">
-        <v>4498.26</v>
+        <v>4492.49</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1025,10 +1025,10 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C11">
-        <v>58.25</v>
+        <v>58.84</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
@@ -1037,10 +1037,10 @@
         <v>6669.88</v>
       </c>
       <c r="F11">
-        <v>4380.61</v>
+        <v>4371.39</v>
       </c>
       <c r="G11">
-        <v>4302.18</v>
+        <v>4266.43</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1057,22 +1057,22 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>224</v>
+        <v>161</v>
       </c>
       <c r="C12">
-        <v>57.38</v>
+        <v>57.9</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>6665.96</v>
+        <v>6306.45</v>
       </c>
       <c r="F12">
-        <v>4256.05</v>
+        <v>4388.57</v>
       </c>
       <c r="G12">
-        <v>4186.73</v>
+        <v>4354.09</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1089,22 +1089,22 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="C13">
-        <v>56.59</v>
+        <v>56.24</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>6483.03</v>
+        <v>6620.98</v>
       </c>
       <c r="F13">
-        <v>4452.12</v>
+        <v>4152.24</v>
       </c>
       <c r="G13">
-        <v>4382.69</v>
+        <v>4149.93</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1121,22 +1121,22 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="C14">
-        <v>52</v>
+        <v>54.47</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>6024.21</v>
+        <v>5817.75</v>
       </c>
       <c r="F14">
-        <v>4016.83</v>
+        <v>4036.9</v>
       </c>
       <c r="G14">
-        <v>3967.7</v>
+        <v>4008.07</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1153,22 +1153,22 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="C15">
-        <v>51.19</v>
+        <v>52.06</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>5951.66</v>
+        <v>6024.21</v>
       </c>
       <c r="F15">
-        <v>4036.9</v>
+        <v>4016.6</v>
       </c>
       <c r="G15">
-        <v>4087.42</v>
+        <v>3973.46</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1185,22 +1185,22 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="C16">
-        <v>49.48</v>
+        <v>48.6</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>5863.42</v>
+        <v>5384.88</v>
       </c>
       <c r="F16">
-        <v>3667.81</v>
+        <v>3575.54</v>
       </c>
       <c r="G16">
-        <v>3748.55</v>
+        <v>3592.84</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1217,22 +1217,22 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="C17">
-        <v>48.6</v>
+        <v>48.45</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>5425.13</v>
+        <v>5863.42</v>
       </c>
       <c r="F17">
-        <v>3684.77</v>
+        <v>3667.81</v>
       </c>
       <c r="G17">
-        <v>3638.63</v>
+        <v>3794.69</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1249,10 +1249,10 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C18">
-        <v>48.15</v>
+        <v>48.45</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1261,10 +1261,10 @@
         <v>5214.64</v>
       </c>
       <c r="F18">
-        <v>3713.95</v>
+        <v>3690.88</v>
       </c>
       <c r="G18">
-        <v>3564.01</v>
+        <v>3598.61</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1281,22 +1281,22 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19">
-        <v>37.68</v>
+        <v>37.45</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>4496.53</v>
+        <v>4457.08</v>
       </c>
       <c r="F19">
-        <v>2708.18</v>
+        <v>2713.83</v>
       </c>
       <c r="G19">
-        <v>2960.78</v>
+        <v>2947.86</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1313,10 +1313,10 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20">
-        <v>37.46</v>
+        <v>36.43</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
@@ -1328,7 +1328,7 @@
         <v>2876.23</v>
       </c>
       <c r="G20">
-        <v>2743.94</v>
+        <v>2703.68</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1345,10 +1345,10 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C21">
-        <v>35.45</v>
+        <v>35.37</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
@@ -1357,10 +1357,10 @@
         <v>4414.52</v>
       </c>
       <c r="F21">
-        <v>2680.5</v>
+        <v>2652.82</v>
       </c>
       <c r="G21">
-        <v>3021.91</v>
+        <v>2941.17</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1377,22 +1377,22 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C22">
-        <v>32.66</v>
+        <v>32.57</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>3529.98</v>
+        <v>3633.33</v>
       </c>
       <c r="F22">
-        <v>2429.52</v>
+        <v>2483.27</v>
       </c>
       <c r="G22">
-        <v>2422.14</v>
+        <v>2404.84</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1418,13 +1418,13 @@
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>3530.79</v>
+        <v>3537.13</v>
       </c>
       <c r="F23">
-        <v>2537.36</v>
+        <v>2422.02</v>
       </c>
       <c r="G23">
-        <v>2399.07</v>
+        <v>2306.8</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1441,10 +1441,10 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C24">
-        <v>28.47</v>
+        <v>28.84</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
@@ -1453,10 +1453,10 @@
         <v>3152.36</v>
       </c>
       <c r="F24">
-        <v>2191.46</v>
+        <v>2174.16</v>
       </c>
       <c r="G24">
-        <v>2104.96</v>
+        <v>2249.13</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1476,19 +1476,19 @@
         <v>228</v>
       </c>
       <c r="C25">
-        <v>25.78</v>
+        <v>25.77</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>2811.07</v>
+        <v>2719.6</v>
       </c>
       <c r="F25">
-        <v>1923.64</v>
+        <v>1894.69</v>
       </c>
       <c r="G25">
-        <v>1914.64</v>
+        <v>1908.88</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1505,19 +1505,19 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C26">
-        <v>21.18</v>
+        <v>21.07</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>2368.85</v>
+        <v>2307.38</v>
       </c>
       <c r="F26">
-        <v>1597.34</v>
+        <v>1596.88</v>
       </c>
       <c r="G26">
         <v>1568.62</v>
@@ -1537,10 +1537,10 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C27">
-        <v>19.93</v>
+        <v>19.79</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
@@ -1549,10 +1549,10 @@
         <v>2307.38</v>
       </c>
       <c r="F27">
-        <v>1474.16</v>
+        <v>1473.81</v>
       </c>
       <c r="G27">
-        <v>1497.11</v>
+        <v>1491.35</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1569,7 +1569,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C28">
         <v>19.53</v>
@@ -1578,13 +1578,13 @@
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>2267.12</v>
+        <v>2360.89</v>
       </c>
       <c r="F28">
-        <v>1487.89</v>
+        <v>1487.66</v>
       </c>
       <c r="G28">
-        <v>1430.1</v>
+        <v>1435.87</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1601,22 +1601,22 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C29">
-        <v>19.5</v>
+        <v>18.84</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>2125.25</v>
+        <v>2181.19</v>
       </c>
       <c r="F29">
-        <v>1384.08</v>
+        <v>1430.22</v>
       </c>
       <c r="G29">
-        <v>1417.53</v>
+        <v>1394.46</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1633,22 +1633,22 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C30">
-        <v>16.26</v>
+        <v>15.46</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>1917.07</v>
+        <v>1967.59</v>
       </c>
       <c r="F30">
-        <v>1265.16</v>
+        <v>1243.37</v>
       </c>
       <c r="G30">
-        <v>1239.91</v>
+        <v>1231.83</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1665,22 +1665,22 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C31">
-        <v>15.64</v>
+        <v>15.19</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>1760.2</v>
+        <v>1917.07</v>
       </c>
       <c r="F31">
-        <v>1250.29</v>
+        <v>1182.24</v>
       </c>
       <c r="G31">
-        <v>1261.7</v>
+        <v>1188</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1697,22 +1697,22 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32">
-        <v>14.23</v>
+        <v>13.96</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>1499.3</v>
+        <v>1505.65</v>
       </c>
       <c r="F32">
         <v>1000</v>
       </c>
       <c r="G32">
-        <v>947.86</v>
+        <v>943.25</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -1732,19 +1732,19 @@
         <v>1747</v>
       </c>
       <c r="C33">
-        <v>13.47</v>
+        <v>13.44</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>1511.88</v>
+        <v>1529.29</v>
       </c>
       <c r="F33">
-        <v>1009.11</v>
+        <v>1013.84</v>
       </c>
       <c r="G33">
-        <v>1017.3</v>
+        <v>1014.88</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -1761,22 +1761,22 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34">
-        <v>13.26</v>
+        <v>13.25</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>1441.75</v>
+        <v>1590.77</v>
       </c>
       <c r="F34">
         <v>975.78</v>
       </c>
       <c r="G34">
-        <v>1037.94</v>
+        <v>1035.75</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -1793,7 +1793,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="C35">
         <v>13.03</v>
@@ -1802,13 +1802,13 @@
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>1564.7</v>
+        <v>1541.06</v>
       </c>
       <c r="F35">
-        <v>957.32</v>
+        <v>978.08</v>
       </c>
       <c r="G35">
-        <v>945.79</v>
+        <v>968.86</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -1837,10 +1837,10 @@
         <v>1418.11</v>
       </c>
       <c r="F36">
-        <v>1033.45</v>
+        <v>1032.06</v>
       </c>
       <c r="G36">
-        <v>977.39</v>
+        <v>977.28</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -1857,22 +1857,22 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>355</v>
+        <v>91</v>
       </c>
       <c r="C37">
-        <v>12.6</v>
+        <v>12.44</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>1417.3</v>
+        <v>1330.56</v>
       </c>
       <c r="F37">
-        <v>945.79</v>
+        <v>979.01</v>
       </c>
       <c r="G37">
-        <v>966.55</v>
+        <v>936.45</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -1889,22 +1889,22 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>87</v>
+        <v>370</v>
       </c>
       <c r="C38">
-        <v>12.52</v>
+        <v>12.36</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1414.99</v>
+        <v>1425.95</v>
       </c>
       <c r="F38">
-        <v>906.57</v>
+        <v>944.52</v>
       </c>
       <c r="G38">
-        <v>944.52</v>
+        <v>942.33</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1921,22 +1921,22 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C39">
-        <v>11.64</v>
+        <v>11.62</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1253.4</v>
+        <v>1263.67</v>
       </c>
       <c r="F39">
-        <v>862.74</v>
+        <v>840.83</v>
       </c>
       <c r="G39">
-        <v>857.9</v>
+        <v>829.76</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -1953,22 +1953,22 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>1779</v>
+        <v>1770</v>
       </c>
       <c r="C40">
-        <v>10.82</v>
+        <v>11.06</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1262.05</v>
+        <v>1342.44</v>
       </c>
       <c r="F40">
-        <v>825.6</v>
+        <v>853.52</v>
       </c>
       <c r="G40">
-        <v>807.38</v>
+        <v>824.22</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -1985,22 +1985,22 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C41">
-        <v>10.71</v>
+        <v>10.42</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1180.85</v>
+        <v>1182.47</v>
       </c>
       <c r="F41">
-        <v>823.07</v>
+        <v>770.47</v>
       </c>
       <c r="G41">
-        <v>823.53</v>
+        <v>741.06</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2017,22 +2017,22 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="C42">
-        <v>10.46</v>
+        <v>10.3</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1097.23</v>
+        <v>1175.31</v>
       </c>
       <c r="F42">
-        <v>748.56</v>
+        <v>788.12</v>
       </c>
       <c r="G42">
-        <v>793.42</v>
+        <v>816.26</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2049,22 +2049,22 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C43">
-        <v>10.42</v>
+        <v>10.28</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1239.91</v>
+        <v>1153.28</v>
       </c>
       <c r="F43">
-        <v>772.78</v>
+        <v>753.63</v>
       </c>
       <c r="G43">
-        <v>741.06</v>
+        <v>807.38</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2081,22 +2081,22 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="C44">
-        <v>10.31</v>
+        <v>10.26</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1153.28</v>
+        <v>1097.23</v>
       </c>
       <c r="F44">
-        <v>758.71</v>
+        <v>748.56</v>
       </c>
       <c r="G44">
-        <v>818.91</v>
+        <v>792.27</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2116,19 +2116,19 @@
         <v>491</v>
       </c>
       <c r="C45">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1129.64</v>
+        <v>1128.83</v>
       </c>
       <c r="F45">
-        <v>736.91</v>
+        <v>734.49</v>
       </c>
       <c r="G45">
-        <v>723.07</v>
+        <v>714.99</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2145,22 +2145,22 @@
         <v>55</v>
       </c>
       <c r="B46">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C46">
-        <v>9.92</v>
+        <v>9.96</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1114.65</v>
+        <v>1103.57</v>
       </c>
       <c r="F46">
+        <v>780.85</v>
+      </c>
+      <c r="G46">
         <v>761.24</v>
-      </c>
-      <c r="G46">
-        <v>760.09</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2177,10 +2177,10 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C47">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
@@ -2189,10 +2189,10 @@
         <v>1016.84</v>
       </c>
       <c r="F47">
-        <v>713.95</v>
+        <v>713.72</v>
       </c>
       <c r="G47">
-        <v>748.56</v>
+        <v>746.25</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2209,7 +2209,7 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="C48">
         <v>9.69</v>
@@ -2218,13 +2218,13 @@
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1178.43</v>
+        <v>1080.74</v>
       </c>
       <c r="F48">
-        <v>747.4</v>
+        <v>744.4</v>
       </c>
       <c r="G48">
-        <v>715.11</v>
+        <v>725.49</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2241,22 +2241,22 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="C49">
-        <v>9.28</v>
+        <v>9.06</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>943.6</v>
+        <v>485.58</v>
       </c>
       <c r="F49">
-        <v>661.36</v>
+        <v>321.57</v>
       </c>
       <c r="G49">
-        <v>677.97</v>
+        <v>291.58</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2273,22 +2273,22 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>699</v>
+        <v>189</v>
       </c>
       <c r="C50">
-        <v>8.63</v>
+        <v>8.92</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>972.78</v>
+        <v>943.6</v>
       </c>
       <c r="F50">
-        <v>640.14</v>
+        <v>654.67</v>
       </c>
       <c r="G50">
-        <v>653.98</v>
+        <v>675.2</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2305,22 +2305,22 @@
         <v>60</v>
       </c>
       <c r="B51">
-        <v>98</v>
+        <v>693</v>
       </c>
       <c r="C51">
-        <v>8.28</v>
+        <v>8.72</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>935.64</v>
+        <v>988.46</v>
       </c>
       <c r="F51">
-        <v>678.2</v>
+        <v>655.13</v>
       </c>
       <c r="G51">
-        <v>632.06</v>
+        <v>649.36</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2337,22 +2337,22 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C52">
-        <v>8.25</v>
+        <v>8.28</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>938.87</v>
+        <v>934.83</v>
       </c>
       <c r="F52">
-        <v>609</v>
+        <v>678.2</v>
       </c>
       <c r="G52">
-        <v>690.66</v>
+        <v>632.06</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2369,22 +2369,22 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>260</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>8.23</v>
+        <v>8.25</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>852.13</v>
+        <v>938.87</v>
       </c>
       <c r="F53">
-        <v>681.08</v>
+        <v>609</v>
       </c>
       <c r="G53">
-        <v>665.51</v>
+        <v>629.3</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2401,22 +2401,22 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>130</v>
+        <v>263</v>
       </c>
       <c r="C54">
-        <v>8.09</v>
+        <v>8.11</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>822.14</v>
+        <v>852.13</v>
       </c>
       <c r="F54">
-        <v>576.7</v>
+        <v>657.44</v>
       </c>
       <c r="G54">
-        <v>584.77</v>
+        <v>640.14</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2433,22 +2433,22 @@
         <v>64</v>
       </c>
       <c r="B55">
-        <v>1427</v>
+        <v>838</v>
       </c>
       <c r="C55">
-        <v>7.99</v>
+        <v>8.04</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>902.54</v>
+        <v>1002.65</v>
       </c>
       <c r="F55">
-        <v>598.61</v>
+        <v>592.85</v>
       </c>
       <c r="G55">
-        <v>578.78</v>
+        <v>588.23</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2465,22 +2465,22 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>834</v>
+        <v>1431</v>
       </c>
       <c r="C56">
-        <v>7.81</v>
+        <v>7.94</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>906.46</v>
+        <v>788.23</v>
       </c>
       <c r="F56">
         <v>599.77</v>
       </c>
       <c r="G56">
-        <v>583.51</v>
+        <v>577.62</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2497,22 +2497,22 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>143</v>
+        <v>747</v>
       </c>
       <c r="C57">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>842.67</v>
+        <v>892.27</v>
       </c>
       <c r="F57">
-        <v>553.86</v>
+        <v>576.7</v>
       </c>
       <c r="G57">
-        <v>571.51</v>
+        <v>576.93</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2529,22 +2529,22 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C58">
-        <v>7.62</v>
+        <v>7.86</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>981.43</v>
+        <v>879.7</v>
       </c>
       <c r="F58">
-        <v>600.11</v>
+        <v>607.84</v>
       </c>
       <c r="G58">
-        <v>589.39</v>
+        <v>599.65</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2561,22 +2561,22 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>744</v>
+        <v>131</v>
       </c>
       <c r="C59">
-        <v>7.36</v>
+        <v>7.78</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>834.02</v>
+        <v>822.95</v>
       </c>
       <c r="F59">
-        <v>582.47</v>
+        <v>584.31</v>
       </c>
       <c r="G59">
-        <v>575.55</v>
+        <v>588.23</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2593,22 +2593,22 @@
         <v>69</v>
       </c>
       <c r="B60">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="C60">
-        <v>7.1</v>
+        <v>7.67</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>755.13</v>
+        <v>848.21</v>
       </c>
       <c r="F60">
-        <v>551.21</v>
+        <v>553.06</v>
       </c>
       <c r="G60">
-        <v>546.71</v>
+        <v>572.32</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -2625,22 +2625,22 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="C61">
-        <v>7.07</v>
+        <v>7.37</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>906.46</v>
+        <v>875.78</v>
       </c>
       <c r="F61">
-        <v>547.87</v>
+        <v>565.17</v>
       </c>
       <c r="G61">
-        <v>546.71</v>
+        <v>536.33</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -2657,22 +2657,22 @@
         <v>71</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="C62">
-        <v>7.07</v>
+        <v>7.12</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>848.9</v>
+        <v>755.13</v>
       </c>
       <c r="F62">
-        <v>521.57</v>
+        <v>530.56</v>
       </c>
       <c r="G62">
-        <v>516.49</v>
+        <v>546.71</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -2689,22 +2689,22 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>388</v>
+        <v>8</v>
       </c>
       <c r="C63">
-        <v>6.78</v>
+        <v>6.91</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>782.7</v>
+        <v>840.25</v>
       </c>
       <c r="F63">
-        <v>489.04</v>
+        <v>518.91</v>
       </c>
       <c r="G63">
-        <v>484.43</v>
+        <v>516.49</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -2721,22 +2721,22 @@
         <v>73</v>
       </c>
       <c r="B64">
-        <v>57</v>
+        <v>393</v>
       </c>
       <c r="C64">
-        <v>6.57</v>
+        <v>6.84</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>731.49</v>
+        <v>786.73</v>
       </c>
       <c r="F64">
-        <v>510.84</v>
+        <v>490.77</v>
       </c>
       <c r="G64">
-        <v>461.36</v>
+        <v>483.27</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -2753,22 +2753,22 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="C65">
-        <v>6.55</v>
+        <v>6.8</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>748.79</v>
+        <v>771.74</v>
       </c>
       <c r="F65">
-        <v>515.45</v>
+        <v>513.26</v>
       </c>
       <c r="G65">
-        <v>519.03</v>
+        <v>512.11</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -2785,22 +2785,22 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>1185</v>
+        <v>57</v>
       </c>
       <c r="C66">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>783.5</v>
+        <v>731.49</v>
       </c>
       <c r="F66">
-        <v>472.89</v>
+        <v>530.33</v>
       </c>
       <c r="G66">
-        <v>471.74</v>
+        <v>461.36</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -2817,7 +2817,7 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>77</v>
+        <v>1189</v>
       </c>
       <c r="C67">
         <v>6.49</v>
@@ -2826,13 +2826,13 @@
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>786.73</v>
+        <v>768.51</v>
       </c>
       <c r="F67">
-        <v>479.01</v>
+        <v>471.63</v>
       </c>
       <c r="G67">
-        <v>579.58</v>
+        <v>481.89</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -2849,22 +2849,22 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="C68">
-        <v>6.3</v>
+        <v>6.49</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>709.46</v>
+        <v>799.31</v>
       </c>
       <c r="F68">
-        <v>471.74</v>
+        <v>479.7</v>
       </c>
       <c r="G68">
-        <v>475.09</v>
+        <v>472.78</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -2881,22 +2881,22 @@
         <v>78</v>
       </c>
       <c r="B69">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C69">
-        <v>6.09</v>
+        <v>6.48</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>554.9</v>
+        <v>755.94</v>
       </c>
       <c r="F69">
-        <v>420.88</v>
+        <v>478.89</v>
       </c>
       <c r="G69">
-        <v>397.35</v>
+        <v>574.74</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -2913,7 +2913,7 @@
         <v>79</v>
       </c>
       <c r="B70">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C70">
         <v>6.05</v>
@@ -2925,10 +2925,10 @@
         <v>684.2</v>
       </c>
       <c r="F70">
-        <v>463.9</v>
+        <v>462.51</v>
       </c>
       <c r="G70">
-        <v>459.17</v>
+        <v>456.05</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -2945,22 +2945,22 @@
         <v>80</v>
       </c>
       <c r="B71">
-        <v>279</v>
+        <v>123</v>
       </c>
       <c r="C71">
-        <v>5.94</v>
+        <v>5.97</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>627.45</v>
+        <v>554.9</v>
       </c>
       <c r="F71">
-        <v>509.8</v>
+        <v>419.61</v>
       </c>
       <c r="G71">
-        <v>482.12</v>
+        <v>392.16</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -2977,22 +2977,22 @@
         <v>81</v>
       </c>
       <c r="B72">
-        <v>106</v>
+        <v>279</v>
       </c>
       <c r="C72">
-        <v>5.81</v>
+        <v>5.91</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>689.73</v>
+        <v>634.49</v>
       </c>
       <c r="F72">
-        <v>417.3</v>
+        <v>507.38</v>
       </c>
       <c r="G72">
-        <v>435.75</v>
+        <v>481.89</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3009,22 +3009,22 @@
         <v>82</v>
       </c>
       <c r="B73">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C73">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>604.61</v>
+        <v>689.73</v>
       </c>
       <c r="F73">
-        <v>524.8</v>
+        <v>416.15</v>
       </c>
       <c r="G73">
-        <v>459.63</v>
+        <v>434.26</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3041,22 +3041,22 @@
         <v>83</v>
       </c>
       <c r="B74">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="C74">
-        <v>5.61</v>
+        <v>5.66</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>622.72</v>
+        <v>602.19</v>
       </c>
       <c r="F74">
-        <v>458.94</v>
+        <v>512.69</v>
       </c>
       <c r="G74">
-        <v>400.23</v>
+        <v>452.13</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3073,22 +3073,22 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="C75">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>685.81</v>
+        <v>619.61</v>
       </c>
       <c r="F75">
-        <v>434.14</v>
+        <v>452.13</v>
       </c>
       <c r="G75">
-        <v>457.78</v>
+        <v>397.92</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3105,22 +3105,22 @@
         <v>85</v>
       </c>
       <c r="B76">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="C76">
-        <v>5.45</v>
+        <v>5.37</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>590.43</v>
+        <v>577.74</v>
       </c>
       <c r="F76">
-        <v>423.07</v>
+        <v>448.44</v>
       </c>
       <c r="G76">
-        <v>426.76</v>
+        <v>404.61</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3137,10 +3137,10 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C77">
-        <v>5.41</v>
+        <v>5.35</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
@@ -3149,7 +3149,7 @@
         <v>568.28</v>
       </c>
       <c r="F77">
-        <v>397.92</v>
+        <v>396.77</v>
       </c>
       <c r="G77">
         <v>386.39</v>
@@ -3169,22 +3169,22 @@
         <v>87</v>
       </c>
       <c r="B78">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C78">
-        <v>5.37</v>
+        <v>5.34</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>601.38</v>
+        <v>580.16</v>
       </c>
       <c r="F78">
-        <v>424.45</v>
+        <v>408.19</v>
       </c>
       <c r="G78">
-        <v>405.07</v>
+        <v>418.34</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3201,22 +3201,22 @@
         <v>88</v>
       </c>
       <c r="B79">
-        <v>890</v>
+        <v>832</v>
       </c>
       <c r="C79">
-        <v>5.31</v>
+        <v>5.33</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>603</v>
+        <v>625.83</v>
       </c>
       <c r="F79">
-        <v>422.14</v>
+        <v>423.3</v>
       </c>
       <c r="G79">
-        <v>430.22</v>
+        <v>415.22</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3233,22 +3233,22 @@
         <v>89</v>
       </c>
       <c r="B80">
-        <v>497</v>
+        <v>99</v>
       </c>
       <c r="C80">
-        <v>5.08</v>
+        <v>5.32</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>613.26</v>
+        <v>684.2</v>
       </c>
       <c r="F80">
-        <v>362.17</v>
+        <v>429.64</v>
       </c>
       <c r="G80">
-        <v>392.16</v>
+        <v>452.59</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3265,10 +3265,10 @@
         <v>90</v>
       </c>
       <c r="B81">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C81">
-        <v>5.03</v>
+        <v>5.15</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
@@ -3280,7 +3280,7 @@
         <v>412.23</v>
       </c>
       <c r="G81">
-        <v>396.77</v>
+        <v>388.7</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3297,22 +3297,22 @@
         <v>91</v>
       </c>
       <c r="B82">
-        <v>73</v>
+        <v>500</v>
       </c>
       <c r="C82">
-        <v>4.92</v>
+        <v>4.96</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>580.16</v>
+        <v>567.47</v>
       </c>
       <c r="F82">
-        <v>386.5</v>
+        <v>362.17</v>
       </c>
       <c r="G82">
-        <v>369.09</v>
+        <v>392.04</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3329,22 +3329,22 @@
         <v>92</v>
       </c>
       <c r="B83">
-        <v>579</v>
+        <v>73</v>
       </c>
       <c r="C83">
-        <v>4.87</v>
+        <v>4.93</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>510.03</v>
+        <v>531.26</v>
       </c>
       <c r="F83">
-        <v>362.86</v>
+        <v>383.04</v>
       </c>
       <c r="G83">
-        <v>344.87</v>
+        <v>369.09</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3361,22 +3361,22 @@
         <v>93</v>
       </c>
       <c r="B84">
-        <v>121</v>
+        <v>617</v>
       </c>
       <c r="C84">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>588.81</v>
+        <v>510.03</v>
       </c>
       <c r="F84">
-        <v>411.42</v>
+        <v>357.9</v>
       </c>
       <c r="G84">
-        <v>379.24</v>
+        <v>357.55</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3393,22 +3393,22 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C85">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>550.98</v>
+        <v>588.81</v>
       </c>
       <c r="F85">
-        <v>344.87</v>
+        <v>411.07</v>
       </c>
       <c r="G85">
-        <v>375.89</v>
+        <v>379.47</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -3425,22 +3425,22 @@
         <v>95</v>
       </c>
       <c r="B86">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C86">
-        <v>4.71</v>
+        <v>4.76</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>521.8</v>
+        <v>599.88</v>
       </c>
       <c r="F86">
-        <v>357.55</v>
+        <v>367.13</v>
       </c>
       <c r="G86">
-        <v>352.94</v>
+        <v>380.62</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -3457,22 +3457,22 @@
         <v>96</v>
       </c>
       <c r="B87">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="C87">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>539.91</v>
+        <v>559.63</v>
       </c>
       <c r="F87">
-        <v>356.4</v>
+        <v>334.49</v>
       </c>
       <c r="G87">
-        <v>322.95</v>
+        <v>373.59</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -3489,22 +3489,22 @@
         <v>97</v>
       </c>
       <c r="B88">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C88">
-        <v>4.61</v>
+        <v>4.65</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>566.78</v>
+        <v>521.8</v>
       </c>
       <c r="F88">
-        <v>363.32</v>
+        <v>359.17</v>
       </c>
       <c r="G88">
-        <v>380.62</v>
+        <v>346.02</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -3533,10 +3533,10 @@
         <v>468.17</v>
       </c>
       <c r="F89">
-        <v>342.21</v>
+        <v>334.26</v>
       </c>
       <c r="G89">
-        <v>328.72</v>
+        <v>331.95</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -3556,19 +3556,19 @@
         <v>109</v>
       </c>
       <c r="C90">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>435.87</v>
+        <v>480.05</v>
       </c>
       <c r="F90">
-        <v>339.56</v>
+        <v>339.45</v>
       </c>
       <c r="G90">
-        <v>334.49</v>
+        <v>329.87</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -3588,19 +3588,19 @@
         <v>42</v>
       </c>
       <c r="C91">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>446.94</v>
+        <v>432.76</v>
       </c>
       <c r="F91">
-        <v>355.13</v>
+        <v>353.98</v>
       </c>
       <c r="G91">
-        <v>311.42</v>
+        <v>312.69</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -3620,7 +3620,7 @@
         <v>101</v>
       </c>
       <c r="C92">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
@@ -3632,7 +3632,7 @@
         <v>339.79</v>
       </c>
       <c r="G92">
-        <v>342.56</v>
+        <v>363.09</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -3649,22 +3649,22 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>2427</v>
+        <v>157</v>
       </c>
       <c r="C93">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>481.66</v>
+        <v>566.78</v>
       </c>
       <c r="F93">
-        <v>339.1</v>
+        <v>345.9</v>
       </c>
       <c r="G93">
-        <v>330.68</v>
+        <v>322.95</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -3681,22 +3681,22 @@
         <v>103</v>
       </c>
       <c r="B94">
-        <v>26</v>
+        <v>2417</v>
       </c>
       <c r="C94">
-        <v>4.09</v>
+        <v>4.31</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>485.58</v>
+        <v>475.32</v>
       </c>
       <c r="F94">
-        <v>322.84</v>
+        <v>333.33</v>
       </c>
       <c r="G94">
-        <v>291.58</v>
+        <v>327.1</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -3713,10 +3713,10 @@
         <v>104</v>
       </c>
       <c r="B95">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C95">
-        <v>4.09</v>
+        <v>4.29</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
@@ -3725,10 +3725,10 @@
         <v>472.89</v>
       </c>
       <c r="F95">
+        <v>305.65</v>
+      </c>
+      <c r="G95">
         <v>303.34</v>
-      </c>
-      <c r="G95">
-        <v>309.11</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -3745,19 +3745,19 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C96">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>429.53</v>
+        <v>421.68</v>
       </c>
       <c r="F96">
-        <v>311.3</v>
+        <v>313.61</v>
       </c>
       <c r="G96">
         <v>310.26</v>
@@ -3780,19 +3780,19 @@
         <v>244</v>
       </c>
       <c r="C97">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>417.76</v>
+        <v>435.06</v>
       </c>
       <c r="F97">
-        <v>299.65</v>
+        <v>310.61</v>
       </c>
       <c r="G97">
-        <v>295.27</v>
+        <v>292.85</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -3809,19 +3809,19 @@
         <v>107</v>
       </c>
       <c r="B98">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C98">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>402.77</v>
+        <v>394.12</v>
       </c>
       <c r="F98">
-        <v>299.65</v>
+        <v>298.73</v>
       </c>
       <c r="G98">
         <v>288.35</v>
@@ -3841,22 +3841,22 @@
         <v>108</v>
       </c>
       <c r="B99">
-        <v>128</v>
+        <v>366</v>
       </c>
       <c r="C99">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>377.51</v>
+        <v>405.19</v>
       </c>
       <c r="F99">
-        <v>285.81</v>
+        <v>291.23</v>
       </c>
       <c r="G99">
-        <v>275.66</v>
+        <v>273.36</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -3873,22 +3873,22 @@
         <v>109</v>
       </c>
       <c r="B100">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="C100">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>507.61</v>
+        <v>378.32</v>
       </c>
       <c r="F100">
-        <v>270.82</v>
+        <v>288.12</v>
       </c>
       <c r="G100">
-        <v>294.12</v>
+        <v>275.66</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -3905,22 +3905,22 @@
         <v>110</v>
       </c>
       <c r="B101">
-        <v>373</v>
+        <v>48</v>
       </c>
       <c r="C101">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>405.19</v>
+        <v>398.85</v>
       </c>
       <c r="F101">
-        <v>290.77</v>
+        <v>263.78</v>
       </c>
       <c r="G101">
-        <v>276.59</v>
+        <v>264.13</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -3937,22 +3937,22 @@
         <v>111</v>
       </c>
       <c r="B102">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C102">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>401.96</v>
+        <v>486.39</v>
       </c>
       <c r="F102">
-        <v>265.17</v>
+        <v>270.36</v>
       </c>
       <c r="G102">
-        <v>264.13</v>
+        <v>288.58</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -3969,7 +3969,7 @@
         <v>112</v>
       </c>
       <c r="B103">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C103">
         <v>3.35</v>
@@ -3978,13 +3978,13 @@
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>360.21</v>
+        <v>357.78</v>
       </c>
       <c r="F103">
-        <v>246.71</v>
+        <v>254.44</v>
       </c>
       <c r="G103">
-        <v>238.29</v>
+        <v>238.52</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4004,19 +4004,19 @@
         <v>245</v>
       </c>
       <c r="C104">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>383.04</v>
+        <v>383.85</v>
       </c>
       <c r="F104">
-        <v>252.48</v>
+        <v>251.33</v>
       </c>
       <c r="G104">
-        <v>251.44</v>
+        <v>250.29</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4033,10 +4033,10 @@
         <v>114</v>
       </c>
       <c r="B105">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C105">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
@@ -4045,10 +4045,10 @@
         <v>340.48</v>
       </c>
       <c r="F105">
-        <v>240.95</v>
+        <v>235.18</v>
       </c>
       <c r="G105">
-        <v>234.95</v>
+        <v>234.83</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4065,22 +4065,22 @@
         <v>115</v>
       </c>
       <c r="B106">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C106">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>336.56</v>
+        <v>363.32</v>
       </c>
       <c r="F106">
-        <v>245.67</v>
+        <v>247.98</v>
       </c>
       <c r="G106">
-        <v>246.6</v>
+        <v>244.17</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4100,19 +4100,19 @@
         <v>182</v>
       </c>
       <c r="C107">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>353.06</v>
+        <v>351.56</v>
       </c>
       <c r="F107">
-        <v>218.34</v>
+        <v>218.11</v>
       </c>
       <c r="G107">
-        <v>223.76</v>
+        <v>217.99</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4129,10 +4129,10 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C108">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
@@ -4141,10 +4141,10 @@
         <v>327.1</v>
       </c>
       <c r="F108">
-        <v>216.84</v>
+        <v>214.42</v>
       </c>
       <c r="G108">
-        <v>210.61</v>
+        <v>201.85</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4161,22 +4161,22 @@
         <v>118</v>
       </c>
       <c r="B109">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C109">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>301.04</v>
+        <v>292.39</v>
       </c>
       <c r="F109">
-        <v>215.57</v>
+        <v>216.84</v>
       </c>
       <c r="G109">
-        <v>213.15</v>
+        <v>219.15</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4193,22 +4193,22 @@
         <v>119</v>
       </c>
       <c r="B110">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="C110">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>250.63</v>
+        <v>230.91</v>
       </c>
       <c r="F110">
-        <v>177.39</v>
+        <v>177.05</v>
       </c>
       <c r="G110">
-        <v>169.55</v>
+        <v>175.32</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4225,22 +4225,22 @@
         <v>120</v>
       </c>
       <c r="B111">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="C111">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>249.83</v>
+        <v>250.63</v>
       </c>
       <c r="F111">
-        <v>171.05</v>
+        <v>170.7</v>
       </c>
       <c r="G111">
-        <v>188</v>
+        <v>165.97</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -4257,22 +4257,22 @@
         <v>121</v>
       </c>
       <c r="B112">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="C112">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>297.12</v>
+        <v>249.83</v>
       </c>
       <c r="F112">
-        <v>175.2</v>
+        <v>171.74</v>
       </c>
       <c r="G112">
-        <v>179.93</v>
+        <v>188</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -4289,22 +4289,22 @@
         <v>122</v>
       </c>
       <c r="B113">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C113">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>230.91</v>
+        <v>295.62</v>
       </c>
       <c r="F113">
-        <v>180.74</v>
+        <v>174.97</v>
       </c>
       <c r="G113">
-        <v>175.32</v>
+        <v>177.62</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -4321,10 +4321,10 @@
         <v>123</v>
       </c>
       <c r="B114">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C114">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
@@ -4353,10 +4353,10 @@
         <v>124</v>
       </c>
       <c r="B115">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C115">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
@@ -4365,10 +4365,10 @@
         <v>255.36</v>
       </c>
       <c r="F115">
-        <v>131.14</v>
+        <v>129.87</v>
       </c>
       <c r="G115">
-        <v>145.33</v>
+        <v>143.02</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -4385,22 +4385,22 @@
         <v>125</v>
       </c>
       <c r="B116">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C116">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>163.09</v>
+        <v>183.62</v>
       </c>
       <c r="F116">
-        <v>123.07</v>
+        <v>129.76</v>
       </c>
       <c r="G116">
-        <v>125.61</v>
+        <v>142.44</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -4417,22 +4417,22 @@
         <v>126</v>
       </c>
       <c r="B117">
-        <v>60</v>
+        <v>297</v>
       </c>
       <c r="C117">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>171.74</v>
+        <v>163.09</v>
       </c>
       <c r="F117">
-        <v>123.07</v>
+        <v>123.41</v>
       </c>
       <c r="G117">
-        <v>123.41</v>
+        <v>125.61</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -4449,22 +4449,22 @@
         <v>127</v>
       </c>
       <c r="B118">
-        <v>275</v>
+        <v>75</v>
       </c>
       <c r="C118">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>178.89</v>
+        <v>166.32</v>
       </c>
       <c r="F118">
-        <v>126.3</v>
+        <v>117.07</v>
       </c>
       <c r="G118">
-        <v>146.25</v>
+        <v>122.03</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -4481,22 +4481,22 @@
         <v>128</v>
       </c>
       <c r="B119">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="C119">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>149.71</v>
+        <v>155.25</v>
       </c>
       <c r="F119">
-        <v>106.8</v>
+        <v>106.69</v>
       </c>
       <c r="G119">
-        <v>101.5</v>
+        <v>104.73</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -4513,10 +4513,10 @@
         <v>129</v>
       </c>
       <c r="B120">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C120">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
@@ -4525,10 +4525,10 @@
         <v>121.34</v>
       </c>
       <c r="F120">
-        <v>78.32</v>
+        <v>75.55</v>
       </c>
       <c r="G120">
-        <v>78.66</v>
+        <v>76.36</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -4545,7 +4545,7 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>247</v>
+        <v>304</v>
       </c>
       <c r="C121">
         <v>0.87</v>
@@ -4554,13 +4554,13 @@
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>93.77</v>
+        <v>91.35</v>
       </c>
       <c r="F121">
-        <v>67.36</v>
+        <v>65.86</v>
       </c>
       <c r="G121">
-        <v>63.21</v>
+        <v>65.63</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -4577,22 +4577,22 @@
         <v>131</v>
       </c>
       <c r="B122">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="C122">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>81.89</v>
+        <v>79.58</v>
       </c>
       <c r="F122">
-        <v>50.98</v>
+        <v>50.17</v>
       </c>
       <c r="G122">
-        <v>50.63</v>
+        <v>50.4</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -4609,22 +4609,22 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C123">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>65.4</v>
+        <v>60.67</v>
       </c>
       <c r="F123">
-        <v>36.45</v>
+        <v>34.6</v>
       </c>
       <c r="G123">
-        <v>35.52</v>
+        <v>35.64</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
-  <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 15:10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+  <si>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 16:23</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -58,6 +58,15 @@
     <t>Разница %</t>
   </si>
   <si>
+    <t>MP9 | Pandora's Box (Factory New)</t>
+  </si>
+  <si>
+    <t>MP9 | Stained Glass (Factory New)</t>
+  </si>
+  <si>
+    <t>USP-S | Whiteout (Minimal Wear)</t>
+  </si>
+  <si>
     <t>M4A4 | Desolate Space (Factory New)</t>
   </si>
   <si>
@@ -70,12 +79,18 @@
     <t>AWP | Containment Breach (Field-Tested)</t>
   </si>
   <si>
+    <t>MP9 | Dark Age (Factory New)</t>
+  </si>
+  <si>
     <t>AK-47 | Legion of Anubis (Factory New)</t>
   </si>
   <si>
     <t>MAC-10 | Fade (Factory New)</t>
   </si>
   <si>
+    <t>USP-S | Whiteout (Field-Tested)</t>
+  </si>
+  <si>
     <t>USP-S | Orion (Minimal Wear)</t>
   </si>
   <si>
@@ -88,6 +103,9 @@
     <t>AWP | Containment Breach (Well-Worn)</t>
   </si>
   <si>
+    <t>MP9 | Hydra (Factory New)</t>
+  </si>
+  <si>
     <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
   </si>
   <si>
@@ -118,6 +136,9 @@
     <t>UMP-45 | Blaze (Factory New)</t>
   </si>
   <si>
+    <t>Chem-Haz Capitaine | Gendarmerie Nationale</t>
+  </si>
+  <si>
     <t>SG 553 | Integrale (Minimal Wear)</t>
   </si>
   <si>
@@ -127,6 +148,9 @@
     <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
+    <t>Nova | Sobek's Bite (Factory New)</t>
+  </si>
+  <si>
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
@@ -139,6 +163,9 @@
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Nova | Sobek's Bite (Minimal Wear)</t>
+  </si>
+  <si>
     <t>'The Doctor' Romanov | Sabre</t>
   </si>
   <si>
@@ -163,165 +190,180 @@
     <t>The Elite Mr. Muhlik | Elite Crew</t>
   </si>
   <si>
+    <t>USP-S | Guardian (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>USP-S | Guardian (Factory New)</t>
-  </si>
-  <si>
     <t>FAMAS | Styx (Field-Tested)</t>
   </si>
   <si>
     <t>P250 | Epicenter (Minimal Wear)</t>
   </si>
   <si>
+    <t>Five-SeveN | Kami (Factory New)</t>
+  </si>
+  <si>
     <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
   </si>
   <si>
     <t>Osiris | Elite Crew</t>
   </si>
   <si>
+    <t>B Squadron Officer | SAS</t>
+  </si>
+  <si>
     <t>AUG | Carved Jade (Minimal Wear)</t>
   </si>
   <si>
-    <t>B Squadron Officer | SAS</t>
+    <t>SSG 08 | Rapid Transit (Factory New)</t>
+  </si>
+  <si>
+    <t>Markus Delrow | FBI HRT</t>
+  </si>
+  <si>
+    <t>MP7 | Fade (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>MP7 | Fade (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Great Wave (Holo)</t>
+  </si>
+  <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Slingshot | Phoenix</t>
+  </si>
+  <si>
+    <t>Rezan The Ready | Sabre</t>
+  </si>
+  <si>
+    <t>SG 553 | Integrale (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Rezan the Redshirt | Sabre</t>
+  </si>
+  <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
+    <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Prof. Shahmat | Elite Crew</t>
+  </si>
+  <si>
+    <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Liquid Fire</t>
+  </si>
+  <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>AK-47 | Crossfade (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Maximus | Sabre</t>
+  </si>
+  <si>
+    <t>Tec-9 | Brass (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Dragomir | Sabre</t>
+  </si>
+  <si>
+    <t>XM1014 | Black Tie (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+  </si>
+  <si>
+    <t>CZ75-Auto | Tacticat (Factory New)</t>
+  </si>
+  <si>
+    <t>MAC-10 | Strats (Factory New)</t>
+  </si>
+  <si>
+    <t>AWP | Black Nile (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>R8 Revolver | Blaze (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Stone Scales (Foil)</t>
+  </si>
+  <si>
+    <t>P250 | Epicenter (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | Gold Web (Foil)</t>
+  </si>
+  <si>
+    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>SSG 08 | Rapid Transit (Factory New)</t>
-  </si>
-  <si>
-    <t>Markus Delrow | FBI HRT</t>
-  </si>
-  <si>
-    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Great Wave (Holo)</t>
-  </si>
-  <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Slingshot | Phoenix</t>
-  </si>
-  <si>
-    <t>Rezan The Ready | Sabre</t>
-  </si>
-  <si>
-    <t>Rezan the Redshirt | Sabre</t>
-  </si>
-  <si>
-    <t>Blackwolf | Sabre</t>
-  </si>
-  <si>
-    <t>SG 553 | Integrale (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Prof. Shahmat | Elite Crew</t>
-  </si>
-  <si>
-    <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Liquid Fire</t>
-  </si>
-  <si>
-    <t>AK-47 | Crossfade (Factory New)</t>
-  </si>
-  <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Maximus | Sabre</t>
-  </si>
-  <si>
-    <t>Dragomir | Sabre</t>
-  </si>
-  <si>
-    <t>Tec-9 | Brass (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>CZ75-Auto | Tacticat (Factory New)</t>
-  </si>
-  <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>MAC-10 | Strats (Factory New)</t>
-  </si>
-  <si>
-    <t>AWP | Black Nile (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>R8 Revolver | Blaze (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Stone Scales (Foil)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
+    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
     <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
     <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Gold Web (Foil)</t>
-  </si>
-  <si>
     <t>AK-47 | Slate (Field-Tested)</t>
   </si>
   <si>
@@ -349,6 +391,9 @@
     <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Five-SeveN | Kami (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Five-SeveN | Retrobution (Minimal Wear)</t>
   </si>
   <si>
@@ -361,13 +406,16 @@
     <t>AK-47 | Crossfade (Minimal Wear)</t>
   </si>
   <si>
+    <t>CZ75-Auto | Tuxedo (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>CZ75-Auto | Tuxedo (Factory New)</t>
-  </si>
-  <si>
     <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
@@ -794,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -816,7 +864,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.7</v>
+        <v>81.78</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -865,22 +913,22 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>97.61</v>
+        <v>162.94</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>10640.58</v>
+        <v>18760.28</v>
       </c>
       <c r="F6">
-        <v>7484.18</v>
+        <v>12053.03</v>
       </c>
       <c r="G6">
-        <v>7468.27</v>
+        <v>11982.79</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -897,22 +945,22 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>196</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>87.23</v>
+        <v>135</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>9160.99</v>
+        <v>18259.71</v>
       </c>
       <c r="F7">
-        <v>6580.15</v>
+        <v>10605.51</v>
       </c>
       <c r="G7">
-        <v>6574.38</v>
+        <v>9913.47</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -929,22 +977,22 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>59</v>
+        <v>369</v>
       </c>
       <c r="C8">
-        <v>84.7</v>
+        <v>119.36</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>8653.27</v>
+        <v>13507.7</v>
       </c>
       <c r="F8">
-        <v>6222.25</v>
+        <v>8875.41</v>
       </c>
       <c r="G8">
-        <v>6435.97</v>
+        <v>8760.07</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -961,22 +1009,22 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="C9">
-        <v>81.05</v>
+        <v>98.11</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>8524.78</v>
+        <v>10640.58</v>
       </c>
       <c r="F9">
-        <v>5920.4</v>
+        <v>7484.18</v>
       </c>
       <c r="G9">
-        <v>5876.57</v>
+        <v>7439.43</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -993,22 +1041,22 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="C10">
-        <v>59.06</v>
+        <v>87.82</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>6620.17</v>
+        <v>9189.37</v>
       </c>
       <c r="F10">
-        <v>4515.56</v>
+        <v>6580.15</v>
       </c>
       <c r="G10">
-        <v>4492.49</v>
+        <v>6574.38</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1025,22 +1073,22 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>298</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>58.84</v>
+        <v>84.65</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>6669.88</v>
+        <v>8653.27</v>
       </c>
       <c r="F11">
-        <v>4371.39</v>
+        <v>6222.25</v>
       </c>
       <c r="G11">
-        <v>4266.43</v>
+        <v>6430.21</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1057,22 +1105,22 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="C12">
-        <v>57.9</v>
+        <v>81.14</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>6306.45</v>
+        <v>8508.17</v>
       </c>
       <c r="F12">
-        <v>4388.57</v>
+        <v>5920.4</v>
       </c>
       <c r="G12">
-        <v>4354.09</v>
+        <v>5882.34</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1089,22 +1137,22 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>56.24</v>
+        <v>69.07</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>6620.98</v>
+        <v>7371.49</v>
       </c>
       <c r="F13">
-        <v>4152.24</v>
+        <v>5755.47</v>
       </c>
       <c r="G13">
-        <v>4149.93</v>
+        <v>5155.7</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1121,22 +1169,22 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>264</v>
+        <v>143</v>
       </c>
       <c r="C14">
-        <v>54.47</v>
+        <v>59.63</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>5817.75</v>
+        <v>6620.17</v>
       </c>
       <c r="F14">
-        <v>4036.9</v>
+        <v>4521.33</v>
       </c>
       <c r="G14">
-        <v>4008.07</v>
+        <v>4504.03</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1153,22 +1201,22 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="C15">
-        <v>52.06</v>
+        <v>58.76</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>6024.21</v>
+        <v>6258.35</v>
       </c>
       <c r="F15">
-        <v>4016.6</v>
+        <v>4371.39</v>
       </c>
       <c r="G15">
-        <v>3973.46</v>
+        <v>4260.66</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1185,22 +1233,22 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="C16">
-        <v>48.6</v>
+        <v>58.2</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>5384.88</v>
+        <v>6306.45</v>
       </c>
       <c r="F16">
-        <v>3575.54</v>
+        <v>4313.72</v>
       </c>
       <c r="G16">
-        <v>3592.84</v>
+        <v>4232.98</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1217,22 +1265,22 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="C17">
-        <v>48.45</v>
+        <v>57.9</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>5863.42</v>
+        <v>6306.45</v>
       </c>
       <c r="F17">
-        <v>3667.81</v>
+        <v>4388.69</v>
       </c>
       <c r="G17">
-        <v>3794.69</v>
+        <v>4354.09</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1249,22 +1297,22 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="C18">
-        <v>48.45</v>
+        <v>56.24</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>5214.64</v>
+        <v>6620.98</v>
       </c>
       <c r="F18">
-        <v>3690.88</v>
+        <v>4152.24</v>
       </c>
       <c r="G18">
-        <v>3598.61</v>
+        <v>4149.93</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1281,22 +1329,22 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="C19">
-        <v>37.45</v>
+        <v>54.5</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>4457.08</v>
+        <v>5808.98</v>
       </c>
       <c r="F19">
-        <v>2713.83</v>
+        <v>4036.9</v>
       </c>
       <c r="G19">
-        <v>2947.86</v>
+        <v>4013.83</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1313,22 +1361,22 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C20">
-        <v>36.43</v>
+        <v>52.69</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>4139.44</v>
+        <v>5515.79</v>
       </c>
       <c r="F20">
-        <v>2876.23</v>
+        <v>4016.48</v>
       </c>
       <c r="G20">
-        <v>2703.68</v>
+        <v>3971.16</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1345,22 +1393,22 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C21">
-        <v>35.37</v>
+        <v>48.73</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>4414.52</v>
+        <v>5717.63</v>
       </c>
       <c r="F21">
-        <v>2652.82</v>
+        <v>3650.51</v>
       </c>
       <c r="G21">
-        <v>2941.17</v>
+        <v>3610.14</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1377,22 +1425,22 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>278</v>
+        <v>111</v>
       </c>
       <c r="C22">
-        <v>32.57</v>
+        <v>48.6</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>3633.33</v>
+        <v>5384.88</v>
       </c>
       <c r="F22">
-        <v>2483.27</v>
+        <v>3633.09</v>
       </c>
       <c r="G22">
-        <v>2404.84</v>
+        <v>3587.07</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1409,22 +1457,22 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="C23">
-        <v>32.25</v>
+        <v>48.45</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>3537.13</v>
+        <v>5863.42</v>
       </c>
       <c r="F23">
-        <v>2422.02</v>
+        <v>3667.81</v>
       </c>
       <c r="G23">
-        <v>2306.8</v>
+        <v>3794.69</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1441,22 +1489,22 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C24">
-        <v>28.84</v>
+        <v>48.45</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>3152.36</v>
+        <v>5214.64</v>
       </c>
       <c r="F24">
-        <v>2174.16</v>
+        <v>3690.88</v>
       </c>
       <c r="G24">
-        <v>2249.13</v>
+        <v>3552.47</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1473,22 +1521,22 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="C25">
-        <v>25.77</v>
+        <v>37.45</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>2719.6</v>
+        <v>4457.08</v>
       </c>
       <c r="F25">
-        <v>1894.69</v>
+        <v>2713.83</v>
       </c>
       <c r="G25">
-        <v>1908.88</v>
+        <v>2942.09</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1505,22 +1553,22 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="C26">
-        <v>21.07</v>
+        <v>36.43</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>2307.38</v>
+        <v>4142.55</v>
       </c>
       <c r="F26">
-        <v>1596.88</v>
+        <v>2876.23</v>
       </c>
       <c r="G26">
-        <v>1568.62</v>
+        <v>2692.84</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1537,22 +1585,22 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C27">
-        <v>19.79</v>
+        <v>35.37</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>2307.38</v>
+        <v>4414.52</v>
       </c>
       <c r="F27">
-        <v>1473.81</v>
+        <v>2652.82</v>
       </c>
       <c r="G27">
-        <v>1491.35</v>
+        <v>2935.4</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1569,22 +1617,22 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="C28">
-        <v>19.53</v>
+        <v>32.57</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>2360.89</v>
+        <v>3633.33</v>
       </c>
       <c r="F28">
-        <v>1487.66</v>
+        <v>2483.27</v>
       </c>
       <c r="G28">
-        <v>1435.87</v>
+        <v>2387.54</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1601,22 +1649,22 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C29">
-        <v>18.84</v>
+        <v>32.25</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>2181.19</v>
+        <v>3537.13</v>
       </c>
       <c r="F29">
-        <v>1430.22</v>
+        <v>2422.02</v>
       </c>
       <c r="G29">
-        <v>1394.46</v>
+        <v>2358.59</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1633,22 +1681,22 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="C30">
-        <v>15.46</v>
+        <v>29.35</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>1967.59</v>
+        <v>3122.48</v>
       </c>
       <c r="F30">
-        <v>1243.37</v>
+        <v>2174.16</v>
       </c>
       <c r="G30">
-        <v>1231.83</v>
+        <v>2237.6</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1665,22 +1713,22 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>46</v>
+        <v>228</v>
       </c>
       <c r="C31">
-        <v>15.19</v>
+        <v>25.77</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>1917.07</v>
+        <v>2719.6</v>
       </c>
       <c r="F31">
-        <v>1182.24</v>
+        <v>1894.69</v>
       </c>
       <c r="G31">
-        <v>1188</v>
+        <v>1908.88</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1697,22 +1745,22 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>67</v>
+        <v>431</v>
       </c>
       <c r="C32">
-        <v>13.96</v>
+        <v>23.41</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>1505.65</v>
+        <v>2839.44</v>
       </c>
       <c r="F32">
-        <v>1000</v>
+        <v>1868.51</v>
       </c>
       <c r="G32">
-        <v>943.25</v>
+        <v>1914.64</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -1729,22 +1777,22 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>1747</v>
+        <v>149</v>
       </c>
       <c r="C33">
-        <v>13.44</v>
+        <v>21.07</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>1529.29</v>
+        <v>2307.38</v>
       </c>
       <c r="F33">
-        <v>1013.84</v>
+        <v>1596.88</v>
       </c>
       <c r="G33">
-        <v>1014.88</v>
+        <v>1568.51</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -1761,22 +1809,22 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C34">
-        <v>13.25</v>
+        <v>19.79</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>1590.77</v>
+        <v>2307.38</v>
       </c>
       <c r="F34">
-        <v>975.78</v>
+        <v>1473.81</v>
       </c>
       <c r="G34">
-        <v>1035.75</v>
+        <v>1491.35</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -1793,22 +1841,22 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>1429</v>
+        <v>167</v>
       </c>
       <c r="C35">
-        <v>13.03</v>
+        <v>19.51</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>1541.06</v>
+        <v>2360.89</v>
       </c>
       <c r="F35">
-        <v>978.08</v>
+        <v>1487.66</v>
       </c>
       <c r="G35">
-        <v>968.86</v>
+        <v>1435.87</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -1825,22 +1873,22 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C36">
-        <v>12.62</v>
+        <v>18.95</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>1418.11</v>
+        <v>2287.65</v>
       </c>
       <c r="F36">
-        <v>1032.06</v>
+        <v>1465.97</v>
       </c>
       <c r="G36">
-        <v>977.28</v>
+        <v>1441.75</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -1857,22 +1905,22 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="C37">
-        <v>12.44</v>
+        <v>18.84</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>1330.56</v>
+        <v>2180.39</v>
       </c>
       <c r="F37">
-        <v>979.01</v>
+        <v>1430.22</v>
       </c>
       <c r="G37">
-        <v>936.45</v>
+        <v>1388.69</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -1889,22 +1937,22 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="C38">
-        <v>12.36</v>
+        <v>15.44</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1425.95</v>
+        <v>1734.25</v>
       </c>
       <c r="F38">
-        <v>944.52</v>
+        <v>1243.37</v>
       </c>
       <c r="G38">
-        <v>942.33</v>
+        <v>1229.52</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1921,22 +1969,22 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="C39">
-        <v>11.62</v>
+        <v>15.01</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1263.67</v>
+        <v>1876.12</v>
       </c>
       <c r="F39">
-        <v>840.83</v>
+        <v>1176.35</v>
       </c>
       <c r="G39">
-        <v>829.76</v>
+        <v>1193.77</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -1953,22 +2001,22 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>1770</v>
+        <v>67</v>
       </c>
       <c r="C40">
-        <v>11.06</v>
+        <v>13.96</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1342.44</v>
+        <v>1505.65</v>
       </c>
       <c r="F40">
-        <v>853.52</v>
+        <v>1000</v>
       </c>
       <c r="G40">
-        <v>824.22</v>
+        <v>942.9</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -1985,22 +2033,22 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>202</v>
+        <v>26</v>
       </c>
       <c r="C41">
-        <v>10.42</v>
+        <v>13.93</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1182.47</v>
+        <v>1455.94</v>
       </c>
       <c r="F41">
-        <v>770.47</v>
+        <v>1068.86</v>
       </c>
       <c r="G41">
-        <v>741.06</v>
+        <v>1092.27</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2017,22 +2065,22 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>166</v>
+        <v>1738</v>
       </c>
       <c r="C42">
-        <v>10.3</v>
+        <v>13.44</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1175.31</v>
+        <v>1505.65</v>
       </c>
       <c r="F42">
-        <v>788.12</v>
+        <v>1013.84</v>
       </c>
       <c r="G42">
-        <v>816.26</v>
+        <v>1019.03</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2049,22 +2097,22 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="C43">
-        <v>10.28</v>
+        <v>13.25</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1153.28</v>
+        <v>1590.77</v>
       </c>
       <c r="F43">
-        <v>753.63</v>
+        <v>975.78</v>
       </c>
       <c r="G43">
-        <v>807.38</v>
+        <v>1035.75</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2081,22 +2129,22 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>98</v>
+        <v>1423</v>
       </c>
       <c r="C44">
-        <v>10.26</v>
+        <v>13.01</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1097.23</v>
+        <v>1541.06</v>
       </c>
       <c r="F44">
-        <v>748.56</v>
+        <v>978.08</v>
       </c>
       <c r="G44">
-        <v>792.27</v>
+        <v>980.39</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2113,22 +2161,22 @@
         <v>54</v>
       </c>
       <c r="B45">
-        <v>491</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>10.1</v>
+        <v>12.62</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1128.83</v>
+        <v>1418.11</v>
       </c>
       <c r="F45">
-        <v>734.49</v>
+        <v>1032.06</v>
       </c>
       <c r="G45">
-        <v>714.99</v>
+        <v>977.28</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2145,22 +2193,22 @@
         <v>55</v>
       </c>
       <c r="B46">
-        <v>1303</v>
+        <v>95</v>
       </c>
       <c r="C46">
-        <v>9.96</v>
+        <v>12.41</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1103.57</v>
+        <v>1330.56</v>
       </c>
       <c r="F46">
-        <v>780.85</v>
+        <v>979.01</v>
       </c>
       <c r="G46">
-        <v>761.24</v>
+        <v>935.29</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2177,22 +2225,22 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="C47">
-        <v>9.77</v>
+        <v>12.36</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1016.84</v>
+        <v>1425.26</v>
       </c>
       <c r="F47">
-        <v>713.72</v>
+        <v>943.37</v>
       </c>
       <c r="G47">
-        <v>746.25</v>
+        <v>942.33</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2209,22 +2257,22 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>988</v>
+        <v>176</v>
       </c>
       <c r="C48">
-        <v>9.69</v>
+        <v>11.62</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1080.74</v>
+        <v>1263.67</v>
       </c>
       <c r="F48">
-        <v>744.4</v>
+        <v>839.68</v>
       </c>
       <c r="G48">
-        <v>725.49</v>
+        <v>853.52</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2241,22 +2289,22 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>24</v>
+        <v>1769</v>
       </c>
       <c r="C49">
-        <v>9.06</v>
+        <v>11.02</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>485.58</v>
+        <v>1342.44</v>
       </c>
       <c r="F49">
-        <v>321.57</v>
+        <v>806.23</v>
       </c>
       <c r="G49">
-        <v>291.58</v>
+        <v>818.91</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2273,22 +2321,22 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="C50">
-        <v>8.92</v>
+        <v>10.58</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>943.6</v>
+        <v>1180.85</v>
       </c>
       <c r="F50">
-        <v>654.67</v>
+        <v>785.7</v>
       </c>
       <c r="G50">
-        <v>675.2</v>
+        <v>813.95</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2305,22 +2353,22 @@
         <v>60</v>
       </c>
       <c r="B51">
-        <v>693</v>
+        <v>202</v>
       </c>
       <c r="C51">
-        <v>8.72</v>
+        <v>10.42</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>988.46</v>
+        <v>1182.47</v>
       </c>
       <c r="F51">
-        <v>655.13</v>
+        <v>772.78</v>
       </c>
       <c r="G51">
-        <v>649.36</v>
+        <v>741.06</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2337,22 +2385,22 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>98</v>
+        <v>189</v>
       </c>
       <c r="C52">
-        <v>8.28</v>
+        <v>10.28</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>934.83</v>
+        <v>1153.28</v>
       </c>
       <c r="F52">
-        <v>678.2</v>
+        <v>753.4</v>
       </c>
       <c r="G52">
-        <v>632.06</v>
+        <v>817.76</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2369,22 +2417,22 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C53">
-        <v>8.25</v>
+        <v>10.26</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>938.87</v>
+        <v>1097.23</v>
       </c>
       <c r="F53">
-        <v>609</v>
+        <v>748.56</v>
       </c>
       <c r="G53">
-        <v>629.3</v>
+        <v>791.23</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2401,22 +2449,22 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>263</v>
+        <v>88</v>
       </c>
       <c r="C54">
-        <v>8.11</v>
+        <v>10.19</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>852.13</v>
+        <v>1132.75</v>
       </c>
       <c r="F54">
-        <v>657.44</v>
+        <v>758.82</v>
       </c>
       <c r="G54">
-        <v>640.14</v>
+        <v>758.94</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2433,22 +2481,22 @@
         <v>64</v>
       </c>
       <c r="B55">
-        <v>838</v>
+        <v>492</v>
       </c>
       <c r="C55">
-        <v>8.04</v>
+        <v>10.1</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1002.65</v>
+        <v>1128.83</v>
       </c>
       <c r="F55">
-        <v>592.85</v>
+        <v>735.64</v>
       </c>
       <c r="G55">
-        <v>588.23</v>
+        <v>713.84</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2465,22 +2513,22 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>1431</v>
+        <v>1311</v>
       </c>
       <c r="C56">
-        <v>7.94</v>
+        <v>9.96</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>788.23</v>
+        <v>1103.57</v>
       </c>
       <c r="F56">
-        <v>599.77</v>
+        <v>771.62</v>
       </c>
       <c r="G56">
-        <v>577.62</v>
+        <v>764.7</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2497,22 +2545,22 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>747</v>
+        <v>987</v>
       </c>
       <c r="C57">
-        <v>7.91</v>
+        <v>9.79</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>892.27</v>
+        <v>1087.77</v>
       </c>
       <c r="F57">
-        <v>576.7</v>
+        <v>692.04</v>
       </c>
       <c r="G57">
-        <v>576.93</v>
+        <v>715.11</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2529,22 +2577,22 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>833</v>
+        <v>95</v>
       </c>
       <c r="C58">
-        <v>7.86</v>
+        <v>9.77</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>879.7</v>
+        <v>1016.84</v>
       </c>
       <c r="F58">
-        <v>607.84</v>
+        <v>713.72</v>
       </c>
       <c r="G58">
-        <v>599.65</v>
+        <v>743.94</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2561,22 +2609,22 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="C59">
-        <v>7.78</v>
+        <v>8.92</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>822.95</v>
+        <v>906.46</v>
       </c>
       <c r="F59">
-        <v>584.31</v>
+        <v>655.94</v>
       </c>
       <c r="G59">
-        <v>588.23</v>
+        <v>668.86</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2593,22 +2641,22 @@
         <v>69</v>
       </c>
       <c r="B60">
-        <v>143</v>
+        <v>689</v>
       </c>
       <c r="C60">
-        <v>7.67</v>
+        <v>8.74</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>848.21</v>
+        <v>988.46</v>
       </c>
       <c r="F60">
-        <v>553.06</v>
+        <v>645.9</v>
       </c>
       <c r="G60">
-        <v>572.32</v>
+        <v>649.36</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -2625,22 +2673,22 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>1139</v>
+        <v>560</v>
       </c>
       <c r="C61">
-        <v>7.37</v>
+        <v>8.67</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>875.78</v>
+        <v>1038.98</v>
       </c>
       <c r="F61">
-        <v>565.17</v>
+        <v>660.78</v>
       </c>
       <c r="G61">
-        <v>536.33</v>
+        <v>645.9</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -2657,22 +2705,22 @@
         <v>71</v>
       </c>
       <c r="B62">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="C62">
-        <v>7.12</v>
+        <v>8.29</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>755.13</v>
+        <v>931.72</v>
       </c>
       <c r="F62">
-        <v>530.56</v>
+        <v>631.26</v>
       </c>
       <c r="G62">
-        <v>546.71</v>
+        <v>611.3</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -2689,22 +2737,22 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="C63">
-        <v>6.91</v>
+        <v>8.28</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>840.25</v>
+        <v>934.83</v>
       </c>
       <c r="F63">
-        <v>518.91</v>
+        <v>678.2</v>
       </c>
       <c r="G63">
-        <v>516.49</v>
+        <v>632.06</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -2721,22 +2769,22 @@
         <v>73</v>
       </c>
       <c r="B64">
-        <v>393</v>
+        <v>25</v>
       </c>
       <c r="C64">
-        <v>6.84</v>
+        <v>8.25</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>786.73</v>
+        <v>938.87</v>
       </c>
       <c r="F64">
-        <v>490.77</v>
+        <v>609</v>
       </c>
       <c r="G64">
-        <v>483.27</v>
+        <v>629.3</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -2753,22 +2801,22 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>1322</v>
+        <v>263</v>
       </c>
       <c r="C65">
-        <v>6.8</v>
+        <v>8.23</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>771.74</v>
+        <v>852.13</v>
       </c>
       <c r="F65">
-        <v>513.26</v>
+        <v>657.44</v>
       </c>
       <c r="G65">
-        <v>512.11</v>
+        <v>640.14</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -2785,22 +2833,22 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>57</v>
+        <v>848</v>
       </c>
       <c r="C66">
-        <v>6.57</v>
+        <v>8.05</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>731.49</v>
+        <v>1002.65</v>
       </c>
       <c r="F66">
-        <v>530.33</v>
+        <v>594</v>
       </c>
       <c r="G66">
-        <v>461.36</v>
+        <v>588.23</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -2817,22 +2865,22 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>1189</v>
+        <v>1430</v>
       </c>
       <c r="C67">
-        <v>6.49</v>
+        <v>7.95</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>768.51</v>
+        <v>904.15</v>
       </c>
       <c r="F67">
-        <v>471.63</v>
+        <v>599.77</v>
       </c>
       <c r="G67">
-        <v>481.89</v>
+        <v>576.7</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -2849,22 +2897,22 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>946</v>
+        <v>131</v>
       </c>
       <c r="C68">
-        <v>6.49</v>
+        <v>7.92</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>799.31</v>
+        <v>826.87</v>
       </c>
       <c r="F68">
-        <v>479.7</v>
+        <v>584.31</v>
       </c>
       <c r="G68">
-        <v>472.78</v>
+        <v>599.77</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -2881,22 +2929,22 @@
         <v>78</v>
       </c>
       <c r="B69">
-        <v>77</v>
+        <v>745</v>
       </c>
       <c r="C69">
-        <v>6.48</v>
+        <v>7.91</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>755.94</v>
+        <v>892.27</v>
       </c>
       <c r="F69">
-        <v>478.89</v>
+        <v>588.12</v>
       </c>
       <c r="G69">
-        <v>574.74</v>
+        <v>576.93</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -2913,22 +2961,22 @@
         <v>79</v>
       </c>
       <c r="B70">
-        <v>104</v>
+        <v>835</v>
       </c>
       <c r="C70">
-        <v>6.05</v>
+        <v>7.88</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>684.2</v>
+        <v>879.7</v>
       </c>
       <c r="F70">
-        <v>462.51</v>
+        <v>609</v>
       </c>
       <c r="G70">
-        <v>456.05</v>
+        <v>597.35</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -2945,22 +2993,22 @@
         <v>80</v>
       </c>
       <c r="B71">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C71">
-        <v>5.97</v>
+        <v>7.67</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>554.9</v>
+        <v>848.21</v>
       </c>
       <c r="F71">
-        <v>419.61</v>
+        <v>553.06</v>
       </c>
       <c r="G71">
-        <v>392.16</v>
+        <v>571.16</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -2977,22 +3025,22 @@
         <v>81</v>
       </c>
       <c r="B72">
-        <v>279</v>
+        <v>1137</v>
       </c>
       <c r="C72">
-        <v>5.91</v>
+        <v>7.46</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>634.49</v>
+        <v>875.78</v>
       </c>
       <c r="F72">
-        <v>507.38</v>
+        <v>563.9</v>
       </c>
       <c r="G72">
-        <v>481.89</v>
+        <v>535.18</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3009,22 +3057,22 @@
         <v>82</v>
       </c>
       <c r="B73">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="C73">
-        <v>5.8</v>
+        <v>7.12</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>689.73</v>
+        <v>755.13</v>
       </c>
       <c r="F73">
-        <v>416.15</v>
+        <v>530.33</v>
       </c>
       <c r="G73">
-        <v>434.26</v>
+        <v>546.71</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3041,22 +3089,22 @@
         <v>83</v>
       </c>
       <c r="B74">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="C74">
-        <v>5.66</v>
+        <v>6.91</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>602.19</v>
+        <v>840.25</v>
       </c>
       <c r="F74">
-        <v>512.69</v>
+        <v>518.91</v>
       </c>
       <c r="G74">
-        <v>452.13</v>
+        <v>515.34</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3073,22 +3121,22 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>175</v>
+        <v>1319</v>
       </c>
       <c r="C75">
-        <v>5.5</v>
+        <v>6.87</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>619.61</v>
+        <v>809.57</v>
       </c>
       <c r="F75">
-        <v>452.13</v>
+        <v>513.26</v>
       </c>
       <c r="G75">
-        <v>397.92</v>
+        <v>507.5</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3105,22 +3153,22 @@
         <v>85</v>
       </c>
       <c r="B76">
-        <v>123</v>
+        <v>393</v>
       </c>
       <c r="C76">
-        <v>5.37</v>
+        <v>6.84</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>577.74</v>
+        <v>765.4</v>
       </c>
       <c r="F76">
-        <v>448.44</v>
+        <v>489.39</v>
       </c>
       <c r="G76">
-        <v>404.61</v>
+        <v>483.27</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3137,22 +3185,22 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>511</v>
+        <v>57</v>
       </c>
       <c r="C77">
-        <v>5.35</v>
+        <v>6.57</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>568.28</v>
+        <v>731.49</v>
       </c>
       <c r="F77">
-        <v>396.77</v>
+        <v>530.22</v>
       </c>
       <c r="G77">
-        <v>386.39</v>
+        <v>461.36</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3169,22 +3217,22 @@
         <v>87</v>
       </c>
       <c r="B78">
-        <v>25</v>
+        <v>1191</v>
       </c>
       <c r="C78">
-        <v>5.34</v>
+        <v>6.49</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>580.16</v>
+        <v>768.51</v>
       </c>
       <c r="F78">
-        <v>408.19</v>
+        <v>470.47</v>
       </c>
       <c r="G78">
-        <v>418.34</v>
+        <v>481.89</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3201,22 +3249,22 @@
         <v>88</v>
       </c>
       <c r="B79">
-        <v>832</v>
+        <v>77</v>
       </c>
       <c r="C79">
-        <v>5.33</v>
+        <v>6.48</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>625.83</v>
+        <v>752.82</v>
       </c>
       <c r="F79">
-        <v>423.3</v>
+        <v>478.89</v>
       </c>
       <c r="G79">
-        <v>415.22</v>
+        <v>574.74</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3233,22 +3281,22 @@
         <v>89</v>
       </c>
       <c r="B80">
-        <v>99</v>
+        <v>944</v>
       </c>
       <c r="C80">
-        <v>5.32</v>
+        <v>6.48</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>684.2</v>
+        <v>799.31</v>
       </c>
       <c r="F80">
-        <v>429.64</v>
+        <v>479.7</v>
       </c>
       <c r="G80">
-        <v>452.59</v>
+        <v>475.09</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3265,22 +3313,22 @@
         <v>90</v>
       </c>
       <c r="B81">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C81">
-        <v>5.15</v>
+        <v>6.29</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>567.47</v>
+        <v>656.63</v>
       </c>
       <c r="F81">
-        <v>412.23</v>
+        <v>478.55</v>
       </c>
       <c r="G81">
-        <v>388.7</v>
+        <v>519.03</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3297,22 +3345,22 @@
         <v>91</v>
       </c>
       <c r="B82">
-        <v>500</v>
+        <v>104</v>
       </c>
       <c r="C82">
-        <v>4.96</v>
+        <v>6.05</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>567.47</v>
+        <v>684.2</v>
       </c>
       <c r="F82">
-        <v>362.17</v>
+        <v>462.51</v>
       </c>
       <c r="G82">
-        <v>392.04</v>
+        <v>456.05</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3329,22 +3377,22 @@
         <v>92</v>
       </c>
       <c r="B83">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C83">
-        <v>4.93</v>
+        <v>6.03</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>531.26</v>
+        <v>468.17</v>
       </c>
       <c r="F83">
-        <v>383.04</v>
+        <v>332.18</v>
       </c>
       <c r="G83">
-        <v>369.09</v>
+        <v>331.95</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3361,22 +3409,22 @@
         <v>93</v>
       </c>
       <c r="B84">
-        <v>617</v>
+        <v>123</v>
       </c>
       <c r="C84">
-        <v>4.82</v>
+        <v>5.97</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>510.03</v>
+        <v>554.9</v>
       </c>
       <c r="F84">
-        <v>357.9</v>
+        <v>419.61</v>
       </c>
       <c r="G84">
-        <v>357.55</v>
+        <v>392.04</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3393,22 +3441,22 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>121</v>
+        <v>279</v>
       </c>
       <c r="C85">
-        <v>4.81</v>
+        <v>5.91</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>588.81</v>
+        <v>634.49</v>
       </c>
       <c r="F85">
-        <v>411.07</v>
+        <v>507.38</v>
       </c>
       <c r="G85">
-        <v>379.47</v>
+        <v>481.89</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -3425,22 +3473,22 @@
         <v>95</v>
       </c>
       <c r="B86">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="C86">
-        <v>4.76</v>
+        <v>5.79</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>599.88</v>
+        <v>689.73</v>
       </c>
       <c r="F86">
-        <v>367.13</v>
+        <v>416.15</v>
       </c>
       <c r="G86">
-        <v>380.62</v>
+        <v>434.26</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -3457,22 +3505,22 @@
         <v>96</v>
       </c>
       <c r="B87">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C87">
-        <v>4.69</v>
+        <v>5.75</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>559.63</v>
+        <v>684.2</v>
       </c>
       <c r="F87">
-        <v>334.49</v>
+        <v>429.64</v>
       </c>
       <c r="G87">
-        <v>373.59</v>
+        <v>452.59</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -3489,22 +3537,22 @@
         <v>97</v>
       </c>
       <c r="B88">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="C88">
-        <v>4.65</v>
+        <v>5.66</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>521.8</v>
+        <v>602.19</v>
       </c>
       <c r="F88">
-        <v>359.17</v>
+        <v>512.69</v>
       </c>
       <c r="G88">
-        <v>346.02</v>
+        <v>449.83</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -3521,22 +3569,22 @@
         <v>98</v>
       </c>
       <c r="B89">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="C89">
-        <v>4.5</v>
+        <v>5.58</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>468.17</v>
+        <v>591.23</v>
       </c>
       <c r="F89">
-        <v>334.26</v>
+        <v>403.69</v>
       </c>
       <c r="G89">
-        <v>331.95</v>
+        <v>426.76</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -3553,22 +3601,22 @@
         <v>99</v>
       </c>
       <c r="B90">
-        <v>109</v>
+        <v>511</v>
       </c>
       <c r="C90">
-        <v>4.44</v>
+        <v>5.41</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>480.05</v>
+        <v>568.28</v>
       </c>
       <c r="F90">
-        <v>339.45</v>
+        <v>396.77</v>
       </c>
       <c r="G90">
-        <v>329.87</v>
+        <v>386.39</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -3585,22 +3633,22 @@
         <v>100</v>
       </c>
       <c r="B91">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="C91">
-        <v>4.42</v>
+        <v>5.4</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>432.76</v>
+        <v>619.61</v>
       </c>
       <c r="F91">
-        <v>353.98</v>
+        <v>452.13</v>
       </c>
       <c r="G91">
-        <v>312.69</v>
+        <v>392.16</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -3617,22 +3665,22 @@
         <v>101</v>
       </c>
       <c r="B92">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C92">
-        <v>4.4</v>
+        <v>5.37</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>475.32</v>
+        <v>600.69</v>
       </c>
       <c r="F92">
-        <v>339.79</v>
+        <v>447.29</v>
       </c>
       <c r="G92">
-        <v>363.09</v>
+        <v>404.61</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -3649,22 +3697,22 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>157</v>
+        <v>842</v>
       </c>
       <c r="C93">
-        <v>4.4</v>
+        <v>5.35</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>566.78</v>
+        <v>625.83</v>
       </c>
       <c r="F93">
-        <v>345.9</v>
+        <v>422.14</v>
       </c>
       <c r="G93">
-        <v>322.95</v>
+        <v>426.53</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -3681,22 +3729,22 @@
         <v>103</v>
       </c>
       <c r="B94">
-        <v>2417</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>4.31</v>
+        <v>5.32</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>475.32</v>
+        <v>580.16</v>
       </c>
       <c r="F94">
-        <v>333.33</v>
+        <v>409.23</v>
       </c>
       <c r="G94">
-        <v>327.1</v>
+        <v>415.11</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -3713,22 +3761,22 @@
         <v>104</v>
       </c>
       <c r="B95">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C95">
-        <v>4.29</v>
+        <v>5.18</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>472.89</v>
+        <v>567.47</v>
       </c>
       <c r="F95">
-        <v>305.65</v>
+        <v>412.23</v>
       </c>
       <c r="G95">
-        <v>303.34</v>
+        <v>387.54</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -3745,22 +3793,22 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>124</v>
+        <v>502</v>
       </c>
       <c r="C96">
-        <v>4.02</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>421.68</v>
+        <v>559.63</v>
       </c>
       <c r="F96">
-        <v>313.61</v>
+        <v>362.17</v>
       </c>
       <c r="G96">
-        <v>310.26</v>
+        <v>392.04</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -3777,22 +3825,22 @@
         <v>106</v>
       </c>
       <c r="B97">
-        <v>244</v>
+        <v>71</v>
       </c>
       <c r="C97">
-        <v>3.86</v>
+        <v>4.91</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>435.06</v>
+        <v>580.16</v>
       </c>
       <c r="F97">
-        <v>310.61</v>
+        <v>383.04</v>
       </c>
       <c r="G97">
-        <v>292.85</v>
+        <v>369.09</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -3809,22 +3857,22 @@
         <v>107</v>
       </c>
       <c r="B98">
-        <v>359</v>
+        <v>616</v>
       </c>
       <c r="C98">
-        <v>3.83</v>
+        <v>4.82</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>394.12</v>
+        <v>507.61</v>
       </c>
       <c r="F98">
-        <v>298.73</v>
+        <v>356.63</v>
       </c>
       <c r="G98">
-        <v>288.35</v>
+        <v>365.4</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -3841,22 +3889,22 @@
         <v>108</v>
       </c>
       <c r="B99">
-        <v>366</v>
+        <v>121</v>
       </c>
       <c r="C99">
-        <v>3.79</v>
+        <v>4.81</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>405.19</v>
+        <v>588.81</v>
       </c>
       <c r="F99">
-        <v>291.23</v>
+        <v>411.07</v>
       </c>
       <c r="G99">
-        <v>273.36</v>
+        <v>379.47</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -3873,22 +3921,22 @@
         <v>109</v>
       </c>
       <c r="B100">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C100">
-        <v>3.62</v>
+        <v>4.76</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>378.32</v>
+        <v>599.88</v>
       </c>
       <c r="F100">
-        <v>288.12</v>
+        <v>366.78</v>
       </c>
       <c r="G100">
-        <v>275.66</v>
+        <v>380.62</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -3905,22 +3953,22 @@
         <v>110</v>
       </c>
       <c r="B101">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="C101">
-        <v>3.52</v>
+        <v>4.69</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>398.85</v>
+        <v>548.56</v>
       </c>
       <c r="F101">
-        <v>263.78</v>
+        <v>334.49</v>
       </c>
       <c r="G101">
-        <v>264.13</v>
+        <v>373.59</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -3937,22 +3985,22 @@
         <v>111</v>
       </c>
       <c r="B102">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="C102">
-        <v>3.51</v>
+        <v>4.66</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>486.39</v>
+        <v>566.78</v>
       </c>
       <c r="F102">
-        <v>270.36</v>
+        <v>344.87</v>
       </c>
       <c r="G102">
-        <v>288.58</v>
+        <v>322.95</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -3969,22 +4017,22 @@
         <v>112</v>
       </c>
       <c r="B103">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C103">
-        <v>3.35</v>
+        <v>4.65</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>357.78</v>
+        <v>521.8</v>
       </c>
       <c r="F103">
-        <v>254.44</v>
+        <v>359.17</v>
       </c>
       <c r="G103">
-        <v>238.52</v>
+        <v>346.02</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4001,22 +4049,22 @@
         <v>113</v>
       </c>
       <c r="B104">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="C104">
-        <v>3.31</v>
+        <v>4.46</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>383.85</v>
+        <v>485.58</v>
       </c>
       <c r="F104">
-        <v>251.33</v>
+        <v>321.57</v>
       </c>
       <c r="G104">
-        <v>250.29</v>
+        <v>291.58</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4033,22 +4081,22 @@
         <v>114</v>
       </c>
       <c r="B105">
-        <v>316</v>
+        <v>42</v>
       </c>
       <c r="C105">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>340.48</v>
+        <v>432.76</v>
       </c>
       <c r="F105">
-        <v>235.18</v>
+        <v>353.98</v>
       </c>
       <c r="G105">
-        <v>234.83</v>
+        <v>312.69</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4065,22 +4113,22 @@
         <v>115</v>
       </c>
       <c r="B106">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="C106">
-        <v>3.18</v>
+        <v>4.41</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>363.32</v>
+        <v>480.05</v>
       </c>
       <c r="F106">
-        <v>247.98</v>
+        <v>339.45</v>
       </c>
       <c r="G106">
-        <v>244.17</v>
+        <v>329.87</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4097,22 +4145,22 @@
         <v>116</v>
       </c>
       <c r="B107">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="C107">
-        <v>2.91</v>
+        <v>4.4</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>351.56</v>
+        <v>475.32</v>
       </c>
       <c r="F107">
-        <v>218.11</v>
+        <v>339.79</v>
       </c>
       <c r="G107">
-        <v>217.99</v>
+        <v>363.09</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4129,22 +4177,22 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>117</v>
+        <v>2409</v>
       </c>
       <c r="C108">
-        <v>2.91</v>
+        <v>4.38</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
       </c>
       <c r="E108">
-        <v>327.1</v>
+        <v>475.32</v>
       </c>
       <c r="F108">
-        <v>214.42</v>
+        <v>334.49</v>
       </c>
       <c r="G108">
-        <v>201.85</v>
+        <v>326.99</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4161,22 +4209,22 @@
         <v>118</v>
       </c>
       <c r="B109">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C109">
-        <v>2.87</v>
+        <v>4.29</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>292.39</v>
+        <v>530.45</v>
       </c>
       <c r="F109">
-        <v>216.84</v>
+        <v>305.65</v>
       </c>
       <c r="G109">
-        <v>219.15</v>
+        <v>303.34</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4193,22 +4241,22 @@
         <v>119</v>
       </c>
       <c r="B110">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C110">
-        <v>2.28</v>
+        <v>4.11</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>230.91</v>
+        <v>421.68</v>
       </c>
       <c r="F110">
-        <v>177.05</v>
+        <v>313.61</v>
       </c>
       <c r="G110">
-        <v>175.32</v>
+        <v>310.26</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4225,22 +4273,22 @@
         <v>120</v>
       </c>
       <c r="B111">
-        <v>136</v>
+        <v>245</v>
       </c>
       <c r="C111">
-        <v>2.26</v>
+        <v>3.86</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>250.63</v>
+        <v>411.42</v>
       </c>
       <c r="F111">
-        <v>170.7</v>
+        <v>310.61</v>
       </c>
       <c r="G111">
-        <v>165.97</v>
+        <v>291.81</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -4257,22 +4305,22 @@
         <v>121</v>
       </c>
       <c r="B112">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="C112">
-        <v>2.23</v>
+        <v>3.83</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>249.83</v>
+        <v>394.12</v>
       </c>
       <c r="F112">
-        <v>171.74</v>
+        <v>298.73</v>
       </c>
       <c r="G112">
-        <v>188</v>
+        <v>282.58</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -4289,22 +4337,22 @@
         <v>122</v>
       </c>
       <c r="B113">
-        <v>108</v>
+        <v>365</v>
       </c>
       <c r="C113">
-        <v>2.2</v>
+        <v>3.79</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>295.62</v>
+        <v>405.19</v>
       </c>
       <c r="F113">
-        <v>174.97</v>
+        <v>291.23</v>
       </c>
       <c r="G113">
-        <v>177.62</v>
+        <v>276.82</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -4321,22 +4369,22 @@
         <v>123</v>
       </c>
       <c r="B114">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="C114">
-        <v>2.06</v>
+        <v>3.62</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>211.99</v>
+        <v>378.32</v>
       </c>
       <c r="F114">
-        <v>146.14</v>
+        <v>286.97</v>
       </c>
       <c r="G114">
-        <v>153.4</v>
+        <v>275.66</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -4353,22 +4401,22 @@
         <v>124</v>
       </c>
       <c r="B115">
-        <v>267</v>
+        <v>48</v>
       </c>
       <c r="C115">
-        <v>1.77</v>
+        <v>3.53</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>255.36</v>
+        <v>398.85</v>
       </c>
       <c r="F115">
-        <v>129.87</v>
+        <v>263.78</v>
       </c>
       <c r="G115">
-        <v>143.02</v>
+        <v>264.13</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -4385,22 +4433,22 @@
         <v>125</v>
       </c>
       <c r="B116">
-        <v>270</v>
+        <v>77</v>
       </c>
       <c r="C116">
-        <v>1.67</v>
+        <v>3.51</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>183.62</v>
+        <v>486.39</v>
       </c>
       <c r="F116">
-        <v>129.76</v>
+        <v>270.24</v>
       </c>
       <c r="G116">
-        <v>142.44</v>
+        <v>291.81</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -4417,22 +4465,22 @@
         <v>126</v>
       </c>
       <c r="B117">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="C117">
-        <v>1.62</v>
+        <v>3.41</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>163.09</v>
+        <v>373.59</v>
       </c>
       <c r="F117">
-        <v>123.41</v>
+        <v>252.59</v>
       </c>
       <c r="G117">
-        <v>125.61</v>
+        <v>257.21</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -4449,22 +4497,22 @@
         <v>127</v>
       </c>
       <c r="B118">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C118">
-        <v>1.52</v>
+        <v>3.35</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>166.32</v>
+        <v>357.78</v>
       </c>
       <c r="F118">
-        <v>117.07</v>
+        <v>254.56</v>
       </c>
       <c r="G118">
-        <v>122.03</v>
+        <v>239.33</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -4481,22 +4529,22 @@
         <v>128</v>
       </c>
       <c r="B119">
-        <v>1037</v>
+        <v>245</v>
       </c>
       <c r="C119">
-        <v>1.36</v>
+        <v>3.3</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>155.25</v>
+        <v>383.85</v>
       </c>
       <c r="F119">
-        <v>106.69</v>
+        <v>250.17</v>
       </c>
       <c r="G119">
-        <v>104.73</v>
+        <v>250.29</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -4513,22 +4561,22 @@
         <v>129</v>
       </c>
       <c r="B120">
-        <v>541</v>
+        <v>315</v>
       </c>
       <c r="C120">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>121.34</v>
+        <v>340.48</v>
       </c>
       <c r="F120">
-        <v>75.55</v>
+        <v>236.33</v>
       </c>
       <c r="G120">
-        <v>76.36</v>
+        <v>234.83</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -4545,22 +4593,22 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C121">
-        <v>0.87</v>
+        <v>3.18</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>91.35</v>
+        <v>363.32</v>
       </c>
       <c r="F121">
-        <v>65.86</v>
+        <v>242.21</v>
       </c>
       <c r="G121">
-        <v>65.63</v>
+        <v>244.06</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -4577,22 +4625,22 @@
         <v>131</v>
       </c>
       <c r="B122">
-        <v>322</v>
+        <v>117</v>
       </c>
       <c r="C122">
-        <v>0.7</v>
+        <v>2.91</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>79.58</v>
+        <v>327.1</v>
       </c>
       <c r="F122">
-        <v>50.17</v>
+        <v>214.42</v>
       </c>
       <c r="G122">
-        <v>50.4</v>
+        <v>201.85</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -4609,22 +4657,22 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="C123">
-        <v>0.49</v>
+        <v>2.91</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>60.67</v>
+        <v>354.67</v>
       </c>
       <c r="F123">
-        <v>34.6</v>
+        <v>218.11</v>
       </c>
       <c r="G123">
-        <v>35.64</v>
+        <v>217.99</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -4634,6 +4682,518 @@
       </c>
       <c r="J123" s="2">
         <f>IF(D123=0,"",(H123-D123)/D123)</f>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124">
+        <v>42</v>
+      </c>
+      <c r="C124">
+        <v>2.9</v>
+      </c>
+      <c r="D124">
+        <f>C124*$B$3</f>
+      </c>
+      <c r="E124">
+        <v>292.39</v>
+      </c>
+      <c r="F124">
+        <v>216.84</v>
+      </c>
+      <c r="G124">
+        <v>219.15</v>
+      </c>
+      <c r="H124">
+        <f>MIN(E124:G124)</f>
+      </c>
+      <c r="I124">
+        <f>H124-D124</f>
+      </c>
+      <c r="J124" s="2">
+        <f>IF(D124=0,"",(H124-D124)/D124)</f>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125">
+        <v>36</v>
+      </c>
+      <c r="C125">
+        <v>2.58</v>
+      </c>
+      <c r="D125">
+        <f>C125*$B$3</f>
+      </c>
+      <c r="E125">
+        <v>368.05</v>
+      </c>
+      <c r="F125">
+        <v>191.81</v>
+      </c>
+      <c r="G125">
+        <v>192.39</v>
+      </c>
+      <c r="H125">
+        <f>MIN(E125:G125)</f>
+      </c>
+      <c r="I125">
+        <f>H125-D125</f>
+      </c>
+      <c r="J125" s="2">
+        <f>IF(D125=0,"",(H125-D125)/D125)</f>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126">
+        <v>67</v>
+      </c>
+      <c r="C126">
+        <v>2.28</v>
+      </c>
+      <c r="D126">
+        <f>C126*$B$3</f>
+      </c>
+      <c r="E126">
+        <v>230.91</v>
+      </c>
+      <c r="F126">
+        <v>176.7</v>
+      </c>
+      <c r="G126">
+        <v>175.32</v>
+      </c>
+      <c r="H126">
+        <f>MIN(E126:G126)</f>
+      </c>
+      <c r="I126">
+        <f>H126-D126</f>
+      </c>
+      <c r="J126" s="2">
+        <f>IF(D126=0,"",(H126-D126)/D126)</f>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127">
+        <v>134</v>
+      </c>
+      <c r="C127">
+        <v>2.26</v>
+      </c>
+      <c r="D127">
+        <f>C127*$B$3</f>
+      </c>
+      <c r="E127">
+        <v>284.54</v>
+      </c>
+      <c r="F127">
+        <v>169.55</v>
+      </c>
+      <c r="G127">
+        <v>165.97</v>
+      </c>
+      <c r="H127">
+        <f>MIN(E127:G127)</f>
+      </c>
+      <c r="I127">
+        <f>H127-D127</f>
+      </c>
+      <c r="J127" s="2">
+        <f>IF(D127=0,"",(H127-D127)/D127)</f>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128">
+        <v>20</v>
+      </c>
+      <c r="C128">
+        <v>2.23</v>
+      </c>
+      <c r="D128">
+        <f>C128*$B$3</f>
+      </c>
+      <c r="E128">
+        <v>249.83</v>
+      </c>
+      <c r="F128">
+        <v>183.39</v>
+      </c>
+      <c r="G128">
+        <v>188</v>
+      </c>
+      <c r="H128">
+        <f>MIN(E128:G128)</f>
+      </c>
+      <c r="I128">
+        <f>H128-D128</f>
+      </c>
+      <c r="J128" s="2">
+        <f>IF(D128=0,"",(H128-D128)/D128)</f>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129">
+        <v>108</v>
+      </c>
+      <c r="C129">
+        <v>2.2</v>
+      </c>
+      <c r="D129">
+        <f>C129*$B$3</f>
+      </c>
+      <c r="E129">
+        <v>295.62</v>
+      </c>
+      <c r="F129">
+        <v>174.86</v>
+      </c>
+      <c r="G129">
+        <v>177.62</v>
+      </c>
+      <c r="H129">
+        <f>MIN(E129:G129)</f>
+      </c>
+      <c r="I129">
+        <f>H129-D129</f>
+      </c>
+      <c r="J129" s="2">
+        <f>IF(D129=0,"",(H129-D129)/D129)</f>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130">
+        <v>24</v>
+      </c>
+      <c r="C130">
+        <v>2.05</v>
+      </c>
+      <c r="D130">
+        <f>C130*$B$3</f>
+      </c>
+      <c r="E130">
+        <v>211.99</v>
+      </c>
+      <c r="F130">
+        <v>144.98</v>
+      </c>
+      <c r="G130">
+        <v>153.29</v>
+      </c>
+      <c r="H130">
+        <f>MIN(E130:G130)</f>
+      </c>
+      <c r="I130">
+        <f>H130-D130</f>
+      </c>
+      <c r="J130" s="2">
+        <f>IF(D130=0,"",(H130-D130)/D130)</f>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131">
+        <v>265</v>
+      </c>
+      <c r="C131">
+        <v>1.77</v>
+      </c>
+      <c r="D131">
+        <f>C131*$B$3</f>
+      </c>
+      <c r="E131">
+        <v>255.36</v>
+      </c>
+      <c r="F131">
+        <v>129.87</v>
+      </c>
+      <c r="G131">
+        <v>143.02</v>
+      </c>
+      <c r="H131">
+        <f>MIN(E131:G131)</f>
+      </c>
+      <c r="I131">
+        <f>H131-D131</f>
+      </c>
+      <c r="J131" s="2">
+        <f>IF(D131=0,"",(H131-D131)/D131)</f>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132">
+        <v>270</v>
+      </c>
+      <c r="C132">
+        <v>1.66</v>
+      </c>
+      <c r="D132">
+        <f>C132*$B$3</f>
+      </c>
+      <c r="E132">
+        <v>183.62</v>
+      </c>
+      <c r="F132">
+        <v>129.76</v>
+      </c>
+      <c r="G132">
+        <v>142.44</v>
+      </c>
+      <c r="H132">
+        <f>MIN(E132:G132)</f>
+      </c>
+      <c r="I132">
+        <f>H132-D132</f>
+      </c>
+      <c r="J132" s="2">
+        <f>IF(D132=0,"",(H132-D132)/D132)</f>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133">
+        <v>297</v>
+      </c>
+      <c r="C133">
+        <v>1.62</v>
+      </c>
+      <c r="D133">
+        <f>C133*$B$3</f>
+      </c>
+      <c r="E133">
+        <v>163.09</v>
+      </c>
+      <c r="F133">
+        <v>123.41</v>
+      </c>
+      <c r="G133">
+        <v>125.61</v>
+      </c>
+      <c r="H133">
+        <f>MIN(E133:G133)</f>
+      </c>
+      <c r="I133">
+        <f>H133-D133</f>
+      </c>
+      <c r="J133" s="2">
+        <f>IF(D133=0,"",(H133-D133)/D133)</f>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134">
+        <v>76</v>
+      </c>
+      <c r="C134">
+        <v>1.52</v>
+      </c>
+      <c r="D134">
+        <f>C134*$B$3</f>
+      </c>
+      <c r="E134">
+        <v>166.32</v>
+      </c>
+      <c r="F134">
+        <v>117.07</v>
+      </c>
+      <c r="G134">
+        <v>122.15</v>
+      </c>
+      <c r="H134">
+        <f>MIN(E134:G134)</f>
+      </c>
+      <c r="I134">
+        <f>H134-D134</f>
+      </c>
+      <c r="J134" s="2">
+        <f>IF(D134=0,"",(H134-D134)/D134)</f>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135">
+        <v>1037</v>
+      </c>
+      <c r="C135">
+        <v>1.36</v>
+      </c>
+      <c r="D135">
+        <f>C135*$B$3</f>
+      </c>
+      <c r="E135">
+        <v>155.25</v>
+      </c>
+      <c r="F135">
+        <v>103.69</v>
+      </c>
+      <c r="G135">
+        <v>104.73</v>
+      </c>
+      <c r="H135">
+        <f>MIN(E135:G135)</f>
+      </c>
+      <c r="I135">
+        <f>H135-D135</f>
+      </c>
+      <c r="J135" s="2">
+        <f>IF(D135=0,"",(H135-D135)/D135)</f>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136">
+        <v>541</v>
+      </c>
+      <c r="C136">
+        <v>1.01</v>
+      </c>
+      <c r="D136">
+        <f>C136*$B$3</f>
+      </c>
+      <c r="E136">
+        <v>121.34</v>
+      </c>
+      <c r="F136">
+        <v>75.55</v>
+      </c>
+      <c r="G136">
+        <v>76.36</v>
+      </c>
+      <c r="H136">
+        <f>MIN(E136:G136)</f>
+      </c>
+      <c r="I136">
+        <f>H136-D136</f>
+      </c>
+      <c r="J136" s="2">
+        <f>IF(D136=0,"",(H136-D136)/D136)</f>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137">
+        <v>306</v>
+      </c>
+      <c r="C137">
+        <v>0.85</v>
+      </c>
+      <c r="D137">
+        <f>C137*$B$3</f>
+      </c>
+      <c r="E137">
+        <v>91.35</v>
+      </c>
+      <c r="F137">
+        <v>66.21</v>
+      </c>
+      <c r="G137">
+        <v>65.17</v>
+      </c>
+      <c r="H137">
+        <f>MIN(E137:G137)</f>
+      </c>
+      <c r="I137">
+        <f>H137-D137</f>
+      </c>
+      <c r="J137" s="2">
+        <f>IF(D137=0,"",(H137-D137)/D137)</f>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138">
+        <v>324</v>
+      </c>
+      <c r="C138">
+        <v>0.7</v>
+      </c>
+      <c r="D138">
+        <f>C138*$B$3</f>
+      </c>
+      <c r="E138">
+        <v>79.58</v>
+      </c>
+      <c r="F138">
+        <v>50.17</v>
+      </c>
+      <c r="G138">
+        <v>50.29</v>
+      </c>
+      <c r="H138">
+        <f>MIN(E138:G138)</f>
+      </c>
+      <c r="I138">
+        <f>H138-D138</f>
+      </c>
+      <c r="J138" s="2">
+        <f>IF(D138=0,"",(H138-D138)/D138)</f>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139">
+        <v>35</v>
+      </c>
+      <c r="C139">
+        <v>0.49</v>
+      </c>
+      <c r="D139">
+        <f>C139*$B$3</f>
+      </c>
+      <c r="E139">
+        <v>60.67</v>
+      </c>
+      <c r="F139">
+        <v>34.49</v>
+      </c>
+      <c r="G139">
+        <v>35.64</v>
+      </c>
+      <c r="H139">
+        <f>MIN(E139:G139)</f>
+      </c>
+      <c r="I139">
+        <f>H139-D139</f>
+      </c>
+      <c r="J139" s="2">
+        <f>IF(D139=0,"",(H139-D139)/D139)</f>
       </c>
     </row>
   </sheetData>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 16:23</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 16:42</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -196,15 +196,15 @@
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>P250 | Epicenter (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Five-SeveN | Kami (Factory New)</t>
+  </si>
+  <si>
     <t>FAMAS | Styx (Field-Tested)</t>
   </si>
   <si>
-    <t>P250 | Epicenter (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Five-SeveN | Kami (Factory New)</t>
-  </si>
-  <si>
     <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
   </si>
   <si>
@@ -226,12 +226,12 @@
     <t>MP7 | Fade (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>MP7 | Fade (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Great Wave (Holo)</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Slingshot | Phoenix</t>
   </si>
   <si>
+    <t>SG 553 | Integrale (Field-Tested)</t>
+  </si>
+  <si>
     <t>Rezan The Ready | Sabre</t>
   </si>
   <si>
-    <t>SG 553 | Integrale (Field-Tested)</t>
-  </si>
-  <si>
     <t>Rezan the Redshirt | Sabre</t>
   </si>
   <si>
@@ -346,15 +346,15 @@
     <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
+    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
-    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
@@ -424,10 +424,10 @@
     <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | Broken Fang (Holo)</t>
+  </si>
+  <si>
     <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
     <t>Sticker | Ancient Beast (Foil)</t>
@@ -945,10 +945,10 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>135.15</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -980,7 +980,7 @@
         <v>369</v>
       </c>
       <c r="C8">
-        <v>119.36</v>
+        <v>119.34</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
@@ -1024,7 +1024,7 @@
         <v>7484.18</v>
       </c>
       <c r="G9">
-        <v>7439.43</v>
+        <v>7416.36</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1044,7 +1044,7 @@
         <v>196</v>
       </c>
       <c r="C10">
-        <v>87.82</v>
+        <v>88.21</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1073,10 +1073,10 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11">
-        <v>84.65</v>
+        <v>86.01</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
@@ -1085,7 +1085,7 @@
         <v>8653.27</v>
       </c>
       <c r="F11">
-        <v>6222.25</v>
+        <v>6221.44</v>
       </c>
       <c r="G11">
         <v>6430.21</v>
@@ -1169,7 +1169,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14">
         <v>59.63</v>
@@ -1184,7 +1184,7 @@
         <v>4521.33</v>
       </c>
       <c r="G14">
-        <v>4504.03</v>
+        <v>4498.26</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1201,7 +1201,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C15">
         <v>58.76</v>
@@ -1233,7 +1233,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C16">
         <v>58.2</v>
@@ -1277,7 +1277,7 @@
         <v>6306.45</v>
       </c>
       <c r="F17">
-        <v>4388.69</v>
+        <v>4394.45</v>
       </c>
       <c r="G17">
         <v>4354.09</v>
@@ -1297,10 +1297,10 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C18">
-        <v>56.24</v>
+        <v>56.3</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1312,7 +1312,7 @@
         <v>4152.24</v>
       </c>
       <c r="G18">
-        <v>4149.93</v>
+        <v>4149.82</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1329,7 +1329,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C19">
         <v>54.5</v>
@@ -1341,10 +1341,10 @@
         <v>5808.98</v>
       </c>
       <c r="F19">
-        <v>4036.9</v>
+        <v>4117.64</v>
       </c>
       <c r="G19">
-        <v>4013.83</v>
+        <v>4008.07</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1364,7 +1364,7 @@
         <v>75</v>
       </c>
       <c r="C20">
-        <v>52.69</v>
+        <v>52.29</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
@@ -1376,7 +1376,7 @@
         <v>4016.48</v>
       </c>
       <c r="G20">
-        <v>3971.16</v>
+        <v>3965.39</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1393,7 +1393,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21">
         <v>48.73</v>
@@ -1437,7 +1437,7 @@
         <v>5384.88</v>
       </c>
       <c r="F22">
-        <v>3633.09</v>
+        <v>3575.54</v>
       </c>
       <c r="G22">
         <v>3587.07</v>
@@ -1489,7 +1489,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C24">
         <v>48.45</v>
@@ -1501,10 +1501,10 @@
         <v>5214.64</v>
       </c>
       <c r="F24">
-        <v>3690.88</v>
+        <v>3685.11</v>
       </c>
       <c r="G24">
-        <v>3552.47</v>
+        <v>3546.71</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1533,10 +1533,10 @@
         <v>4457.08</v>
       </c>
       <c r="F25">
-        <v>2713.83</v>
+        <v>2708.18</v>
       </c>
       <c r="G25">
-        <v>2942.09</v>
+        <v>2940.94</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1565,7 +1565,7 @@
         <v>4142.55</v>
       </c>
       <c r="F26">
-        <v>2876.23</v>
+        <v>2870.47</v>
       </c>
       <c r="G26">
         <v>2692.84</v>
@@ -1585,7 +1585,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>35.37</v>
@@ -1600,7 +1600,7 @@
         <v>2652.82</v>
       </c>
       <c r="G27">
-        <v>2935.4</v>
+        <v>3016.14</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1649,7 +1649,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C29">
         <v>32.25</v>
@@ -1681,7 +1681,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C30">
         <v>29.35</v>
@@ -1693,7 +1693,7 @@
         <v>3122.48</v>
       </c>
       <c r="F30">
-        <v>2174.16</v>
+        <v>2237.6</v>
       </c>
       <c r="G30">
         <v>2237.6</v>
@@ -1745,10 +1745,10 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C32">
-        <v>23.41</v>
+        <v>23.45</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
@@ -1757,7 +1757,7 @@
         <v>2839.44</v>
       </c>
       <c r="F32">
-        <v>1868.51</v>
+        <v>1880.04</v>
       </c>
       <c r="G32">
         <v>1914.64</v>
@@ -1777,7 +1777,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33">
         <v>21.07</v>
@@ -1841,7 +1841,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C35">
         <v>19.51</v>
@@ -1937,7 +1937,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>15.44</v>
@@ -1952,7 +1952,7 @@
         <v>1243.37</v>
       </c>
       <c r="G38">
-        <v>1229.52</v>
+        <v>1229.41</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1981,10 +1981,10 @@
         <v>1876.12</v>
       </c>
       <c r="F39">
-        <v>1176.35</v>
+        <v>1170.59</v>
       </c>
       <c r="G39">
-        <v>1193.77</v>
+        <v>1188</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2065,7 +2065,7 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>1738</v>
+        <v>1745</v>
       </c>
       <c r="C42">
         <v>13.44</v>
@@ -2129,7 +2129,7 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C44">
         <v>13.01</v>
@@ -2208,7 +2208,7 @@
         <v>979.01</v>
       </c>
       <c r="G46">
-        <v>935.29</v>
+        <v>934.14</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2225,7 +2225,7 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C47">
         <v>12.36</v>
@@ -2237,7 +2237,7 @@
         <v>1425.26</v>
       </c>
       <c r="F47">
-        <v>943.37</v>
+        <v>942.21</v>
       </c>
       <c r="G47">
         <v>942.33</v>
@@ -2272,7 +2272,7 @@
         <v>839.68</v>
       </c>
       <c r="G48">
-        <v>853.52</v>
+        <v>856.86</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2289,10 +2289,10 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="C49">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
@@ -2301,7 +2301,7 @@
         <v>1342.44</v>
       </c>
       <c r="F49">
-        <v>806.23</v>
+        <v>829.29</v>
       </c>
       <c r="G49">
         <v>818.91</v>
@@ -2321,7 +2321,7 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C50">
         <v>10.58</v>
@@ -2333,10 +2333,10 @@
         <v>1180.85</v>
       </c>
       <c r="F50">
-        <v>785.7</v>
+        <v>788.12</v>
       </c>
       <c r="G50">
-        <v>813.95</v>
+        <v>813.84</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2385,22 +2385,22 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>189</v>
+        <v>98</v>
       </c>
       <c r="C52">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1153.28</v>
+        <v>1097.23</v>
       </c>
       <c r="F52">
-        <v>753.4</v>
+        <v>748.56</v>
       </c>
       <c r="G52">
-        <v>817.76</v>
+        <v>791.23</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2417,22 +2417,22 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C53">
-        <v>10.26</v>
+        <v>10.19</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1097.23</v>
+        <v>1132.75</v>
       </c>
       <c r="F53">
-        <v>748.56</v>
+        <v>757.67</v>
       </c>
       <c r="G53">
-        <v>791.23</v>
+        <v>757.78</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2449,7 +2449,7 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="C54">
         <v>10.19</v>
@@ -2458,13 +2458,13 @@
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1132.75</v>
+        <v>1153.28</v>
       </c>
       <c r="F54">
-        <v>758.82</v>
+        <v>749.71</v>
       </c>
       <c r="G54">
-        <v>758.94</v>
+        <v>821.91</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2481,10 +2481,10 @@
         <v>64</v>
       </c>
       <c r="B55">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
@@ -2493,7 +2493,7 @@
         <v>1128.83</v>
       </c>
       <c r="F55">
-        <v>735.64</v>
+        <v>726.64</v>
       </c>
       <c r="G55">
         <v>713.84</v>
@@ -2513,7 +2513,7 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="C56">
         <v>9.96</v>
@@ -2522,13 +2522,13 @@
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1103.57</v>
+        <v>1093.31</v>
       </c>
       <c r="F56">
-        <v>771.62</v>
+        <v>777.39</v>
       </c>
       <c r="G56">
-        <v>764.7</v>
+        <v>763.55</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2545,7 +2545,7 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C57">
         <v>9.79</v>
@@ -2557,7 +2557,7 @@
         <v>1087.77</v>
       </c>
       <c r="F57">
-        <v>692.04</v>
+        <v>743.94</v>
       </c>
       <c r="G57">
         <v>715.11</v>
@@ -2577,7 +2577,7 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58">
         <v>9.77</v>
@@ -2624,7 +2624,7 @@
         <v>655.94</v>
       </c>
       <c r="G59">
-        <v>668.86</v>
+        <v>674.74</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2641,7 +2641,7 @@
         <v>69</v>
       </c>
       <c r="B60">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C60">
         <v>8.74</v>
@@ -2653,10 +2653,10 @@
         <v>988.46</v>
       </c>
       <c r="F60">
+        <v>655.13</v>
+      </c>
+      <c r="G60">
         <v>645.9</v>
-      </c>
-      <c r="G60">
-        <v>649.36</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -2673,7 +2673,7 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C61">
         <v>8.67</v>
@@ -2705,22 +2705,22 @@
         <v>71</v>
       </c>
       <c r="B62">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="C62">
-        <v>8.29</v>
+        <v>8.28</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>931.72</v>
+        <v>934.83</v>
       </c>
       <c r="F62">
-        <v>631.26</v>
+        <v>678.2</v>
       </c>
       <c r="G62">
-        <v>611.3</v>
+        <v>632.06</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -2737,22 +2737,22 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C63">
-        <v>8.28</v>
+        <v>8.27</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>934.83</v>
+        <v>931.72</v>
       </c>
       <c r="F63">
-        <v>678.2</v>
+        <v>631.26</v>
       </c>
       <c r="G63">
-        <v>632.06</v>
+        <v>611.3</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -2801,7 +2801,7 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C65">
         <v>8.23</v>
@@ -2833,7 +2833,7 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C66">
         <v>8.05</v>
@@ -2845,7 +2845,7 @@
         <v>1002.65</v>
       </c>
       <c r="F66">
-        <v>594</v>
+        <v>597.46</v>
       </c>
       <c r="G66">
         <v>588.23</v>
@@ -2865,22 +2865,22 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>1430</v>
+        <v>131</v>
       </c>
       <c r="C67">
-        <v>7.95</v>
+        <v>7.99</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>904.15</v>
+        <v>826.87</v>
       </c>
       <c r="F67">
-        <v>599.77</v>
+        <v>584.31</v>
       </c>
       <c r="G67">
-        <v>576.7</v>
+        <v>599.65</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -2897,22 +2897,22 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>131</v>
+        <v>1431</v>
       </c>
       <c r="C68">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>826.87</v>
+        <v>904.15</v>
       </c>
       <c r="F68">
-        <v>584.31</v>
+        <v>599.65</v>
       </c>
       <c r="G68">
-        <v>599.77</v>
+        <v>576.7</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -2929,7 +2929,7 @@
         <v>78</v>
       </c>
       <c r="B69">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C69">
         <v>7.91</v>
@@ -2941,7 +2941,7 @@
         <v>892.27</v>
       </c>
       <c r="F69">
-        <v>588.12</v>
+        <v>576.7</v>
       </c>
       <c r="G69">
         <v>576.93</v>
@@ -2961,7 +2961,7 @@
         <v>79</v>
       </c>
       <c r="B70">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C70">
         <v>7.88</v>
@@ -2973,7 +2973,7 @@
         <v>879.7</v>
       </c>
       <c r="F70">
-        <v>609</v>
+        <v>608.42</v>
       </c>
       <c r="G70">
         <v>597.35</v>
@@ -3121,10 +3121,10 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="C75">
-        <v>6.87</v>
+        <v>6.9</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
@@ -3133,7 +3133,7 @@
         <v>809.57</v>
       </c>
       <c r="F75">
-        <v>513.26</v>
+        <v>510.96</v>
       </c>
       <c r="G75">
         <v>507.5</v>
@@ -3165,7 +3165,7 @@
         <v>765.4</v>
       </c>
       <c r="F76">
-        <v>489.39</v>
+        <v>490.54</v>
       </c>
       <c r="G76">
         <v>483.27</v>
@@ -3185,7 +3185,7 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C77">
         <v>6.57</v>
@@ -3217,10 +3217,10 @@
         <v>87</v>
       </c>
       <c r="B78">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="C78">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
@@ -3264,7 +3264,7 @@
         <v>478.89</v>
       </c>
       <c r="G79">
-        <v>574.74</v>
+        <v>573.47</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3281,7 +3281,7 @@
         <v>89</v>
       </c>
       <c r="B80">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C80">
         <v>6.48</v>
@@ -3328,7 +3328,7 @@
         <v>478.55</v>
       </c>
       <c r="G81">
-        <v>519.03</v>
+        <v>507.5</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3441,7 +3441,7 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="C85">
         <v>5.91</v>
@@ -3505,7 +3505,7 @@
         <v>96</v>
       </c>
       <c r="B87">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C87">
         <v>5.75</v>
@@ -3569,10 +3569,10 @@
         <v>98</v>
       </c>
       <c r="B89">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C89">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
@@ -3581,7 +3581,7 @@
         <v>591.23</v>
       </c>
       <c r="F89">
-        <v>403.69</v>
+        <v>392.16</v>
       </c>
       <c r="G89">
         <v>426.76</v>
@@ -3697,10 +3697,10 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C93">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
@@ -3712,7 +3712,7 @@
         <v>422.14</v>
       </c>
       <c r="G93">
-        <v>426.53</v>
+        <v>425.37</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -3732,7 +3732,7 @@
         <v>29</v>
       </c>
       <c r="C94">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
@@ -3776,7 +3776,7 @@
         <v>412.23</v>
       </c>
       <c r="G95">
-        <v>387.54</v>
+        <v>388.7</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -3793,7 +3793,7 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C96">
         <v>5</v>
@@ -3825,7 +3825,7 @@
         <v>106</v>
       </c>
       <c r="B97">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C97">
         <v>4.91</v>
@@ -3857,7 +3857,7 @@
         <v>107</v>
       </c>
       <c r="B98">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C98">
         <v>4.82</v>
@@ -3872,7 +3872,7 @@
         <v>356.63</v>
       </c>
       <c r="G98">
-        <v>365.4</v>
+        <v>364.24</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -3985,22 +3985,22 @@
         <v>111</v>
       </c>
       <c r="B102">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="C102">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>566.78</v>
+        <v>521.8</v>
       </c>
       <c r="F102">
-        <v>344.87</v>
+        <v>359.17</v>
       </c>
       <c r="G102">
-        <v>322.95</v>
+        <v>346.02</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4017,22 +4017,22 @@
         <v>112</v>
       </c>
       <c r="B103">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C103">
-        <v>4.65</v>
+        <v>4.46</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>521.8</v>
+        <v>485.58</v>
       </c>
       <c r="F103">
-        <v>359.17</v>
+        <v>321.57</v>
       </c>
       <c r="G103">
-        <v>346.02</v>
+        <v>291.58</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4049,22 +4049,22 @@
         <v>113</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="C104">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>485.58</v>
+        <v>562.74</v>
       </c>
       <c r="F104">
-        <v>321.57</v>
+        <v>344.87</v>
       </c>
       <c r="G104">
-        <v>291.58</v>
+        <v>322.95</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4177,7 +4177,7 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>2409</v>
+        <v>2415</v>
       </c>
       <c r="C108">
         <v>4.38</v>
@@ -4192,7 +4192,7 @@
         <v>334.49</v>
       </c>
       <c r="G108">
-        <v>326.99</v>
+        <v>325.84</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4349,10 +4349,10 @@
         <v>405.19</v>
       </c>
       <c r="F113">
-        <v>291.23</v>
+        <v>288.35</v>
       </c>
       <c r="G113">
-        <v>276.82</v>
+        <v>275.66</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -4512,7 +4512,7 @@
         <v>254.56</v>
       </c>
       <c r="G118">
-        <v>239.33</v>
+        <v>239.56</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -4544,7 +4544,7 @@
         <v>250.17</v>
       </c>
       <c r="G119">
-        <v>250.29</v>
+        <v>249.13</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -4561,7 +4561,7 @@
         <v>129</v>
       </c>
       <c r="B120">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C120">
         <v>3.2</v>
@@ -4576,7 +4576,7 @@
         <v>236.33</v>
       </c>
       <c r="G120">
-        <v>234.83</v>
+        <v>236.1</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -4593,7 +4593,7 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C121">
         <v>3.18</v>
@@ -4657,7 +4657,7 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C123">
         <v>2.91</v>
@@ -4689,7 +4689,7 @@
         <v>133</v>
       </c>
       <c r="B124">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C124">
         <v>2.9</v>
@@ -4698,7 +4698,7 @@
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>292.39</v>
+        <v>316.84</v>
       </c>
       <c r="F124">
         <v>216.84</v>
@@ -4724,7 +4724,7 @@
         <v>36</v>
       </c>
       <c r="C125">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
@@ -4733,7 +4733,7 @@
         <v>368.05</v>
       </c>
       <c r="F125">
-        <v>191.81</v>
+        <v>191.93</v>
       </c>
       <c r="G125">
         <v>192.39</v>
@@ -4785,7 +4785,7 @@
         <v>136</v>
       </c>
       <c r="B127">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C127">
         <v>2.26</v>
@@ -4817,22 +4817,22 @@
         <v>137</v>
       </c>
       <c r="B128">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="C128">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>249.83</v>
+        <v>295.62</v>
       </c>
       <c r="F128">
-        <v>183.39</v>
+        <v>174.86</v>
       </c>
       <c r="G128">
-        <v>188</v>
+        <v>177.62</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -4849,22 +4849,22 @@
         <v>138</v>
       </c>
       <c r="B129">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="C129">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>295.62</v>
+        <v>249.83</v>
       </c>
       <c r="F129">
-        <v>174.86</v>
+        <v>183.39</v>
       </c>
       <c r="G129">
-        <v>177.62</v>
+        <v>188</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -4913,7 +4913,7 @@
         <v>140</v>
       </c>
       <c r="B131">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C131">
         <v>1.77</v>
@@ -4977,7 +4977,7 @@
         <v>142</v>
       </c>
       <c r="B133">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C133">
         <v>1.62</v>
@@ -4992,7 +4992,7 @@
         <v>123.41</v>
       </c>
       <c r="G133">
-        <v>125.61</v>
+        <v>124.45</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5009,7 +5009,7 @@
         <v>143</v>
       </c>
       <c r="B134">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C134">
         <v>1.52</v>
@@ -5024,7 +5024,7 @@
         <v>117.07</v>
       </c>
       <c r="G134">
-        <v>122.15</v>
+        <v>125.61</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5053,7 +5053,7 @@
         <v>155.25</v>
       </c>
       <c r="F135">
-        <v>103.69</v>
+        <v>106.69</v>
       </c>
       <c r="G135">
         <v>104.73</v>
@@ -5085,10 +5085,10 @@
         <v>121.34</v>
       </c>
       <c r="F136">
-        <v>75.55</v>
+        <v>75.43</v>
       </c>
       <c r="G136">
-        <v>76.36</v>
+        <v>76.12</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5105,7 +5105,7 @@
         <v>146</v>
       </c>
       <c r="B137">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C137">
         <v>0.85</v>
@@ -5114,13 +5114,13 @@
         <f>C137*$B$3</f>
       </c>
       <c r="E137">
-        <v>91.35</v>
+        <v>95.27</v>
       </c>
       <c r="F137">
         <v>66.21</v>
       </c>
       <c r="G137">
-        <v>65.17</v>
+        <v>65.05</v>
       </c>
       <c r="H137">
         <f>MIN(E137:G137)</f>
@@ -5169,7 +5169,7 @@
         <v>148</v>
       </c>
       <c r="B139">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C139">
         <v>0.49</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 16:42</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 17:42</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -160,12 +160,12 @@
     <t>MP9 | Music Box (Factory New)</t>
   </si>
   <si>
+    <t>Nova | Sobek's Bite (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Nova | Sobek's Bite (Minimal Wear)</t>
-  </si>
-  <si>
     <t>'The Doctor' Romanov | Sabre</t>
   </si>
   <si>
@@ -178,12 +178,12 @@
     <t>Sticker | Great Wave (Foil)</t>
   </si>
   <si>
+    <t>M4A4 | Evil Daimyo (Factory New)</t>
+  </si>
+  <si>
     <t>SG 553 | Candy Apple (Factory New)</t>
   </si>
   <si>
-    <t>M4A4 | Evil Daimyo (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
@@ -196,15 +196,15 @@
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Five-SeveN | Kami (Factory New)</t>
+  </si>
+  <si>
+    <t>FAMAS | Styx (Field-Tested)</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Minimal Wear)</t>
   </si>
   <si>
-    <t>Five-SeveN | Kami (Factory New)</t>
-  </si>
-  <si>
-    <t>FAMAS | Styx (Field-Tested)</t>
-  </si>
-  <si>
     <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>SG 553 | Integrale (Field-Tested)</t>
+  </si>
+  <si>
     <t>Slingshot | Phoenix</t>
   </si>
   <si>
-    <t>SG 553 | Integrale (Field-Tested)</t>
-  </si>
-  <si>
     <t>Rezan The Ready | Sabre</t>
   </si>
   <si>
@@ -274,12 +274,12 @@
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Tec-9 | Brass (Field-Tested)</t>
+  </si>
+  <si>
     <t>Maximus | Sabre</t>
   </si>
   <si>
-    <t>Tec-9 | Brass (Field-Tested)</t>
-  </si>
-  <si>
     <t>Dragomir | Sabre</t>
   </si>
   <si>
@@ -289,15 +289,15 @@
     <t>Sticker | BIG (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -313,12 +313,12 @@
     <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
   </si>
   <si>
@@ -334,33 +334,33 @@
     <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>R8 Revolver | Blaze (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Stone Scales (Foil)</t>
   </si>
   <si>
     <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
+    <t>Sticker | Gold Web (Foil)</t>
+  </si>
+  <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Sticker | Gold Web (Foil)</t>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -406,25 +406,25 @@
     <t>AK-47 | Crossfade (Minimal Wear)</t>
   </si>
   <si>
+    <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
+  </si>
+  <si>
     <t>CZ75-Auto | Tuxedo (Factory New)</t>
   </si>
   <si>
     <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
-  </si>
-  <si>
     <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Broken Fang (Holo)</t>
+  </si>
+  <si>
     <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
     <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
@@ -864,7 +864,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.78</v>
+        <v>81.76</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -948,7 +948,7 @@
         <v>66</v>
       </c>
       <c r="C7">
-        <v>135.15</v>
+        <v>135.25</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -977,7 +977,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C8">
         <v>119.34</v>
@@ -992,7 +992,7 @@
         <v>8875.41</v>
       </c>
       <c r="G8">
-        <v>8760.07</v>
+        <v>8718.55</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1009,22 +1009,22 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C9">
-        <v>98.11</v>
+        <v>97.13</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>10640.58</v>
+        <v>10635.04</v>
       </c>
       <c r="F9">
         <v>7484.18</v>
       </c>
       <c r="G9">
-        <v>7416.36</v>
+        <v>7497.1</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1041,10 +1041,10 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10">
-        <v>88.21</v>
+        <v>88.48</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1085,7 +1085,7 @@
         <v>8653.27</v>
       </c>
       <c r="F11">
-        <v>6221.44</v>
+        <v>6215.67</v>
       </c>
       <c r="G11">
         <v>6430.21</v>
@@ -1105,10 +1105,10 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C12">
-        <v>81.14</v>
+        <v>80.84</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
@@ -1169,10 +1169,10 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C14">
-        <v>59.63</v>
+        <v>59.68</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
@@ -1204,13 +1204,13 @@
         <v>299</v>
       </c>
       <c r="C15">
-        <v>58.76</v>
+        <v>58.25</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>6258.35</v>
+        <v>6315.1</v>
       </c>
       <c r="F15">
         <v>4371.39</v>
@@ -1233,7 +1233,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C16">
         <v>58.2</v>
@@ -1265,10 +1265,10 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17">
-        <v>57.9</v>
+        <v>57.32</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
@@ -1297,7 +1297,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C18">
         <v>56.3</v>
@@ -1312,7 +1312,7 @@
         <v>4152.24</v>
       </c>
       <c r="G18">
-        <v>4149.82</v>
+        <v>4167</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1329,7 +1329,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19">
         <v>54.5</v>
@@ -1338,13 +1338,13 @@
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5808.98</v>
+        <v>5807.48</v>
       </c>
       <c r="F19">
         <v>4117.64</v>
       </c>
       <c r="G19">
-        <v>4008.07</v>
+        <v>3979.23</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1364,16 +1364,16 @@
         <v>75</v>
       </c>
       <c r="C20">
-        <v>52.29</v>
+        <v>52.69</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>5515.79</v>
+        <v>6024.21</v>
       </c>
       <c r="F20">
-        <v>4016.48</v>
+        <v>4016.25</v>
       </c>
       <c r="G20">
         <v>3965.39</v>
@@ -1393,7 +1393,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <v>48.73</v>
@@ -1405,7 +1405,7 @@
         <v>5717.63</v>
       </c>
       <c r="F21">
-        <v>3650.51</v>
+        <v>3633.21</v>
       </c>
       <c r="G21">
         <v>3610.14</v>
@@ -1437,7 +1437,7 @@
         <v>5384.88</v>
       </c>
       <c r="F22">
-        <v>3575.54</v>
+        <v>3569.77</v>
       </c>
       <c r="G22">
         <v>3587.07</v>
@@ -1489,7 +1489,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C24">
         <v>48.45</v>
@@ -1524,7 +1524,7 @@
         <v>110</v>
       </c>
       <c r="C25">
-        <v>37.45</v>
+        <v>37.08</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
@@ -1556,7 +1556,7 @@
         <v>66</v>
       </c>
       <c r="C26">
-        <v>36.43</v>
+        <v>36.07</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
@@ -1565,10 +1565,10 @@
         <v>4142.55</v>
       </c>
       <c r="F26">
-        <v>2870.47</v>
+        <v>2841.75</v>
       </c>
       <c r="G26">
-        <v>2692.84</v>
+        <v>2687.42</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1585,10 +1585,10 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27">
-        <v>35.37</v>
+        <v>35.02</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
@@ -1600,7 +1600,7 @@
         <v>2652.82</v>
       </c>
       <c r="G27">
-        <v>3016.14</v>
+        <v>2952.7</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1617,7 +1617,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C28">
         <v>32.57</v>
@@ -1629,10 +1629,10 @@
         <v>3633.33</v>
       </c>
       <c r="F28">
-        <v>2483.27</v>
+        <v>2483.15</v>
       </c>
       <c r="G28">
-        <v>2387.54</v>
+        <v>2399.07</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1649,10 +1649,10 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C29">
-        <v>32.25</v>
+        <v>32.05</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
@@ -1664,7 +1664,7 @@
         <v>2422.02</v>
       </c>
       <c r="G29">
-        <v>2358.59</v>
+        <v>2421.68</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1681,22 +1681,22 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C30">
-        <v>29.35</v>
+        <v>29.46</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>3122.48</v>
+        <v>3123.29</v>
       </c>
       <c r="F30">
         <v>2237.6</v>
       </c>
       <c r="G30">
-        <v>2237.6</v>
+        <v>2208.76</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1713,22 +1713,22 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C31">
-        <v>25.77</v>
+        <v>25.58</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2719.6</v>
+        <v>2708.64</v>
       </c>
       <c r="F31">
         <v>1894.69</v>
       </c>
       <c r="G31">
-        <v>1908.88</v>
+        <v>1903.11</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1745,10 +1745,10 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C32">
-        <v>23.45</v>
+        <v>23.23</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
@@ -1757,7 +1757,7 @@
         <v>2839.44</v>
       </c>
       <c r="F32">
-        <v>1880.04</v>
+        <v>1874.28</v>
       </c>
       <c r="G32">
         <v>1914.64</v>
@@ -1777,10 +1777,10 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C33">
-        <v>21.07</v>
+        <v>20.86</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
@@ -1789,10 +1789,10 @@
         <v>2307.38</v>
       </c>
       <c r="F33">
-        <v>1596.88</v>
+        <v>1603.23</v>
       </c>
       <c r="G33">
-        <v>1568.51</v>
+        <v>1551.32</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -1812,7 +1812,7 @@
         <v>80</v>
       </c>
       <c r="C34">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
@@ -1853,10 +1853,10 @@
         <v>2360.89</v>
       </c>
       <c r="F35">
-        <v>1487.66</v>
+        <v>1480.85</v>
       </c>
       <c r="G35">
-        <v>1435.87</v>
+        <v>1441.63</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -1873,7 +1873,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C36">
         <v>18.95</v>
@@ -1888,7 +1888,7 @@
         <v>1465.97</v>
       </c>
       <c r="G36">
-        <v>1441.75</v>
+        <v>1451.9</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -1905,7 +1905,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C37">
         <v>18.84</v>
@@ -1914,10 +1914,10 @@
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2180.39</v>
+        <v>2170.12</v>
       </c>
       <c r="F37">
-        <v>1430.22</v>
+        <v>1441.75</v>
       </c>
       <c r="G37">
         <v>1388.69</v>
@@ -1937,22 +1937,22 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38">
-        <v>15.44</v>
+        <v>15.43</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1734.25</v>
+        <v>1967.59</v>
       </c>
       <c r="F38">
         <v>1243.37</v>
       </c>
       <c r="G38">
-        <v>1229.41</v>
+        <v>1227.1</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1981,7 +1981,7 @@
         <v>1876.12</v>
       </c>
       <c r="F39">
-        <v>1170.59</v>
+        <v>1164.82</v>
       </c>
       <c r="G39">
         <v>1188</v>
@@ -2001,22 +2001,22 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C40">
-        <v>13.96</v>
+        <v>13.93</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1505.65</v>
+        <v>1455.94</v>
       </c>
       <c r="F40">
-        <v>1000</v>
+        <v>1068.86</v>
       </c>
       <c r="G40">
-        <v>942.9</v>
+        <v>1092.27</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2033,22 +2033,22 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="C41">
-        <v>13.93</v>
+        <v>13.82</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1455.94</v>
+        <v>1505.65</v>
       </c>
       <c r="F41">
-        <v>1068.86</v>
+        <v>1000</v>
       </c>
       <c r="G41">
-        <v>1092.27</v>
+        <v>942.9</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2065,10 +2065,10 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>1745</v>
+        <v>1738</v>
       </c>
       <c r="C42">
-        <v>13.44</v>
+        <v>13.49</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
@@ -2080,7 +2080,7 @@
         <v>1013.84</v>
       </c>
       <c r="G42">
-        <v>1019.03</v>
+        <v>1038.06</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2097,7 +2097,7 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C43">
         <v>13.25</v>
@@ -2106,7 +2106,7 @@
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1590.77</v>
+        <v>1441.75</v>
       </c>
       <c r="F43">
         <v>975.78</v>
@@ -2129,7 +2129,7 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C44">
         <v>13.01</v>
@@ -2138,13 +2138,13 @@
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1541.06</v>
+        <v>1530.1</v>
       </c>
       <c r="F44">
-        <v>978.08</v>
+        <v>976.93</v>
       </c>
       <c r="G44">
-        <v>980.39</v>
+        <v>981.54</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2193,22 +2193,22 @@
         <v>55</v>
       </c>
       <c r="B46">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="C46">
-        <v>12.41</v>
+        <v>12.36</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1330.56</v>
+        <v>1414.99</v>
       </c>
       <c r="F46">
-        <v>979.01</v>
+        <v>942.21</v>
       </c>
       <c r="G46">
-        <v>934.14</v>
+        <v>940.02</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2225,22 +2225,22 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>371</v>
+        <v>95</v>
       </c>
       <c r="C47">
-        <v>12.36</v>
+        <v>12.32</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1425.26</v>
+        <v>1329.87</v>
       </c>
       <c r="F47">
-        <v>942.21</v>
+        <v>979.01</v>
       </c>
       <c r="G47">
-        <v>942.33</v>
+        <v>931.83</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2269,7 +2269,7 @@
         <v>1263.67</v>
       </c>
       <c r="F48">
-        <v>839.68</v>
+        <v>838.52</v>
       </c>
       <c r="G48">
         <v>856.86</v>
@@ -2289,7 +2289,7 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="C49">
         <v>11.06</v>
@@ -2298,13 +2298,13 @@
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1342.44</v>
+        <v>1303</v>
       </c>
       <c r="F49">
-        <v>829.29</v>
+        <v>847.75</v>
       </c>
       <c r="G49">
-        <v>818.91</v>
+        <v>824.22</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2330,13 +2330,13 @@
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1180.85</v>
+        <v>1174.51</v>
       </c>
       <c r="F50">
-        <v>788.12</v>
+        <v>785.81</v>
       </c>
       <c r="G50">
-        <v>813.84</v>
+        <v>812.69</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2365,7 +2365,7 @@
         <v>1182.47</v>
       </c>
       <c r="F51">
-        <v>772.78</v>
+        <v>771.62</v>
       </c>
       <c r="G51">
         <v>741.06</v>
@@ -2385,22 +2385,22 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C52">
-        <v>10.26</v>
+        <v>10.19</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1097.23</v>
+        <v>1132.75</v>
       </c>
       <c r="F52">
-        <v>748.56</v>
+        <v>757.67</v>
       </c>
       <c r="G52">
-        <v>791.23</v>
+        <v>756.63</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2417,7 +2417,7 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="C53">
         <v>10.19</v>
@@ -2426,13 +2426,13 @@
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1132.75</v>
+        <v>1153.28</v>
       </c>
       <c r="F53">
-        <v>757.67</v>
+        <v>749.71</v>
       </c>
       <c r="G53">
-        <v>757.78</v>
+        <v>821.91</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2449,22 +2449,22 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="C54">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1153.28</v>
+        <v>1097.23</v>
       </c>
       <c r="F54">
-        <v>749.71</v>
+        <v>748.56</v>
       </c>
       <c r="G54">
-        <v>821.91</v>
+        <v>791.12</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2484,19 +2484,19 @@
         <v>493</v>
       </c>
       <c r="C55">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1128.83</v>
+        <v>1129.64</v>
       </c>
       <c r="F55">
         <v>726.64</v>
       </c>
       <c r="G55">
-        <v>713.84</v>
+        <v>711.53</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2513,10 +2513,10 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C56">
-        <v>9.96</v>
+        <v>9.86</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
@@ -2525,7 +2525,7 @@
         <v>1093.31</v>
       </c>
       <c r="F56">
-        <v>777.39</v>
+        <v>776.24</v>
       </c>
       <c r="G56">
         <v>763.55</v>
@@ -2545,10 +2545,10 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C57">
-        <v>9.79</v>
+        <v>9.7</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
@@ -2557,10 +2557,10 @@
         <v>1087.77</v>
       </c>
       <c r="F57">
-        <v>743.94</v>
+        <v>744.4</v>
       </c>
       <c r="G57">
-        <v>715.11</v>
+        <v>713.95</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2577,10 +2577,10 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C58">
-        <v>9.77</v>
+        <v>9.67</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
@@ -2589,7 +2589,7 @@
         <v>1016.84</v>
       </c>
       <c r="F58">
-        <v>713.72</v>
+        <v>712.57</v>
       </c>
       <c r="G58">
         <v>743.94</v>
@@ -2609,7 +2609,7 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C59">
         <v>8.92</v>
@@ -2621,10 +2621,10 @@
         <v>906.46</v>
       </c>
       <c r="F59">
-        <v>655.94</v>
+        <v>645.9</v>
       </c>
       <c r="G59">
-        <v>674.74</v>
+        <v>671.28</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2641,16 +2641,16 @@
         <v>69</v>
       </c>
       <c r="B60">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C60">
-        <v>8.74</v>
+        <v>8.65</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>988.46</v>
+        <v>964.01</v>
       </c>
       <c r="F60">
         <v>655.13</v>
@@ -2673,22 +2673,22 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C61">
-        <v>8.67</v>
+        <v>8.59</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>1038.98</v>
+        <v>963.32</v>
       </c>
       <c r="F61">
         <v>660.78</v>
       </c>
       <c r="G61">
-        <v>645.9</v>
+        <v>644.75</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -2737,7 +2737,7 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C63">
         <v>8.27</v>
@@ -2746,7 +2746,7 @@
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>931.72</v>
+        <v>910.49</v>
       </c>
       <c r="F63">
         <v>631.26</v>
@@ -2816,7 +2816,7 @@
         <v>657.44</v>
       </c>
       <c r="G65">
-        <v>640.14</v>
+        <v>634.37</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -2833,22 +2833,22 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>847</v>
+        <v>131</v>
       </c>
       <c r="C66">
-        <v>8.05</v>
+        <v>7.99</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>1002.65</v>
+        <v>845.79</v>
       </c>
       <c r="F66">
-        <v>597.46</v>
+        <v>588.12</v>
       </c>
       <c r="G66">
-        <v>588.23</v>
+        <v>598.61</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -2865,22 +2865,22 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>131</v>
+        <v>846</v>
       </c>
       <c r="C67">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>826.87</v>
+        <v>922.26</v>
       </c>
       <c r="F67">
-        <v>584.31</v>
+        <v>597.35</v>
       </c>
       <c r="G67">
-        <v>599.65</v>
+        <v>588.23</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -2897,10 +2897,10 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C68">
-        <v>7.95</v>
+        <v>7.88</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
@@ -2929,19 +2929,19 @@
         <v>78</v>
       </c>
       <c r="B69">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C69">
-        <v>7.91</v>
+        <v>7.83</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>892.27</v>
+        <v>837.95</v>
       </c>
       <c r="F69">
-        <v>576.7</v>
+        <v>587.08</v>
       </c>
       <c r="G69">
         <v>576.93</v>
@@ -2961,22 +2961,22 @@
         <v>79</v>
       </c>
       <c r="B70">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C70">
-        <v>7.88</v>
+        <v>7.82</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>879.7</v>
+        <v>900.23</v>
       </c>
       <c r="F70">
-        <v>608.42</v>
+        <v>603.23</v>
       </c>
       <c r="G70">
-        <v>597.35</v>
+        <v>593.89</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -2996,7 +2996,7 @@
         <v>143</v>
       </c>
       <c r="C71">
-        <v>7.67</v>
+        <v>7.62</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
@@ -3025,22 +3025,22 @@
         <v>81</v>
       </c>
       <c r="B72">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C72">
-        <v>7.46</v>
+        <v>7.39</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>875.78</v>
+        <v>906.46</v>
       </c>
       <c r="F72">
-        <v>563.9</v>
+        <v>559.4</v>
       </c>
       <c r="G72">
-        <v>535.18</v>
+        <v>536.33</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3069,7 +3069,7 @@
         <v>755.13</v>
       </c>
       <c r="F73">
-        <v>530.33</v>
+        <v>530.22</v>
       </c>
       <c r="G73">
         <v>546.71</v>
@@ -3101,7 +3101,7 @@
         <v>840.25</v>
       </c>
       <c r="F74">
-        <v>518.91</v>
+        <v>517.76</v>
       </c>
       <c r="G74">
         <v>515.34</v>
@@ -3121,10 +3121,10 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C75">
-        <v>6.9</v>
+        <v>6.84</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
@@ -3133,10 +3133,10 @@
         <v>809.57</v>
       </c>
       <c r="F75">
-        <v>510.96</v>
+        <v>513.26</v>
       </c>
       <c r="G75">
-        <v>507.5</v>
+        <v>514.42</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3153,10 +3153,10 @@
         <v>85</v>
       </c>
       <c r="B76">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C76">
-        <v>6.84</v>
+        <v>6.82</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
@@ -3165,10 +3165,10 @@
         <v>765.4</v>
       </c>
       <c r="F76">
-        <v>490.54</v>
+        <v>484.43</v>
       </c>
       <c r="G76">
-        <v>483.27</v>
+        <v>480.97</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3185,7 +3185,7 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C77">
         <v>6.57</v>
@@ -3217,22 +3217,22 @@
         <v>87</v>
       </c>
       <c r="B78">
-        <v>1194</v>
+        <v>77</v>
       </c>
       <c r="C78">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>768.51</v>
+        <v>752.82</v>
       </c>
       <c r="F78">
-        <v>470.47</v>
+        <v>478.89</v>
       </c>
       <c r="G78">
-        <v>481.89</v>
+        <v>573.47</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3249,22 +3249,22 @@
         <v>88</v>
       </c>
       <c r="B79">
-        <v>77</v>
+        <v>1194</v>
       </c>
       <c r="C79">
-        <v>6.48</v>
+        <v>6.44</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>752.82</v>
+        <v>768.51</v>
       </c>
       <c r="F79">
-        <v>478.89</v>
+        <v>475.32</v>
       </c>
       <c r="G79">
-        <v>573.47</v>
+        <v>480.74</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3281,22 +3281,22 @@
         <v>89</v>
       </c>
       <c r="B80">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C80">
-        <v>6.48</v>
+        <v>6.44</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>799.31</v>
+        <v>784.31</v>
       </c>
       <c r="F80">
-        <v>479.7</v>
+        <v>479.81</v>
       </c>
       <c r="G80">
-        <v>475.09</v>
+        <v>473.93</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3313,7 +3313,7 @@
         <v>90</v>
       </c>
       <c r="B81">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81">
         <v>6.29</v>
@@ -3325,7 +3325,7 @@
         <v>656.63</v>
       </c>
       <c r="F81">
-        <v>478.55</v>
+        <v>461.36</v>
       </c>
       <c r="G81">
         <v>507.5</v>
@@ -3360,7 +3360,7 @@
         <v>462.51</v>
       </c>
       <c r="G82">
-        <v>456.05</v>
+        <v>454.79</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3377,7 +3377,7 @@
         <v>92</v>
       </c>
       <c r="B83">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="C83">
         <v>6.03</v>
@@ -3386,13 +3386,13 @@
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>468.17</v>
+        <v>634.49</v>
       </c>
       <c r="F83">
-        <v>332.18</v>
+        <v>507.38</v>
       </c>
       <c r="G83">
-        <v>331.95</v>
+        <v>481.89</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3409,22 +3409,22 @@
         <v>93</v>
       </c>
       <c r="B84">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C84">
-        <v>5.97</v>
+        <v>6.03</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>554.9</v>
+        <v>468.17</v>
       </c>
       <c r="F84">
-        <v>419.61</v>
+        <v>334.49</v>
       </c>
       <c r="G84">
-        <v>392.04</v>
+        <v>331.95</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3441,7 +3441,7 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>229</v>
+        <v>123</v>
       </c>
       <c r="C85">
         <v>5.91</v>
@@ -3450,13 +3450,13 @@
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>634.49</v>
+        <v>554.9</v>
       </c>
       <c r="F85">
-        <v>507.38</v>
+        <v>419.61</v>
       </c>
       <c r="G85">
-        <v>481.89</v>
+        <v>392.04</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -3488,7 +3488,7 @@
         <v>416.15</v>
       </c>
       <c r="G86">
-        <v>434.26</v>
+        <v>433.1</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -3505,7 +3505,7 @@
         <v>96</v>
       </c>
       <c r="B87">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C87">
         <v>5.75</v>
@@ -3520,7 +3520,7 @@
         <v>429.64</v>
       </c>
       <c r="G87">
-        <v>452.59</v>
+        <v>452.48</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -3540,7 +3540,7 @@
         <v>136</v>
       </c>
       <c r="C88">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
@@ -3569,22 +3569,22 @@
         <v>98</v>
       </c>
       <c r="B89">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C89">
-        <v>5.54</v>
+        <v>5.58</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>591.23</v>
+        <v>585.7</v>
       </c>
       <c r="F89">
-        <v>392.16</v>
+        <v>415.11</v>
       </c>
       <c r="G89">
-        <v>426.76</v>
+        <v>427.91</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -3616,7 +3616,7 @@
         <v>396.77</v>
       </c>
       <c r="G90">
-        <v>386.39</v>
+        <v>385.24</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -3633,22 +3633,22 @@
         <v>100</v>
       </c>
       <c r="B91">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="C91">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>619.61</v>
+        <v>600.69</v>
       </c>
       <c r="F91">
-        <v>452.13</v>
+        <v>447.29</v>
       </c>
       <c r="G91">
-        <v>392.16</v>
+        <v>403.69</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -3665,7 +3665,7 @@
         <v>101</v>
       </c>
       <c r="B92">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="C92">
         <v>5.37</v>
@@ -3674,13 +3674,13 @@
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>600.69</v>
+        <v>619.61</v>
       </c>
       <c r="F92">
-        <v>447.29</v>
+        <v>452.13</v>
       </c>
       <c r="G92">
-        <v>404.61</v>
+        <v>389.85</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -3697,10 +3697,10 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C93">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
@@ -3709,10 +3709,10 @@
         <v>625.83</v>
       </c>
       <c r="F93">
-        <v>422.14</v>
+        <v>422.03</v>
       </c>
       <c r="G93">
-        <v>425.37</v>
+        <v>403.69</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -3732,7 +3732,7 @@
         <v>29</v>
       </c>
       <c r="C94">
-        <v>5.31</v>
+        <v>5.3</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
@@ -3744,7 +3744,7 @@
         <v>409.23</v>
       </c>
       <c r="G94">
-        <v>415.11</v>
+        <v>413.96</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -3793,22 +3793,22 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>559.63</v>
+        <v>547.06</v>
       </c>
       <c r="F96">
-        <v>362.17</v>
+        <v>357.55</v>
       </c>
       <c r="G96">
-        <v>392.04</v>
+        <v>391</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -3840,7 +3840,7 @@
         <v>383.04</v>
       </c>
       <c r="G97">
-        <v>369.09</v>
+        <v>370.24</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -3857,22 +3857,22 @@
         <v>107</v>
       </c>
       <c r="B98">
-        <v>618</v>
+        <v>120</v>
       </c>
       <c r="C98">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>507.61</v>
+        <v>588.81</v>
       </c>
       <c r="F98">
-        <v>356.63</v>
+        <v>411.07</v>
       </c>
       <c r="G98">
-        <v>364.24</v>
+        <v>379.47</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -3889,22 +3889,22 @@
         <v>108</v>
       </c>
       <c r="B99">
-        <v>121</v>
+        <v>618</v>
       </c>
       <c r="C99">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>588.81</v>
+        <v>507.61</v>
       </c>
       <c r="F99">
-        <v>411.07</v>
+        <v>356.75</v>
       </c>
       <c r="G99">
-        <v>379.47</v>
+        <v>364.24</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -3924,7 +3924,7 @@
         <v>78</v>
       </c>
       <c r="C100">
-        <v>4.76</v>
+        <v>4.71</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
@@ -3933,7 +3933,7 @@
         <v>599.88</v>
       </c>
       <c r="F100">
-        <v>366.78</v>
+        <v>373.59</v>
       </c>
       <c r="G100">
         <v>380.62</v>
@@ -3953,7 +3953,7 @@
         <v>110</v>
       </c>
       <c r="B101">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C101">
         <v>4.69</v>
@@ -3962,7 +3962,7 @@
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>548.56</v>
+        <v>535.18</v>
       </c>
       <c r="F101">
         <v>334.49</v>
@@ -3985,22 +3985,22 @@
         <v>111</v>
       </c>
       <c r="B102">
-        <v>55</v>
+        <v>158</v>
       </c>
       <c r="C102">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>521.8</v>
+        <v>562.74</v>
       </c>
       <c r="F102">
-        <v>359.17</v>
+        <v>344.75</v>
       </c>
       <c r="G102">
-        <v>346.02</v>
+        <v>322.95</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4017,22 +4017,22 @@
         <v>112</v>
       </c>
       <c r="B103">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C103">
-        <v>4.46</v>
+        <v>4.6</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>485.58</v>
+        <v>521.8</v>
       </c>
       <c r="F103">
-        <v>321.57</v>
+        <v>359.17</v>
       </c>
       <c r="G103">
-        <v>291.58</v>
+        <v>346.02</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4049,22 +4049,22 @@
         <v>113</v>
       </c>
       <c r="B104">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="C104">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>562.74</v>
+        <v>485.58</v>
       </c>
       <c r="F104">
-        <v>344.87</v>
+        <v>321.57</v>
       </c>
       <c r="G104">
-        <v>322.95</v>
+        <v>291.58</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4081,22 +4081,22 @@
         <v>114</v>
       </c>
       <c r="B105">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="C105">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>432.76</v>
+        <v>480.05</v>
       </c>
       <c r="F105">
-        <v>353.98</v>
+        <v>339.45</v>
       </c>
       <c r="G105">
-        <v>312.69</v>
+        <v>329.87</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4113,22 +4113,22 @@
         <v>115</v>
       </c>
       <c r="B106">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="C106">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>480.05</v>
+        <v>432.76</v>
       </c>
       <c r="F106">
-        <v>339.45</v>
+        <v>353.98</v>
       </c>
       <c r="G106">
-        <v>329.87</v>
+        <v>312.69</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4148,7 +4148,7 @@
         <v>101</v>
       </c>
       <c r="C107">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
@@ -4160,7 +4160,7 @@
         <v>339.79</v>
       </c>
       <c r="G107">
-        <v>363.09</v>
+        <v>360.78</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4177,10 +4177,10 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="C108">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
@@ -4189,10 +4189,10 @@
         <v>475.32</v>
       </c>
       <c r="F108">
-        <v>334.49</v>
+        <v>324.11</v>
       </c>
       <c r="G108">
-        <v>325.84</v>
+        <v>322.95</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4244,7 +4244,7 @@
         <v>123</v>
       </c>
       <c r="C110">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
@@ -4273,7 +4273,7 @@
         <v>120</v>
       </c>
       <c r="B111">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C111">
         <v>3.86</v>
@@ -4282,10 +4282,10 @@
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>411.42</v>
+        <v>412.23</v>
       </c>
       <c r="F111">
-        <v>310.61</v>
+        <v>309.46</v>
       </c>
       <c r="G111">
         <v>291.81</v>
@@ -4340,7 +4340,7 @@
         <v>365</v>
       </c>
       <c r="C113">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
@@ -4349,10 +4349,10 @@
         <v>405.19</v>
       </c>
       <c r="F113">
-        <v>288.35</v>
+        <v>288.23</v>
       </c>
       <c r="G113">
-        <v>275.66</v>
+        <v>276.82</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -4372,7 +4372,7 @@
         <v>128</v>
       </c>
       <c r="C114">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
@@ -4436,7 +4436,7 @@
         <v>77</v>
       </c>
       <c r="C116">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
@@ -4465,7 +4465,7 @@
         <v>126</v>
       </c>
       <c r="B117">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C117">
         <v>3.41</v>
@@ -4509,7 +4509,7 @@
         <v>357.78</v>
       </c>
       <c r="F118">
-        <v>254.56</v>
+        <v>253.4</v>
       </c>
       <c r="G118">
         <v>239.56</v>
@@ -4529,7 +4529,7 @@
         <v>128</v>
       </c>
       <c r="B119">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C119">
         <v>3.3</v>
@@ -4564,7 +4564,7 @@
         <v>316</v>
       </c>
       <c r="C120">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
@@ -4593,10 +4593,10 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C121">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
@@ -4605,10 +4605,10 @@
         <v>363.32</v>
       </c>
       <c r="F121">
-        <v>242.21</v>
+        <v>242.1</v>
       </c>
       <c r="G121">
-        <v>244.06</v>
+        <v>243.94</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -4625,22 +4625,22 @@
         <v>131</v>
       </c>
       <c r="B122">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="C122">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>327.1</v>
+        <v>316.84</v>
       </c>
       <c r="F122">
-        <v>214.42</v>
+        <v>216.84</v>
       </c>
       <c r="G122">
-        <v>201.85</v>
+        <v>221.57</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -4657,22 +4657,22 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="C123">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>354.67</v>
+        <v>327.1</v>
       </c>
       <c r="F123">
-        <v>218.11</v>
+        <v>214.3</v>
       </c>
       <c r="G123">
-        <v>217.99</v>
+        <v>201.85</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -4689,22 +4689,22 @@
         <v>133</v>
       </c>
       <c r="B124">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="C124">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>316.84</v>
+        <v>354.67</v>
       </c>
       <c r="F124">
-        <v>216.84</v>
+        <v>218.11</v>
       </c>
       <c r="G124">
-        <v>219.15</v>
+        <v>217.76</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -4724,7 +4724,7 @@
         <v>36</v>
       </c>
       <c r="C125">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
@@ -4756,7 +4756,7 @@
         <v>67</v>
       </c>
       <c r="C126">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
@@ -4765,7 +4765,7 @@
         <v>230.91</v>
       </c>
       <c r="F126">
-        <v>176.7</v>
+        <v>176.24</v>
       </c>
       <c r="G126">
         <v>175.32</v>
@@ -4785,22 +4785,22 @@
         <v>136</v>
       </c>
       <c r="B127">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C127">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>284.54</v>
+        <v>295.62</v>
       </c>
       <c r="F127">
-        <v>169.55</v>
+        <v>174.86</v>
       </c>
       <c r="G127">
-        <v>165.97</v>
+        <v>177.62</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -4817,7 +4817,7 @@
         <v>137</v>
       </c>
       <c r="B128">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C128">
         <v>2.25</v>
@@ -4826,13 +4826,13 @@
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>295.62</v>
+        <v>285.35</v>
       </c>
       <c r="F128">
-        <v>174.86</v>
+        <v>177.28</v>
       </c>
       <c r="G128">
-        <v>177.62</v>
+        <v>165.97</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -4884,7 +4884,7 @@
         <v>24</v>
       </c>
       <c r="C130">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
@@ -4896,7 +4896,7 @@
         <v>144.98</v>
       </c>
       <c r="G130">
-        <v>153.29</v>
+        <v>153.4</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -4960,7 +4960,7 @@
         <v>129.76</v>
       </c>
       <c r="G132">
-        <v>142.44</v>
+        <v>141.29</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -4977,7 +4977,7 @@
         <v>142</v>
       </c>
       <c r="B133">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C133">
         <v>1.62</v>
@@ -5009,7 +5009,7 @@
         <v>143</v>
       </c>
       <c r="B134">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C134">
         <v>1.52</v>
@@ -5041,10 +5041,10 @@
         <v>144</v>
       </c>
       <c r="B135">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="C135">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
@@ -5056,7 +5056,7 @@
         <v>106.69</v>
       </c>
       <c r="G135">
-        <v>104.73</v>
+        <v>104.61</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5073,7 +5073,7 @@
         <v>145</v>
       </c>
       <c r="B136">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C136">
         <v>1.01</v>
@@ -5088,7 +5088,7 @@
         <v>75.43</v>
       </c>
       <c r="G136">
-        <v>76.12</v>
+        <v>76.01</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5105,7 +5105,7 @@
         <v>146</v>
       </c>
       <c r="B137">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C137">
         <v>0.85</v>
@@ -5120,7 +5120,7 @@
         <v>66.21</v>
       </c>
       <c r="G137">
-        <v>65.05</v>
+        <v>64.59</v>
       </c>
       <c r="H137">
         <f>MIN(E137:G137)</f>
@@ -5137,10 +5137,10 @@
         <v>147</v>
       </c>
       <c r="B138">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C138">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="D138">
         <f>C138*$B$3</f>
@@ -5172,16 +5172,16 @@
         <v>36</v>
       </c>
       <c r="C139">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="D139">
         <f>C139*$B$3</f>
       </c>
       <c r="E139">
-        <v>60.67</v>
+        <v>59.86</v>
       </c>
       <c r="F139">
-        <v>34.49</v>
+        <v>34.6</v>
       </c>
       <c r="G139">
         <v>35.64</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
-  <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 17:42</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="171">
+  <si>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 17:57</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -58,18 +58,42 @@
     <t>Разница %</t>
   </si>
   <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Редкость</t>
+  </si>
+  <si>
     <t>MP9 | Pandora's Box (Factory New)</t>
   </si>
   <si>
+    <t>SMG</t>
+  </si>
+  <si>
+    <t>Mil-Spec Grade</t>
+  </si>
+  <si>
     <t>MP9 | Stained Glass (Factory New)</t>
   </si>
   <si>
+    <t>Restricted</t>
+  </si>
+  <si>
     <t>USP-S | Whiteout (Minimal Wear)</t>
   </si>
   <si>
+    <t>Pistol</t>
+  </si>
+  <si>
+    <t>Classified</t>
+  </si>
+  <si>
     <t>M4A4 | Desolate Space (Factory New)</t>
   </si>
   <si>
+    <t>Rifle</t>
+  </si>
+  <si>
     <t>AK-47 | Point Disarray (Factory New)</t>
   </si>
   <si>
@@ -79,6 +103,12 @@
     <t>AWP | Containment Breach (Field-Tested)</t>
   </si>
   <si>
+    <t>Sniper Rifle</t>
+  </si>
+  <si>
+    <t>Covert</t>
+  </si>
+  <si>
     <t>MP9 | Dark Age (Factory New)</t>
   </si>
   <si>
@@ -139,6 +169,12 @@
     <t>Chem-Haz Capitaine | Gendarmerie Nationale</t>
   </si>
   <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Superior</t>
+  </si>
+  <si>
     <t>SG 553 | Integrale (Minimal Wear)</t>
   </si>
   <si>
@@ -151,6 +187,9 @@
     <t>Nova | Sobek's Bite (Factory New)</t>
   </si>
   <si>
+    <t>Shotgun</t>
+  </si>
+  <si>
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
@@ -166,9 +205,18 @@
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker</t>
+  </si>
+  <si>
+    <t>Remarkable</t>
+  </si>
+  <si>
     <t>'The Doctor' Romanov | Sabre</t>
   </si>
   <si>
+    <t>Master</t>
+  </si>
+  <si>
     <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
   </si>
   <si>
@@ -178,12 +226,18 @@
     <t>Sticker | Great Wave (Foil)</t>
   </si>
   <si>
+    <t>Exotic</t>
+  </si>
+  <si>
     <t>M4A4 | Evil Daimyo (Factory New)</t>
   </si>
   <si>
     <t>SG 553 | Candy Apple (Factory New)</t>
   </si>
   <si>
+    <t>Industrial Grade</t>
+  </si>
+  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
@@ -211,9 +265,15 @@
     <t>Osiris | Elite Crew</t>
   </si>
   <si>
+    <t>Exceptional</t>
+  </si>
+  <si>
     <t>B Squadron Officer | SAS</t>
   </si>
   <si>
+    <t>Distinguished</t>
+  </si>
+  <si>
     <t>AUG | Carved Jade (Minimal Wear)</t>
   </si>
   <si>
@@ -226,15 +286,15 @@
     <t>MP7 | Fade (Minimal Wear)</t>
   </si>
   <si>
+    <t>MP7 | Fade (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | Great Wave (Holo)</t>
+  </si>
+  <si>
     <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>MP7 | Fade (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Great Wave (Holo)</t>
-  </si>
-  <si>
     <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -265,24 +325,27 @@
     <t>Sticker | Liquid Fire</t>
   </si>
   <si>
+    <t>High Grade</t>
+  </si>
+  <si>
+    <t>AK-47 | Crossfade (Factory New)</t>
+  </si>
+  <si>
     <t>AK-47 | Slate (Minimal Wear)</t>
   </si>
   <si>
-    <t>AK-47 | Crossfade (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Tec-9 | Brass (Field-Tested)</t>
   </si>
   <si>
+    <t>Dragomir | Sabre</t>
+  </si>
+  <si>
     <t>Maximus | Sabre</t>
   </si>
   <si>
-    <t>Dragomir | Sabre</t>
-  </si>
-  <si>
     <t>XM1014 | Black Tie (Factory New)</t>
   </si>
   <si>
@@ -328,12 +391,18 @@
     <t>MAC-10 | Strats (Factory New)</t>
   </si>
   <si>
+    <t>Consumer Grade</t>
+  </si>
+  <si>
     <t>AWP | Black Nile (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Gold Web (Foil)</t>
+  </si>
+  <si>
     <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -346,9 +415,6 @@
     <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | Gold Web (Foil)</t>
-  </si>
-  <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -421,10 +487,10 @@
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Broken Fang (Holo)</t>
-  </si>
-  <si>
-    <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
@@ -842,11 +908,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="10" width="14" customWidth="1"/>
+    <col min="2" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -876,7 +942,7 @@
         <v>11.534</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -907,10 +973,16 @@
       <c r="J5" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>49</v>
@@ -939,16 +1011,22 @@
       <c r="J6" s="2">
         <f>IF(D6=0,"",(H6-D6)/D6)</f>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>66</v>
       </c>
       <c r="C7">
-        <v>135.25</v>
+        <v>135.3</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -971,13 +1049,19 @@
       <c r="J7" s="2">
         <f>IF(D7=0,"",(H7-D7)/D7)</f>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C8">
         <v>119.34</v>
@@ -992,7 +1076,7 @@
         <v>8875.41</v>
       </c>
       <c r="G8">
-        <v>8718.55</v>
+        <v>8737.01</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1003,13 +1087,19 @@
       <c r="J8" s="2">
         <f>IF(D8=0,"",(H8-D8)/D8)</f>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C9">
         <v>97.13</v>
@@ -1024,7 +1114,7 @@
         <v>7484.18</v>
       </c>
       <c r="G9">
-        <v>7497.1</v>
+        <v>7554.65</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1035,16 +1125,22 @@
       <c r="J9" s="2">
         <f>IF(D9=0,"",(H9-D9)/D9)</f>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B10">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C10">
-        <v>88.48</v>
+        <v>88.5</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1067,10 +1163,16 @@
       <c r="J10" s="2">
         <f>IF(D10=0,"",(H10-D10)/D10)</f>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>58</v>
@@ -1099,16 +1201,22 @@
       <c r="J11" s="2">
         <f>IF(D11=0,"",(H11-D11)/D11)</f>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B12">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C12">
-        <v>80.84</v>
+        <v>81.14</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
@@ -1131,10 +1239,16 @@
       <c r="J12" s="2">
         <f>IF(D12=0,"",(H12-D12)/D12)</f>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>35</v>
@@ -1163,16 +1277,22 @@
       <c r="J13" s="2">
         <f>IF(D13=0,"",(H13-D13)/D13)</f>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B14">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14">
-        <v>59.68</v>
+        <v>59.89</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
@@ -1195,10 +1315,16 @@
       <c r="J14" s="2">
         <f>IF(D14=0,"",(H14-D14)/D14)</f>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>299</v>
@@ -1227,10 +1353,16 @@
       <c r="J15" s="2">
         <f>IF(D15=0,"",(H15-D15)/D15)</f>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>262</v>
@@ -1259,13 +1391,19 @@
       <c r="J16" s="2">
         <f>IF(D16=0,"",(H16-D16)/D16)</f>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B17">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C17">
         <v>57.32</v>
@@ -1280,7 +1418,7 @@
         <v>4394.45</v>
       </c>
       <c r="G17">
-        <v>4354.09</v>
+        <v>4348.32</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1291,13 +1429,19 @@
       <c r="J17" s="2">
         <f>IF(D17=0,"",(H17-D17)/D17)</f>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B18">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C18">
         <v>56.3</v>
@@ -1309,10 +1453,10 @@
         <v>6620.98</v>
       </c>
       <c r="F18">
+        <v>4244.51</v>
+      </c>
+      <c r="G18">
         <v>4152.24</v>
-      </c>
-      <c r="G18">
-        <v>4167</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1323,10 +1467,16 @@
       <c r="J18" s="2">
         <f>IF(D18=0,"",(H18-D18)/D18)</f>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B19">
         <v>274</v>
@@ -1355,10 +1505,16 @@
       <c r="J19" s="2">
         <f>IF(D19=0,"",(H19-D19)/D19)</f>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B20">
         <v>75</v>
@@ -1387,10 +1543,16 @@
       <c r="J20" s="2">
         <f>IF(D20=0,"",(H20-D20)/D20)</f>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B21">
         <v>72</v>
@@ -1419,13 +1581,19 @@
       <c r="J21" s="2">
         <f>IF(D21=0,"",(H21-D21)/D21)</f>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B22">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22">
         <v>48.6</v>
@@ -1451,10 +1619,16 @@
       <c r="J22" s="2">
         <f>IF(D22=0,"",(H22-D22)/D22)</f>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B23">
         <v>60</v>
@@ -1483,13 +1657,19 @@
       <c r="J23" s="2">
         <f>IF(D23=0,"",(H23-D23)/D23)</f>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B24">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C24">
         <v>48.45</v>
@@ -1515,10 +1695,16 @@
       <c r="J24" s="2">
         <f>IF(D24=0,"",(H24-D24)/D24)</f>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B25">
         <v>110</v>
@@ -1547,10 +1733,16 @@
       <c r="J25" s="2">
         <f>IF(D25=0,"",(H25-D25)/D25)</f>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B26">
         <v>66</v>
@@ -1579,10 +1771,16 @@
       <c r="J26" s="2">
         <f>IF(D26=0,"",(H26-D26)/D26)</f>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>94</v>
@@ -1611,16 +1809,22 @@
       <c r="J27" s="2">
         <f>IF(D27=0,"",(H27-D27)/D27)</f>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B28">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C28">
-        <v>32.57</v>
+        <v>32.66</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
@@ -1643,16 +1847,22 @@
       <c r="J28" s="2">
         <f>IF(D28=0,"",(H28-D28)/D28)</f>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B29">
         <v>137</v>
       </c>
       <c r="C29">
-        <v>32.05</v>
+        <v>31.67</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
@@ -1675,16 +1885,22 @@
       <c r="J29" s="2">
         <f>IF(D29=0,"",(H29-D29)/D29)</f>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B30">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C30">
-        <v>29.46</v>
+        <v>29.48</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
@@ -1707,10 +1923,16 @@
       <c r="J30" s="2">
         <f>IF(D30=0,"",(H30-D30)/D30)</f>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>229</v>
@@ -1739,16 +1961,22 @@
       <c r="J31" s="2">
         <f>IF(D31=0,"",(H31-D31)/D31)</f>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B32">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C32">
-        <v>23.23</v>
+        <v>23.24</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
@@ -1771,10 +1999,16 @@
       <c r="J32" s="2">
         <f>IF(D32=0,"",(H32-D32)/D32)</f>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" t="s">
+        <v>52</v>
+      </c>
+      <c r="L32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B33">
         <v>149</v>
@@ -1803,16 +2037,22 @@
       <c r="J33" s="2">
         <f>IF(D33=0,"",(H33-D33)/D33)</f>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B34">
         <v>80</v>
       </c>
       <c r="C34">
-        <v>19.8</v>
+        <v>19.79</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
@@ -1835,13 +2075,19 @@
       <c r="J34" s="2">
         <f>IF(D34=0,"",(H34-D34)/D34)</f>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B35">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C35">
         <v>19.51</v>
@@ -1867,13 +2113,19 @@
       <c r="J35" s="2">
         <f>IF(D35=0,"",(H35-D35)/D35)</f>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>18.95</v>
@@ -1899,13 +2151,19 @@
       <c r="J36" s="2">
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B37">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C37">
         <v>18.84</v>
@@ -1931,16 +2189,22 @@
       <c r="J37" s="2">
         <f>IF(D37=0,"",(H37-D37)/D37)</f>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B38">
         <v>79</v>
       </c>
       <c r="C38">
-        <v>15.43</v>
+        <v>15.41</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
@@ -1963,10 +2227,16 @@
       <c r="J38" s="2">
         <f>IF(D38=0,"",(H38-D38)/D38)</f>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B39">
         <v>47</v>
@@ -1995,10 +2265,16 @@
       <c r="J39" s="2">
         <f>IF(D39=0,"",(H39-D39)/D39)</f>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B40">
         <v>26</v>
@@ -2027,10 +2303,16 @@
       <c r="J40" s="2">
         <f>IF(D40=0,"",(H40-D40)/D40)</f>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B41">
         <v>67</v>
@@ -2059,13 +2341,19 @@
       <c r="J41" s="2">
         <f>IF(D41=0,"",(H41-D41)/D41)</f>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>64</v>
+      </c>
+      <c r="L41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B42">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="C42">
         <v>13.49</v>
@@ -2091,10 +2379,16 @@
       <c r="J42" s="2">
         <f>IF(D42=0,"",(H42-D42)/D42)</f>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
+        <v>52</v>
+      </c>
+      <c r="L42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B43">
         <v>60</v>
@@ -2123,13 +2417,19 @@
       <c r="J43" s="2">
         <f>IF(D43=0,"",(H43-D43)/D43)</f>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B44">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C44">
         <v>13.01</v>
@@ -2155,10 +2455,16 @@
       <c r="J44" s="2">
         <f>IF(D44=0,"",(H44-D44)/D44)</f>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>52</v>
+      </c>
+      <c r="L44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -2187,10 +2493,16 @@
       <c r="J45" s="2">
         <f>IF(D45=0,"",(H45-D45)/D45)</f>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>64</v>
+      </c>
+      <c r="L45" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B46">
         <v>371</v>
@@ -2219,10 +2531,16 @@
       <c r="J46" s="2">
         <f>IF(D46=0,"",(H46-D46)/D46)</f>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B47">
         <v>95</v>
@@ -2251,10 +2569,16 @@
       <c r="J47" s="2">
         <f>IF(D47=0,"",(H47-D47)/D47)</f>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B48">
         <v>176</v>
@@ -2283,10 +2607,16 @@
       <c r="J48" s="2">
         <f>IF(D48=0,"",(H48-D48)/D48)</f>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B49">
         <v>1768</v>
@@ -2315,13 +2645,19 @@
       <c r="J49" s="2">
         <f>IF(D49=0,"",(H49-D49)/D49)</f>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="B50">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C50">
         <v>10.58</v>
@@ -2347,10 +2683,16 @@
       <c r="J50" s="2">
         <f>IF(D50=0,"",(H50-D50)/D50)</f>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B51">
         <v>202</v>
@@ -2379,10 +2721,16 @@
       <c r="J51" s="2">
         <f>IF(D51=0,"",(H51-D51)/D51)</f>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>64</v>
+      </c>
+      <c r="L51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B52">
         <v>84</v>
@@ -2411,13 +2759,19 @@
       <c r="J52" s="2">
         <f>IF(D52=0,"",(H52-D52)/D52)</f>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B53">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C53">
         <v>10.19</v>
@@ -2443,10 +2797,16 @@
       <c r="J53" s="2">
         <f>IF(D53=0,"",(H53-D53)/D53)</f>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B54">
         <v>100</v>
@@ -2475,10 +2835,16 @@
       <c r="J54" s="2">
         <f>IF(D54=0,"",(H54-D54)/D54)</f>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B55">
         <v>493</v>
@@ -2507,10 +2873,16 @@
       <c r="J55" s="2">
         <f>IF(D55=0,"",(H55-D55)/D55)</f>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B56">
         <v>1313</v>
@@ -2539,13 +2911,19 @@
       <c r="J56" s="2">
         <f>IF(D56=0,"",(H56-D56)/D56)</f>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>52</v>
+      </c>
+      <c r="L56" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B57">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C57">
         <v>9.7</v>
@@ -2571,10 +2949,16 @@
       <c r="J57" s="2">
         <f>IF(D57=0,"",(H57-D57)/D57)</f>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>52</v>
+      </c>
+      <c r="L57" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="B58">
         <v>95</v>
@@ -2603,13 +2987,19 @@
       <c r="J58" s="2">
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B59">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C59">
         <v>8.92</v>
@@ -2635,10 +3025,16 @@
       <c r="J59" s="2">
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B60">
         <v>688</v>
@@ -2667,10 +3063,16 @@
       <c r="J60" s="2">
         <f>IF(D60=0,"",(H60-D60)/D60)</f>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K60" t="s">
+        <v>52</v>
+      </c>
+      <c r="L60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B61">
         <v>561</v>
@@ -2699,28 +3101,34 @@
       <c r="J61" s="2">
         <f>IF(D61=0,"",(H61-D61)/D61)</f>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K61" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B62">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="C62">
-        <v>8.28</v>
+        <v>8.29</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>934.83</v>
+        <v>910.49</v>
       </c>
       <c r="F62">
-        <v>678.2</v>
+        <v>631.26</v>
       </c>
       <c r="G62">
-        <v>632.06</v>
+        <v>611.3</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -2731,28 +3139,34 @@
       <c r="J62" s="2">
         <f>IF(D62=0,"",(H62-D62)/D62)</f>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K62" t="s">
+        <v>18</v>
+      </c>
+      <c r="L62" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B63">
-        <v>190</v>
+        <v>25</v>
       </c>
       <c r="C63">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>910.49</v>
+        <v>938.87</v>
       </c>
       <c r="F63">
-        <v>631.26</v>
+        <v>609</v>
       </c>
       <c r="G63">
-        <v>611.3</v>
+        <v>629.3</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -2763,13 +3177,19 @@
       <c r="J63" s="2">
         <f>IF(D63=0,"",(H63-D63)/D63)</f>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K63" t="s">
+        <v>64</v>
+      </c>
+      <c r="L63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B64">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C64">
         <v>8.25</v>
@@ -2778,13 +3198,13 @@
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>938.87</v>
+        <v>934.83</v>
       </c>
       <c r="F64">
-        <v>609</v>
+        <v>678.2</v>
       </c>
       <c r="G64">
-        <v>629.3</v>
+        <v>632.06</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -2795,10 +3215,16 @@
       <c r="J64" s="2">
         <f>IF(D64=0,"",(H64-D64)/D64)</f>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K64" t="s">
+        <v>64</v>
+      </c>
+      <c r="L64" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B65">
         <v>268</v>
@@ -2827,10 +3253,16 @@
       <c r="J65" s="2">
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K65" t="s">
+        <v>64</v>
+      </c>
+      <c r="L65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B66">
         <v>131</v>
@@ -2859,16 +3291,22 @@
       <c r="J66" s="2">
         <f>IF(D66=0,"",(H66-D66)/D66)</f>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K66" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B67">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="C67">
-        <v>7.98</v>
+        <v>7.99</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
@@ -2891,13 +3329,19 @@
       <c r="J67" s="2">
         <f>IF(D67=0,"",(H67-D67)/D67)</f>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K67" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B68">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C68">
         <v>7.88</v>
@@ -2923,13 +3367,19 @@
       <c r="J68" s="2">
         <f>IF(D68=0,"",(H68-D68)/D68)</f>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K68" t="s">
+        <v>52</v>
+      </c>
+      <c r="L68" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B69">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C69">
         <v>7.83</v>
@@ -2955,13 +3405,19 @@
       <c r="J69" s="2">
         <f>IF(D69=0,"",(H69-D69)/D69)</f>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K69" t="s">
+        <v>52</v>
+      </c>
+      <c r="L69" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B70">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C70">
         <v>7.82</v>
@@ -2987,10 +3443,16 @@
       <c r="J70" s="2">
         <f>IF(D70=0,"",(H70-D70)/D70)</f>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K70" t="s">
+        <v>52</v>
+      </c>
+      <c r="L70" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B71">
         <v>143</v>
@@ -3019,13 +3481,19 @@
       <c r="J71" s="2">
         <f>IF(D71=0,"",(H71-D71)/D71)</f>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K71" t="s">
+        <v>64</v>
+      </c>
+      <c r="L71" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B72">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C72">
         <v>7.39</v>
@@ -3051,10 +3519,16 @@
       <c r="J72" s="2">
         <f>IF(D72=0,"",(H72-D72)/D72)</f>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K72" t="s">
+        <v>52</v>
+      </c>
+      <c r="L72" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B73">
         <v>207</v>
@@ -3083,10 +3557,16 @@
       <c r="J73" s="2">
         <f>IF(D73=0,"",(H73-D73)/D73)</f>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K73" t="s">
+        <v>64</v>
+      </c>
+      <c r="L73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B74">
         <v>8</v>
@@ -3115,28 +3595,34 @@
       <c r="J74" s="2">
         <f>IF(D74=0,"",(H74-D74)/D74)</f>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K74" t="s">
+        <v>64</v>
+      </c>
+      <c r="L74" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B75">
-        <v>1326</v>
+        <v>394</v>
       </c>
       <c r="C75">
-        <v>6.84</v>
+        <v>6.82</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>809.57</v>
+        <v>765.4</v>
       </c>
       <c r="F75">
-        <v>513.26</v>
+        <v>484.43</v>
       </c>
       <c r="G75">
-        <v>514.42</v>
+        <v>480.97</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3147,28 +3633,34 @@
       <c r="J75" s="2">
         <f>IF(D75=0,"",(H75-D75)/D75)</f>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K75" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B76">
-        <v>389</v>
+        <v>1326</v>
       </c>
       <c r="C76">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>765.4</v>
+        <v>809.57</v>
       </c>
       <c r="F76">
-        <v>484.43</v>
+        <v>513.26</v>
       </c>
       <c r="G76">
-        <v>480.97</v>
+        <v>514.42</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3179,10 +3671,16 @@
       <c r="J76" s="2">
         <f>IF(D76=0,"",(H76-D76)/D76)</f>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K76" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B77">
         <v>59</v>
@@ -3211,10 +3709,16 @@
       <c r="J77" s="2">
         <f>IF(D77=0,"",(H77-D77)/D77)</f>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K77" t="s">
+        <v>64</v>
+      </c>
+      <c r="L77" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B78">
         <v>77</v>
@@ -3243,28 +3747,34 @@
       <c r="J78" s="2">
         <f>IF(D78=0,"",(H78-D78)/D78)</f>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B79">
-        <v>1194</v>
+        <v>940</v>
       </c>
       <c r="C79">
-        <v>6.44</v>
+        <v>6.45</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>768.51</v>
+        <v>784.31</v>
       </c>
       <c r="F79">
-        <v>475.32</v>
+        <v>479.81</v>
       </c>
       <c r="G79">
-        <v>480.74</v>
+        <v>473.93</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3275,13 +3785,19 @@
       <c r="J79" s="2">
         <f>IF(D79=0,"",(H79-D79)/D79)</f>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K79" t="s">
+        <v>52</v>
+      </c>
+      <c r="L79" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B80">
-        <v>940</v>
+        <v>1193</v>
       </c>
       <c r="C80">
         <v>6.44</v>
@@ -3290,13 +3806,13 @@
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>784.31</v>
+        <v>768.51</v>
       </c>
       <c r="F80">
-        <v>479.81</v>
+        <v>475.32</v>
       </c>
       <c r="G80">
-        <v>473.93</v>
+        <v>480.74</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3307,10 +3823,16 @@
       <c r="J80" s="2">
         <f>IF(D80=0,"",(H80-D80)/D80)</f>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K80" t="s">
+        <v>52</v>
+      </c>
+      <c r="L80" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B81">
         <v>72</v>
@@ -3339,10 +3861,16 @@
       <c r="J81" s="2">
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K81" t="s">
+        <v>58</v>
+      </c>
+      <c r="L81" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B82">
         <v>104</v>
@@ -3371,10 +3899,16 @@
       <c r="J82" s="2">
         <f>IF(D82=0,"",(H82-D82)/D82)</f>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K82" t="s">
+        <v>64</v>
+      </c>
+      <c r="L82" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B83">
         <v>227</v>
@@ -3403,10 +3937,16 @@
       <c r="J83" s="2">
         <f>IF(D83=0,"",(H83-D83)/D83)</f>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K83" t="s">
+        <v>64</v>
+      </c>
+      <c r="L83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B84">
         <v>72</v>
@@ -3435,10 +3975,16 @@
       <c r="J84" s="2">
         <f>IF(D84=0,"",(H84-D84)/D84)</f>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K84" t="s">
+        <v>64</v>
+      </c>
+      <c r="L84" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B85">
         <v>123</v>
@@ -3467,10 +4013,16 @@
       <c r="J85" s="2">
         <f>IF(D85=0,"",(H85-D85)/D85)</f>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K85" t="s">
+        <v>64</v>
+      </c>
+      <c r="L85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B86">
         <v>112</v>
@@ -3499,10 +4051,16 @@
       <c r="J86" s="2">
         <f>IF(D86=0,"",(H86-D86)/D86)</f>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K86" t="s">
+        <v>64</v>
+      </c>
+      <c r="L86" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B87">
         <v>97</v>
@@ -3531,10 +4089,16 @@
       <c r="J87" s="2">
         <f>IF(D87=0,"",(H87-D87)/D87)</f>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K87" t="s">
+        <v>64</v>
+      </c>
+      <c r="L87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B88">
         <v>136</v>
@@ -3563,10 +4127,16 @@
       <c r="J88" s="2">
         <f>IF(D88=0,"",(H88-D88)/D88)</f>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K88" t="s">
+        <v>64</v>
+      </c>
+      <c r="L88" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B89">
         <v>155</v>
@@ -3595,10 +4165,16 @@
       <c r="J89" s="2">
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="B90">
         <v>511</v>
@@ -3627,10 +4203,16 @@
       <c r="J90" s="2">
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K90" t="s">
+        <v>64</v>
+      </c>
+      <c r="L90" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B91">
         <v>122</v>
@@ -3659,10 +4241,16 @@
       <c r="J91" s="2">
         <f>IF(D91=0,"",(H91-D91)/D91)</f>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K91" t="s">
+        <v>64</v>
+      </c>
+      <c r="L91" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="B92">
         <v>175</v>
@@ -3691,13 +4279,19 @@
       <c r="J92" s="2">
         <f>IF(D92=0,"",(H92-D92)/D92)</f>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K92" t="s">
+        <v>64</v>
+      </c>
+      <c r="L92" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="B93">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C93">
         <v>5.31</v>
@@ -3723,10 +4317,16 @@
       <c r="J93" s="2">
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K93" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B94">
         <v>29</v>
@@ -3755,10 +4355,16 @@
       <c r="J94" s="2">
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B95">
         <v>62</v>
@@ -3787,13 +4393,19 @@
       <c r="J95" s="2">
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K95" t="s">
+        <v>18</v>
+      </c>
+      <c r="L95" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B96">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C96">
         <v>4.96</v>
@@ -3819,10 +4431,16 @@
       <c r="J96" s="2">
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K96" t="s">
+        <v>30</v>
+      </c>
+      <c r="L96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B97">
         <v>73</v>
@@ -3851,28 +4469,34 @@
       <c r="J97" s="2">
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K97" t="s">
+        <v>64</v>
+      </c>
+      <c r="L97" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B98">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="C98">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>588.81</v>
+        <v>562.74</v>
       </c>
       <c r="F98">
-        <v>411.07</v>
+        <v>344.75</v>
       </c>
       <c r="G98">
-        <v>379.47</v>
+        <v>322.95</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -3883,28 +4507,34 @@
       <c r="J98" s="2">
         <f>IF(D98=0,"",(H98-D98)/D98)</f>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K98" t="s">
+        <v>64</v>
+      </c>
+      <c r="L98" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="B99">
-        <v>618</v>
+        <v>121</v>
       </c>
       <c r="C99">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>507.61</v>
+        <v>588.81</v>
       </c>
       <c r="F99">
-        <v>356.75</v>
+        <v>411.07</v>
       </c>
       <c r="G99">
-        <v>364.24</v>
+        <v>379.47</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -3915,28 +4545,34 @@
       <c r="J99" s="2">
         <f>IF(D99=0,"",(H99-D99)/D99)</f>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K99" t="s">
+        <v>64</v>
+      </c>
+      <c r="L99" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B100">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="C100">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>599.88</v>
+        <v>507.61</v>
       </c>
       <c r="F100">
-        <v>373.59</v>
+        <v>356.75</v>
       </c>
       <c r="G100">
-        <v>380.62</v>
+        <v>364.24</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -3947,28 +4583,34 @@
       <c r="J100" s="2">
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B101">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C101">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>535.18</v>
+        <v>599.88</v>
       </c>
       <c r="F101">
-        <v>334.49</v>
+        <v>373.59</v>
       </c>
       <c r="G101">
-        <v>373.59</v>
+        <v>380.62</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -3979,28 +4621,34 @@
       <c r="J101" s="2">
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K101" t="s">
+        <v>64</v>
+      </c>
+      <c r="L101" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B102">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="C102">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>562.74</v>
+        <v>535.18</v>
       </c>
       <c r="F102">
-        <v>344.75</v>
+        <v>334.49</v>
       </c>
       <c r="G102">
-        <v>322.95</v>
+        <v>373.59</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4011,10 +4659,16 @@
       <c r="J102" s="2">
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B103">
         <v>55</v>
@@ -4043,10 +4697,16 @@
       <c r="J103" s="2">
         <f>IF(D103=0,"",(H103-D103)/D103)</f>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K103" t="s">
+        <v>64</v>
+      </c>
+      <c r="L103" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B104">
         <v>25</v>
@@ -4075,10 +4735,16 @@
       <c r="J104" s="2">
         <f>IF(D104=0,"",(H104-D104)/D104)</f>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K104" t="s">
+        <v>64</v>
+      </c>
+      <c r="L104" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B105">
         <v>110</v>
@@ -4107,10 +4773,16 @@
       <c r="J105" s="2">
         <f>IF(D105=0,"",(H105-D105)/D105)</f>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K105" t="s">
+        <v>64</v>
+      </c>
+      <c r="L105" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="B106">
         <v>42</v>
@@ -4139,10 +4811,16 @@
       <c r="J106" s="2">
         <f>IF(D106=0,"",(H106-D106)/D106)</f>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K106" t="s">
+        <v>64</v>
+      </c>
+      <c r="L106" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B107">
         <v>101</v>
@@ -4171,16 +4849,22 @@
       <c r="J107" s="2">
         <f>IF(D107=0,"",(H107-D107)/D107)</f>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K107" t="s">
+        <v>64</v>
+      </c>
+      <c r="L107" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B108">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="C108">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
@@ -4203,10 +4887,16 @@
       <c r="J108" s="2">
         <f>IF(D108=0,"",(H108-D108)/D108)</f>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K108" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B109">
         <v>54</v>
@@ -4235,10 +4925,16 @@
       <c r="J109" s="2">
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K109" t="s">
+        <v>64</v>
+      </c>
+      <c r="L109" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B110">
         <v>123</v>
@@ -4267,13 +4963,19 @@
       <c r="J110" s="2">
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K110" t="s">
+        <v>64</v>
+      </c>
+      <c r="L110" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="B111">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C111">
         <v>3.86</v>
@@ -4299,10 +5001,16 @@
       <c r="J111" s="2">
         <f>IF(D111=0,"",(H111-D111)/D111)</f>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K111" t="s">
+        <v>26</v>
+      </c>
+      <c r="L111" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B112">
         <v>360</v>
@@ -4331,10 +5039,16 @@
       <c r="J112" s="2">
         <f>IF(D112=0,"",(H112-D112)/D112)</f>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K112" t="s">
+        <v>64</v>
+      </c>
+      <c r="L112" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B113">
         <v>365</v>
@@ -4349,7 +5063,7 @@
         <v>405.19</v>
       </c>
       <c r="F113">
-        <v>288.23</v>
+        <v>292.39</v>
       </c>
       <c r="G113">
         <v>276.82</v>
@@ -4363,10 +5077,16 @@
       <c r="J113" s="2">
         <f>IF(D113=0,"",(H113-D113)/D113)</f>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K113" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B114">
         <v>128</v>
@@ -4395,10 +5115,16 @@
       <c r="J114" s="2">
         <f>IF(D114=0,"",(H114-D114)/D114)</f>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K114" t="s">
+        <v>64</v>
+      </c>
+      <c r="L114" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="B115">
         <v>48</v>
@@ -4427,10 +5153,16 @@
       <c r="J115" s="2">
         <f>IF(D115=0,"",(H115-D115)/D115)</f>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K115" t="s">
+        <v>58</v>
+      </c>
+      <c r="L115" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B116">
         <v>77</v>
@@ -4459,16 +5191,22 @@
       <c r="J116" s="2">
         <f>IF(D116=0,"",(H116-D116)/D116)</f>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K116" t="s">
+        <v>64</v>
+      </c>
+      <c r="L116" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="B117">
         <v>78</v>
       </c>
       <c r="C117">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
@@ -4491,13 +5229,19 @@
       <c r="J117" s="2">
         <f>IF(D117=0,"",(H117-D117)/D117)</f>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K117" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="B118">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C118">
         <v>3.35</v>
@@ -4523,10 +5267,16 @@
       <c r="J118" s="2">
         <f>IF(D118=0,"",(H118-D118)/D118)</f>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B119">
         <v>247</v>
@@ -4555,13 +5305,19 @@
       <c r="J119" s="2">
         <f>IF(D119=0,"",(H119-D119)/D119)</f>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K119" t="s">
+        <v>64</v>
+      </c>
+      <c r="L119" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B120">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C120">
         <v>3.17</v>
@@ -4587,13 +5343,19 @@
       <c r="J120" s="2">
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K120" t="s">
+        <v>23</v>
+      </c>
+      <c r="L120" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B121">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C121">
         <v>3.16</v>
@@ -4619,10 +5381,16 @@
       <c r="J121" s="2">
         <f>IF(D121=0,"",(H121-D121)/D121)</f>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K121" t="s">
+        <v>26</v>
+      </c>
+      <c r="L121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B122">
         <v>43</v>
@@ -4651,10 +5419,16 @@
       <c r="J122" s="2">
         <f>IF(D122=0,"",(H122-D122)/D122)</f>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K122" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="B123">
         <v>117</v>
@@ -4683,13 +5457,19 @@
       <c r="J123" s="2">
         <f>IF(D123=0,"",(H123-D123)/D123)</f>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B124">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C124">
         <v>2.88</v>
@@ -4715,10 +5495,16 @@
       <c r="J124" s="2">
         <f>IF(D124=0,"",(H124-D124)/D124)</f>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K124" t="s">
+        <v>64</v>
+      </c>
+      <c r="L124" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B125">
         <v>36</v>
@@ -4747,16 +5533,22 @@
       <c r="J125" s="2">
         <f>IF(D125=0,"",(H125-D125)/D125)</f>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K125" t="s">
+        <v>58</v>
+      </c>
+      <c r="L125" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B126">
         <v>67</v>
       </c>
       <c r="C126">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
@@ -4779,13 +5571,19 @@
       <c r="J126" s="2">
         <f>IF(D126=0,"",(H126-D126)/D126)</f>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K126" t="s">
+        <v>64</v>
+      </c>
+      <c r="L126" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>158</v>
+      </c>
+      <c r="B127">
         <v>136</v>
-      </c>
-      <c r="B127">
-        <v>106</v>
       </c>
       <c r="C127">
         <v>2.25</v>
@@ -4794,13 +5592,13 @@
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>295.62</v>
+        <v>285.35</v>
       </c>
       <c r="F127">
-        <v>174.86</v>
+        <v>177.28</v>
       </c>
       <c r="G127">
-        <v>177.62</v>
+        <v>165.97</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -4811,13 +5609,19 @@
       <c r="J127" s="2">
         <f>IF(D127=0,"",(H127-D127)/D127)</f>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K127" t="s">
+        <v>30</v>
+      </c>
+      <c r="L127" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B128">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="C128">
         <v>2.25</v>
@@ -4826,13 +5630,13 @@
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>285.35</v>
+        <v>295.62</v>
       </c>
       <c r="F128">
-        <v>177.28</v>
+        <v>174.86</v>
       </c>
       <c r="G128">
-        <v>165.97</v>
+        <v>177.62</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -4843,10 +5647,16 @@
       <c r="J128" s="2">
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K128" t="s">
+        <v>64</v>
+      </c>
+      <c r="L128" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="B129">
         <v>20</v>
@@ -4875,10 +5685,16 @@
       <c r="J129" s="2">
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K129" t="s">
+        <v>64</v>
+      </c>
+      <c r="L129" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B130">
         <v>24</v>
@@ -4907,10 +5723,16 @@
       <c r="J130" s="2">
         <f>IF(D130=0,"",(H130-D130)/D130)</f>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K130" t="s">
+        <v>64</v>
+      </c>
+      <c r="L130" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B131">
         <v>266</v>
@@ -4939,10 +5761,16 @@
       <c r="J131" s="2">
         <f>IF(D131=0,"",(H131-D131)/D131)</f>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K131" t="s">
+        <v>64</v>
+      </c>
+      <c r="L131" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="B132">
         <v>270</v>
@@ -4971,10 +5799,16 @@
       <c r="J132" s="2">
         <f>IF(D132=0,"",(H132-D132)/D132)</f>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K132" t="s">
+        <v>64</v>
+      </c>
+      <c r="L132" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B133">
         <v>296</v>
@@ -5003,10 +5837,16 @@
       <c r="J133" s="2">
         <f>IF(D133=0,"",(H133-D133)/D133)</f>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K133" t="s">
+        <v>64</v>
+      </c>
+      <c r="L133" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="B134">
         <v>75</v>
@@ -5035,16 +5875,22 @@
       <c r="J134" s="2">
         <f>IF(D134=0,"",(H134-D134)/D134)</f>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K134" t="s">
+        <v>26</v>
+      </c>
+      <c r="L134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B135">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C135">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
@@ -5067,13 +5913,19 @@
       <c r="J135" s="2">
         <f>IF(D135=0,"",(H135-D135)/D135)</f>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K135" t="s">
+        <v>64</v>
+      </c>
+      <c r="L135" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="B136">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C136">
         <v>1.01</v>
@@ -5099,10 +5951,16 @@
       <c r="J136" s="2">
         <f>IF(D136=0,"",(H136-D136)/D136)</f>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K136" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B137">
         <v>310</v>
@@ -5131,13 +5989,19 @@
       <c r="J137" s="2">
         <f>IF(D137=0,"",(H137-D137)/D137)</f>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K137" t="s">
+        <v>23</v>
+      </c>
+      <c r="L137" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B138">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C138">
         <v>0.67</v>
@@ -5163,10 +6027,16 @@
       <c r="J138" s="2">
         <f>IF(D138=0,"",(H138-D138)/D138)</f>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K138" t="s">
+        <v>26</v>
+      </c>
+      <c r="L138" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B139">
         <v>36</v>
@@ -5194,6 +6064,12 @@
       </c>
       <c r="J139" s="2">
         <f>IF(D139=0,"",(H139-D139)/D139)</f>
+      </c>
+      <c r="K139" t="s">
+        <v>58</v>
+      </c>
+      <c r="L139" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="171">
-  <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 17:57</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
+  <si>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 19:12</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -139,12 +139,12 @@
     <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
   </si>
   <si>
+    <t>Desert Eagle | Starcade (Field-Tested)</t>
+  </si>
+  <si>
     <t>P250 | Apep's Curse (Field-Tested)</t>
   </si>
   <si>
-    <t>Desert Eagle | Starcade (Field-Tested)</t>
-  </si>
-  <si>
     <t>Dual Berettas | Emerald (Factory New)</t>
   </si>
   <si>
@@ -184,6 +184,9 @@
     <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
+    <t>Safecracker Voltzmann | The Professionals</t>
+  </si>
+  <si>
     <t>Nova | Sobek's Bite (Factory New)</t>
   </si>
   <si>
@@ -247,12 +250,12 @@
     <t>USP-S | Guardian (Factory New)</t>
   </si>
   <si>
+    <t>Five-SeveN | Kami (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Five-SeveN | Kami (Factory New)</t>
-  </si>
-  <si>
     <t>FAMAS | Styx (Field-Tested)</t>
   </si>
   <si>
@@ -307,12 +310,12 @@
     <t>Rezan The Ready | Sabre</t>
   </si>
   <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
     <t>Rezan the Redshirt | Sabre</t>
   </si>
   <si>
-    <t>Blackwolf | Sabre</t>
-  </si>
-  <si>
     <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -328,60 +331,60 @@
     <t>High Grade</t>
   </si>
   <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
+  </si>
+  <si>
     <t>AK-47 | Crossfade (Factory New)</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Maximus | Sabre</t>
+  </si>
+  <si>
     <t>Tec-9 | Brass (Field-Tested)</t>
   </si>
   <si>
+    <t>XM1014 | Black Tie (Factory New)</t>
+  </si>
+  <si>
     <t>Dragomir | Sabre</t>
   </si>
   <si>
-    <t>Maximus | Sabre</t>
-  </si>
-  <si>
-    <t>XM1014 | Black Tie (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | BIG (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
     <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
     <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
   </si>
   <si>
@@ -448,15 +451,15 @@
     <t>Galil AR | Tuxedo (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>XM1014 | Seasons (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Five-SeveN | Kami (Minimal Wear)</t>
   </si>
   <si>
@@ -484,13 +487,13 @@
     <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
   </si>
   <si>
+    <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Broken Fang (Holo)</t>
+  </si>
+  <si>
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
     <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
@@ -908,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L140"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -930,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.76</v>
+        <v>81.78</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -1026,7 +1029,7 @@
         <v>66</v>
       </c>
       <c r="C7">
-        <v>135.3</v>
+        <v>135.39</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -1061,10 +1064,10 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C8">
-        <v>119.34</v>
+        <v>119.3</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
@@ -1073,10 +1076,10 @@
         <v>13507.7</v>
       </c>
       <c r="F8">
-        <v>8875.41</v>
+        <v>8869.65</v>
       </c>
       <c r="G8">
-        <v>8737.01</v>
+        <v>8714.51</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1111,10 +1114,10 @@
         <v>10635.04</v>
       </c>
       <c r="F9">
-        <v>7484.18</v>
+        <v>7497.1</v>
       </c>
       <c r="G9">
-        <v>7554.65</v>
+        <v>7485.57</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1137,10 +1140,10 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10">
-        <v>88.5</v>
+        <v>88.72</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1175,7 +1178,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>86.01</v>
@@ -1213,7 +1216,7 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C12">
         <v>81.14</v>
@@ -1289,10 +1292,10 @@
         <v>33</v>
       </c>
       <c r="B14">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14">
-        <v>59.89</v>
+        <v>60.09</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
@@ -1304,7 +1307,7 @@
         <v>4521.33</v>
       </c>
       <c r="G14">
-        <v>4498.26</v>
+        <v>4504.03</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1327,7 +1330,7 @@
         <v>34</v>
       </c>
       <c r="B15">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C15">
         <v>58.25</v>
@@ -1365,7 +1368,7 @@
         <v>35</v>
       </c>
       <c r="B16">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C16">
         <v>58.2</v>
@@ -1377,7 +1380,7 @@
         <v>6306.45</v>
       </c>
       <c r="F16">
-        <v>4313.72</v>
+        <v>4319.48</v>
       </c>
       <c r="G16">
         <v>4232.98</v>
@@ -1403,7 +1406,7 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17">
         <v>57.32</v>
@@ -1441,10 +1444,10 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C18">
-        <v>56.3</v>
+        <v>57.1</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1453,7 +1456,7 @@
         <v>6620.98</v>
       </c>
       <c r="F18">
-        <v>4244.51</v>
+        <v>4254.66</v>
       </c>
       <c r="G18">
         <v>4152.24</v>
@@ -1479,7 +1482,7 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C19">
         <v>54.5</v>
@@ -1491,10 +1494,10 @@
         <v>5807.48</v>
       </c>
       <c r="F19">
-        <v>4117.64</v>
+        <v>4025.37</v>
       </c>
       <c r="G19">
-        <v>3979.23</v>
+        <v>4008.07</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1529,7 +1532,7 @@
         <v>6024.21</v>
       </c>
       <c r="F20">
-        <v>4016.25</v>
+        <v>4016.14</v>
       </c>
       <c r="G20">
         <v>3965.39</v>
@@ -1567,7 +1570,7 @@
         <v>5717.63</v>
       </c>
       <c r="F21">
-        <v>3633.21</v>
+        <v>3627.44</v>
       </c>
       <c r="G21">
         <v>3610.14</v>
@@ -1593,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22">
         <v>48.6</v>
@@ -1605,10 +1608,10 @@
         <v>5384.88</v>
       </c>
       <c r="F22">
-        <v>3569.77</v>
+        <v>3564.01</v>
       </c>
       <c r="G22">
-        <v>3587.07</v>
+        <v>3581.31</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1631,22 +1634,22 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="C23">
-        <v>48.45</v>
+        <v>48.53</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>5863.42</v>
+        <v>5214.64</v>
       </c>
       <c r="F23">
-        <v>3667.81</v>
+        <v>3685.11</v>
       </c>
       <c r="G23">
-        <v>3794.69</v>
+        <v>3546.71</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1669,7 +1672,7 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="C24">
         <v>48.45</v>
@@ -1678,13 +1681,13 @@
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>5214.64</v>
+        <v>5863.42</v>
       </c>
       <c r="F24">
-        <v>3685.11</v>
+        <v>3662.05</v>
       </c>
       <c r="G24">
-        <v>3546.71</v>
+        <v>3794.69</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1707,7 +1710,7 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25">
         <v>37.08</v>
@@ -1719,7 +1722,7 @@
         <v>4457.08</v>
       </c>
       <c r="F25">
-        <v>2708.18</v>
+        <v>2702.42</v>
       </c>
       <c r="G25">
         <v>2940.94</v>
@@ -1760,7 +1763,7 @@
         <v>2841.75</v>
       </c>
       <c r="G26">
-        <v>2687.42</v>
+        <v>2682</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1783,7 +1786,7 @@
         <v>46</v>
       </c>
       <c r="B27">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>35.02</v>
@@ -1795,7 +1798,7 @@
         <v>4414.52</v>
       </c>
       <c r="F27">
-        <v>2652.82</v>
+        <v>2641.29</v>
       </c>
       <c r="G27">
         <v>2952.7</v>
@@ -1821,10 +1824,10 @@
         <v>47</v>
       </c>
       <c r="B28">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C28">
-        <v>32.66</v>
+        <v>32.57</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
@@ -1833,10 +1836,10 @@
         <v>3633.33</v>
       </c>
       <c r="F28">
-        <v>2483.15</v>
+        <v>2479.81</v>
       </c>
       <c r="G28">
-        <v>2399.07</v>
+        <v>2403.69</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1859,7 +1862,7 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C29">
         <v>31.67</v>
@@ -1868,7 +1871,7 @@
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>3537.13</v>
+        <v>3511.87</v>
       </c>
       <c r="F29">
         <v>2422.02</v>
@@ -1897,10 +1900,10 @@
         <v>49</v>
       </c>
       <c r="B30">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C30">
-        <v>29.48</v>
+        <v>29.3</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
@@ -1909,7 +1912,7 @@
         <v>3123.29</v>
       </c>
       <c r="F30">
-        <v>2237.6</v>
+        <v>2252.82</v>
       </c>
       <c r="G30">
         <v>2208.76</v>
@@ -1935,7 +1938,7 @@
         <v>50</v>
       </c>
       <c r="B31">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C31">
         <v>25.58</v>
@@ -1973,7 +1976,7 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C32">
         <v>23.24</v>
@@ -1982,13 +1985,13 @@
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2839.44</v>
+        <v>2877.27</v>
       </c>
       <c r="F32">
-        <v>1874.28</v>
+        <v>1868.51</v>
       </c>
       <c r="G32">
-        <v>1914.64</v>
+        <v>1914.53</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2011,7 +2014,7 @@
         <v>54</v>
       </c>
       <c r="B33">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C33">
         <v>20.86</v>
@@ -2026,7 +2029,7 @@
         <v>1603.23</v>
       </c>
       <c r="G33">
-        <v>1551.32</v>
+        <v>1557.09</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2049,7 +2052,7 @@
         <v>55</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C34">
         <v>19.79</v>
@@ -2061,7 +2064,7 @@
         <v>2307.38</v>
       </c>
       <c r="F34">
-        <v>1473.81</v>
+        <v>1473.7</v>
       </c>
       <c r="G34">
         <v>1491.35</v>
@@ -2099,7 +2102,7 @@
         <v>2360.89</v>
       </c>
       <c r="F35">
-        <v>1480.85</v>
+        <v>1474.05</v>
       </c>
       <c r="G35">
         <v>1441.63</v>
@@ -2125,22 +2128,22 @@
         <v>57</v>
       </c>
       <c r="B36">
-        <v>37</v>
+        <v>1128</v>
       </c>
       <c r="C36">
-        <v>18.95</v>
+        <v>19.08</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>2287.65</v>
+        <v>2186.73</v>
       </c>
       <c r="F36">
-        <v>1465.97</v>
+        <v>1493.65</v>
       </c>
       <c r="G36">
-        <v>1451.9</v>
+        <v>1457.9</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2152,33 +2155,33 @@
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
       <c r="K36" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="C37">
-        <v>18.84</v>
+        <v>18.95</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2170.12</v>
+        <v>2287.65</v>
       </c>
       <c r="F37">
-        <v>1441.75</v>
+        <v>1454.44</v>
       </c>
       <c r="G37">
-        <v>1388.69</v>
+        <v>1451.78</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2190,7 +2193,7 @@
         <f>IF(D37=0,"",(H37-D37)/D37)</f>
       </c>
       <c r="K37" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="L37" t="s">
         <v>21</v>
@@ -2201,22 +2204,22 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="C38">
-        <v>15.41</v>
+        <v>18.84</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1967.59</v>
+        <v>2170.12</v>
       </c>
       <c r="F38">
-        <v>1243.37</v>
+        <v>1442.9</v>
       </c>
       <c r="G38">
-        <v>1227.1</v>
+        <v>1394.46</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2228,10 +2231,10 @@
         <f>IF(D38=0,"",(H38-D38)/D38)</f>
       </c>
       <c r="K38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L38" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2239,22 +2242,22 @@
         <v>61</v>
       </c>
       <c r="B39">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C39">
-        <v>15.01</v>
+        <v>15.4</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1876.12</v>
+        <v>1967.59</v>
       </c>
       <c r="F39">
-        <v>1164.82</v>
+        <v>1243.37</v>
       </c>
       <c r="G39">
-        <v>1188</v>
+        <v>1224.8</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2266,7 +2269,7 @@
         <f>IF(D39=0,"",(H39-D39)/D39)</f>
       </c>
       <c r="K39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L39" t="s">
         <v>19</v>
@@ -2277,22 +2280,22 @@
         <v>62</v>
       </c>
       <c r="B40">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C40">
-        <v>13.93</v>
+        <v>15.01</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1455.94</v>
+        <v>1876.12</v>
       </c>
       <c r="F40">
-        <v>1068.86</v>
+        <v>1164.82</v>
       </c>
       <c r="G40">
-        <v>1092.27</v>
+        <v>1182.24</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2304,10 +2307,10 @@
         <f>IF(D40=0,"",(H40-D40)/D40)</f>
       </c>
       <c r="K40" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="L40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2315,22 +2318,22 @@
         <v>63</v>
       </c>
       <c r="B41">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C41">
-        <v>13.82</v>
+        <v>13.93</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1505.65</v>
+        <v>1455.94</v>
       </c>
       <c r="F41">
-        <v>1000</v>
+        <v>1068.86</v>
       </c>
       <c r="G41">
-        <v>942.9</v>
+        <v>1092.27</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2342,33 +2345,33 @@
         <f>IF(D41=0,"",(H41-D41)/D41)</f>
       </c>
       <c r="K41" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L41" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B42">
-        <v>1735</v>
+        <v>74</v>
       </c>
       <c r="C42">
-        <v>13.49</v>
+        <v>13.82</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1505.65</v>
+        <v>1537.94</v>
       </c>
       <c r="F42">
-        <v>1013.84</v>
+        <v>982.7</v>
       </c>
       <c r="G42">
-        <v>1038.06</v>
+        <v>942.9</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2380,33 +2383,33 @@
         <f>IF(D42=0,"",(H42-D42)/D42)</f>
       </c>
       <c r="K42" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="L42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43">
-        <v>60</v>
+        <v>1733</v>
       </c>
       <c r="C43">
-        <v>13.25</v>
+        <v>13.49</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1441.75</v>
+        <v>1407.84</v>
       </c>
       <c r="F43">
-        <v>975.78</v>
+        <v>1038.06</v>
       </c>
       <c r="G43">
-        <v>1035.75</v>
+        <v>1037.94</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2418,10 +2421,10 @@
         <f>IF(D43=0,"",(H43-D43)/D43)</f>
       </c>
       <c r="K43" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2429,22 +2432,22 @@
         <v>69</v>
       </c>
       <c r="B44">
-        <v>1420</v>
+        <v>60</v>
       </c>
       <c r="C44">
-        <v>13.01</v>
+        <v>13.25</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1530.1</v>
+        <v>1441.75</v>
       </c>
       <c r="F44">
-        <v>976.93</v>
+        <v>975.78</v>
       </c>
       <c r="G44">
-        <v>981.54</v>
+        <v>1035.75</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2456,10 +2459,10 @@
         <f>IF(D44=0,"",(H44-D44)/D44)</f>
       </c>
       <c r="K44" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2467,22 +2470,22 @@
         <v>70</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>1422</v>
       </c>
       <c r="C45">
-        <v>12.62</v>
+        <v>13.01</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1418.11</v>
+        <v>1481.2</v>
       </c>
       <c r="F45">
-        <v>1032.06</v>
+        <v>992.96</v>
       </c>
       <c r="G45">
-        <v>977.28</v>
+        <v>991.92</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2494,33 +2497,33 @@
         <f>IF(D45=0,"",(H45-D45)/D45)</f>
       </c>
       <c r="K45" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L45" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B46">
-        <v>371</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>12.36</v>
+        <v>12.62</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1414.99</v>
+        <v>1418.11</v>
       </c>
       <c r="F46">
-        <v>942.21</v>
+        <v>1031.95</v>
       </c>
       <c r="G46">
-        <v>940.02</v>
+        <v>977.28</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2532,10 +2535,10 @@
         <f>IF(D46=0,"",(H46-D46)/D46)</f>
       </c>
       <c r="K46" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L46" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2543,22 +2546,22 @@
         <v>73</v>
       </c>
       <c r="B47">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="C47">
-        <v>12.32</v>
+        <v>12.37</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1329.87</v>
+        <v>1414.99</v>
       </c>
       <c r="F47">
-        <v>979.01</v>
+        <v>938.87</v>
       </c>
       <c r="G47">
-        <v>931.83</v>
+        <v>941.17</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2573,30 +2576,30 @@
         <v>26</v>
       </c>
       <c r="L47" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B48">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="C48">
-        <v>11.62</v>
+        <v>12.32</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1263.67</v>
+        <v>1329.87</v>
       </c>
       <c r="F48">
-        <v>838.52</v>
+        <v>978.54</v>
       </c>
       <c r="G48">
-        <v>856.86</v>
+        <v>930.68</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2608,10 +2611,10 @@
         <f>IF(D48=0,"",(H48-D48)/D48)</f>
       </c>
       <c r="K48" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2619,22 +2622,22 @@
         <v>76</v>
       </c>
       <c r="B49">
-        <v>1768</v>
+        <v>177</v>
       </c>
       <c r="C49">
-        <v>11.06</v>
+        <v>11.62</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1303</v>
+        <v>1263.67</v>
       </c>
       <c r="F49">
-        <v>847.75</v>
+        <v>863.9</v>
       </c>
       <c r="G49">
-        <v>824.22</v>
+        <v>856.86</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2646,10 +2649,10 @@
         <f>IF(D49=0,"",(H49-D49)/D49)</f>
       </c>
       <c r="K49" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="L49" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2657,22 +2660,22 @@
         <v>77</v>
       </c>
       <c r="B50">
-        <v>159</v>
+        <v>1780</v>
       </c>
       <c r="C50">
-        <v>10.58</v>
+        <v>11.06</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1174.51</v>
+        <v>1242.33</v>
       </c>
       <c r="F50">
-        <v>785.81</v>
+        <v>846.71</v>
       </c>
       <c r="G50">
-        <v>812.69</v>
+        <v>825.72</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2684,10 +2687,10 @@
         <f>IF(D50=0,"",(H50-D50)/D50)</f>
       </c>
       <c r="K50" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L50" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2695,22 +2698,22 @@
         <v>78</v>
       </c>
       <c r="B51">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="C51">
-        <v>10.42</v>
+        <v>10.59</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1182.47</v>
+        <v>1174.51</v>
       </c>
       <c r="F51">
-        <v>771.62</v>
+        <v>781.66</v>
       </c>
       <c r="G51">
-        <v>741.06</v>
+        <v>806.11</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2722,10 +2725,10 @@
         <f>IF(D51=0,"",(H51-D51)/D51)</f>
       </c>
       <c r="K51" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="L51" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2733,10 +2736,10 @@
         <v>79</v>
       </c>
       <c r="B52">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52">
-        <v>10.19</v>
+        <v>10.49</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
@@ -2745,10 +2748,10 @@
         <v>1132.75</v>
       </c>
       <c r="F52">
-        <v>757.67</v>
+        <v>757.55</v>
       </c>
       <c r="G52">
-        <v>756.63</v>
+        <v>754.32</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2771,22 +2774,22 @@
         <v>80</v>
       </c>
       <c r="B53">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C53">
-        <v>10.19</v>
+        <v>10.42</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1153.28</v>
+        <v>1182.47</v>
       </c>
       <c r="F53">
-        <v>749.71</v>
+        <v>782.01</v>
       </c>
       <c r="G53">
-        <v>821.91</v>
+        <v>741.06</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2798,10 +2801,10 @@
         <f>IF(D53=0,"",(H53-D53)/D53)</f>
       </c>
       <c r="K53" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2809,22 +2812,22 @@
         <v>81</v>
       </c>
       <c r="B54">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="C54">
-        <v>10.16</v>
+        <v>10.19</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1097.23</v>
+        <v>1153.28</v>
       </c>
       <c r="F54">
-        <v>748.56</v>
+        <v>749.59</v>
       </c>
       <c r="G54">
-        <v>791.12</v>
+        <v>821.91</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2836,10 +2839,10 @@
         <f>IF(D54=0,"",(H54-D54)/D54)</f>
       </c>
       <c r="K54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L54" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2847,22 +2850,22 @@
         <v>82</v>
       </c>
       <c r="B55">
-        <v>493</v>
+        <v>100</v>
       </c>
       <c r="C55">
-        <v>10.06</v>
+        <v>10.16</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1129.64</v>
+        <v>1097.23</v>
       </c>
       <c r="F55">
-        <v>726.64</v>
+        <v>748.56</v>
       </c>
       <c r="G55">
-        <v>711.53</v>
+        <v>789.96</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2877,7 +2880,7 @@
         <v>23</v>
       </c>
       <c r="L55" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2885,22 +2888,22 @@
         <v>83</v>
       </c>
       <c r="B56">
-        <v>1313</v>
+        <v>495</v>
       </c>
       <c r="C56">
-        <v>9.86</v>
+        <v>10.03</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1093.31</v>
+        <v>1129.64</v>
       </c>
       <c r="F56">
-        <v>776.24</v>
+        <v>725.49</v>
       </c>
       <c r="G56">
-        <v>763.55</v>
+        <v>710.38</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2912,33 +2915,33 @@
         <f>IF(D56=0,"",(H56-D56)/D56)</f>
       </c>
       <c r="K56" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L56" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B57">
-        <v>986</v>
+        <v>1309</v>
       </c>
       <c r="C57">
-        <v>9.7</v>
+        <v>9.86</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1087.77</v>
+        <v>1093.31</v>
       </c>
       <c r="F57">
-        <v>744.4</v>
+        <v>778.43</v>
       </c>
       <c r="G57">
-        <v>713.95</v>
+        <v>763.55</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2953,30 +2956,30 @@
         <v>52</v>
       </c>
       <c r="L57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58">
-        <v>95</v>
+        <v>983</v>
       </c>
       <c r="C58">
-        <v>9.67</v>
+        <v>9.71</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1016.84</v>
+        <v>1087.77</v>
       </c>
       <c r="F58">
-        <v>712.57</v>
+        <v>744.4</v>
       </c>
       <c r="G58">
-        <v>743.94</v>
+        <v>725.49</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2988,10 +2991,10 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L58" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2999,22 +3002,22 @@
         <v>88</v>
       </c>
       <c r="B59">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="C59">
-        <v>8.92</v>
+        <v>9.67</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>906.46</v>
+        <v>1016.84</v>
       </c>
       <c r="F59">
-        <v>645.9</v>
+        <v>711.42</v>
       </c>
       <c r="G59">
-        <v>671.28</v>
+        <v>743.94</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3026,10 +3029,10 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3037,22 +3040,22 @@
         <v>89</v>
       </c>
       <c r="B60">
-        <v>688</v>
+        <v>189</v>
       </c>
       <c r="C60">
-        <v>8.65</v>
+        <v>8.92</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>964.01</v>
+        <v>906.46</v>
       </c>
       <c r="F60">
-        <v>655.13</v>
+        <v>657.32</v>
       </c>
       <c r="G60">
-        <v>645.9</v>
+        <v>667.7</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3064,10 +3067,10 @@
         <f>IF(D60=0,"",(H60-D60)/D60)</f>
       </c>
       <c r="K60" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="L60" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3075,22 +3078,22 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>561</v>
+        <v>689</v>
       </c>
       <c r="C61">
-        <v>8.59</v>
+        <v>8.67</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>963.32</v>
+        <v>964.01</v>
       </c>
       <c r="F61">
-        <v>660.78</v>
+        <v>657.44</v>
       </c>
       <c r="G61">
-        <v>644.75</v>
+        <v>645.9</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3102,10 +3105,10 @@
         <f>IF(D61=0,"",(H61-D61)/D61)</f>
       </c>
       <c r="K61" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="L61" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3113,22 +3116,22 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>189</v>
+        <v>561</v>
       </c>
       <c r="C62">
-        <v>8.29</v>
+        <v>8.59</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>910.49</v>
+        <v>963.32</v>
       </c>
       <c r="F62">
-        <v>631.26</v>
+        <v>660.78</v>
       </c>
       <c r="G62">
-        <v>611.3</v>
+        <v>644.75</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3151,22 +3154,22 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="C63">
-        <v>8.25</v>
+        <v>8.29</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>938.87</v>
+        <v>910.49</v>
       </c>
       <c r="F63">
-        <v>609</v>
+        <v>631.26</v>
       </c>
       <c r="G63">
-        <v>629.3</v>
+        <v>611.3</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3178,10 +3181,10 @@
         <f>IF(D63=0,"",(H63-D63)/D63)</f>
       </c>
       <c r="K63" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="L63" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3189,7 +3192,7 @@
         <v>93</v>
       </c>
       <c r="B64">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C64">
         <v>8.25</v>
@@ -3198,13 +3201,13 @@
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>934.83</v>
+        <v>938.87</v>
       </c>
       <c r="F64">
-        <v>678.2</v>
+        <v>609</v>
       </c>
       <c r="G64">
-        <v>632.06</v>
+        <v>629.3</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3216,10 +3219,10 @@
         <f>IF(D64=0,"",(H64-D64)/D64)</f>
       </c>
       <c r="K64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L64" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3227,22 +3230,22 @@
         <v>94</v>
       </c>
       <c r="B65">
-        <v>268</v>
+        <v>100</v>
       </c>
       <c r="C65">
-        <v>8.23</v>
+        <v>8.25</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>852.13</v>
+        <v>889.96</v>
       </c>
       <c r="F65">
-        <v>657.44</v>
+        <v>678.2</v>
       </c>
       <c r="G65">
-        <v>634.37</v>
+        <v>630.91</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3254,10 +3257,10 @@
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
       <c r="K65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L65" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3265,23 +3268,14 @@
         <v>95</v>
       </c>
       <c r="B66">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="C66">
-        <v>7.99</v>
+        <v>8.22</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
-      <c r="E66">
-        <v>845.79</v>
-      </c>
-      <c r="F66">
-        <v>588.12</v>
-      </c>
-      <c r="G66">
-        <v>598.61</v>
-      </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
       </c>
@@ -3292,10 +3286,10 @@
         <f>IF(D66=0,"",(H66-D66)/D66)</f>
       </c>
       <c r="K66" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L66" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3303,7 +3297,7 @@
         <v>96</v>
       </c>
       <c r="B67">
-        <v>842</v>
+        <v>130</v>
       </c>
       <c r="C67">
         <v>7.99</v>
@@ -3311,15 +3305,6 @@
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
-      <c r="E67">
-        <v>922.26</v>
-      </c>
-      <c r="F67">
-        <v>597.35</v>
-      </c>
-      <c r="G67">
-        <v>588.23</v>
-      </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
       </c>
@@ -3330,10 +3315,10 @@
         <f>IF(D67=0,"",(H67-D67)/D67)</f>
       </c>
       <c r="K67" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L67" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3341,23 +3326,14 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>1428</v>
+        <v>840</v>
       </c>
       <c r="C68">
-        <v>7.88</v>
+        <v>7.99</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
-      <c r="E68">
-        <v>904.15</v>
-      </c>
-      <c r="F68">
-        <v>599.65</v>
-      </c>
-      <c r="G68">
-        <v>576.7</v>
-      </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
       </c>
@@ -3371,7 +3347,7 @@
         <v>52</v>
       </c>
       <c r="L68" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3379,22 +3355,13 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>748</v>
+        <v>1433</v>
       </c>
       <c r="C69">
-        <v>7.83</v>
+        <v>7.88</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
-      </c>
-      <c r="E69">
-        <v>837.95</v>
-      </c>
-      <c r="F69">
-        <v>587.08</v>
-      </c>
-      <c r="G69">
-        <v>576.93</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3417,22 +3384,13 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C70">
-        <v>7.82</v>
+        <v>7.87</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
-      </c>
-      <c r="E70">
-        <v>900.23</v>
-      </c>
-      <c r="F70">
-        <v>603.23</v>
-      </c>
-      <c r="G70">
-        <v>593.89</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3455,23 +3413,14 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>143</v>
+        <v>748</v>
       </c>
       <c r="C71">
-        <v>7.62</v>
+        <v>7.83</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
-      <c r="E71">
-        <v>848.21</v>
-      </c>
-      <c r="F71">
-        <v>553.06</v>
-      </c>
-      <c r="G71">
-        <v>571.16</v>
-      </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
       </c>
@@ -3482,10 +3431,10 @@
         <f>IF(D71=0,"",(H71-D71)/D71)</f>
       </c>
       <c r="K71" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L71" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3493,23 +3442,14 @@
         <v>101</v>
       </c>
       <c r="B72">
-        <v>1134</v>
+        <v>143</v>
       </c>
       <c r="C72">
-        <v>7.39</v>
+        <v>7.62</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
-      <c r="E72">
-        <v>906.46</v>
-      </c>
-      <c r="F72">
-        <v>559.4</v>
-      </c>
-      <c r="G72">
-        <v>536.33</v>
-      </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
       </c>
@@ -3520,10 +3460,10 @@
         <f>IF(D72=0,"",(H72-D72)/D72)</f>
       </c>
       <c r="K72" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="L72" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3531,23 +3471,14 @@
         <v>102</v>
       </c>
       <c r="B73">
-        <v>207</v>
+        <v>1140</v>
       </c>
       <c r="C73">
-        <v>7.12</v>
+        <v>7.39</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
-      <c r="E73">
-        <v>755.13</v>
-      </c>
-      <c r="F73">
-        <v>530.22</v>
-      </c>
-      <c r="G73">
-        <v>546.71</v>
-      </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
       </c>
@@ -3558,10 +3489,10 @@
         <f>IF(D73=0,"",(H73-D73)/D73)</f>
       </c>
       <c r="K73" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L73" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3569,23 +3500,14 @@
         <v>103</v>
       </c>
       <c r="B74">
-        <v>8</v>
+        <v>207</v>
       </c>
       <c r="C74">
-        <v>6.91</v>
+        <v>7.12</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
-      <c r="E74">
-        <v>840.25</v>
-      </c>
-      <c r="F74">
-        <v>517.76</v>
-      </c>
-      <c r="G74">
-        <v>515.34</v>
-      </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
       </c>
@@ -3596,34 +3518,25 @@
         <f>IF(D74=0,"",(H74-D74)/D74)</f>
       </c>
       <c r="K74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L74" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B75">
-        <v>394</v>
+        <v>8</v>
       </c>
       <c r="C75">
-        <v>6.82</v>
+        <v>6.91</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
-      <c r="E75">
-        <v>765.4</v>
-      </c>
-      <c r="F75">
-        <v>484.43</v>
-      </c>
-      <c r="G75">
-        <v>480.97</v>
-      </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
       </c>
@@ -3634,10 +3547,10 @@
         <f>IF(D75=0,"",(H75-D75)/D75)</f>
       </c>
       <c r="K75" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L75" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3645,22 +3558,13 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="C76">
-        <v>6.78</v>
+        <v>6.84</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
-      </c>
-      <c r="E76">
-        <v>809.57</v>
-      </c>
-      <c r="F76">
-        <v>513.26</v>
-      </c>
-      <c r="G76">
-        <v>514.42</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3683,23 +3587,14 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>59</v>
+        <v>394</v>
       </c>
       <c r="C77">
-        <v>6.57</v>
+        <v>6.82</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
-      <c r="E77">
-        <v>731.49</v>
-      </c>
-      <c r="F77">
-        <v>530.22</v>
-      </c>
-      <c r="G77">
-        <v>461.36</v>
-      </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
       </c>
@@ -3710,10 +3605,10 @@
         <f>IF(D77=0,"",(H77-D77)/D77)</f>
       </c>
       <c r="K77" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="L77" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3721,23 +3616,14 @@
         <v>108</v>
       </c>
       <c r="B78">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C78">
-        <v>6.48</v>
+        <v>6.73</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
-      <c r="E78">
-        <v>752.82</v>
-      </c>
-      <c r="F78">
-        <v>478.89</v>
-      </c>
-      <c r="G78">
-        <v>573.47</v>
-      </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
       </c>
@@ -3748,10 +3634,10 @@
         <f>IF(D78=0,"",(H78-D78)/D78)</f>
       </c>
       <c r="K78" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3759,7 +3645,7 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>940</v>
+        <v>1194</v>
       </c>
       <c r="C79">
         <v>6.45</v>
@@ -3767,15 +3653,6 @@
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
-      <c r="E79">
-        <v>784.31</v>
-      </c>
-      <c r="F79">
-        <v>479.81</v>
-      </c>
-      <c r="G79">
-        <v>473.93</v>
-      </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
       </c>
@@ -3789,7 +3666,7 @@
         <v>52</v>
       </c>
       <c r="L79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3797,7 +3674,7 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>1193</v>
+        <v>77</v>
       </c>
       <c r="C80">
         <v>6.44</v>
@@ -3806,13 +3683,13 @@
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>768.51</v>
+        <v>752.82</v>
       </c>
       <c r="F80">
         <v>475.32</v>
       </c>
       <c r="G80">
-        <v>480.74</v>
+        <v>573.47</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3824,10 +3701,10 @@
         <f>IF(D80=0,"",(H80-D80)/D80)</f>
       </c>
       <c r="K80" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L80" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3847,7 +3724,7 @@
         <v>656.63</v>
       </c>
       <c r="F81">
-        <v>461.36</v>
+        <v>474.85</v>
       </c>
       <c r="G81">
         <v>507.5</v>
@@ -3862,7 +3739,7 @@
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
       <c r="K81" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L81" t="s">
         <v>21</v>
@@ -3873,23 +3750,14 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>104</v>
+        <v>938</v>
       </c>
       <c r="C82">
-        <v>6.05</v>
+        <v>6.28</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
-      <c r="E82">
-        <v>684.2</v>
-      </c>
-      <c r="F82">
-        <v>462.51</v>
-      </c>
-      <c r="G82">
-        <v>454.79</v>
-      </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
       </c>
@@ -3900,10 +3768,10 @@
         <f>IF(D82=0,"",(H82-D82)/D82)</f>
       </c>
       <c r="K82" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L82" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3911,23 +3779,14 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>227</v>
+        <v>104</v>
       </c>
       <c r="C83">
-        <v>6.03</v>
+        <v>6.05</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
-      <c r="E83">
-        <v>634.49</v>
-      </c>
-      <c r="F83">
-        <v>507.38</v>
-      </c>
-      <c r="G83">
-        <v>481.89</v>
-      </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
       </c>
@@ -3938,10 +3797,10 @@
         <f>IF(D83=0,"",(H83-D83)/D83)</f>
       </c>
       <c r="K83" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L83" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3949,23 +3808,14 @@
         <v>114</v>
       </c>
       <c r="B84">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C84">
-        <v>6.03</v>
+        <v>5.91</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
-      <c r="E84">
-        <v>468.17</v>
-      </c>
-      <c r="F84">
-        <v>334.49</v>
-      </c>
-      <c r="G84">
-        <v>331.95</v>
-      </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
       </c>
@@ -3976,10 +3826,10 @@
         <f>IF(D84=0,"",(H84-D84)/D84)</f>
       </c>
       <c r="K84" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L84" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3987,23 +3837,14 @@
         <v>115</v>
       </c>
       <c r="B85">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="C85">
-        <v>5.91</v>
+        <v>5.8</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
-      <c r="E85">
-        <v>554.9</v>
-      </c>
-      <c r="F85">
-        <v>419.61</v>
-      </c>
-      <c r="G85">
-        <v>392.04</v>
-      </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
       </c>
@@ -4014,10 +3855,10 @@
         <f>IF(D85=0,"",(H85-D85)/D85)</f>
       </c>
       <c r="K85" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L85" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4033,15 +3874,6 @@
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
-      <c r="E86">
-        <v>689.73</v>
-      </c>
-      <c r="F86">
-        <v>416.15</v>
-      </c>
-      <c r="G86">
-        <v>433.1</v>
-      </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
       </c>
@@ -4052,10 +3884,10 @@
         <f>IF(D86=0,"",(H86-D86)/D86)</f>
       </c>
       <c r="K86" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L86" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4071,15 +3903,6 @@
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
-      <c r="E87">
-        <v>684.2</v>
-      </c>
-      <c r="F87">
-        <v>429.64</v>
-      </c>
-      <c r="G87">
-        <v>452.48</v>
-      </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
       </c>
@@ -4090,10 +3913,10 @@
         <f>IF(D87=0,"",(H87-D87)/D87)</f>
       </c>
       <c r="K87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4101,23 +3924,14 @@
         <v>118</v>
       </c>
       <c r="B88">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C88">
-        <v>5.6</v>
+        <v>5.63</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
-      <c r="E88">
-        <v>602.19</v>
-      </c>
-      <c r="F88">
-        <v>512.69</v>
-      </c>
-      <c r="G88">
-        <v>449.83</v>
-      </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
       </c>
@@ -4128,10 +3942,10 @@
         <f>IF(D88=0,"",(H88-D88)/D88)</f>
       </c>
       <c r="K88" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L88" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4139,23 +3953,14 @@
         <v>119</v>
       </c>
       <c r="B89">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C89">
-        <v>5.58</v>
+        <v>5.6</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
-      <c r="E89">
-        <v>585.7</v>
-      </c>
-      <c r="F89">
-        <v>415.11</v>
-      </c>
-      <c r="G89">
-        <v>427.91</v>
-      </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
       </c>
@@ -4166,10 +3971,10 @@
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
       <c r="K89" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L89" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4177,23 +3982,14 @@
         <v>120</v>
       </c>
       <c r="B90">
-        <v>511</v>
+        <v>157</v>
       </c>
       <c r="C90">
-        <v>5.41</v>
+        <v>5.53</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
-      <c r="E90">
-        <v>568.28</v>
-      </c>
-      <c r="F90">
-        <v>396.77</v>
-      </c>
-      <c r="G90">
-        <v>385.24</v>
-      </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
       </c>
@@ -4204,10 +4000,10 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="L90" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4215,23 +4011,14 @@
         <v>121</v>
       </c>
       <c r="B91">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="C91">
-        <v>5.37</v>
+        <v>5.46</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
-      <c r="E91">
-        <v>600.69</v>
-      </c>
-      <c r="F91">
-        <v>447.29</v>
-      </c>
-      <c r="G91">
-        <v>403.69</v>
-      </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
       </c>
@@ -4242,10 +4029,10 @@
         <f>IF(D91=0,"",(H91-D91)/D91)</f>
       </c>
       <c r="K91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L91" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4253,23 +4040,14 @@
         <v>122</v>
       </c>
       <c r="B92">
-        <v>175</v>
+        <v>510</v>
       </c>
       <c r="C92">
-        <v>5.37</v>
+        <v>5.4</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
-      <c r="E92">
-        <v>619.61</v>
-      </c>
-      <c r="F92">
-        <v>452.13</v>
-      </c>
-      <c r="G92">
-        <v>389.85</v>
-      </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
       </c>
@@ -4280,10 +4058,10 @@
         <f>IF(D92=0,"",(H92-D92)/D92)</f>
       </c>
       <c r="K92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L92" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4291,23 +4069,14 @@
         <v>123</v>
       </c>
       <c r="B93">
-        <v>851</v>
+        <v>122</v>
       </c>
       <c r="C93">
-        <v>5.31</v>
+        <v>5.37</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
-      <c r="E93">
-        <v>625.83</v>
-      </c>
-      <c r="F93">
-        <v>422.03</v>
-      </c>
-      <c r="G93">
-        <v>403.69</v>
-      </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
       </c>
@@ -4318,10 +4087,10 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L93" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4329,22 +4098,22 @@
         <v>124</v>
       </c>
       <c r="B94">
-        <v>29</v>
+        <v>858</v>
       </c>
       <c r="C94">
-        <v>5.3</v>
+        <v>5.32</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>580.16</v>
+        <v>622.72</v>
       </c>
       <c r="F94">
-        <v>409.23</v>
+        <v>415.22</v>
       </c>
       <c r="G94">
-        <v>413.96</v>
+        <v>424.45</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4356,10 +4125,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L94" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4367,22 +4136,22 @@
         <v>125</v>
       </c>
       <c r="B95">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>5.18</v>
+        <v>5.29</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>567.47</v>
+        <v>580.16</v>
       </c>
       <c r="F95">
-        <v>412.23</v>
+        <v>405.77</v>
       </c>
       <c r="G95">
-        <v>388.7</v>
+        <v>413.96</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4394,34 +4163,25 @@
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
       <c r="K95" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L95" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B96">
-        <v>500</v>
+        <v>62</v>
       </c>
       <c r="C96">
-        <v>4.96</v>
+        <v>5.18</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
-      <c r="E96">
-        <v>547.06</v>
-      </c>
-      <c r="F96">
-        <v>357.55</v>
-      </c>
-      <c r="G96">
-        <v>391</v>
-      </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
       </c>
@@ -4432,10 +4192,10 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L96" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4443,23 +4203,14 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>73</v>
+        <v>505</v>
       </c>
       <c r="C97">
-        <v>4.91</v>
+        <v>4.95</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
-      <c r="E97">
-        <v>580.16</v>
-      </c>
-      <c r="F97">
-        <v>383.04</v>
-      </c>
-      <c r="G97">
-        <v>370.24</v>
-      </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
       </c>
@@ -4470,10 +4221,10 @@
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
       <c r="K97" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="L97" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4481,23 +4232,14 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="C98">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
-      <c r="E98">
-        <v>562.74</v>
-      </c>
-      <c r="F98">
-        <v>344.75</v>
-      </c>
-      <c r="G98">
-        <v>322.95</v>
-      </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
       </c>
@@ -4508,10 +4250,10 @@
         <f>IF(D98=0,"",(H98-D98)/D98)</f>
       </c>
       <c r="K98" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4519,22 +4261,22 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C99">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>588.81</v>
+        <v>566.78</v>
       </c>
       <c r="F99">
-        <v>411.07</v>
+        <v>344.75</v>
       </c>
       <c r="G99">
-        <v>379.47</v>
+        <v>322.95</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4546,10 +4288,10 @@
         <f>IF(D99=0,"",(H99-D99)/D99)</f>
       </c>
       <c r="K99" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4557,23 +4299,14 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>619</v>
+        <v>121</v>
       </c>
       <c r="C100">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
-      <c r="E100">
-        <v>507.61</v>
-      </c>
-      <c r="F100">
-        <v>356.75</v>
-      </c>
-      <c r="G100">
-        <v>364.24</v>
-      </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
       </c>
@@ -4584,10 +4317,10 @@
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
       <c r="K100" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L100" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4595,23 +4328,14 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>78</v>
+        <v>622</v>
       </c>
       <c r="C101">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
-      <c r="E101">
-        <v>599.88</v>
-      </c>
-      <c r="F101">
-        <v>373.59</v>
-      </c>
-      <c r="G101">
-        <v>380.62</v>
-      </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
       </c>
@@ -4622,10 +4346,10 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="L101" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4633,22 +4357,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C102">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>535.18</v>
+        <v>599.08</v>
       </c>
       <c r="F102">
-        <v>334.49</v>
+        <v>372.43</v>
       </c>
       <c r="G102">
-        <v>373.59</v>
+        <v>380.62</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4660,10 +4384,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L102" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4671,23 +4395,14 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C103">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
-      <c r="E103">
-        <v>521.8</v>
-      </c>
-      <c r="F103">
-        <v>359.17</v>
-      </c>
-      <c r="G103">
-        <v>346.02</v>
-      </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
       </c>
@@ -4698,10 +4413,10 @@
         <f>IF(D103=0,"",(H103-D103)/D103)</f>
       </c>
       <c r="K103" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="L103" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4709,22 +4424,22 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C104">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>485.58</v>
+        <v>521.8</v>
       </c>
       <c r="F104">
-        <v>321.57</v>
+        <v>369.09</v>
       </c>
       <c r="G104">
-        <v>291.58</v>
+        <v>351.79</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4736,10 +4451,10 @@
         <f>IF(D104=0,"",(H104-D104)/D104)</f>
       </c>
       <c r="K104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L104" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4747,23 +4462,14 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="C105">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
-      <c r="E105">
-        <v>480.05</v>
-      </c>
-      <c r="F105">
-        <v>339.45</v>
-      </c>
-      <c r="G105">
-        <v>329.87</v>
-      </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
       </c>
@@ -4774,10 +4480,10 @@
         <f>IF(D105=0,"",(H105-D105)/D105)</f>
       </c>
       <c r="K105" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L105" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4785,22 +4491,22 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="C106">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>432.76</v>
+        <v>480.05</v>
       </c>
       <c r="F106">
-        <v>353.98</v>
+        <v>339.21</v>
       </c>
       <c r="G106">
-        <v>312.69</v>
+        <v>329.87</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4812,10 +4518,10 @@
         <f>IF(D106=0,"",(H106-D106)/D106)</f>
       </c>
       <c r="K106" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L106" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4823,23 +4529,14 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="C107">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
-      <c r="E107">
-        <v>475.32</v>
-      </c>
-      <c r="F107">
-        <v>339.79</v>
-      </c>
-      <c r="G107">
-        <v>360.78</v>
-      </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
       </c>
@@ -4850,10 +4547,10 @@
         <f>IF(D107=0,"",(H107-D107)/D107)</f>
       </c>
       <c r="K107" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L107" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4861,10 +4558,10 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>2419</v>
+        <v>101</v>
       </c>
       <c r="C108">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
@@ -4873,10 +4570,10 @@
         <v>475.32</v>
       </c>
       <c r="F108">
-        <v>324.11</v>
+        <v>339.79</v>
       </c>
       <c r="G108">
-        <v>322.95</v>
+        <v>360.78</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4888,10 +4585,10 @@
         <f>IF(D108=0,"",(H108-D108)/D108)</f>
       </c>
       <c r="K108" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L108" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4899,22 +4596,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>54</v>
+        <v>2427</v>
       </c>
       <c r="C109">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>530.45</v>
+        <v>474.51</v>
       </c>
       <c r="F109">
-        <v>305.65</v>
+        <v>322.95</v>
       </c>
       <c r="G109">
-        <v>303.34</v>
+        <v>325.72</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4926,10 +4623,10 @@
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
       <c r="K109" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="L109" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4937,22 +4634,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="C110">
-        <v>4.09</v>
+        <v>4.29</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>421.68</v>
+        <v>530.45</v>
       </c>
       <c r="F110">
-        <v>313.61</v>
+        <v>303.34</v>
       </c>
       <c r="G110">
-        <v>310.26</v>
+        <v>303.34</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4964,10 +4661,10 @@
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
       <c r="K110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L110" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4975,22 +4672,22 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>245</v>
+        <v>123</v>
       </c>
       <c r="C111">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>412.23</v>
+        <v>421.68</v>
       </c>
       <c r="F111">
-        <v>309.46</v>
+        <v>313.61</v>
       </c>
       <c r="G111">
-        <v>291.81</v>
+        <v>310.26</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -5002,10 +4699,10 @@
         <f>IF(D111=0,"",(H111-D111)/D111)</f>
       </c>
       <c r="K111" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L111" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5013,23 +4710,14 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>360</v>
+        <v>247</v>
       </c>
       <c r="C112">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
-      <c r="E112">
-        <v>394.12</v>
-      </c>
-      <c r="F112">
-        <v>298.73</v>
-      </c>
-      <c r="G112">
-        <v>282.58</v>
-      </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
       </c>
@@ -5040,10 +4728,10 @@
         <f>IF(D112=0,"",(H112-D112)/D112)</f>
       </c>
       <c r="K112" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="L112" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -5051,23 +4739,14 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C113">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
-      <c r="E113">
-        <v>405.19</v>
-      </c>
-      <c r="F113">
-        <v>292.39</v>
-      </c>
-      <c r="G113">
-        <v>276.82</v>
-      </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
       </c>
@@ -5078,10 +4757,10 @@
         <f>IF(D113=0,"",(H113-D113)/D113)</f>
       </c>
       <c r="K113" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L113" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5089,22 +4768,22 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>128</v>
+        <v>362</v>
       </c>
       <c r="C114">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>378.32</v>
+        <v>405.19</v>
       </c>
       <c r="F114">
-        <v>286.97</v>
+        <v>291.58</v>
       </c>
       <c r="G114">
-        <v>275.66</v>
+        <v>276.82</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5116,10 +4795,10 @@
         <f>IF(D114=0,"",(H114-D114)/D114)</f>
       </c>
       <c r="K114" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="L114" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5127,22 +4806,22 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C115">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>398.85</v>
+        <v>486.39</v>
       </c>
       <c r="F115">
-        <v>263.78</v>
+        <v>270.13</v>
       </c>
       <c r="G115">
-        <v>264.13</v>
+        <v>289.73</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5154,10 +4833,10 @@
         <f>IF(D115=0,"",(H115-D115)/D115)</f>
       </c>
       <c r="K115" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L115" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5165,22 +4844,22 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C116">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>486.39</v>
+        <v>378.32</v>
       </c>
       <c r="F116">
-        <v>270.24</v>
+        <v>286.97</v>
       </c>
       <c r="G116">
-        <v>291.81</v>
+        <v>274.51</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5192,10 +4871,10 @@
         <f>IF(D116=0,"",(H116-D116)/D116)</f>
       </c>
       <c r="K116" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L116" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5203,22 +4882,22 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C117">
-        <v>3.39</v>
+        <v>3.53</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>373.59</v>
+        <v>398.85</v>
       </c>
       <c r="F117">
-        <v>252.59</v>
+        <v>263.78</v>
       </c>
       <c r="G117">
-        <v>257.21</v>
+        <v>264.13</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5230,10 +4909,10 @@
         <f>IF(D117=0,"",(H117-D117)/D117)</f>
       </c>
       <c r="K117" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="L117" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5241,22 +4920,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C118">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>357.78</v>
+        <v>373.59</v>
       </c>
       <c r="F118">
-        <v>253.4</v>
+        <v>252.36</v>
       </c>
       <c r="G118">
-        <v>239.56</v>
+        <v>257.21</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5271,7 +4950,7 @@
         <v>23</v>
       </c>
       <c r="L118" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5279,22 +4958,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>247</v>
+        <v>70</v>
       </c>
       <c r="C119">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>383.85</v>
+        <v>357.78</v>
       </c>
       <c r="F119">
-        <v>250.17</v>
+        <v>254.56</v>
       </c>
       <c r="G119">
-        <v>249.13</v>
+        <v>239.56</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5306,10 +4985,10 @@
         <f>IF(D119=0,"",(H119-D119)/D119)</f>
       </c>
       <c r="K119" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="L119" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5317,22 +4996,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="C120">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>340.48</v>
+        <v>383.04</v>
       </c>
       <c r="F120">
-        <v>236.33</v>
+        <v>254.79</v>
       </c>
       <c r="G120">
-        <v>236.1</v>
+        <v>249.13</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5344,10 +5023,10 @@
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
       <c r="K120" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L120" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5355,22 +5034,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C121">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>363.32</v>
+        <v>340.48</v>
       </c>
       <c r="F121">
-        <v>242.1</v>
+        <v>236.33</v>
       </c>
       <c r="G121">
-        <v>243.94</v>
+        <v>236.1</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5382,10 +5061,10 @@
         <f>IF(D121=0,"",(H121-D121)/D121)</f>
       </c>
       <c r="K121" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L121" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5393,23 +5072,14 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>43</v>
+        <v>303</v>
       </c>
       <c r="C122">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
-      <c r="E122">
-        <v>316.84</v>
-      </c>
-      <c r="F122">
-        <v>216.84</v>
-      </c>
-      <c r="G122">
-        <v>221.57</v>
-      </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
       </c>
@@ -5420,10 +5090,10 @@
         <f>IF(D122=0,"",(H122-D122)/D122)</f>
       </c>
       <c r="K122" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L122" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5431,23 +5101,14 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="C123">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
-      <c r="E123">
-        <v>327.1</v>
-      </c>
-      <c r="F123">
-        <v>214.3</v>
-      </c>
-      <c r="G123">
-        <v>201.85</v>
-      </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
       </c>
@@ -5461,7 +5122,7 @@
         <v>23</v>
       </c>
       <c r="L123" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5469,22 +5130,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="C124">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>354.67</v>
+        <v>327.1</v>
       </c>
       <c r="F124">
-        <v>218.11</v>
+        <v>214.3</v>
       </c>
       <c r="G124">
-        <v>217.76</v>
+        <v>201.85</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5496,10 +5157,10 @@
         <f>IF(D124=0,"",(H124-D124)/D124)</f>
       </c>
       <c r="K124" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="L124" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5507,22 +5168,22 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C125">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>368.05</v>
+        <v>354.67</v>
       </c>
       <c r="F125">
-        <v>191.93</v>
+        <v>218.11</v>
       </c>
       <c r="G125">
-        <v>192.39</v>
+        <v>217.76</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5534,10 +5195,10 @@
         <f>IF(D125=0,"",(H125-D125)/D125)</f>
       </c>
       <c r="K125" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L125" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5545,22 +5206,22 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C126">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>230.91</v>
+        <v>368.05</v>
       </c>
       <c r="F126">
-        <v>176.24</v>
+        <v>191.93</v>
       </c>
       <c r="G126">
-        <v>175.32</v>
+        <v>191.58</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5572,10 +5233,10 @@
         <f>IF(D126=0,"",(H126-D126)/D126)</f>
       </c>
       <c r="K126" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L126" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5583,10 +5244,10 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C127">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
@@ -5595,10 +5256,10 @@
         <v>285.35</v>
       </c>
       <c r="F127">
-        <v>177.28</v>
+        <v>176.12</v>
       </c>
       <c r="G127">
-        <v>165.97</v>
+        <v>169.43</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5633,7 +5294,7 @@
         <v>295.62</v>
       </c>
       <c r="F128">
-        <v>174.86</v>
+        <v>177.62</v>
       </c>
       <c r="G128">
         <v>177.62</v>
@@ -5648,10 +5309,10 @@
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
       <c r="K128" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L128" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5659,22 +5320,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C129">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>249.83</v>
+        <v>230.91</v>
       </c>
       <c r="F129">
-        <v>183.39</v>
+        <v>175.55</v>
       </c>
       <c r="G129">
-        <v>188</v>
+        <v>174.16</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5686,10 +5347,10 @@
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
       <c r="K129" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5697,22 +5358,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C130">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>211.99</v>
+        <v>249.83</v>
       </c>
       <c r="F130">
-        <v>144.98</v>
+        <v>183.39</v>
       </c>
       <c r="G130">
-        <v>153.4</v>
+        <v>188</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5724,10 +5385,10 @@
         <f>IF(D130=0,"",(H130-D130)/D130)</f>
       </c>
       <c r="K130" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5735,22 +5396,22 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="C131">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
       </c>
       <c r="E131">
-        <v>255.36</v>
+        <v>211.99</v>
       </c>
       <c r="F131">
-        <v>129.87</v>
+        <v>144.98</v>
       </c>
       <c r="G131">
-        <v>143.02</v>
+        <v>152.25</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5762,10 +5423,10 @@
         <f>IF(D131=0,"",(H131-D131)/D131)</f>
       </c>
       <c r="K131" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L131" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5773,22 +5434,22 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C132">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>183.62</v>
+        <v>255.36</v>
       </c>
       <c r="F132">
-        <v>129.76</v>
+        <v>134.6</v>
       </c>
       <c r="G132">
-        <v>141.29</v>
+        <v>143.02</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5800,10 +5461,10 @@
         <f>IF(D132=0,"",(H132-D132)/D132)</f>
       </c>
       <c r="K132" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L132" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5811,22 +5472,22 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="C133">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>163.09</v>
+        <v>171.74</v>
       </c>
       <c r="F133">
-        <v>123.41</v>
+        <v>125.72</v>
       </c>
       <c r="G133">
-        <v>124.45</v>
+        <v>140.14</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5838,10 +5499,10 @@
         <f>IF(D133=0,"",(H133-D133)/D133)</f>
       </c>
       <c r="K133" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L133" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5849,22 +5510,22 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="C134">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>166.32</v>
+        <v>163.09</v>
       </c>
       <c r="F134">
-        <v>117.07</v>
+        <v>117.65</v>
       </c>
       <c r="G134">
-        <v>125.61</v>
+        <v>124.34</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5876,10 +5537,10 @@
         <f>IF(D134=0,"",(H134-D134)/D134)</f>
       </c>
       <c r="K134" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L134" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5887,22 +5548,22 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>1028</v>
+        <v>74</v>
       </c>
       <c r="C135">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>155.25</v>
+        <v>165.51</v>
       </c>
       <c r="F135">
-        <v>106.69</v>
+        <v>117.07</v>
       </c>
       <c r="G135">
-        <v>104.61</v>
+        <v>124.57</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5914,10 +5575,10 @@
         <f>IF(D135=0,"",(H135-D135)/D135)</f>
       </c>
       <c r="K135" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="L135" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5925,22 +5586,22 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>542</v>
+        <v>1028</v>
       </c>
       <c r="C136">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="D136">
         <f>C136*$B$3</f>
       </c>
       <c r="E136">
-        <v>121.34</v>
+        <v>155.25</v>
       </c>
       <c r="F136">
-        <v>75.43</v>
+        <v>103.81</v>
       </c>
       <c r="G136">
-        <v>76.01</v>
+        <v>104.61</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5952,10 +5613,10 @@
         <f>IF(D136=0,"",(H136-D136)/D136)</f>
       </c>
       <c r="K136" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L136" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5963,22 +5624,22 @@
         <v>168</v>
       </c>
       <c r="B137">
-        <v>310</v>
+        <v>538</v>
       </c>
       <c r="C137">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="D137">
         <f>C137*$B$3</f>
       </c>
       <c r="E137">
-        <v>95.27</v>
+        <v>121.34</v>
       </c>
       <c r="F137">
-        <v>66.21</v>
+        <v>74.97</v>
       </c>
       <c r="G137">
-        <v>64.59</v>
+        <v>80.74</v>
       </c>
       <c r="H137">
         <f>MIN(E137:G137)</f>
@@ -5993,7 +5654,7 @@
         <v>23</v>
       </c>
       <c r="L137" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -6001,22 +5662,22 @@
         <v>169</v>
       </c>
       <c r="B138">
-        <v>329</v>
+        <v>258</v>
       </c>
       <c r="C138">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="D138">
         <f>C138*$B$3</f>
       </c>
       <c r="E138">
-        <v>79.58</v>
+        <v>92.96</v>
       </c>
       <c r="F138">
-        <v>50.17</v>
+        <v>66.21</v>
       </c>
       <c r="G138">
-        <v>50.29</v>
+        <v>64.48</v>
       </c>
       <c r="H138">
         <f>MIN(E138:G138)</f>
@@ -6028,10 +5689,10 @@
         <f>IF(D138=0,"",(H138-D138)/D138)</f>
       </c>
       <c r="K138" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L138" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -6039,22 +5700,22 @@
         <v>170</v>
       </c>
       <c r="B139">
-        <v>36</v>
+        <v>368</v>
       </c>
       <c r="C139">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="D139">
         <f>C139*$B$3</f>
       </c>
       <c r="E139">
-        <v>59.86</v>
+        <v>79.58</v>
       </c>
       <c r="F139">
-        <v>34.6</v>
+        <v>50.17</v>
       </c>
       <c r="G139">
-        <v>35.64</v>
+        <v>50.29</v>
       </c>
       <c r="H139">
         <f>MIN(E139:G139)</f>
@@ -6066,9 +5727,47 @@
         <f>IF(D139=0,"",(H139-D139)/D139)</f>
       </c>
       <c r="K139" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="L139" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140">
+        <v>36</v>
+      </c>
+      <c r="C140">
+        <v>0.48</v>
+      </c>
+      <c r="D140">
+        <f>C140*$B$3</f>
+      </c>
+      <c r="E140">
+        <v>60.67</v>
+      </c>
+      <c r="F140">
+        <v>34.37</v>
+      </c>
+      <c r="G140">
+        <v>35.64</v>
+      </c>
+      <c r="H140">
+        <f>MIN(E140:G140)</f>
+      </c>
+      <c r="I140">
+        <f>H140-D140</f>
+      </c>
+      <c r="J140" s="2">
+        <f>IF(D140=0,"",(H140-D140)/D140)</f>
+      </c>
+      <c r="K140" t="s">
+        <v>59</v>
+      </c>
+      <c r="L140" t="s">
         <v>19</v>
       </c>
     </row>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 19:12</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 20:54</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -94,12 +94,12 @@
     <t>Rifle</t>
   </si>
   <si>
+    <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
+  </si>
+  <si>
     <t>AK-47 | Point Disarray (Factory New)</t>
   </si>
   <si>
-    <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
-  </si>
-  <si>
     <t>AWP | Containment Breach (Field-Tested)</t>
   </si>
   <si>
@@ -232,27 +232,27 @@
     <t>Exotic</t>
   </si>
   <si>
+    <t>SG 553 | Candy Apple (Factory New)</t>
+  </si>
+  <si>
+    <t>Industrial Grade</t>
+  </si>
+  <si>
     <t>M4A4 | Evil Daimyo (Factory New)</t>
   </si>
   <si>
-    <t>SG 553 | Candy Apple (Factory New)</t>
-  </si>
-  <si>
-    <t>Industrial Grade</t>
-  </si>
-  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
     <t>The Elite Mr. Muhlik | Elite Crew</t>
   </si>
   <si>
+    <t>Five-SeveN | Kami (Factory New)</t>
+  </si>
+  <si>
     <t>USP-S | Guardian (Factory New)</t>
   </si>
   <si>
-    <t>Five-SeveN | Kami (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -271,15 +271,15 @@
     <t>Exceptional</t>
   </si>
   <si>
+    <t>AUG | Carved Jade (Minimal Wear)</t>
+  </si>
+  <si>
     <t>B Squadron Officer | SAS</t>
   </si>
   <si>
     <t>Distinguished</t>
   </si>
   <si>
-    <t>AUG | Carved Jade (Minimal Wear)</t>
-  </si>
-  <si>
     <t>SSG 08 | Rapid Transit (Factory New)</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>Slingshot | Phoenix</t>
   </si>
   <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
     <t>Rezan The Ready | Sabre</t>
   </si>
   <si>
-    <t>Blackwolf | Sabre</t>
-  </si>
-  <si>
     <t>Rezan the Redshirt | Sabre</t>
   </si>
   <si>
@@ -331,15 +331,18 @@
     <t>High Grade</t>
   </si>
   <si>
+    <t>AK-47 | Crossfade (Factory New)</t>
+  </si>
+  <si>
     <t>AK-47 | Slate (Minimal Wear)</t>
   </si>
   <si>
-    <t>AK-47 | Crossfade (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Dragomir | Sabre</t>
+  </si>
+  <si>
     <t>Maximus | Sabre</t>
   </si>
   <si>
@@ -349,75 +352,72 @@
     <t>XM1014 | Black Tie (Factory New)</t>
   </si>
   <si>
-    <t>Dragomir | Sabre</t>
-  </si>
-  <si>
     <t>Sticker | BIG (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+  </si>
+  <si>
+    <t>CZ75-Auto | Tacticat (Factory New)</t>
+  </si>
+  <si>
+    <t>MAC-10 | Strats (Factory New)</t>
+  </si>
+  <si>
+    <t>Consumer Grade</t>
+  </si>
+  <si>
+    <t>AWP | Black Nile (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Gold Web (Foil)</t>
+  </si>
+  <si>
+    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>R8 Revolver | Blaze (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Stone Scales (Foil)</t>
+  </si>
+  <si>
+    <t>P250 | Epicenter (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
-  </si>
-  <si>
-    <t>CZ75-Auto | Tacticat (Factory New)</t>
-  </si>
-  <si>
-    <t>MAC-10 | Strats (Factory New)</t>
-  </si>
-  <si>
-    <t>Consumer Grade</t>
-  </si>
-  <si>
-    <t>AWP | Black Nile (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Gold Web (Foil)</t>
-  </si>
-  <si>
-    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>R8 Revolver | Blaze (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Stone Scales (Foil)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
-  </si>
-  <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -433,12 +433,12 @@
     <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>AK-47 | Slate (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Sticker | Team Liquid (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -463,15 +463,15 @@
     <t>Five-SeveN | Kami (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>P2000 | Amber Fade (Factory New)</t>
+  </si>
+  <si>
     <t>Five-SeveN | Retrobution (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>P2000 | Amber Fade (Factory New)</t>
-  </si>
-  <si>
     <t>AK-47 | Crossfade (Minimal Wear)</t>
   </si>
   <si>
@@ -487,16 +487,16 @@
     <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | Broken Fang (Holo)</t>
+  </si>
+  <si>
     <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | Broken Fang (Holo)</t>
+    <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | Ancient Beast (Foil)</t>
@@ -933,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.78</v>
+        <v>81.83</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -988,10 +988,10 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6">
-        <v>162.94</v>
+        <v>165.26</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
@@ -1029,7 +1029,7 @@
         <v>66</v>
       </c>
       <c r="C7">
-        <v>135.39</v>
+        <v>135.36</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -1067,7 +1067,7 @@
         <v>368</v>
       </c>
       <c r="C8">
-        <v>119.3</v>
+        <v>118.69</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
@@ -1079,7 +1079,7 @@
         <v>8869.65</v>
       </c>
       <c r="G8">
-        <v>8714.51</v>
+        <v>8737.01</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1114,10 +1114,10 @@
         <v>10635.04</v>
       </c>
       <c r="F9">
-        <v>7497.1</v>
+        <v>7538.62</v>
       </c>
       <c r="G9">
-        <v>7485.57</v>
+        <v>7581.07</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1140,22 +1140,22 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>195</v>
+        <v>57</v>
       </c>
       <c r="C10">
-        <v>88.72</v>
+        <v>86.01</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>9189.37</v>
+        <v>8653.27</v>
       </c>
       <c r="F10">
-        <v>6580.15</v>
+        <v>6205.29</v>
       </c>
       <c r="G10">
-        <v>6574.38</v>
+        <v>6430.21</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1178,22 +1178,22 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="C11">
-        <v>86.01</v>
+        <v>84.29</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>8653.27</v>
+        <v>9301.25</v>
       </c>
       <c r="F11">
-        <v>6215.67</v>
+        <v>6574.38</v>
       </c>
       <c r="G11">
-        <v>6430.21</v>
+        <v>6574.38</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1219,7 +1219,7 @@
         <v>262</v>
       </c>
       <c r="C12">
-        <v>81.14</v>
+        <v>81.24</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
@@ -1231,7 +1231,7 @@
         <v>5920.4</v>
       </c>
       <c r="G12">
-        <v>5882.34</v>
+        <v>5893.87</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1295,19 +1295,19 @@
         <v>140</v>
       </c>
       <c r="C14">
-        <v>60.09</v>
+        <v>61.33</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>6620.17</v>
+        <v>6610.71</v>
       </c>
       <c r="F14">
-        <v>4521.33</v>
+        <v>4601.95</v>
       </c>
       <c r="G14">
-        <v>4504.03</v>
+        <v>4531.36</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1330,7 +1330,7 @@
         <v>34</v>
       </c>
       <c r="B15">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C15">
         <v>58.25</v>
@@ -1368,7 +1368,7 @@
         <v>35</v>
       </c>
       <c r="B16">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C16">
         <v>58.2</v>
@@ -1406,7 +1406,7 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17">
         <v>57.32</v>
@@ -1444,22 +1444,22 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C18">
-        <v>57.1</v>
+        <v>55.88</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>6620.98</v>
+        <v>6345.89</v>
       </c>
       <c r="F18">
-        <v>4254.66</v>
+        <v>4241.05</v>
       </c>
       <c r="G18">
-        <v>4152.24</v>
+        <v>4094.57</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1482,19 +1482,19 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C19">
-        <v>54.5</v>
+        <v>54.34</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5807.48</v>
+        <v>5713.6</v>
       </c>
       <c r="F19">
-        <v>4025.37</v>
+        <v>3961.93</v>
       </c>
       <c r="G19">
         <v>4008.07</v>
@@ -1523,7 +1523,7 @@
         <v>75</v>
       </c>
       <c r="C20">
-        <v>52.69</v>
+        <v>50.87</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
@@ -1558,10 +1558,10 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C21">
-        <v>48.73</v>
+        <v>49.97</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
@@ -1573,7 +1573,7 @@
         <v>3627.44</v>
       </c>
       <c r="G21">
-        <v>3610.14</v>
+        <v>3604.38</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22">
         <v>48.6</v>
@@ -1608,7 +1608,7 @@
         <v>5384.88</v>
       </c>
       <c r="F22">
-        <v>3564.01</v>
+        <v>3517.87</v>
       </c>
       <c r="G22">
         <v>3581.31</v>
@@ -1634,10 +1634,10 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C23">
-        <v>48.53</v>
+        <v>48.45</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
@@ -1675,7 +1675,7 @@
         <v>60</v>
       </c>
       <c r="C24">
-        <v>48.45</v>
+        <v>48.29</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
@@ -1719,13 +1719,13 @@
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>4457.08</v>
+        <v>4170.12</v>
       </c>
       <c r="F25">
-        <v>2702.42</v>
+        <v>2652.82</v>
       </c>
       <c r="G25">
-        <v>2940.94</v>
+        <v>2934.94</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1748,10 +1748,10 @@
         <v>45</v>
       </c>
       <c r="B26">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C26">
-        <v>36.07</v>
+        <v>36.43</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
@@ -1763,7 +1763,7 @@
         <v>2841.75</v>
       </c>
       <c r="G26">
-        <v>2682</v>
+        <v>2730.44</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1786,7 +1786,7 @@
         <v>46</v>
       </c>
       <c r="B27">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C27">
         <v>35.02</v>
@@ -1795,13 +1795,13 @@
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>4414.52</v>
+        <v>4301.72</v>
       </c>
       <c r="F27">
         <v>2641.29</v>
       </c>
       <c r="G27">
-        <v>2952.7</v>
+        <v>2946.94</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1824,10 +1824,10 @@
         <v>47</v>
       </c>
       <c r="B28">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C28">
-        <v>32.57</v>
+        <v>32.54</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
@@ -1836,7 +1836,7 @@
         <v>3633.33</v>
       </c>
       <c r="F28">
-        <v>2479.81</v>
+        <v>2476</v>
       </c>
       <c r="G28">
         <v>2403.69</v>
@@ -1862,10 +1862,10 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C29">
-        <v>31.67</v>
+        <v>31.49</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
@@ -1874,7 +1874,7 @@
         <v>3511.87</v>
       </c>
       <c r="F29">
-        <v>2422.02</v>
+        <v>2520.06</v>
       </c>
       <c r="G29">
         <v>2421.68</v>
@@ -1900,10 +1900,10 @@
         <v>49</v>
       </c>
       <c r="B30">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C30">
-        <v>29.3</v>
+        <v>29.26</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
@@ -1912,7 +1912,7 @@
         <v>3123.29</v>
       </c>
       <c r="F30">
-        <v>2252.82</v>
+        <v>2241.52</v>
       </c>
       <c r="G30">
         <v>2208.76</v>
@@ -1938,7 +1938,7 @@
         <v>50</v>
       </c>
       <c r="B31">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C31">
         <v>25.58</v>
@@ -1947,7 +1947,7 @@
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2708.64</v>
+        <v>2811.07</v>
       </c>
       <c r="F31">
         <v>1894.69</v>
@@ -1976,22 +1976,22 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C32">
-        <v>23.24</v>
+        <v>23.32</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2877.27</v>
+        <v>2884.42</v>
       </c>
       <c r="F32">
-        <v>1868.51</v>
+        <v>1903.11</v>
       </c>
       <c r="G32">
-        <v>1914.53</v>
+        <v>1937.71</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2023,13 +2023,13 @@
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>2307.38</v>
+        <v>2420.06</v>
       </c>
       <c r="F33">
-        <v>1603.23</v>
+        <v>1649.25</v>
       </c>
       <c r="G33">
-        <v>1557.09</v>
+        <v>1574.39</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2052,7 +2052,7 @@
         <v>55</v>
       </c>
       <c r="B34">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34">
         <v>19.79</v>
@@ -2090,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="B35">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C35">
         <v>19.51</v>
@@ -2102,10 +2102,10 @@
         <v>2360.89</v>
       </c>
       <c r="F35">
-        <v>1474.05</v>
+        <v>1480.85</v>
       </c>
       <c r="G35">
-        <v>1441.63</v>
+        <v>1435.87</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2128,10 +2128,10 @@
         <v>57</v>
       </c>
       <c r="B36">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="C36">
-        <v>19.08</v>
+        <v>19.1</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
@@ -2140,7 +2140,7 @@
         <v>2186.73</v>
       </c>
       <c r="F36">
-        <v>1493.65</v>
+        <v>1497.11</v>
       </c>
       <c r="G36">
         <v>1457.9</v>
@@ -2166,7 +2166,7 @@
         <v>58</v>
       </c>
       <c r="B37">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C37">
         <v>18.95</v>
@@ -2204,7 +2204,7 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C38">
         <v>18.84</v>
@@ -2213,7 +2213,7 @@
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>2170.12</v>
+        <v>2030.68</v>
       </c>
       <c r="F38">
         <v>1442.9</v>
@@ -2245,7 +2245,7 @@
         <v>79</v>
       </c>
       <c r="C39">
-        <v>15.4</v>
+        <v>15.39</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
@@ -2257,7 +2257,7 @@
         <v>1243.37</v>
       </c>
       <c r="G39">
-        <v>1224.8</v>
+        <v>1220.18</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2289,13 +2289,13 @@
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1876.12</v>
+        <v>1874.51</v>
       </c>
       <c r="F40">
-        <v>1164.82</v>
+        <v>1187.89</v>
       </c>
       <c r="G40">
-        <v>1182.24</v>
+        <v>1188</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2394,7 +2394,7 @@
         <v>67</v>
       </c>
       <c r="B43">
-        <v>1733</v>
+        <v>1766</v>
       </c>
       <c r="C43">
         <v>13.49</v>
@@ -2403,13 +2403,13 @@
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1407.84</v>
+        <v>1404.73</v>
       </c>
       <c r="F43">
         <v>1038.06</v>
       </c>
       <c r="G43">
-        <v>1037.94</v>
+        <v>1036.79</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2432,7 +2432,7 @@
         <v>69</v>
       </c>
       <c r="B44">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C44">
         <v>13.25</v>
@@ -2441,7 +2441,7 @@
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1441.75</v>
+        <v>1571.85</v>
       </c>
       <c r="F44">
         <v>975.78</v>
@@ -2482,7 +2482,7 @@
         <v>1481.2</v>
       </c>
       <c r="F45">
-        <v>992.96</v>
+        <v>997.23</v>
       </c>
       <c r="G45">
         <v>991.92</v>
@@ -2546,22 +2546,22 @@
         <v>73</v>
       </c>
       <c r="B47">
-        <v>369</v>
+        <v>95</v>
       </c>
       <c r="C47">
-        <v>12.37</v>
+        <v>12.32</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1414.99</v>
+        <v>1321.1</v>
       </c>
       <c r="F47">
-        <v>938.87</v>
+        <v>978.54</v>
       </c>
       <c r="G47">
-        <v>941.17</v>
+        <v>930.68</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2576,30 +2576,30 @@
         <v>26</v>
       </c>
       <c r="L47" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B48">
-        <v>97</v>
+        <v>374</v>
       </c>
       <c r="C48">
-        <v>12.32</v>
+        <v>12.27</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1329.87</v>
+        <v>1433.91</v>
       </c>
       <c r="F48">
-        <v>978.54</v>
+        <v>922.72</v>
       </c>
       <c r="G48">
-        <v>930.68</v>
+        <v>940.02</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2614,7 +2614,7 @@
         <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2622,10 +2622,10 @@
         <v>76</v>
       </c>
       <c r="B49">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C49">
-        <v>11.62</v>
+        <v>11.64</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
@@ -2660,7 +2660,7 @@
         <v>77</v>
       </c>
       <c r="B50">
-        <v>1780</v>
+        <v>1805</v>
       </c>
       <c r="C50">
         <v>11.06</v>
@@ -2672,10 +2672,10 @@
         <v>1242.33</v>
       </c>
       <c r="F50">
-        <v>846.71</v>
+        <v>830.45</v>
       </c>
       <c r="G50">
-        <v>825.72</v>
+        <v>841.87</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2698,22 +2698,22 @@
         <v>78</v>
       </c>
       <c r="B51">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="C51">
-        <v>10.59</v>
+        <v>10.9</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1174.51</v>
+        <v>1132.75</v>
       </c>
       <c r="F51">
-        <v>781.66</v>
+        <v>757.55</v>
       </c>
       <c r="G51">
-        <v>806.11</v>
+        <v>753.17</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2728,7 +2728,7 @@
         <v>23</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2736,22 +2736,22 @@
         <v>79</v>
       </c>
       <c r="B52">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C52">
-        <v>10.49</v>
+        <v>10.59</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1132.75</v>
+        <v>1174.51</v>
       </c>
       <c r="F52">
-        <v>757.55</v>
+        <v>781.43</v>
       </c>
       <c r="G52">
-        <v>754.32</v>
+        <v>801.61</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2766,7 +2766,7 @@
         <v>23</v>
       </c>
       <c r="L52" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2789,7 +2789,7 @@
         <v>782.01</v>
       </c>
       <c r="G53">
-        <v>741.06</v>
+        <v>749.71</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2888,10 +2888,10 @@
         <v>83</v>
       </c>
       <c r="B56">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C56">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
@@ -2926,7 +2926,7 @@
         <v>84</v>
       </c>
       <c r="B57">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C57">
         <v>9.86</v>
@@ -2935,10 +2935,10 @@
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1093.31</v>
+        <v>1085.46</v>
       </c>
       <c r="F57">
-        <v>778.43</v>
+        <v>772.78</v>
       </c>
       <c r="G57">
         <v>763.55</v>
@@ -2964,22 +2964,22 @@
         <v>86</v>
       </c>
       <c r="B58">
-        <v>983</v>
+        <v>94</v>
       </c>
       <c r="C58">
-        <v>9.71</v>
+        <v>9.67</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1087.77</v>
+        <v>1016.84</v>
       </c>
       <c r="F58">
-        <v>744.4</v>
+        <v>711.42</v>
       </c>
       <c r="G58">
-        <v>725.49</v>
+        <v>743.94</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2991,33 +2991,33 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L58" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B59">
-        <v>95</v>
+        <v>981</v>
       </c>
       <c r="C59">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>1016.84</v>
+        <v>1158.01</v>
       </c>
       <c r="F59">
-        <v>711.42</v>
+        <v>745.67</v>
       </c>
       <c r="G59">
-        <v>743.94</v>
+        <v>726.64</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3029,10 +3029,10 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L59" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,10 +3040,10 @@
         <v>89</v>
       </c>
       <c r="B60">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C60">
-        <v>8.92</v>
+        <v>8.7</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
@@ -3055,7 +3055,7 @@
         <v>657.32</v>
       </c>
       <c r="G60">
-        <v>667.7</v>
+        <v>666.55</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3078,10 +3078,10 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C61">
-        <v>8.67</v>
+        <v>8.7</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
@@ -3093,7 +3093,7 @@
         <v>657.44</v>
       </c>
       <c r="G61">
-        <v>645.9</v>
+        <v>634.37</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3116,16 +3116,16 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C62">
-        <v>8.59</v>
+        <v>8.64</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>963.32</v>
+        <v>954.55</v>
       </c>
       <c r="F62">
         <v>660.78</v>
@@ -3154,19 +3154,19 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C63">
-        <v>8.29</v>
+        <v>8.33</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>910.49</v>
+        <v>922.26</v>
       </c>
       <c r="F63">
-        <v>631.26</v>
+        <v>630.68</v>
       </c>
       <c r="G63">
         <v>611.3</v>
@@ -3201,10 +3201,10 @@
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>938.87</v>
+        <v>927.79</v>
       </c>
       <c r="F64">
-        <v>609</v>
+        <v>607.84</v>
       </c>
       <c r="G64">
         <v>629.3</v>
@@ -3276,6 +3276,15 @@
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
+      <c r="E66">
+        <v>852.13</v>
+      </c>
+      <c r="F66">
+        <v>657.44</v>
+      </c>
+      <c r="G66">
+        <v>628.6</v>
+      </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
       </c>
@@ -3297,13 +3306,22 @@
         <v>96</v>
       </c>
       <c r="B67">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C67">
-        <v>7.99</v>
+        <v>8.06</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
+      </c>
+      <c r="E67">
+        <v>827.68</v>
+      </c>
+      <c r="F67">
+        <v>588.12</v>
+      </c>
+      <c r="G67">
+        <v>599.77</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3326,13 +3344,22 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="C68">
-        <v>7.99</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
+      </c>
+      <c r="E68">
+        <v>994</v>
+      </c>
+      <c r="F68">
+        <v>576.7</v>
+      </c>
+      <c r="G68">
+        <v>587.08</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3355,13 +3382,22 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>1433</v>
+        <v>833</v>
       </c>
       <c r="C69">
-        <v>7.88</v>
+        <v>7.89</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
+      </c>
+      <c r="E69">
+        <v>900.23</v>
+      </c>
+      <c r="F69">
+        <v>606.11</v>
+      </c>
+      <c r="G69">
+        <v>593.89</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3384,13 +3420,22 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>836</v>
+        <v>1437</v>
       </c>
       <c r="C70">
         <v>7.87</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
+      </c>
+      <c r="E70">
+        <v>866.32</v>
+      </c>
+      <c r="F70">
+        <v>599.65</v>
+      </c>
+      <c r="G70">
+        <v>584.66</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3413,13 +3458,22 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C71">
-        <v>7.83</v>
+        <v>7.85</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
+      </c>
+      <c r="E71">
+        <v>892.27</v>
+      </c>
+      <c r="F71">
+        <v>587.08</v>
+      </c>
+      <c r="G71">
+        <v>576.93</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3450,6 +3504,15 @@
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
+      <c r="E72">
+        <v>848.21</v>
+      </c>
+      <c r="F72">
+        <v>551.56</v>
+      </c>
+      <c r="G72">
+        <v>571.16</v>
+      </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
       </c>
@@ -3471,13 +3534,22 @@
         <v>102</v>
       </c>
       <c r="B73">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="C73">
         <v>7.39</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
+      </c>
+      <c r="E73">
+        <v>907.26</v>
+      </c>
+      <c r="F73">
+        <v>552.48</v>
+      </c>
+      <c r="G73">
+        <v>538.52</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3508,6 +3580,15 @@
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
+      <c r="E74">
+        <v>755.13</v>
+      </c>
+      <c r="F74">
+        <v>516.72</v>
+      </c>
+      <c r="G74">
+        <v>551.33</v>
+      </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
       </c>
@@ -3537,6 +3618,15 @@
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
+      <c r="E75">
+        <v>840.25</v>
+      </c>
+      <c r="F75">
+        <v>516.49</v>
+      </c>
+      <c r="G75">
+        <v>515.34</v>
+      </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
       </c>
@@ -3558,14 +3648,23 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>1329</v>
+        <v>391</v>
       </c>
       <c r="C76">
-        <v>6.84</v>
+        <v>6.82</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
+      <c r="E76">
+        <v>770.13</v>
+      </c>
+      <c r="F76">
+        <v>489.39</v>
+      </c>
+      <c r="G76">
+        <v>479.81</v>
+      </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
       </c>
@@ -3579,7 +3678,7 @@
         <v>26</v>
       </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3587,14 +3686,23 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>394</v>
+        <v>1334</v>
       </c>
       <c r="C77">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
+      <c r="E77">
+        <v>770.13</v>
+      </c>
+      <c r="F77">
+        <v>519.38</v>
+      </c>
+      <c r="G77">
+        <v>519.03</v>
+      </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
       </c>
@@ -3608,7 +3716,7 @@
         <v>26</v>
       </c>
       <c r="L77" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3624,6 +3732,15 @@
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
+      <c r="E78">
+        <v>900.23</v>
+      </c>
+      <c r="F78">
+        <v>529.99</v>
+      </c>
+      <c r="G78">
+        <v>461.36</v>
+      </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
       </c>
@@ -3645,13 +3762,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>1194</v>
+        <v>948</v>
       </c>
       <c r="C79">
-        <v>6.45</v>
+        <v>6.48</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
+      </c>
+      <c r="E79">
+        <v>730.68</v>
+      </c>
+      <c r="F79">
+        <v>483.27</v>
+      </c>
+      <c r="G79">
+        <v>473.93</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3674,22 +3800,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>77</v>
+        <v>1201</v>
       </c>
       <c r="C80">
-        <v>6.44</v>
+        <v>6.45</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>752.82</v>
+        <v>768.51</v>
       </c>
       <c r="F80">
-        <v>475.32</v>
+        <v>477.62</v>
       </c>
       <c r="G80">
-        <v>573.47</v>
+        <v>478.66</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3701,10 +3827,10 @@
         <f>IF(D80=0,"",(H80-D80)/D80)</f>
       </c>
       <c r="K80" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L80" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3712,22 +3838,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C81">
-        <v>6.29</v>
+        <v>6.44</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>656.63</v>
+        <v>752.82</v>
       </c>
       <c r="F81">
-        <v>474.85</v>
+        <v>475.32</v>
       </c>
       <c r="G81">
-        <v>507.5</v>
+        <v>573.47</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3739,10 +3865,10 @@
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
       <c r="K81" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="L81" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3750,14 +3876,23 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>938</v>
+        <v>73</v>
       </c>
       <c r="C82">
-        <v>6.28</v>
+        <v>6.22</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
+      <c r="E82">
+        <v>656.63</v>
+      </c>
+      <c r="F82">
+        <v>474.85</v>
+      </c>
+      <c r="G82">
+        <v>505.19</v>
+      </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
       </c>
@@ -3768,10 +3903,10 @@
         <f>IF(D82=0,"",(H82-D82)/D82)</f>
       </c>
       <c r="K82" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L82" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3787,6 +3922,15 @@
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
+      <c r="E83">
+        <v>681.89</v>
+      </c>
+      <c r="F83">
+        <v>462.4</v>
+      </c>
+      <c r="G83">
+        <v>454.32</v>
+      </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
       </c>
@@ -3816,6 +3960,15 @@
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
+      <c r="E84">
+        <v>556.52</v>
+      </c>
+      <c r="F84">
+        <v>419.61</v>
+      </c>
+      <c r="G84">
+        <v>391</v>
+      </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
       </c>
@@ -3837,13 +3990,22 @@
         <v>115</v>
       </c>
       <c r="B85">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C85">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
+      </c>
+      <c r="E85">
+        <v>698.38</v>
+      </c>
+      <c r="F85">
+        <v>449.83</v>
+      </c>
+      <c r="G85">
+        <v>432.87</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -3866,13 +4028,22 @@
         <v>116</v>
       </c>
       <c r="B86">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C86">
-        <v>5.79</v>
+        <v>5.75</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
+      </c>
+      <c r="E86">
+        <v>685</v>
+      </c>
+      <c r="F86">
+        <v>428.83</v>
+      </c>
+      <c r="G86">
+        <v>448.67</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -3895,13 +4066,22 @@
         <v>117</v>
       </c>
       <c r="B87">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C87">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
+      </c>
+      <c r="E87">
+        <v>602.19</v>
+      </c>
+      <c r="F87">
+        <v>511.53</v>
+      </c>
+      <c r="G87">
+        <v>444.06</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -3927,10 +4107,19 @@
         <v>226</v>
       </c>
       <c r="C88">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
+      </c>
+      <c r="E88">
+        <v>634.49</v>
+      </c>
+      <c r="F88">
+        <v>507.38</v>
+      </c>
+      <c r="G88">
+        <v>481.89</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -3953,14 +4142,23 @@
         <v>119</v>
       </c>
       <c r="B89">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C89">
-        <v>5.6</v>
+        <v>5.51</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
+      <c r="E89">
+        <v>588.81</v>
+      </c>
+      <c r="F89">
+        <v>409.46</v>
+      </c>
+      <c r="G89">
+        <v>427.8</v>
+      </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
       </c>
@@ -3971,10 +4169,10 @@
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
       <c r="K89" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L89" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -3982,14 +4180,23 @@
         <v>120</v>
       </c>
       <c r="B90">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C90">
-        <v>5.53</v>
+        <v>5.45</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
+      <c r="E90">
+        <v>619.61</v>
+      </c>
+      <c r="F90">
+        <v>452.13</v>
+      </c>
+      <c r="G90">
+        <v>406</v>
+      </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
       </c>
@@ -4000,10 +4207,10 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4011,14 +4218,23 @@
         <v>121</v>
       </c>
       <c r="B91">
-        <v>174</v>
+        <v>511</v>
       </c>
       <c r="C91">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
+      <c r="E91">
+        <v>568.28</v>
+      </c>
+      <c r="F91">
+        <v>396.77</v>
+      </c>
+      <c r="G91">
+        <v>385.24</v>
+      </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
       </c>
@@ -4032,7 +4248,7 @@
         <v>65</v>
       </c>
       <c r="L91" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4040,13 +4256,22 @@
         <v>122</v>
       </c>
       <c r="B92">
-        <v>510</v>
+        <v>122</v>
       </c>
       <c r="C92">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
+      </c>
+      <c r="E92">
+        <v>600.69</v>
+      </c>
+      <c r="F92">
+        <v>445.21</v>
+      </c>
+      <c r="G92">
+        <v>402.54</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4069,14 +4294,23 @@
         <v>123</v>
       </c>
       <c r="B93">
-        <v>122</v>
+        <v>855</v>
       </c>
       <c r="C93">
-        <v>5.37</v>
+        <v>5.33</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
+      <c r="E93">
+        <v>622.72</v>
+      </c>
+      <c r="F93">
+        <v>422.03</v>
+      </c>
+      <c r="G93">
+        <v>424.45</v>
+      </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
       </c>
@@ -4087,10 +4321,10 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L93" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4098,22 +4332,22 @@
         <v>124</v>
       </c>
       <c r="B94">
-        <v>858</v>
+        <v>31</v>
       </c>
       <c r="C94">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>622.72</v>
+        <v>580.16</v>
       </c>
       <c r="F94">
-        <v>415.22</v>
+        <v>403.57</v>
       </c>
       <c r="G94">
-        <v>424.45</v>
+        <v>413.84</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4125,10 +4359,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4136,22 +4370,22 @@
         <v>125</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C95">
-        <v>5.29</v>
+        <v>5.18</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>580.16</v>
+        <v>567.47</v>
       </c>
       <c r="F95">
-        <v>405.77</v>
+        <v>412.23</v>
       </c>
       <c r="G95">
-        <v>413.96</v>
+        <v>388.7</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4163,25 +4397,34 @@
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
       <c r="K95" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L95" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B96">
-        <v>62</v>
+        <v>504</v>
       </c>
       <c r="C96">
-        <v>5.18</v>
+        <v>5.01</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
+      <c r="E96">
+        <v>547.06</v>
+      </c>
+      <c r="F96">
+        <v>363.32</v>
+      </c>
+      <c r="G96">
+        <v>391.93</v>
+      </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
       </c>
@@ -4192,10 +4435,10 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L96" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4203,14 +4446,23 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>505</v>
+        <v>73</v>
       </c>
       <c r="C97">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
+      <c r="E97">
+        <v>580.16</v>
+      </c>
+      <c r="F97">
+        <v>384.2</v>
+      </c>
+      <c r="G97">
+        <v>370.24</v>
+      </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
       </c>
@@ -4221,10 +4473,10 @@
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
       <c r="K97" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L97" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4232,13 +4484,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="C98">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
+      </c>
+      <c r="E98">
+        <v>565.97</v>
+      </c>
+      <c r="F98">
+        <v>343.6</v>
+      </c>
+      <c r="G98">
+        <v>322.95</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4261,22 +4522,22 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="C99">
-        <v>4.86</v>
+        <v>4.81</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>566.78</v>
+        <v>584.89</v>
       </c>
       <c r="F99">
-        <v>344.75</v>
+        <v>410.96</v>
       </c>
       <c r="G99">
-        <v>322.95</v>
+        <v>379.47</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4299,14 +4560,23 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>121</v>
+        <v>625</v>
       </c>
       <c r="C100">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
+      <c r="E100">
+        <v>509.23</v>
+      </c>
+      <c r="F100">
+        <v>360.21</v>
+      </c>
+      <c r="G100">
+        <v>356.4</v>
+      </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
       </c>
@@ -4317,10 +4587,10 @@
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
       <c r="K100" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L100" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4328,14 +4598,23 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>622</v>
+        <v>79</v>
       </c>
       <c r="C101">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
+      <c r="E101">
+        <v>599.08</v>
+      </c>
+      <c r="F101">
+        <v>372.43</v>
+      </c>
+      <c r="G101">
+        <v>380.62</v>
+      </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
       </c>
@@ -4346,10 +4625,10 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L101" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4357,22 +4636,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C102">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>599.08</v>
+        <v>535.18</v>
       </c>
       <c r="F102">
-        <v>372.43</v>
+        <v>333.33</v>
       </c>
       <c r="G102">
-        <v>380.62</v>
+        <v>373.36</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4384,10 +4663,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L102" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4395,14 +4674,23 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C103">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
+      <c r="E103">
+        <v>468.17</v>
+      </c>
+      <c r="F103">
+        <v>334.49</v>
+      </c>
+      <c r="G103">
+        <v>333.1</v>
+      </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
       </c>
@@ -4413,10 +4701,10 @@
         <f>IF(D103=0,"",(H103-D103)/D103)</f>
       </c>
       <c r="K103" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L103" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4424,10 +4712,10 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C104">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
@@ -4436,7 +4724,7 @@
         <v>521.8</v>
       </c>
       <c r="F104">
-        <v>369.09</v>
+        <v>359.17</v>
       </c>
       <c r="G104">
         <v>351.79</v>
@@ -4470,6 +4758,15 @@
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
+      <c r="E105">
+        <v>485.58</v>
+      </c>
+      <c r="F105">
+        <v>321.57</v>
+      </c>
+      <c r="G105">
+        <v>291.58</v>
+      </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
       </c>
@@ -4537,6 +4834,15 @@
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
+      <c r="E107">
+        <v>446.94</v>
+      </c>
+      <c r="F107">
+        <v>353.98</v>
+      </c>
+      <c r="G107">
+        <v>312.69</v>
+      </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
       </c>
@@ -4573,7 +4879,7 @@
         <v>339.79</v>
       </c>
       <c r="G108">
-        <v>360.78</v>
+        <v>361.94</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4596,22 +4902,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>2427</v>
+        <v>55</v>
       </c>
       <c r="C109">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>474.51</v>
+        <v>530.45</v>
       </c>
       <c r="F109">
-        <v>322.95</v>
+        <v>303.34</v>
       </c>
       <c r="G109">
-        <v>325.72</v>
+        <v>303.34</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4623,10 +4929,10 @@
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
       <c r="K109" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L109" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4634,22 +4940,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>54</v>
+        <v>2436</v>
       </c>
       <c r="C110">
-        <v>4.29</v>
+        <v>4.14</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>530.45</v>
+        <v>474.51</v>
       </c>
       <c r="F110">
-        <v>303.34</v>
+        <v>339.1</v>
       </c>
       <c r="G110">
-        <v>303.34</v>
+        <v>325.72</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4661,10 +4967,10 @@
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
       <c r="K110" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L110" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4672,10 +4978,10 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C111">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
@@ -4684,7 +4990,7 @@
         <v>421.68</v>
       </c>
       <c r="F111">
-        <v>313.61</v>
+        <v>312.46</v>
       </c>
       <c r="G111">
         <v>310.26</v>
@@ -4710,13 +5016,22 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C112">
         <v>3.85</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
+      </c>
+      <c r="E112">
+        <v>431.95</v>
+      </c>
+      <c r="F112">
+        <v>310.96</v>
+      </c>
+      <c r="G112">
+        <v>290.66</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -4739,13 +5054,22 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C113">
         <v>3.83</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
+      </c>
+      <c r="E113">
+        <v>383.04</v>
+      </c>
+      <c r="F113">
+        <v>295.27</v>
+      </c>
+      <c r="G113">
+        <v>277.97</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -4768,7 +5092,7 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C114">
         <v>3.78</v>
@@ -4780,10 +5104,10 @@
         <v>405.19</v>
       </c>
       <c r="F114">
-        <v>291.58</v>
+        <v>291.46</v>
       </c>
       <c r="G114">
-        <v>276.82</v>
+        <v>286.97</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -4806,7 +5130,7 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C115">
         <v>3.7</v>
@@ -4821,7 +5145,7 @@
         <v>270.13</v>
       </c>
       <c r="G115">
-        <v>289.73</v>
+        <v>288.58</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -4891,13 +5215,13 @@
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>398.85</v>
+        <v>500.58</v>
       </c>
       <c r="F117">
-        <v>263.78</v>
+        <v>262.63</v>
       </c>
       <c r="G117">
-        <v>264.13</v>
+        <v>266.44</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -4920,22 +5244,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C118">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>373.59</v>
+        <v>365.74</v>
       </c>
       <c r="F118">
-        <v>252.36</v>
+        <v>251.21</v>
       </c>
       <c r="G118">
-        <v>257.21</v>
+        <v>260.44</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -4958,22 +5282,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>70</v>
+        <v>251</v>
       </c>
       <c r="C119">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>357.78</v>
+        <v>382.24</v>
       </c>
       <c r="F119">
-        <v>254.56</v>
+        <v>254.79</v>
       </c>
       <c r="G119">
-        <v>239.56</v>
+        <v>247.98</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -4985,10 +5309,10 @@
         <f>IF(D119=0,"",(H119-D119)/D119)</f>
       </c>
       <c r="K119" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L119" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -4996,22 +5320,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="C120">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>383.04</v>
+        <v>340.48</v>
       </c>
       <c r="F120">
-        <v>254.79</v>
+        <v>236.33</v>
       </c>
       <c r="G120">
-        <v>249.13</v>
+        <v>236.45</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5023,10 +5347,10 @@
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
       <c r="K120" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L120" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5034,22 +5358,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>324</v>
+        <v>69</v>
       </c>
       <c r="C121">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>340.48</v>
+        <v>350.75</v>
       </c>
       <c r="F121">
-        <v>236.33</v>
+        <v>253.75</v>
       </c>
       <c r="G121">
-        <v>236.1</v>
+        <v>239.79</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5072,13 +5396,22 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C122">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
+      </c>
+      <c r="E122">
+        <v>360.21</v>
+      </c>
+      <c r="F122">
+        <v>249.13</v>
+      </c>
+      <c r="G122">
+        <v>244.29</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -5109,6 +5442,15 @@
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
+      <c r="E123">
+        <v>297.12</v>
+      </c>
+      <c r="F123">
+        <v>226.64</v>
+      </c>
+      <c r="G123">
+        <v>222.61</v>
+      </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
       </c>
@@ -5130,7 +5472,7 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C124">
         <v>2.89</v>
@@ -5139,13 +5481,13 @@
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>327.1</v>
+        <v>326.3</v>
       </c>
       <c r="F124">
         <v>214.3</v>
       </c>
       <c r="G124">
-        <v>201.85</v>
+        <v>208.77</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5177,7 +5519,7 @@
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>354.67</v>
+        <v>334.95</v>
       </c>
       <c r="F125">
         <v>218.11</v>
@@ -5209,16 +5551,16 @@
         <v>36</v>
       </c>
       <c r="C126">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>368.05</v>
+        <v>367.24</v>
       </c>
       <c r="F126">
-        <v>191.93</v>
+        <v>190.77</v>
       </c>
       <c r="G126">
         <v>191.58</v>
@@ -5244,7 +5586,7 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="C127">
         <v>2.26</v>
@@ -5253,13 +5595,13 @@
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>285.35</v>
+        <v>295.62</v>
       </c>
       <c r="F127">
-        <v>176.12</v>
+        <v>177.62</v>
       </c>
       <c r="G127">
-        <v>169.43</v>
+        <v>184.54</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5271,10 +5613,10 @@
         <f>IF(D127=0,"",(H127-D127)/D127)</f>
       </c>
       <c r="K127" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L127" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5282,22 +5624,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="C128">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>295.62</v>
+        <v>260.09</v>
       </c>
       <c r="F128">
-        <v>177.62</v>
+        <v>174.16</v>
       </c>
       <c r="G128">
-        <v>177.62</v>
+        <v>171.63</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5309,10 +5651,10 @@
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
       <c r="K128" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L128" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5320,22 +5662,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C129">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>230.91</v>
+        <v>249.83</v>
       </c>
       <c r="F129">
-        <v>175.55</v>
+        <v>183.39</v>
       </c>
       <c r="G129">
-        <v>174.16</v>
+        <v>188</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5358,22 +5700,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C130">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>249.83</v>
+        <v>230.91</v>
       </c>
       <c r="F130">
-        <v>183.39</v>
+        <v>175.09</v>
       </c>
       <c r="G130">
-        <v>188</v>
+        <v>174.16</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5396,10 +5738,10 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C131">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
@@ -5434,7 +5776,7 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C132">
         <v>1.77</v>
@@ -5443,10 +5785,10 @@
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>255.36</v>
+        <v>253.75</v>
       </c>
       <c r="F132">
-        <v>134.6</v>
+        <v>133.45</v>
       </c>
       <c r="G132">
         <v>143.02</v>
@@ -5525,7 +5867,7 @@
         <v>117.65</v>
       </c>
       <c r="G134">
-        <v>124.34</v>
+        <v>123.88</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5548,7 +5890,7 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C135">
         <v>1.56</v>
@@ -5560,10 +5902,10 @@
         <v>165.51</v>
       </c>
       <c r="F135">
-        <v>117.07</v>
+        <v>115.92</v>
       </c>
       <c r="G135">
-        <v>124.57</v>
+        <v>124.45</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5598,10 +5940,10 @@
         <v>155.25</v>
       </c>
       <c r="F136">
-        <v>103.81</v>
+        <v>106.46</v>
       </c>
       <c r="G136">
-        <v>104.61</v>
+        <v>104.5</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5624,7 +5966,7 @@
         <v>168</v>
       </c>
       <c r="B137">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C137">
         <v>1.01</v>
@@ -5639,7 +5981,7 @@
         <v>74.97</v>
       </c>
       <c r="G137">
-        <v>80.74</v>
+        <v>80.62</v>
       </c>
       <c r="H137">
         <f>MIN(E137:G137)</f>
@@ -5662,7 +6004,7 @@
         <v>169</v>
       </c>
       <c r="B138">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C138">
         <v>0.85</v>
@@ -5671,13 +6013,13 @@
         <f>C138*$B$3</f>
       </c>
       <c r="E138">
-        <v>92.96</v>
+        <v>88.24</v>
       </c>
       <c r="F138">
-        <v>66.21</v>
+        <v>66.09</v>
       </c>
       <c r="G138">
-        <v>64.48</v>
+        <v>64.36</v>
       </c>
       <c r="H138">
         <f>MIN(E138:G138)</f>
@@ -5700,7 +6042,7 @@
         <v>170</v>
       </c>
       <c r="B139">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C139">
         <v>0.7</v>
@@ -5730,7 +6072,7 @@
         <v>26</v>
       </c>
       <c r="L139" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5738,7 +6080,7 @@
         <v>171</v>
       </c>
       <c r="B140">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C140">
         <v>0.48</v>
@@ -5750,7 +6092,7 @@
         <v>60.67</v>
       </c>
       <c r="F140">
-        <v>34.37</v>
+        <v>34.26</v>
       </c>
       <c r="G140">
         <v>35.64</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 20:54</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 22:48</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -115,12 +115,12 @@
     <t>AK-47 | Legion of Anubis (Factory New)</t>
   </si>
   <si>
+    <t>USP-S | Whiteout (Field-Tested)</t>
+  </si>
+  <si>
     <t>MAC-10 | Fade (Factory New)</t>
   </si>
   <si>
-    <t>USP-S | Whiteout (Field-Tested)</t>
-  </si>
-  <si>
     <t>USP-S | Orion (Minimal Wear)</t>
   </si>
   <si>
@@ -136,21 +136,21 @@
     <t>MP9 | Hydra (Factory New)</t>
   </si>
   <si>
+    <t>P250 | Apep's Curse (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Desert Eagle | Starcade (Field-Tested)</t>
+  </si>
+  <si>
     <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
   </si>
   <si>
-    <t>Desert Eagle | Starcade (Field-Tested)</t>
-  </si>
-  <si>
-    <t>P250 | Apep's Curse (Field-Tested)</t>
+    <t>CZ75-Auto | Emerald (Factory New)</t>
   </si>
   <si>
     <t>Dual Berettas | Emerald (Factory New)</t>
   </si>
   <si>
-    <t>CZ75-Auto | Emerald (Factory New)</t>
-  </si>
-  <si>
     <t>SCAR-20 | Cyrex (Factory New)</t>
   </si>
   <si>
@@ -184,15 +184,15 @@
     <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
+    <t>Nova | Sobek's Bite (Factory New)</t>
+  </si>
+  <si>
+    <t>Shotgun</t>
+  </si>
+  <si>
     <t>Safecracker Voltzmann | The Professionals</t>
   </si>
   <si>
-    <t>Nova | Sobek's Bite (Factory New)</t>
-  </si>
-  <si>
-    <t>Shotgun</t>
-  </si>
-  <si>
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
@@ -232,15 +232,15 @@
     <t>Exotic</t>
   </si>
   <si>
+    <t>M4A4 | Evil Daimyo (Factory New)</t>
+  </si>
+  <si>
     <t>SG 553 | Candy Apple (Factory New)</t>
   </si>
   <si>
     <t>Industrial Grade</t>
   </si>
   <si>
-    <t>M4A4 | Evil Daimyo (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
@@ -271,15 +271,15 @@
     <t>Exceptional</t>
   </si>
   <si>
+    <t>B Squadron Officer | SAS</t>
+  </si>
+  <si>
+    <t>Distinguished</t>
+  </si>
+  <si>
     <t>AUG | Carved Jade (Minimal Wear)</t>
   </si>
   <si>
-    <t>B Squadron Officer | SAS</t>
-  </si>
-  <si>
-    <t>Distinguished</t>
-  </si>
-  <si>
     <t>SSG 08 | Rapid Transit (Factory New)</t>
   </si>
   <si>
@@ -340,21 +340,24 @@
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Tec-9 | Brass (Field-Tested)</t>
+  </si>
+  <si>
     <t>Dragomir | Sabre</t>
   </si>
   <si>
     <t>Maximus | Sabre</t>
   </si>
   <si>
-    <t>Tec-9 | Brass (Field-Tested)</t>
-  </si>
-  <si>
     <t>XM1014 | Black Tie (Factory New)</t>
   </si>
   <si>
     <t>Sticker | BIG (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
   </si>
   <si>
@@ -379,12 +382,12 @@
     <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
-  </si>
-  <si>
     <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
@@ -400,24 +403,21 @@
     <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
-    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>R8 Revolver | Blaze (Factory New)</t>
   </si>
   <si>
+    <t>P250 | Epicenter (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | Stone Scales (Foil)</t>
   </si>
   <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>AK-47 | Crossfade (Minimal Wear)</t>
   </si>
   <si>
+    <t>CZ75-Auto | Tuxedo (Factory New)</t>
+  </si>
+  <si>
     <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
   </si>
   <si>
-    <t>CZ75-Auto | Tuxedo (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -490,13 +490,13 @@
     <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
+    <t>Sticker | BIG (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | BIG (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | Ancient Beast (Foil)</t>
@@ -933,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.83</v>
+        <v>82.22</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -988,7 +988,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>165.26</v>
@@ -1026,10 +1026,10 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>135.36</v>
+        <v>136.65</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -1041,7 +1041,7 @@
         <v>10605.51</v>
       </c>
       <c r="G7">
-        <v>9913.47</v>
+        <v>9907.71</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1064,10 +1064,10 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C8">
-        <v>118.69</v>
+        <v>118.65</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
@@ -1079,7 +1079,7 @@
         <v>8869.65</v>
       </c>
       <c r="G8">
-        <v>8737.01</v>
+        <v>8708.17</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1105,7 +1105,7 @@
         <v>141</v>
       </c>
       <c r="C9">
-        <v>97.13</v>
+        <v>96.16</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
@@ -1143,7 +1143,7 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>86.01</v>
+        <v>85.99</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1181,13 +1181,13 @@
         <v>199</v>
       </c>
       <c r="C11">
-        <v>84.29</v>
+        <v>84.37</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>9301.25</v>
+        <v>9194.1</v>
       </c>
       <c r="F11">
         <v>6574.38</v>
@@ -1216,10 +1216,10 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C12">
-        <v>81.24</v>
+        <v>80.92</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
@@ -1263,7 +1263,7 @@
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>7371.49</v>
+        <v>7374.61</v>
       </c>
       <c r="F13">
         <v>5755.47</v>
@@ -1295,19 +1295,19 @@
         <v>140</v>
       </c>
       <c r="C14">
-        <v>61.33</v>
+        <v>60.18</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>6610.71</v>
+        <v>6620.17</v>
       </c>
       <c r="F14">
-        <v>4601.95</v>
+        <v>4596.18</v>
       </c>
       <c r="G14">
-        <v>4531.36</v>
+        <v>4565.16</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1330,22 +1330,22 @@
         <v>34</v>
       </c>
       <c r="B15">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="C15">
-        <v>58.25</v>
+        <v>58.2</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>6315.1</v>
+        <v>6306.45</v>
       </c>
       <c r="F15">
-        <v>4371.39</v>
+        <v>4319.48</v>
       </c>
       <c r="G15">
-        <v>4260.66</v>
+        <v>4232.98</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1357,10 +1357,10 @@
         <f>IF(D15=0,"",(H15-D15)/D15)</f>
       </c>
       <c r="K15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1368,22 +1368,22 @@
         <v>35</v>
       </c>
       <c r="B16">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="C16">
-        <v>58.2</v>
+        <v>57.67</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>6306.45</v>
+        <v>6148.78</v>
       </c>
       <c r="F16">
-        <v>4319.48</v>
+        <v>4371.39</v>
       </c>
       <c r="G16">
-        <v>4232.98</v>
+        <v>4260.66</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1395,10 +1395,10 @@
         <f>IF(D16=0,"",(H16-D16)/D16)</f>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1406,16 +1406,16 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C17">
-        <v>57.32</v>
+        <v>57.18</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>6306.45</v>
+        <v>6294.68</v>
       </c>
       <c r="F17">
         <v>4394.45</v>
@@ -1444,10 +1444,10 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C18">
-        <v>55.88</v>
+        <v>56</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1456,10 +1456,10 @@
         <v>6345.89</v>
       </c>
       <c r="F18">
-        <v>4241.05</v>
+        <v>4232.98</v>
       </c>
       <c r="G18">
-        <v>4094.57</v>
+        <v>4150.86</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1482,7 +1482,7 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C19">
         <v>54.34</v>
@@ -1491,13 +1491,13 @@
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5713.6</v>
+        <v>5797.22</v>
       </c>
       <c r="F19">
-        <v>3961.93</v>
+        <v>3979.23</v>
       </c>
       <c r="G19">
-        <v>4008.07</v>
+        <v>3990.76</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1523,7 +1523,7 @@
         <v>75</v>
       </c>
       <c r="C20">
-        <v>50.87</v>
+        <v>52.69</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
@@ -1558,7 +1558,7 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <v>49.97</v>
@@ -1570,7 +1570,7 @@
         <v>5717.63</v>
       </c>
       <c r="F21">
-        <v>3627.44</v>
+        <v>3610.03</v>
       </c>
       <c r="G21">
         <v>3604.38</v>
@@ -1596,22 +1596,22 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C22">
-        <v>48.6</v>
+        <v>49.48</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>5384.88</v>
+        <v>5863.42</v>
       </c>
       <c r="F22">
-        <v>3517.87</v>
+        <v>3662.05</v>
       </c>
       <c r="G22">
-        <v>3581.31</v>
+        <v>3794.69</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1623,7 +1623,7 @@
         <f>IF(D22=0,"",(H22-D22)/D22)</f>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L22" t="s">
         <v>24</v>
@@ -1634,10 +1634,10 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C23">
-        <v>48.45</v>
+        <v>48.53</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
@@ -1646,10 +1646,10 @@
         <v>5214.64</v>
       </c>
       <c r="F23">
-        <v>3685.11</v>
+        <v>3679.35</v>
       </c>
       <c r="G23">
-        <v>3546.71</v>
+        <v>3540.94</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1672,22 +1672,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C24">
-        <v>48.29</v>
+        <v>48.08</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>5863.42</v>
+        <v>5384.88</v>
       </c>
       <c r="F24">
-        <v>3662.05</v>
+        <v>3460.2</v>
       </c>
       <c r="G24">
-        <v>3794.69</v>
+        <v>3569.77</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1699,7 +1699,7 @@
         <f>IF(D24=0,"",(H24-D24)/D24)</f>
       </c>
       <c r="K24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
         <v>24</v>
@@ -1710,22 +1710,22 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="C25">
-        <v>37.08</v>
+        <v>37.57</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>4170.12</v>
+        <v>4142.55</v>
       </c>
       <c r="F25">
-        <v>2652.82</v>
+        <v>2835.98</v>
       </c>
       <c r="G25">
-        <v>2934.94</v>
+        <v>2755.47</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1748,22 +1748,22 @@
         <v>45</v>
       </c>
       <c r="B26">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C26">
-        <v>36.43</v>
+        <v>36.75</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>4142.55</v>
+        <v>4058.24</v>
       </c>
       <c r="F26">
-        <v>2841.75</v>
+        <v>2652.82</v>
       </c>
       <c r="G26">
-        <v>2730.44</v>
+        <v>2929.17</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1789,7 +1789,7 @@
         <v>92</v>
       </c>
       <c r="C27">
-        <v>35.02</v>
+        <v>34.67</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
@@ -1824,19 +1824,19 @@
         <v>47</v>
       </c>
       <c r="B28">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C28">
-        <v>32.54</v>
+        <v>32.66</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>3633.33</v>
+        <v>3686.15</v>
       </c>
       <c r="F28">
-        <v>2476</v>
+        <v>2468.28</v>
       </c>
       <c r="G28">
         <v>2403.69</v>
@@ -1862,7 +1862,7 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C29">
         <v>31.49</v>
@@ -1900,10 +1900,10 @@
         <v>49</v>
       </c>
       <c r="B30">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C30">
-        <v>29.26</v>
+        <v>29.27</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
@@ -1938,10 +1938,10 @@
         <v>50</v>
       </c>
       <c r="B31">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C31">
-        <v>25.58</v>
+        <v>25.32</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
@@ -1976,22 +1976,22 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C32">
-        <v>23.32</v>
+        <v>23.88</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2884.42</v>
+        <v>2708.64</v>
       </c>
       <c r="F32">
-        <v>1903.11</v>
+        <v>1914.64</v>
       </c>
       <c r="G32">
-        <v>1937.71</v>
+        <v>1926.18</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2017,7 +2017,7 @@
         <v>150</v>
       </c>
       <c r="C33">
-        <v>20.86</v>
+        <v>20.65</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
@@ -2052,10 +2052,10 @@
         <v>55</v>
       </c>
       <c r="B34">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
@@ -2064,7 +2064,7 @@
         <v>2307.38</v>
       </c>
       <c r="F34">
-        <v>1473.7</v>
+        <v>1473.58</v>
       </c>
       <c r="G34">
         <v>1491.35</v>
@@ -2090,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="B35">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C35">
         <v>19.51</v>
@@ -2099,7 +2099,7 @@
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>2360.89</v>
+        <v>2364.12</v>
       </c>
       <c r="F35">
         <v>1480.85</v>
@@ -2128,22 +2128,22 @@
         <v>57</v>
       </c>
       <c r="B36">
-        <v>1124</v>
+        <v>35</v>
       </c>
       <c r="C36">
-        <v>19.1</v>
+        <v>18.95</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>2186.73</v>
+        <v>2287.65</v>
       </c>
       <c r="F36">
-        <v>1497.11</v>
+        <v>1454.44</v>
       </c>
       <c r="G36">
-        <v>1457.9</v>
+        <v>1451.78</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2155,33 +2155,33 @@
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
       <c r="K36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L36" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37">
-        <v>35</v>
+        <v>1119</v>
       </c>
       <c r="C37">
-        <v>18.95</v>
+        <v>18.92</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2287.65</v>
+        <v>2107.15</v>
       </c>
       <c r="F37">
-        <v>1454.44</v>
+        <v>1491.35</v>
       </c>
       <c r="G37">
-        <v>1451.78</v>
+        <v>1464.59</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2193,10 +2193,10 @@
         <f>IF(D37=0,"",(H37-D37)/D37)</f>
       </c>
       <c r="K37" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L37" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2204,7 +2204,7 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38">
         <v>18.84</v>
@@ -2213,10 +2213,10 @@
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>2030.68</v>
+        <v>2170.12</v>
       </c>
       <c r="F38">
-        <v>1442.9</v>
+        <v>1444.75</v>
       </c>
       <c r="G38">
         <v>1394.46</v>
@@ -2242,10 +2242,10 @@
         <v>61</v>
       </c>
       <c r="B39">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C39">
-        <v>15.39</v>
+        <v>15.92</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
@@ -2257,7 +2257,7 @@
         <v>1243.37</v>
       </c>
       <c r="G39">
-        <v>1220.18</v>
+        <v>1215.57</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2280,22 +2280,22 @@
         <v>62</v>
       </c>
       <c r="B40">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C40">
-        <v>15.01</v>
+        <v>15.68</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1874.51</v>
+        <v>1754.78</v>
       </c>
       <c r="F40">
         <v>1187.89</v>
       </c>
       <c r="G40">
-        <v>1188</v>
+        <v>1197.58</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2345,7 +2345,7 @@
         <f>IF(D41=0,"",(H41-D41)/D41)</f>
       </c>
       <c r="K41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L41" t="s">
         <v>21</v>
@@ -2359,7 +2359,7 @@
         <v>74</v>
       </c>
       <c r="C42">
-        <v>13.82</v>
+        <v>13.68</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
@@ -2368,7 +2368,7 @@
         <v>1537.94</v>
       </c>
       <c r="F42">
-        <v>982.7</v>
+        <v>980.39</v>
       </c>
       <c r="G42">
         <v>942.9</v>
@@ -2394,22 +2394,22 @@
         <v>67</v>
       </c>
       <c r="B43">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="C43">
-        <v>13.49</v>
+        <v>13.38</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1404.73</v>
+        <v>1418.91</v>
       </c>
       <c r="F43">
         <v>1038.06</v>
       </c>
       <c r="G43">
-        <v>1036.79</v>
+        <v>1037.94</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2435,13 +2435,13 @@
         <v>61</v>
       </c>
       <c r="C44">
-        <v>13.25</v>
+        <v>13.26</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1571.85</v>
+        <v>1450.4</v>
       </c>
       <c r="F44">
         <v>975.78</v>
@@ -2479,13 +2479,13 @@
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1481.2</v>
+        <v>1565.51</v>
       </c>
       <c r="F45">
-        <v>997.23</v>
+        <v>1003.46</v>
       </c>
       <c r="G45">
-        <v>991.92</v>
+        <v>996.42</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2520,7 +2520,7 @@
         <v>1418.11</v>
       </c>
       <c r="F46">
-        <v>1031.95</v>
+        <v>1031.83</v>
       </c>
       <c r="G46">
         <v>977.28</v>
@@ -2546,22 +2546,22 @@
         <v>73</v>
       </c>
       <c r="B47">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="C47">
-        <v>12.32</v>
+        <v>12.27</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1321.1</v>
+        <v>1396.88</v>
       </c>
       <c r="F47">
-        <v>978.54</v>
+        <v>938.87</v>
       </c>
       <c r="G47">
-        <v>930.68</v>
+        <v>940.02</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2576,30 +2576,30 @@
         <v>26</v>
       </c>
       <c r="L47" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B48">
-        <v>374</v>
+        <v>96</v>
       </c>
       <c r="C48">
-        <v>12.27</v>
+        <v>12.2</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1433.91</v>
+        <v>1321.1</v>
       </c>
       <c r="F48">
-        <v>922.72</v>
+        <v>978.78</v>
       </c>
       <c r="G48">
-        <v>940.02</v>
+        <v>930.68</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2614,7 +2614,7 @@
         <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2622,7 +2622,7 @@
         <v>76</v>
       </c>
       <c r="B49">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C49">
         <v>11.64</v>
@@ -2631,10 +2631,10 @@
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1263.67</v>
+        <v>1252.59</v>
       </c>
       <c r="F49">
-        <v>863.9</v>
+        <v>862.74</v>
       </c>
       <c r="G49">
         <v>856.86</v>
@@ -2660,7 +2660,7 @@
         <v>77</v>
       </c>
       <c r="B50">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="C50">
         <v>11.06</v>
@@ -2669,13 +2669,13 @@
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1242.33</v>
+        <v>1303</v>
       </c>
       <c r="F50">
-        <v>830.45</v>
+        <v>807.38</v>
       </c>
       <c r="G50">
-        <v>841.87</v>
+        <v>841.52</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2698,10 +2698,10 @@
         <v>78</v>
       </c>
       <c r="B51">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C51">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
@@ -2713,7 +2713,7 @@
         <v>757.55</v>
       </c>
       <c r="G51">
-        <v>753.17</v>
+        <v>749.71</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2745,13 +2745,13 @@
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1174.51</v>
+        <v>1173.7</v>
       </c>
       <c r="F52">
-        <v>781.43</v>
+        <v>779.01</v>
       </c>
       <c r="G52">
-        <v>801.61</v>
+        <v>795.85</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2812,7 +2812,7 @@
         <v>81</v>
       </c>
       <c r="B54">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C54">
         <v>10.19</v>
@@ -2824,7 +2824,7 @@
         <v>1153.28</v>
       </c>
       <c r="F54">
-        <v>749.59</v>
+        <v>749.48</v>
       </c>
       <c r="G54">
         <v>821.91</v>
@@ -2850,10 +2850,10 @@
         <v>82</v>
       </c>
       <c r="B55">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C55">
-        <v>10.16</v>
+        <v>10.06</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
@@ -2865,7 +2865,7 @@
         <v>748.56</v>
       </c>
       <c r="G55">
-        <v>789.96</v>
+        <v>761.24</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2891,13 +2891,13 @@
         <v>496</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>9.86</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1129.64</v>
+        <v>1113.03</v>
       </c>
       <c r="F56">
         <v>725.49</v>
@@ -2926,22 +2926,22 @@
         <v>84</v>
       </c>
       <c r="B57">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C57">
-        <v>9.86</v>
+        <v>9.76</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1085.46</v>
+        <v>1064.13</v>
       </c>
       <c r="F57">
-        <v>772.78</v>
+        <v>784.08</v>
       </c>
       <c r="G57">
-        <v>763.55</v>
+        <v>764.7</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2964,22 +2964,22 @@
         <v>86</v>
       </c>
       <c r="B58">
-        <v>94</v>
+        <v>985</v>
       </c>
       <c r="C58">
-        <v>9.67</v>
+        <v>9.62</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1016.84</v>
+        <v>1080.74</v>
       </c>
       <c r="F58">
-        <v>711.42</v>
+        <v>749.59</v>
       </c>
       <c r="G58">
-        <v>743.94</v>
+        <v>726.53</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2991,33 +2991,33 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L58" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B59">
-        <v>981</v>
+        <v>90</v>
       </c>
       <c r="C59">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>1158.01</v>
+        <v>1016.84</v>
       </c>
       <c r="F59">
-        <v>745.67</v>
+        <v>711.42</v>
       </c>
       <c r="G59">
-        <v>726.64</v>
+        <v>743.94</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3029,10 +3029,10 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,22 +3040,22 @@
         <v>89</v>
       </c>
       <c r="B60">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C60">
-        <v>8.7</v>
+        <v>8.89</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>906.46</v>
+        <v>902.54</v>
       </c>
       <c r="F60">
         <v>657.32</v>
       </c>
       <c r="G60">
-        <v>666.55</v>
+        <v>665.4</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3078,22 +3078,22 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C61">
-        <v>8.7</v>
+        <v>8.62</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>964.01</v>
+        <v>931.72</v>
       </c>
       <c r="F61">
-        <v>657.44</v>
+        <v>657.32</v>
       </c>
       <c r="G61">
-        <v>634.37</v>
+        <v>642.44</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3116,22 +3116,22 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="C62">
-        <v>8.64</v>
+        <v>8.61</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>954.55</v>
+        <v>955.36</v>
       </c>
       <c r="F62">
-        <v>660.78</v>
+        <v>645.9</v>
       </c>
       <c r="G62">
-        <v>644.75</v>
+        <v>647.63</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3154,7 +3154,7 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C63">
         <v>8.33</v>
@@ -3163,13 +3163,13 @@
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>922.26</v>
+        <v>930.91</v>
       </c>
       <c r="F63">
-        <v>630.68</v>
+        <v>629.53</v>
       </c>
       <c r="G63">
-        <v>611.3</v>
+        <v>619.03</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3201,7 +3201,7 @@
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>927.79</v>
+        <v>930.1</v>
       </c>
       <c r="F64">
         <v>607.84</v>
@@ -3239,7 +3239,7 @@
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>889.96</v>
+        <v>934.83</v>
       </c>
       <c r="F65">
         <v>678.2</v>
@@ -3277,10 +3277,10 @@
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>852.13</v>
+        <v>893.08</v>
       </c>
       <c r="F66">
-        <v>657.44</v>
+        <v>622.84</v>
       </c>
       <c r="G66">
         <v>628.6</v>
@@ -3306,7 +3306,7 @@
         <v>96</v>
       </c>
       <c r="B67">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C67">
         <v>8.06</v>
@@ -3315,7 +3315,7 @@
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>827.68</v>
+        <v>845.79</v>
       </c>
       <c r="F67">
         <v>588.12</v>
@@ -3344,22 +3344,22 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>994</v>
+        <v>989.27</v>
       </c>
       <c r="F68">
-        <v>576.7</v>
+        <v>597.35</v>
       </c>
       <c r="G68">
-        <v>587.08</v>
+        <v>588.23</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3382,22 +3382,22 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C69">
-        <v>7.89</v>
+        <v>7.85</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>900.23</v>
+        <v>899.42</v>
       </c>
       <c r="F69">
-        <v>606.11</v>
+        <v>608.42</v>
       </c>
       <c r="G69">
-        <v>593.89</v>
+        <v>576.7</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3420,22 +3420,22 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="C70">
-        <v>7.87</v>
+        <v>7.81</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>866.32</v>
+        <v>935.64</v>
       </c>
       <c r="F70">
-        <v>599.65</v>
+        <v>576.58</v>
       </c>
       <c r="G70">
-        <v>584.66</v>
+        <v>594.46</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3458,22 +3458,22 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="C71">
-        <v>7.85</v>
+        <v>7.77</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>892.27</v>
+        <v>891.58</v>
       </c>
       <c r="F71">
-        <v>587.08</v>
+        <v>598.61</v>
       </c>
       <c r="G71">
-        <v>576.93</v>
+        <v>585.93</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3496,10 +3496,10 @@
         <v>101</v>
       </c>
       <c r="B72">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C72">
-        <v>7.62</v>
+        <v>7.54</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
@@ -3534,22 +3534,22 @@
         <v>102</v>
       </c>
       <c r="B73">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="C73">
-        <v>7.39</v>
+        <v>7.32</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>907.26</v>
+        <v>910.49</v>
       </c>
       <c r="F73">
-        <v>552.48</v>
+        <v>570.93</v>
       </c>
       <c r="G73">
-        <v>538.52</v>
+        <v>540.71</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3575,7 +3575,7 @@
         <v>207</v>
       </c>
       <c r="C74">
-        <v>7.12</v>
+        <v>7.05</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
@@ -3584,10 +3584,10 @@
         <v>755.13</v>
       </c>
       <c r="F74">
-        <v>516.72</v>
+        <v>583.39</v>
       </c>
       <c r="G74">
-        <v>551.33</v>
+        <v>577.85</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3619,10 +3619,10 @@
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>840.25</v>
+        <v>838.75</v>
       </c>
       <c r="F75">
-        <v>516.49</v>
+        <v>516.38</v>
       </c>
       <c r="G75">
         <v>515.34</v>
@@ -3648,7 +3648,7 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C76">
         <v>6.82</v>
@@ -3660,7 +3660,7 @@
         <v>770.13</v>
       </c>
       <c r="F76">
-        <v>489.39</v>
+        <v>487.08</v>
       </c>
       <c r="G76">
         <v>479.81</v>
@@ -3686,22 +3686,22 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="C77">
-        <v>6.78</v>
+        <v>6.81</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>770.13</v>
+        <v>811.88</v>
       </c>
       <c r="F77">
-        <v>519.38</v>
+        <v>507.5</v>
       </c>
       <c r="G77">
-        <v>519.03</v>
+        <v>517.88</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3762,22 +3762,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>948</v>
+        <v>77</v>
       </c>
       <c r="C79">
-        <v>6.48</v>
+        <v>6.44</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>730.68</v>
+        <v>752.82</v>
       </c>
       <c r="F79">
-        <v>483.27</v>
+        <v>475.32</v>
       </c>
       <c r="G79">
-        <v>473.93</v>
+        <v>573.47</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3789,10 +3789,10 @@
         <f>IF(D79=0,"",(H79-D79)/D79)</f>
       </c>
       <c r="K79" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L79" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3800,22 +3800,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>1201</v>
+        <v>956</v>
       </c>
       <c r="C80">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>768.51</v>
+        <v>750.4</v>
       </c>
       <c r="F80">
-        <v>477.62</v>
+        <v>483.27</v>
       </c>
       <c r="G80">
-        <v>478.66</v>
+        <v>473.93</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3838,22 +3838,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>77</v>
+        <v>1202</v>
       </c>
       <c r="C81">
-        <v>6.44</v>
+        <v>6.34</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>752.82</v>
+        <v>788.23</v>
       </c>
       <c r="F81">
-        <v>475.32</v>
+        <v>477.62</v>
       </c>
       <c r="G81">
-        <v>573.47</v>
+        <v>478.43</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3865,10 +3865,10 @@
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
       <c r="K81" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L81" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3876,7 +3876,7 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C82">
         <v>6.22</v>
@@ -3885,13 +3885,13 @@
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>656.63</v>
+        <v>682.58</v>
       </c>
       <c r="F82">
         <v>474.85</v>
       </c>
       <c r="G82">
-        <v>505.19</v>
+        <v>503.46</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3903,7 +3903,7 @@
         <f>IF(D82=0,"",(H82-D82)/D82)</f>
       </c>
       <c r="K82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L82" t="s">
         <v>21</v>
@@ -3926,10 +3926,10 @@
         <v>681.89</v>
       </c>
       <c r="F83">
-        <v>462.4</v>
+        <v>461.94</v>
       </c>
       <c r="G83">
-        <v>454.32</v>
+        <v>453.75</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3952,22 +3952,22 @@
         <v>114</v>
       </c>
       <c r="B84">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C84">
-        <v>5.91</v>
+        <v>6.03</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>556.52</v>
+        <v>467.36</v>
       </c>
       <c r="F84">
-        <v>419.61</v>
+        <v>334.49</v>
       </c>
       <c r="G84">
-        <v>391</v>
+        <v>336.79</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3982,7 +3982,7 @@
         <v>65</v>
       </c>
       <c r="L84" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3990,22 +3990,22 @@
         <v>115</v>
       </c>
       <c r="B85">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C85">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>698.38</v>
+        <v>556.52</v>
       </c>
       <c r="F85">
-        <v>449.83</v>
+        <v>419.03</v>
       </c>
       <c r="G85">
-        <v>432.87</v>
+        <v>391</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4020,7 +4020,7 @@
         <v>65</v>
       </c>
       <c r="L85" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4028,22 +4028,22 @@
         <v>116</v>
       </c>
       <c r="B86">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C86">
-        <v>5.75</v>
+        <v>5.79</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>685</v>
+        <v>698.38</v>
       </c>
       <c r="F86">
-        <v>428.83</v>
+        <v>449.6</v>
       </c>
       <c r="G86">
-        <v>448.67</v>
+        <v>432.87</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4066,22 +4066,22 @@
         <v>117</v>
       </c>
       <c r="B87">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="C87">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>602.19</v>
+        <v>690.54</v>
       </c>
       <c r="F87">
-        <v>511.53</v>
+        <v>429.06</v>
       </c>
       <c r="G87">
-        <v>444.06</v>
+        <v>448.44</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4104,22 +4104,22 @@
         <v>118</v>
       </c>
       <c r="B88">
-        <v>226</v>
+        <v>125</v>
       </c>
       <c r="C88">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>634.49</v>
+        <v>602.19</v>
       </c>
       <c r="F88">
-        <v>507.38</v>
+        <v>510.96</v>
       </c>
       <c r="G88">
-        <v>481.89</v>
+        <v>444.06</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4134,7 +4134,7 @@
         <v>65</v>
       </c>
       <c r="L88" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4142,22 +4142,22 @@
         <v>119</v>
       </c>
       <c r="B89">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="C89">
-        <v>5.51</v>
+        <v>5.53</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>588.81</v>
+        <v>634.49</v>
       </c>
       <c r="F89">
-        <v>409.46</v>
+        <v>507.38</v>
       </c>
       <c r="G89">
-        <v>427.8</v>
+        <v>481.89</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4169,10 +4169,10 @@
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
       <c r="K89" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L89" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4180,22 +4180,22 @@
         <v>120</v>
       </c>
       <c r="B90">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="C90">
-        <v>5.45</v>
+        <v>5.51</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>619.61</v>
+        <v>591.23</v>
       </c>
       <c r="F90">
-        <v>452.13</v>
+        <v>415.22</v>
       </c>
       <c r="G90">
-        <v>406</v>
+        <v>427.91</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4207,10 +4207,10 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L90" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4218,22 +4218,22 @@
         <v>121</v>
       </c>
       <c r="B91">
-        <v>511</v>
+        <v>174</v>
       </c>
       <c r="C91">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>568.28</v>
+        <v>619.61</v>
       </c>
       <c r="F91">
-        <v>396.77</v>
+        <v>455.59</v>
       </c>
       <c r="G91">
-        <v>385.24</v>
+        <v>406</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4248,7 +4248,7 @@
         <v>65</v>
       </c>
       <c r="L91" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4256,22 +4256,22 @@
         <v>122</v>
       </c>
       <c r="B92">
-        <v>122</v>
+        <v>509</v>
       </c>
       <c r="C92">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>600.69</v>
+        <v>576.24</v>
       </c>
       <c r="F92">
-        <v>445.21</v>
+        <v>397.92</v>
       </c>
       <c r="G92">
-        <v>402.54</v>
+        <v>385.24</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4294,22 +4294,22 @@
         <v>123</v>
       </c>
       <c r="B93">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C93">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>622.72</v>
+        <v>587.2</v>
       </c>
       <c r="F93">
-        <v>422.03</v>
+        <v>414.07</v>
       </c>
       <c r="G93">
-        <v>424.45</v>
+        <v>423.3</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4332,22 +4332,22 @@
         <v>124</v>
       </c>
       <c r="B94">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="C94">
-        <v>5.25</v>
+        <v>5.36</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>580.16</v>
+        <v>600.69</v>
       </c>
       <c r="F94">
-        <v>403.57</v>
+        <v>445.21</v>
       </c>
       <c r="G94">
-        <v>413.84</v>
+        <v>402.54</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4359,10 +4359,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L94" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4370,22 +4370,22 @@
         <v>125</v>
       </c>
       <c r="B95">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C95">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>567.47</v>
+        <v>580.16</v>
       </c>
       <c r="F95">
-        <v>412.23</v>
+        <v>402.42</v>
       </c>
       <c r="G95">
-        <v>388.7</v>
+        <v>413.72</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4397,33 +4397,33 @@
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
       <c r="K95" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L95" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B96">
-        <v>504</v>
+        <v>65</v>
       </c>
       <c r="C96">
-        <v>5.01</v>
+        <v>5.2</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>547.06</v>
+        <v>567.47</v>
       </c>
       <c r="F96">
-        <v>363.32</v>
+        <v>412.23</v>
       </c>
       <c r="G96">
-        <v>391.93</v>
+        <v>388.7</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4435,10 +4435,10 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L96" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4446,22 +4446,22 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>73</v>
+        <v>507</v>
       </c>
       <c r="C97">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>580.16</v>
+        <v>541.52</v>
       </c>
       <c r="F97">
-        <v>384.2</v>
+        <v>363.32</v>
       </c>
       <c r="G97">
-        <v>370.24</v>
+        <v>390.77</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4473,10 +4473,10 @@
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
       <c r="K97" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L97" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4484,22 +4484,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="C98">
-        <v>4.83</v>
+        <v>4.91</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>565.97</v>
+        <v>580.16</v>
       </c>
       <c r="F98">
-        <v>343.6</v>
+        <v>381.89</v>
       </c>
       <c r="G98">
-        <v>322.95</v>
+        <v>374.86</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4531,10 +4531,10 @@
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>584.89</v>
+        <v>619.61</v>
       </c>
       <c r="F99">
-        <v>410.96</v>
+        <v>410.84</v>
       </c>
       <c r="G99">
         <v>379.47</v>
@@ -4560,22 +4560,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>625</v>
+        <v>159</v>
       </c>
       <c r="C100">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>509.23</v>
+        <v>565.97</v>
       </c>
       <c r="F100">
-        <v>360.21</v>
+        <v>334.49</v>
       </c>
       <c r="G100">
-        <v>356.4</v>
+        <v>322.95</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4587,10 +4587,10 @@
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
       <c r="K100" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L100" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4598,22 +4598,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>79</v>
+        <v>626</v>
       </c>
       <c r="C101">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>599.08</v>
+        <v>509.23</v>
       </c>
       <c r="F101">
-        <v>372.43</v>
+        <v>357.9</v>
       </c>
       <c r="G101">
-        <v>380.62</v>
+        <v>357.55</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4625,10 +4625,10 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L101" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4636,22 +4636,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C102">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>535.18</v>
+        <v>528.14</v>
       </c>
       <c r="F102">
         <v>333.33</v>
       </c>
       <c r="G102">
-        <v>373.36</v>
+        <v>373.47</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4674,22 +4674,22 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C103">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>468.17</v>
+        <v>599.08</v>
       </c>
       <c r="F103">
-        <v>334.49</v>
+        <v>372.43</v>
       </c>
       <c r="G103">
-        <v>333.1</v>
+        <v>380.62</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4704,7 +4704,7 @@
         <v>65</v>
       </c>
       <c r="L103" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4712,10 +4712,10 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C104">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
@@ -4759,7 +4759,7 @@
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>485.58</v>
+        <v>487.08</v>
       </c>
       <c r="F105">
         <v>321.57</v>
@@ -4803,7 +4803,7 @@
         <v>339.21</v>
       </c>
       <c r="G106">
-        <v>329.87</v>
+        <v>332.18</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4829,7 +4829,7 @@
         <v>42</v>
       </c>
       <c r="C107">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
@@ -4867,7 +4867,7 @@
         <v>101</v>
       </c>
       <c r="C108">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
@@ -4905,7 +4905,7 @@
         <v>55</v>
       </c>
       <c r="C109">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
@@ -4940,7 +4940,7 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>2436</v>
+        <v>2432</v>
       </c>
       <c r="C110">
         <v>4.14</v>
@@ -4949,10 +4949,10 @@
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>474.51</v>
+        <v>485.58</v>
       </c>
       <c r="F110">
-        <v>339.1</v>
+        <v>328.72</v>
       </c>
       <c r="G110">
         <v>325.72</v>
@@ -4978,16 +4978,16 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C111">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>421.68</v>
+        <v>420.88</v>
       </c>
       <c r="F111">
         <v>312.46</v>
@@ -5016,22 +5016,22 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C112">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>431.95</v>
+        <v>431.14</v>
       </c>
       <c r="F112">
         <v>310.96</v>
       </c>
       <c r="G112">
-        <v>290.66</v>
+        <v>288.35</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5063,7 +5063,7 @@
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>383.04</v>
+        <v>394.12</v>
       </c>
       <c r="F113">
         <v>295.27</v>
@@ -5092,19 +5092,19 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C114">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>405.19</v>
+        <v>393.31</v>
       </c>
       <c r="F114">
-        <v>291.46</v>
+        <v>288.35</v>
       </c>
       <c r="G114">
         <v>286.97</v>
@@ -5130,10 +5130,10 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C115">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
@@ -5142,7 +5142,7 @@
         <v>486.39</v>
       </c>
       <c r="F115">
-        <v>270.13</v>
+        <v>270.01</v>
       </c>
       <c r="G115">
         <v>288.58</v>
@@ -5171,19 +5171,19 @@
         <v>128</v>
       </c>
       <c r="C116">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>378.32</v>
+        <v>394.12</v>
       </c>
       <c r="F116">
         <v>286.97</v>
       </c>
       <c r="G116">
-        <v>274.51</v>
+        <v>275.66</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5209,13 +5209,13 @@
         <v>48</v>
       </c>
       <c r="C117">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>500.58</v>
+        <v>464.24</v>
       </c>
       <c r="F117">
         <v>262.63</v>
@@ -5233,7 +5233,7 @@
         <f>IF(D117=0,"",(H117-D117)/D117)</f>
       </c>
       <c r="K117" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L117" t="s">
         <v>21</v>
@@ -5244,22 +5244,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C118">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>365.74</v>
+        <v>369.66</v>
       </c>
       <c r="F118">
         <v>251.21</v>
       </c>
       <c r="G118">
-        <v>260.44</v>
+        <v>259.28</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5320,10 +5320,10 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C120">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
@@ -5335,7 +5335,7 @@
         <v>236.33</v>
       </c>
       <c r="G120">
-        <v>236.45</v>
+        <v>236.1</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5358,7 +5358,7 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C121">
         <v>3.2</v>
@@ -5367,7 +5367,7 @@
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>350.75</v>
+        <v>349.94</v>
       </c>
       <c r="F121">
         <v>253.75</v>
@@ -5396,7 +5396,7 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C122">
         <v>3.18</v>
@@ -5405,10 +5405,10 @@
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>360.21</v>
+        <v>376.7</v>
       </c>
       <c r="F122">
-        <v>249.13</v>
+        <v>250.29</v>
       </c>
       <c r="G122">
         <v>244.29</v>
@@ -5434,22 +5434,22 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="C123">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>297.12</v>
+        <v>326.3</v>
       </c>
       <c r="F123">
-        <v>226.64</v>
+        <v>214.3</v>
       </c>
       <c r="G123">
-        <v>222.61</v>
+        <v>208.77</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5464,7 +5464,7 @@
         <v>23</v>
       </c>
       <c r="L123" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5472,22 +5472,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="C124">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>326.3</v>
+        <v>297.12</v>
       </c>
       <c r="F124">
-        <v>214.3</v>
+        <v>219.15</v>
       </c>
       <c r="G124">
-        <v>208.77</v>
+        <v>222.61</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5502,7 +5502,7 @@
         <v>23</v>
       </c>
       <c r="L124" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5510,16 +5510,16 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C125">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>334.95</v>
+        <v>315.22</v>
       </c>
       <c r="F125">
         <v>218.11</v>
@@ -5548,10 +5548,10 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C126">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
@@ -5560,10 +5560,10 @@
         <v>367.24</v>
       </c>
       <c r="F126">
-        <v>190.77</v>
+        <v>191.93</v>
       </c>
       <c r="G126">
-        <v>191.58</v>
+        <v>192.39</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5575,7 +5575,7 @@
         <f>IF(D126=0,"",(H126-D126)/D126)</f>
       </c>
       <c r="K126" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L126" t="s">
         <v>21</v>
@@ -5586,7 +5586,7 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C127">
         <v>2.26</v>
@@ -5601,7 +5601,7 @@
         <v>177.62</v>
       </c>
       <c r="G127">
-        <v>184.54</v>
+        <v>183.39</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5624,22 +5624,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="C128">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>260.09</v>
+        <v>230.91</v>
       </c>
       <c r="F128">
+        <v>174.62</v>
+      </c>
+      <c r="G128">
         <v>174.16</v>
-      </c>
-      <c r="G128">
-        <v>171.63</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5651,10 +5651,10 @@
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
       <c r="K128" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L128" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5662,22 +5662,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="C129">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>249.83</v>
+        <v>283.74</v>
       </c>
       <c r="F129">
-        <v>183.39</v>
+        <v>173.01</v>
       </c>
       <c r="G129">
-        <v>188</v>
+        <v>169.43</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5689,10 +5689,10 @@
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
       <c r="K129" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L129" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5700,22 +5700,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C130">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>230.91</v>
+        <v>249.83</v>
       </c>
       <c r="F130">
-        <v>175.09</v>
+        <v>183.39</v>
       </c>
       <c r="G130">
-        <v>174.16</v>
+        <v>188</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5750,7 +5750,7 @@
         <v>211.99</v>
       </c>
       <c r="F131">
-        <v>144.98</v>
+        <v>146.14</v>
       </c>
       <c r="G131">
         <v>152.25</v>
@@ -5776,10 +5776,10 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C132">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
@@ -5814,10 +5814,10 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C133">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
@@ -5829,7 +5829,7 @@
         <v>125.72</v>
       </c>
       <c r="G133">
-        <v>140.14</v>
+        <v>139.56</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5855,7 +5855,7 @@
         <v>298</v>
       </c>
       <c r="C134">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
@@ -5864,10 +5864,10 @@
         <v>163.09</v>
       </c>
       <c r="F134">
-        <v>117.65</v>
+        <v>120.99</v>
       </c>
       <c r="G134">
-        <v>123.88</v>
+        <v>122.61</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5890,10 +5890,10 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C135">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
@@ -5905,7 +5905,7 @@
         <v>115.92</v>
       </c>
       <c r="G135">
-        <v>124.45</v>
+        <v>123.3</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5931,7 +5931,7 @@
         <v>1028</v>
       </c>
       <c r="C136">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="D136">
         <f>C136*$B$3</f>
@@ -5940,7 +5940,7 @@
         <v>155.25</v>
       </c>
       <c r="F136">
-        <v>106.46</v>
+        <v>107.04</v>
       </c>
       <c r="G136">
         <v>104.5</v>
@@ -5966,7 +5966,7 @@
         <v>168</v>
       </c>
       <c r="B137">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="C137">
         <v>1.01</v>
@@ -5978,10 +5978,10 @@
         <v>121.34</v>
       </c>
       <c r="F137">
-        <v>74.97</v>
+        <v>74.86</v>
       </c>
       <c r="G137">
-        <v>80.62</v>
+        <v>80.51</v>
       </c>
       <c r="H137">
         <f>MIN(E137:G137)</f>
@@ -6004,7 +6004,7 @@
         <v>169</v>
       </c>
       <c r="B138">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="C138">
         <v>0.85</v>
@@ -6013,10 +6013,10 @@
         <f>C138*$B$3</f>
       </c>
       <c r="E138">
-        <v>88.24</v>
+        <v>91.35</v>
       </c>
       <c r="F138">
-        <v>66.09</v>
+        <v>65.97</v>
       </c>
       <c r="G138">
         <v>64.36</v>
@@ -6042,10 +6042,10 @@
         <v>170</v>
       </c>
       <c r="B139">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C139">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="D139">
         <f>C139*$B$3</f>
@@ -6057,7 +6057,7 @@
         <v>50.17</v>
       </c>
       <c r="G139">
-        <v>50.29</v>
+        <v>50.52</v>
       </c>
       <c r="H139">
         <f>MIN(E139:G139)</f>
@@ -6072,7 +6072,7 @@
         <v>26</v>
       </c>
       <c r="L139" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -6080,7 +6080,7 @@
         <v>171</v>
       </c>
       <c r="B140">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C140">
         <v>0.48</v>
@@ -6089,7 +6089,7 @@
         <f>C140*$B$3</f>
       </c>
       <c r="E140">
-        <v>60.67</v>
+        <v>59.86</v>
       </c>
       <c r="F140">
         <v>34.26</v>
@@ -6107,7 +6107,7 @@
         <f>IF(D140=0,"",(H140-D140)/D140)</f>
       </c>
       <c r="K140" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L140" t="s">
         <v>19</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 18.07.2026 22:48</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 19.07.2026 01:17</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -214,15 +214,15 @@
     <t>Remarkable</t>
   </si>
   <si>
+    <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
+  </si>
+  <si>
     <t>'The Doctor' Romanov | Sabre</t>
   </si>
   <si>
     <t>Master</t>
   </si>
   <si>
-    <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Michael Syfers  | FBI Sniper</t>
   </si>
   <si>
@@ -247,24 +247,24 @@
     <t>The Elite Mr. Muhlik | Elite Crew</t>
   </si>
   <si>
+    <t>USP-S | Guardian (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Five-SeveN | Kami (Factory New)</t>
   </si>
   <si>
-    <t>USP-S | Guardian (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>FAMAS | Styx (Field-Tested)</t>
   </si>
   <si>
+    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Minimal Wear)</t>
   </si>
   <si>
-    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
-  </si>
-  <si>
     <t>Osiris | Elite Crew</t>
   </si>
   <si>
@@ -289,18 +289,18 @@
     <t>MP7 | Fade (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | Great Wave (Holo)</t>
+  </si>
+  <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>MP7 | Fade (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | Great Wave (Holo)</t>
-  </si>
-  <si>
     <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>SG 553 | Integrale (Field-Tested)</t>
   </si>
   <si>
@@ -331,12 +331,12 @@
     <t>High Grade</t>
   </si>
   <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
+  </si>
+  <si>
     <t>AK-47 | Crossfade (Factory New)</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -367,6 +367,9 @@
     <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
     <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -376,18 +379,15 @@
     <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
     <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
@@ -406,21 +406,21 @@
     <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>R8 Revolver | Blaze (Factory New)</t>
+  </si>
+  <si>
+    <t>P250 | Epicenter (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | Stone Scales (Foil)</t>
+  </si>
+  <si>
+    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
-    <t>R8 Revolver | Blaze (Factory New)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Stone Scales (Foil)</t>
-  </si>
-  <si>
-    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -433,12 +433,12 @@
     <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>AK-47 | Slate (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Field-Tested)</t>
-  </si>
-  <si>
     <t>Sticker | Team Liquid (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -463,40 +463,40 @@
     <t>Five-SeveN | Kami (Minimal Wear)</t>
   </si>
   <si>
+    <t>Five-SeveN | Retrobution (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>P2000 | Amber Fade (Factory New)</t>
   </si>
   <si>
-    <t>Five-SeveN | Retrobution (Minimal Wear)</t>
-  </si>
-  <si>
     <t>AK-47 | Crossfade (Minimal Wear)</t>
   </si>
   <si>
     <t>CZ75-Auto | Tuxedo (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
   </si>
   <si>
+    <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
+    <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | Ancient Beast (Foil)</t>
@@ -933,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>82.22</v>
+        <v>81.9</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -988,10 +988,10 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6">
-        <v>165.26</v>
+        <v>165.31</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
@@ -1003,7 +1003,7 @@
         <v>12053.03</v>
       </c>
       <c r="G6">
-        <v>11982.79</v>
+        <v>12099.17</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -1026,7 +1026,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>136.65</v>
@@ -1064,7 +1064,7 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C8">
         <v>118.65</v>
@@ -1079,7 +1079,7 @@
         <v>8869.65</v>
       </c>
       <c r="G8">
-        <v>8708.17</v>
+        <v>8783.14</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1102,7 +1102,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C9">
         <v>96.16</v>
@@ -1117,7 +1117,7 @@
         <v>7538.62</v>
       </c>
       <c r="G9">
-        <v>7581.07</v>
+        <v>7681.64</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1178,10 +1178,10 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11">
-        <v>84.37</v>
+        <v>85.47</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
@@ -1193,7 +1193,7 @@
         <v>6574.38</v>
       </c>
       <c r="G11">
-        <v>6574.38</v>
+        <v>6562.85</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1292,10 +1292,10 @@
         <v>33</v>
       </c>
       <c r="B14">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C14">
-        <v>60.18</v>
+        <v>61.34</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
@@ -1368,16 +1368,16 @@
         <v>35</v>
       </c>
       <c r="B16">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C16">
-        <v>57.67</v>
+        <v>58.18</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>6148.78</v>
+        <v>6351.43</v>
       </c>
       <c r="F16">
         <v>4371.39</v>
@@ -1406,10 +1406,10 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C17">
-        <v>57.18</v>
+        <v>57.14</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
@@ -1444,10 +1444,10 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="C18">
-        <v>56</v>
+        <v>56.9</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1456,7 +1456,7 @@
         <v>6345.89</v>
       </c>
       <c r="F18">
-        <v>4232.98</v>
+        <v>4241.05</v>
       </c>
       <c r="G18">
         <v>4150.86</v>
@@ -1482,19 +1482,19 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C19">
-        <v>54.34</v>
+        <v>53.57</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5797.22</v>
+        <v>5686.84</v>
       </c>
       <c r="F19">
-        <v>3979.23</v>
+        <v>4036.9</v>
       </c>
       <c r="G19">
         <v>3990.76</v>
@@ -1520,10 +1520,10 @@
         <v>39</v>
       </c>
       <c r="B20">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20">
-        <v>52.69</v>
+        <v>51.97</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
@@ -1532,7 +1532,7 @@
         <v>6024.21</v>
       </c>
       <c r="F20">
-        <v>4016.14</v>
+        <v>4015.91</v>
       </c>
       <c r="G20">
         <v>3965.39</v>
@@ -1558,7 +1558,7 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <v>49.97</v>
@@ -1573,7 +1573,7 @@
         <v>3610.03</v>
       </c>
       <c r="G21">
-        <v>3604.38</v>
+        <v>3610.14</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1599,7 +1599,7 @@
         <v>59</v>
       </c>
       <c r="C22">
-        <v>49.48</v>
+        <v>49.86</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
@@ -1634,7 +1634,7 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C23">
         <v>48.53</v>
@@ -1649,7 +1649,7 @@
         <v>3679.35</v>
       </c>
       <c r="G23">
-        <v>3540.94</v>
+        <v>3552.47</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1672,10 +1672,10 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24">
-        <v>48.08</v>
+        <v>47.75</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
@@ -1687,7 +1687,7 @@
         <v>3460.2</v>
       </c>
       <c r="G24">
-        <v>3569.77</v>
+        <v>3569.66</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1710,10 +1710,10 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25">
-        <v>37.57</v>
+        <v>37.54</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
@@ -1725,7 +1725,7 @@
         <v>2835.98</v>
       </c>
       <c r="G25">
-        <v>2755.47</v>
+        <v>2807.38</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1763,7 +1763,7 @@
         <v>2652.82</v>
       </c>
       <c r="G26">
-        <v>2929.17</v>
+        <v>2923.41</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1786,7 +1786,7 @@
         <v>46</v>
       </c>
       <c r="B27">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>34.67</v>
@@ -1827,19 +1827,19 @@
         <v>266</v>
       </c>
       <c r="C28">
-        <v>32.66</v>
+        <v>32.56</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>3686.15</v>
+        <v>3705.07</v>
       </c>
       <c r="F28">
-        <v>2468.28</v>
+        <v>2462.51</v>
       </c>
       <c r="G28">
-        <v>2403.69</v>
+        <v>2450.98</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1862,16 +1862,16 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C29">
-        <v>31.49</v>
+        <v>31.73</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>3511.87</v>
+        <v>3507.95</v>
       </c>
       <c r="F29">
         <v>2520.06</v>
@@ -1900,7 +1900,7 @@
         <v>49</v>
       </c>
       <c r="B30">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C30">
         <v>29.27</v>
@@ -1912,10 +1912,10 @@
         <v>3123.29</v>
       </c>
       <c r="F30">
-        <v>2241.52</v>
+        <v>2241.4</v>
       </c>
       <c r="G30">
-        <v>2208.76</v>
+        <v>2204.15</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1947,7 +1947,7 @@
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2811.07</v>
+        <v>2617.99</v>
       </c>
       <c r="F31">
         <v>1894.69</v>
@@ -1976,16 +1976,16 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C32">
-        <v>23.88</v>
+        <v>24.11</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2708.64</v>
+        <v>2897.8</v>
       </c>
       <c r="F32">
         <v>1914.64</v>
@@ -2014,7 +2014,7 @@
         <v>54</v>
       </c>
       <c r="B33">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C33">
         <v>20.65</v>
@@ -2052,7 +2052,7 @@
         <v>55</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34">
         <v>19.8</v>
@@ -2090,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="B35">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C35">
         <v>19.51</v>
@@ -2099,7 +2099,7 @@
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>2364.12</v>
+        <v>2388.58</v>
       </c>
       <c r="F35">
         <v>1480.85</v>
@@ -2166,19 +2166,19 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="C37">
-        <v>18.92</v>
+        <v>18.94</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2107.15</v>
+        <v>2286.04</v>
       </c>
       <c r="F37">
-        <v>1491.35</v>
+        <v>1493.65</v>
       </c>
       <c r="G37">
         <v>1464.59</v>
@@ -2204,7 +2204,7 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38">
         <v>18.84</v>
@@ -2213,7 +2213,7 @@
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>2170.12</v>
+        <v>2049.59</v>
       </c>
       <c r="F38">
         <v>1444.75</v>
@@ -2245,7 +2245,7 @@
         <v>74</v>
       </c>
       <c r="C39">
-        <v>15.92</v>
+        <v>15.99</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
@@ -2254,10 +2254,10 @@
         <v>1967.59</v>
       </c>
       <c r="F39">
-        <v>1243.37</v>
+        <v>1244.52</v>
       </c>
       <c r="G39">
-        <v>1215.57</v>
+        <v>1251.44</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2289,7 +2289,7 @@
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1754.78</v>
+        <v>1800.46</v>
       </c>
       <c r="F40">
         <v>1187.89</v>
@@ -2394,22 +2394,22 @@
         <v>67</v>
       </c>
       <c r="B43">
-        <v>1765</v>
+        <v>61</v>
       </c>
       <c r="C43">
-        <v>13.38</v>
+        <v>13.42</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1418.91</v>
+        <v>1450.4</v>
       </c>
       <c r="F43">
-        <v>1038.06</v>
+        <v>975.78</v>
       </c>
       <c r="G43">
-        <v>1037.94</v>
+        <v>1035.75</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2421,33 +2421,33 @@
         <f>IF(D43=0,"",(H43-D43)/D43)</f>
       </c>
       <c r="K43" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L43" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44">
-        <v>61</v>
+        <v>1757</v>
       </c>
       <c r="C44">
-        <v>13.26</v>
+        <v>13.39</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1450.4</v>
+        <v>1496.19</v>
       </c>
       <c r="F44">
-        <v>975.78</v>
+        <v>1038.06</v>
       </c>
       <c r="G44">
-        <v>1035.75</v>
+        <v>1036.68</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2459,10 +2459,10 @@
         <f>IF(D44=0,"",(H44-D44)/D44)</f>
       </c>
       <c r="K44" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2470,7 +2470,7 @@
         <v>70</v>
       </c>
       <c r="B45">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="C45">
         <v>13.01</v>
@@ -2479,7 +2479,7 @@
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1565.51</v>
+        <v>1519.84</v>
       </c>
       <c r="F45">
         <v>1003.46</v>
@@ -2546,7 +2546,7 @@
         <v>73</v>
       </c>
       <c r="B47">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C47">
         <v>12.27</v>
@@ -2555,13 +2555,13 @@
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1396.88</v>
+        <v>1384.2</v>
       </c>
       <c r="F47">
         <v>938.87</v>
       </c>
       <c r="G47">
-        <v>940.02</v>
+        <v>939.91</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2593,7 +2593,7 @@
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1321.1</v>
+        <v>1330.56</v>
       </c>
       <c r="F48">
         <v>978.78</v>
@@ -2660,7 +2660,7 @@
         <v>77</v>
       </c>
       <c r="B50">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="C50">
         <v>11.06</v>
@@ -2669,10 +2669,10 @@
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1303</v>
+        <v>1260.44</v>
       </c>
       <c r="F50">
-        <v>807.38</v>
+        <v>848.67</v>
       </c>
       <c r="G50">
         <v>841.52</v>
@@ -2690,7 +2690,7 @@
         <v>52</v>
       </c>
       <c r="L50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2698,22 +2698,22 @@
         <v>78</v>
       </c>
       <c r="B51">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C51">
-        <v>10.6</v>
+        <v>10.85</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1132.75</v>
+        <v>1080.74</v>
       </c>
       <c r="F51">
-        <v>757.55</v>
+        <v>779.12</v>
       </c>
       <c r="G51">
-        <v>749.71</v>
+        <v>793.54</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2728,7 +2728,7 @@
         <v>23</v>
       </c>
       <c r="L51" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2736,22 +2736,22 @@
         <v>79</v>
       </c>
       <c r="B52">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="C52">
-        <v>10.59</v>
+        <v>10.39</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1173.7</v>
+        <v>1182.47</v>
       </c>
       <c r="F52">
-        <v>779.01</v>
+        <v>782.01</v>
       </c>
       <c r="G52">
-        <v>795.85</v>
+        <v>749.71</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2763,10 +2763,10 @@
         <f>IF(D52=0,"",(H52-D52)/D52)</f>
       </c>
       <c r="K52" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L52" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2774,19 +2774,19 @@
         <v>80</v>
       </c>
       <c r="B53">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="C53">
-        <v>10.42</v>
+        <v>10.39</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1182.47</v>
+        <v>1080.74</v>
       </c>
       <c r="F53">
-        <v>782.01</v>
+        <v>757.55</v>
       </c>
       <c r="G53">
         <v>749.71</v>
@@ -2801,10 +2801,10 @@
         <f>IF(D53=0,"",(H53-D53)/D53)</f>
       </c>
       <c r="K53" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L53" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2812,10 +2812,10 @@
         <v>81</v>
       </c>
       <c r="B54">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C54">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
@@ -2850,22 +2850,22 @@
         <v>82</v>
       </c>
       <c r="B55">
-        <v>99</v>
+        <v>494</v>
       </c>
       <c r="C55">
-        <v>10.06</v>
+        <v>10.1</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1097.23</v>
+        <v>1129.64</v>
       </c>
       <c r="F55">
-        <v>748.56</v>
+        <v>725.49</v>
       </c>
       <c r="G55">
-        <v>761.24</v>
+        <v>714.99</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2880,7 +2880,7 @@
         <v>23</v>
       </c>
       <c r="L55" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2888,22 +2888,22 @@
         <v>83</v>
       </c>
       <c r="B56">
-        <v>496</v>
+        <v>102</v>
       </c>
       <c r="C56">
-        <v>9.86</v>
+        <v>10.06</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1113.03</v>
+        <v>1097.23</v>
       </c>
       <c r="F56">
-        <v>725.49</v>
+        <v>726.64</v>
       </c>
       <c r="G56">
-        <v>710.38</v>
+        <v>788.81</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2918,7 +2918,7 @@
         <v>23</v>
       </c>
       <c r="L56" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -2926,7 +2926,7 @@
         <v>84</v>
       </c>
       <c r="B57">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="C57">
         <v>9.76</v>
@@ -2935,10 +2935,10 @@
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1064.13</v>
+        <v>1076.81</v>
       </c>
       <c r="F57">
-        <v>784.08</v>
+        <v>737.02</v>
       </c>
       <c r="G57">
         <v>764.7</v>
@@ -2964,7 +2964,7 @@
         <v>86</v>
       </c>
       <c r="B58">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C58">
         <v>9.62</v>
@@ -2973,13 +2973,13 @@
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1080.74</v>
+        <v>1182.47</v>
       </c>
       <c r="F58">
-        <v>749.59</v>
+        <v>738.18</v>
       </c>
       <c r="G58">
-        <v>726.53</v>
+        <v>725.49</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -3002,7 +3002,7 @@
         <v>88</v>
       </c>
       <c r="B59">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C59">
         <v>9.57</v>
@@ -3049,7 +3049,7 @@
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>902.54</v>
+        <v>906.46</v>
       </c>
       <c r="F60">
         <v>657.32</v>
@@ -3078,22 +3078,22 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C61">
-        <v>8.62</v>
+        <v>8.65</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>931.72</v>
+        <v>1008.19</v>
       </c>
       <c r="F61">
-        <v>657.32</v>
+        <v>663.21</v>
       </c>
       <c r="G61">
-        <v>642.44</v>
+        <v>641.29</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3116,7 +3116,7 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C62">
         <v>8.61</v>
@@ -3125,10 +3125,10 @@
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>955.36</v>
+        <v>931.72</v>
       </c>
       <c r="F62">
-        <v>645.9</v>
+        <v>668.63</v>
       </c>
       <c r="G62">
         <v>647.63</v>
@@ -3154,22 +3154,22 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="C63">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>930.91</v>
+        <v>930.1</v>
       </c>
       <c r="F63">
-        <v>629.53</v>
+        <v>607.84</v>
       </c>
       <c r="G63">
-        <v>619.03</v>
+        <v>629.3</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3181,10 +3181,10 @@
         <f>IF(D63=0,"",(H63-D63)/D63)</f>
       </c>
       <c r="K63" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="L63" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3192,22 +3192,22 @@
         <v>93</v>
       </c>
       <c r="B64">
-        <v>25</v>
+        <v>268</v>
       </c>
       <c r="C64">
-        <v>8.25</v>
+        <v>8.22</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>930.1</v>
+        <v>893.08</v>
       </c>
       <c r="F64">
-        <v>607.84</v>
+        <v>622.84</v>
       </c>
       <c r="G64">
-        <v>629.3</v>
+        <v>628.6</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3230,22 +3230,22 @@
         <v>94</v>
       </c>
       <c r="B65">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="C65">
-        <v>8.25</v>
+        <v>8.18</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>934.83</v>
+        <v>930.91</v>
       </c>
       <c r="F65">
-        <v>678.2</v>
+        <v>631.37</v>
       </c>
       <c r="G65">
-        <v>630.91</v>
+        <v>619.03</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3257,10 +3257,10 @@
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
       <c r="K65" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="L65" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3268,22 +3268,22 @@
         <v>95</v>
       </c>
       <c r="B66">
-        <v>268</v>
+        <v>100</v>
       </c>
       <c r="C66">
-        <v>8.22</v>
+        <v>8.14</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>893.08</v>
+        <v>1008.99</v>
       </c>
       <c r="F66">
-        <v>622.84</v>
+        <v>678.2</v>
       </c>
       <c r="G66">
-        <v>628.6</v>
+        <v>630.91</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3298,7 +3298,7 @@
         <v>65</v>
       </c>
       <c r="L66" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3315,7 +3315,7 @@
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>845.79</v>
+        <v>892.27</v>
       </c>
       <c r="F67">
         <v>588.12</v>
@@ -3344,22 +3344,22 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C68">
-        <v>7.95</v>
+        <v>7.98</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>989.27</v>
+        <v>990.89</v>
       </c>
       <c r="F68">
-        <v>597.35</v>
+        <v>596.31</v>
       </c>
       <c r="G68">
-        <v>588.23</v>
+        <v>590.54</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3382,22 +3382,22 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C69">
-        <v>7.85</v>
+        <v>7.88</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>899.42</v>
+        <v>906.46</v>
       </c>
       <c r="F69">
-        <v>608.42</v>
+        <v>599.77</v>
       </c>
       <c r="G69">
-        <v>576.7</v>
+        <v>592.73</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3420,22 +3420,22 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>1433</v>
+        <v>1424</v>
       </c>
       <c r="C70">
-        <v>7.81</v>
+        <v>7.84</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>935.64</v>
+        <v>900.23</v>
       </c>
       <c r="F70">
-        <v>576.58</v>
+        <v>599.77</v>
       </c>
       <c r="G70">
-        <v>594.46</v>
+        <v>593.77</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3458,22 +3458,22 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="C71">
-        <v>7.77</v>
+        <v>7.81</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>891.58</v>
+        <v>929.41</v>
       </c>
       <c r="F71">
         <v>598.61</v>
       </c>
       <c r="G71">
-        <v>585.93</v>
+        <v>576.7</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3505,7 +3505,7 @@
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>848.21</v>
+        <v>847.4</v>
       </c>
       <c r="F72">
         <v>551.56</v>
@@ -3534,7 +3534,7 @@
         <v>102</v>
       </c>
       <c r="B73">
-        <v>1131</v>
+        <v>1121</v>
       </c>
       <c r="C73">
         <v>7.32</v>
@@ -3543,13 +3543,13 @@
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>910.49</v>
+        <v>922.26</v>
       </c>
       <c r="F73">
         <v>570.93</v>
       </c>
       <c r="G73">
-        <v>540.71</v>
+        <v>540.83</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3581,13 +3581,13 @@
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>755.13</v>
+        <v>748.79</v>
       </c>
       <c r="F74">
         <v>583.39</v>
       </c>
       <c r="G74">
-        <v>577.85</v>
+        <v>576.7</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3648,22 +3648,22 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>392</v>
+        <v>1337</v>
       </c>
       <c r="C76">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>770.13</v>
+        <v>765.4</v>
       </c>
       <c r="F76">
-        <v>487.08</v>
+        <v>507.5</v>
       </c>
       <c r="G76">
-        <v>479.81</v>
+        <v>517.88</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3678,7 +3678,7 @@
         <v>26</v>
       </c>
       <c r="L76" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3686,22 +3686,22 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>1343</v>
+        <v>397</v>
       </c>
       <c r="C77">
-        <v>6.81</v>
+        <v>6.83</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>811.88</v>
+        <v>748.79</v>
       </c>
       <c r="F77">
-        <v>507.5</v>
+        <v>490.54</v>
       </c>
       <c r="G77">
-        <v>517.88</v>
+        <v>479.81</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3716,7 +3716,7 @@
         <v>26</v>
       </c>
       <c r="L77" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3733,10 +3733,10 @@
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>900.23</v>
+        <v>802.42</v>
       </c>
       <c r="F78">
-        <v>529.99</v>
+        <v>530.33</v>
       </c>
       <c r="G78">
         <v>461.36</v>
@@ -3762,7 +3762,7 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C79">
         <v>6.44</v>
@@ -3771,7 +3771,7 @@
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>752.82</v>
+        <v>750.4</v>
       </c>
       <c r="F79">
         <v>475.32</v>
@@ -3800,7 +3800,7 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C80">
         <v>6.38</v>
@@ -3809,10 +3809,10 @@
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>750.4</v>
+        <v>749.59</v>
       </c>
       <c r="F80">
-        <v>483.27</v>
+        <v>482.7</v>
       </c>
       <c r="G80">
         <v>473.93</v>
@@ -3838,7 +3838,7 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C81">
         <v>6.34</v>
@@ -3847,13 +3847,13 @@
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>788.23</v>
+        <v>685.81</v>
       </c>
       <c r="F81">
-        <v>477.62</v>
+        <v>477.85</v>
       </c>
       <c r="G81">
-        <v>478.43</v>
+        <v>479.58</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3876,22 +3876,22 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C82">
-        <v>6.22</v>
+        <v>6.14</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>682.58</v>
+        <v>673.12</v>
       </c>
       <c r="F82">
         <v>474.85</v>
       </c>
       <c r="G82">
-        <v>503.46</v>
+        <v>502.77</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3914,10 +3914,10 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C83">
-        <v>6.05</v>
+        <v>6.11</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
@@ -3926,10 +3926,10 @@
         <v>681.89</v>
       </c>
       <c r="F83">
-        <v>461.94</v>
+        <v>461.59</v>
       </c>
       <c r="G83">
-        <v>453.75</v>
+        <v>453.17</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3961,13 +3961,13 @@
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>467.36</v>
+        <v>466.67</v>
       </c>
       <c r="F84">
         <v>334.49</v>
       </c>
       <c r="G84">
-        <v>336.79</v>
+        <v>336.22</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3999,7 +3999,7 @@
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>556.52</v>
+        <v>685</v>
       </c>
       <c r="F85">
         <v>419.03</v>
@@ -4075,13 +4075,13 @@
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>690.54</v>
+        <v>692.85</v>
       </c>
       <c r="F87">
-        <v>429.06</v>
+        <v>427.8</v>
       </c>
       <c r="G87">
-        <v>448.44</v>
+        <v>448.33</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4104,22 +4104,22 @@
         <v>118</v>
       </c>
       <c r="B88">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C88">
-        <v>5.54</v>
+        <v>5.59</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>602.19</v>
+        <v>620.3</v>
       </c>
       <c r="F88">
-        <v>510.96</v>
+        <v>454.67</v>
       </c>
       <c r="G88">
-        <v>444.06</v>
+        <v>406</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4134,7 +4134,7 @@
         <v>65</v>
       </c>
       <c r="L88" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4142,22 +4142,22 @@
         <v>119</v>
       </c>
       <c r="B89">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="C89">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>634.49</v>
+        <v>599.88</v>
       </c>
       <c r="F89">
-        <v>507.38</v>
+        <v>510.96</v>
       </c>
       <c r="G89">
-        <v>481.89</v>
+        <v>444.06</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4172,7 +4172,7 @@
         <v>65</v>
       </c>
       <c r="L89" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4180,22 +4180,22 @@
         <v>120</v>
       </c>
       <c r="B90">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="C90">
-        <v>5.51</v>
+        <v>5.53</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>591.23</v>
+        <v>634.49</v>
       </c>
       <c r="F90">
-        <v>415.22</v>
+        <v>507.38</v>
       </c>
       <c r="G90">
-        <v>427.91</v>
+        <v>481.89</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4207,10 +4207,10 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4218,22 +4218,22 @@
         <v>121</v>
       </c>
       <c r="B91">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="C91">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>619.61</v>
+        <v>572.2</v>
       </c>
       <c r="F91">
-        <v>455.59</v>
+        <v>415.22</v>
       </c>
       <c r="G91">
-        <v>406</v>
+        <v>428.95</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4245,10 +4245,10 @@
         <f>IF(D91=0,"",(H91-D91)/D91)</f>
       </c>
       <c r="K91" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L91" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4256,7 +4256,7 @@
         <v>122</v>
       </c>
       <c r="B92">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C92">
         <v>5.4</v>
@@ -4294,7 +4294,7 @@
         <v>123</v>
       </c>
       <c r="B93">
-        <v>858</v>
+        <v>123</v>
       </c>
       <c r="C93">
         <v>5.36</v>
@@ -4303,13 +4303,13 @@
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>587.2</v>
+        <v>600.69</v>
       </c>
       <c r="F93">
-        <v>414.07</v>
+        <v>445.21</v>
       </c>
       <c r="G93">
-        <v>423.3</v>
+        <v>402.54</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4321,10 +4321,10 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L93" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4332,22 +4332,22 @@
         <v>124</v>
       </c>
       <c r="B94">
-        <v>122</v>
+        <v>871</v>
       </c>
       <c r="C94">
-        <v>5.36</v>
+        <v>5.32</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>600.69</v>
+        <v>585.7</v>
       </c>
       <c r="F94">
-        <v>445.21</v>
+        <v>403.69</v>
       </c>
       <c r="G94">
-        <v>402.54</v>
+        <v>422.14</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4359,10 +4359,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L94" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4370,7 +4370,7 @@
         <v>125</v>
       </c>
       <c r="B95">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95">
         <v>5.25</v>
@@ -4379,13 +4379,13 @@
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>580.16</v>
+        <v>577.74</v>
       </c>
       <c r="F95">
-        <v>402.42</v>
+        <v>401.15</v>
       </c>
       <c r="G95">
-        <v>413.72</v>
+        <v>411.19</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4446,22 +4446,22 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>541.52</v>
+        <v>563.55</v>
       </c>
       <c r="F97">
         <v>363.32</v>
       </c>
       <c r="G97">
-        <v>390.77</v>
+        <v>391.93</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4484,7 +4484,7 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C98">
         <v>4.91</v>
@@ -4525,19 +4525,19 @@
         <v>121</v>
       </c>
       <c r="C99">
-        <v>4.81</v>
+        <v>4.73</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>619.61</v>
+        <v>592.73</v>
       </c>
       <c r="F99">
         <v>410.84</v>
       </c>
       <c r="G99">
-        <v>379.47</v>
+        <v>378.32</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4560,22 +4560,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>159</v>
+        <v>639</v>
       </c>
       <c r="C100">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>565.97</v>
+        <v>502.88</v>
       </c>
       <c r="F100">
-        <v>334.49</v>
+        <v>357.9</v>
       </c>
       <c r="G100">
-        <v>322.95</v>
+        <v>363.09</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4587,10 +4587,10 @@
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
       <c r="K100" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L100" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4598,22 +4598,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>626</v>
+        <v>96</v>
       </c>
       <c r="C101">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>509.23</v>
+        <v>535.18</v>
       </c>
       <c r="F101">
-        <v>357.9</v>
+        <v>333.33</v>
       </c>
       <c r="G101">
-        <v>357.55</v>
+        <v>373.47</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4628,7 +4628,7 @@
         <v>23</v>
       </c>
       <c r="L101" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4636,22 +4636,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C102">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>528.14</v>
+        <v>518.68</v>
       </c>
       <c r="F102">
-        <v>333.33</v>
+        <v>372.43</v>
       </c>
       <c r="G102">
-        <v>373.47</v>
+        <v>380.62</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4663,10 +4663,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L102" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4674,22 +4674,22 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C103">
-        <v>4.66</v>
+        <v>4.55</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>599.08</v>
+        <v>521.8</v>
       </c>
       <c r="F103">
-        <v>372.43</v>
+        <v>359.17</v>
       </c>
       <c r="G103">
-        <v>380.62</v>
+        <v>351.79</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4704,7 +4704,7 @@
         <v>65</v>
       </c>
       <c r="L103" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4712,22 +4712,22 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="C104">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>521.8</v>
+        <v>565.97</v>
       </c>
       <c r="F104">
-        <v>359.17</v>
+        <v>343.6</v>
       </c>
       <c r="G104">
-        <v>351.79</v>
+        <v>336.79</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4742,7 +4742,7 @@
         <v>65</v>
       </c>
       <c r="L104" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4753,7 +4753,7 @@
         <v>25</v>
       </c>
       <c r="C105">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
@@ -4879,7 +4879,7 @@
         <v>339.79</v>
       </c>
       <c r="G108">
-        <v>361.94</v>
+        <v>361.82</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4902,22 +4902,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>55</v>
+        <v>2449</v>
       </c>
       <c r="C109">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>530.45</v>
+        <v>496.54</v>
       </c>
       <c r="F109">
-        <v>303.34</v>
+        <v>334.49</v>
       </c>
       <c r="G109">
-        <v>303.34</v>
+        <v>322.95</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4929,10 +4929,10 @@
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
       <c r="K109" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L109" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4940,22 +4940,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>2432</v>
+        <v>55</v>
       </c>
       <c r="C110">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>485.58</v>
+        <v>530.45</v>
       </c>
       <c r="F110">
-        <v>328.72</v>
+        <v>303.34</v>
       </c>
       <c r="G110">
-        <v>325.72</v>
+        <v>303.34</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4967,10 +4967,10 @@
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
       <c r="K110" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L110" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C111">
         <v>4.1</v>
@@ -5025,13 +5025,13 @@
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>431.14</v>
+        <v>440.6</v>
       </c>
       <c r="F112">
         <v>310.96</v>
       </c>
       <c r="G112">
-        <v>288.35</v>
+        <v>290.54</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5092,19 +5092,19 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C114">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>393.31</v>
+        <v>402.77</v>
       </c>
       <c r="F114">
-        <v>288.35</v>
+        <v>287.2</v>
       </c>
       <c r="G114">
         <v>286.97</v>
@@ -5142,10 +5142,10 @@
         <v>486.39</v>
       </c>
       <c r="F115">
-        <v>270.01</v>
+        <v>269.9</v>
       </c>
       <c r="G115">
-        <v>288.58</v>
+        <v>288.35</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5168,7 +5168,7 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C116">
         <v>3.54</v>
@@ -5206,10 +5206,10 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C117">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
@@ -5218,7 +5218,7 @@
         <v>464.24</v>
       </c>
       <c r="F117">
-        <v>262.63</v>
+        <v>259.52</v>
       </c>
       <c r="G117">
         <v>266.44</v>
@@ -5244,7 +5244,7 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C118">
         <v>3.44</v>
@@ -5253,13 +5253,13 @@
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>369.66</v>
+        <v>364.94</v>
       </c>
       <c r="F118">
-        <v>251.21</v>
+        <v>252.36</v>
       </c>
       <c r="G118">
-        <v>259.28</v>
+        <v>259.17</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5282,22 +5282,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>251</v>
+        <v>67</v>
       </c>
       <c r="C119">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>382.24</v>
+        <v>349.94</v>
       </c>
       <c r="F119">
-        <v>254.79</v>
+        <v>253.75</v>
       </c>
       <c r="G119">
-        <v>247.98</v>
+        <v>239.79</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5309,10 +5309,10 @@
         <f>IF(D119=0,"",(H119-D119)/D119)</f>
       </c>
       <c r="K119" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L119" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5320,22 +5320,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="C120">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>340.48</v>
+        <v>382.24</v>
       </c>
       <c r="F120">
-        <v>236.33</v>
+        <v>254.79</v>
       </c>
       <c r="G120">
-        <v>236.1</v>
+        <v>246.83</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5347,10 +5347,10 @@
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
       <c r="K120" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L120" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5358,22 +5358,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>67</v>
+        <v>326</v>
       </c>
       <c r="C121">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>349.94</v>
+        <v>340.48</v>
       </c>
       <c r="F121">
-        <v>253.75</v>
+        <v>236.33</v>
       </c>
       <c r="G121">
-        <v>239.79</v>
+        <v>234.95</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5396,22 +5396,22 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C122">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>376.7</v>
+        <v>360.21</v>
       </c>
       <c r="F122">
         <v>250.29</v>
       </c>
       <c r="G122">
-        <v>244.29</v>
+        <v>242.21</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -5437,7 +5437,7 @@
         <v>123</v>
       </c>
       <c r="C123">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
@@ -5472,22 +5472,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="C124">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>297.12</v>
+        <v>334.95</v>
       </c>
       <c r="F124">
-        <v>219.15</v>
+        <v>218.11</v>
       </c>
       <c r="G124">
-        <v>222.61</v>
+        <v>217.76</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5499,10 +5499,10 @@
         <f>IF(D124=0,"",(H124-D124)/D124)</f>
       </c>
       <c r="K124" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L124" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5510,7 +5510,7 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="C125">
         <v>2.85</v>
@@ -5519,13 +5519,13 @@
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>315.22</v>
+        <v>297.12</v>
       </c>
       <c r="F125">
-        <v>218.11</v>
+        <v>226.07</v>
       </c>
       <c r="G125">
-        <v>217.76</v>
+        <v>222.61</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5537,10 +5537,10 @@
         <f>IF(D125=0,"",(H125-D125)/D125)</f>
       </c>
       <c r="K125" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L125" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5548,10 +5548,10 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C126">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
@@ -5563,7 +5563,7 @@
         <v>191.93</v>
       </c>
       <c r="G126">
-        <v>192.39</v>
+        <v>191.46</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5586,22 +5586,22 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C127">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>295.62</v>
+        <v>279.01</v>
       </c>
       <c r="F127">
-        <v>177.62</v>
+        <v>173.01</v>
       </c>
       <c r="G127">
-        <v>183.39</v>
+        <v>169.43</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5613,10 +5613,10 @@
         <f>IF(D127=0,"",(H127-D127)/D127)</f>
       </c>
       <c r="K127" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L127" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5624,22 +5624,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C128">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>230.91</v>
+        <v>287.66</v>
       </c>
       <c r="F128">
-        <v>174.62</v>
+        <v>177.51</v>
       </c>
       <c r="G128">
-        <v>174.16</v>
+        <v>183.39</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5654,7 +5654,7 @@
         <v>65</v>
       </c>
       <c r="L128" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5662,22 +5662,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="C129">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>283.74</v>
+        <v>249.83</v>
       </c>
       <c r="F129">
-        <v>173.01</v>
+        <v>183.39</v>
       </c>
       <c r="G129">
-        <v>169.43</v>
+        <v>188</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5689,10 +5689,10 @@
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
       <c r="K129" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L129" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5700,22 +5700,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C130">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>249.83</v>
+        <v>230.91</v>
       </c>
       <c r="F130">
-        <v>183.39</v>
+        <v>174.28</v>
       </c>
       <c r="G130">
-        <v>188</v>
+        <v>174.16</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5747,7 +5747,7 @@
         <f>C131*$B$3</f>
       </c>
       <c r="E131">
-        <v>211.99</v>
+        <v>211.19</v>
       </c>
       <c r="F131">
         <v>146.14</v>
@@ -5785,7 +5785,7 @@
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>253.75</v>
+        <v>206.46</v>
       </c>
       <c r="F132">
         <v>133.45</v>
@@ -5817,7 +5817,7 @@
         <v>268</v>
       </c>
       <c r="C133">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
@@ -5855,7 +5855,7 @@
         <v>298</v>
       </c>
       <c r="C134">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
@@ -5864,7 +5864,7 @@
         <v>163.09</v>
       </c>
       <c r="F134">
-        <v>120.99</v>
+        <v>120.88</v>
       </c>
       <c r="G134">
         <v>122.61</v>
@@ -5890,7 +5890,7 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C135">
         <v>1.53</v>
@@ -5899,7 +5899,7 @@
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>165.51</v>
+        <v>166.32</v>
       </c>
       <c r="F135">
         <v>115.92</v>
@@ -5928,7 +5928,7 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C136">
         <v>1.43</v>
@@ -5966,7 +5966,7 @@
         <v>168</v>
       </c>
       <c r="B137">
-        <v>510</v>
+        <v>559</v>
       </c>
       <c r="C137">
         <v>1.01</v>
@@ -6004,7 +6004,7 @@
         <v>169</v>
       </c>
       <c r="B138">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C138">
         <v>0.85</v>
@@ -6013,13 +6013,13 @@
         <f>C138*$B$3</f>
       </c>
       <c r="E138">
-        <v>91.35</v>
+        <v>92.96</v>
       </c>
       <c r="F138">
         <v>65.97</v>
       </c>
       <c r="G138">
-        <v>64.36</v>
+        <v>64.24</v>
       </c>
       <c r="H138">
         <f>MIN(E138:G138)</f>
@@ -6042,19 +6042,19 @@
         <v>170</v>
       </c>
       <c r="B139">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C139">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="D139">
         <f>C139*$B$3</f>
       </c>
       <c r="E139">
-        <v>79.58</v>
+        <v>81.08</v>
       </c>
       <c r="F139">
-        <v>50.17</v>
+        <v>50.06</v>
       </c>
       <c r="G139">
         <v>50.52</v>
@@ -6089,7 +6089,7 @@
         <f>C140*$B$3</f>
       </c>
       <c r="E140">
-        <v>59.86</v>
+        <v>66.9</v>
       </c>
       <c r="F140">
         <v>34.26</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 19.07.2026 01:17</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 19.07.2026 16:35</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -94,12 +94,12 @@
     <t>Rifle</t>
   </si>
   <si>
+    <t>AK-47 | Point Disarray (Factory New)</t>
+  </si>
+  <si>
     <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
   </si>
   <si>
-    <t>AK-47 | Point Disarray (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Containment Breach (Field-Tested)</t>
   </si>
   <si>
@@ -115,15 +115,15 @@
     <t>AK-47 | Legion of Anubis (Factory New)</t>
   </si>
   <si>
+    <t>USP-S | Orion (Minimal Wear)</t>
+  </si>
+  <si>
     <t>USP-S | Whiteout (Field-Tested)</t>
   </si>
   <si>
     <t>MAC-10 | Fade (Factory New)</t>
   </si>
   <si>
-    <t>USP-S | Orion (Minimal Wear)</t>
-  </si>
-  <si>
     <t>AWP | Neo-Noir (Factory New)</t>
   </si>
   <si>
@@ -133,12 +133,12 @@
     <t>AWP | Containment Breach (Well-Worn)</t>
   </si>
   <si>
+    <t>P250 | Apep's Curse (Field-Tested)</t>
+  </si>
+  <si>
     <t>MP9 | Hydra (Factory New)</t>
   </si>
   <si>
-    <t>P250 | Apep's Curse (Field-Tested)</t>
-  </si>
-  <si>
     <t>Desert Eagle | Starcade (Field-Tested)</t>
   </si>
   <si>
@@ -184,15 +184,15 @@
     <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
+    <t>Safecracker Voltzmann | The Professionals</t>
+  </si>
+  <si>
     <t>Nova | Sobek's Bite (Factory New)</t>
   </si>
   <si>
     <t>Shotgun</t>
   </si>
   <si>
-    <t>Safecracker Voltzmann | The Professionals</t>
-  </si>
-  <si>
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
@@ -253,39 +253,42 @@
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>FAMAS | Styx (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
+  </si>
+  <si>
+    <t>P250 | Epicenter (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Osiris | Elite Crew</t>
+  </si>
+  <si>
+    <t>Exceptional</t>
+  </si>
+  <si>
+    <t>B Squadron Officer | SAS</t>
+  </si>
+  <si>
+    <t>Distinguished</t>
+  </si>
+  <si>
+    <t>AUG | Carved Jade (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Markus Delrow | FBI HRT</t>
+  </si>
+  <si>
+    <t>SSG 08 | Rapid Transit (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Five-SeveN | Kami (Factory New)</t>
   </si>
   <si>
-    <t>FAMAS | Styx (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Osiris | Elite Crew</t>
-  </si>
-  <si>
-    <t>Exceptional</t>
-  </si>
-  <si>
-    <t>B Squadron Officer | SAS</t>
-  </si>
-  <si>
-    <t>Distinguished</t>
-  </si>
-  <si>
-    <t>AUG | Carved Jade (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>SSG 08 | Rapid Transit (Factory New)</t>
-  </si>
-  <si>
-    <t>Markus Delrow | FBI HRT</t>
-  </si>
-  <si>
     <t>MP7 | Fade (Minimal Wear)</t>
   </si>
   <si>
@@ -298,9 +301,6 @@
     <t>MP7 | Fade (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>SG 553 | Integrale (Field-Tested)</t>
   </si>
   <si>
@@ -325,72 +325,75 @@
     <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>AK-47 | Crossfade (Factory New)</t>
+  </si>
+  <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Liquid Fire</t>
   </si>
   <si>
     <t>High Grade</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>AK-47 | Crossfade (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
+    <t>Dragomir | Sabre</t>
+  </si>
+  <si>
+    <t>Maximus | Sabre</t>
   </si>
   <si>
     <t>Tec-9 | Brass (Field-Tested)</t>
   </si>
   <si>
-    <t>Dragomir | Sabre</t>
-  </si>
-  <si>
-    <t>Maximus | Sabre</t>
-  </si>
-  <si>
     <t>XM1014 | Black Tie (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | BIG (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
   </si>
   <si>
     <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
   </si>
   <si>
     <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
-  </si>
-  <si>
     <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>MAC-10 | Strats (Factory New)</t>
   </si>
   <si>
@@ -403,30 +406,27 @@
     <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>R8 Revolver | Blaze (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Stone Scales (Foil)</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
-    <t>Sticker | Stone Scales (Foil)</t>
-  </si>
-  <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
     <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
@@ -448,10 +448,13 @@
     <t>Sticker | Perfect World (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Galil AR | Tuxedo (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
+    <t>Five-SeveN | Retrobution (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
@@ -463,9 +466,6 @@
     <t>Five-SeveN | Kami (Minimal Wear)</t>
   </si>
   <si>
-    <t>Five-SeveN | Retrobution (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -475,13 +475,13 @@
     <t>AK-47 | Crossfade (Minimal Wear)</t>
   </si>
   <si>
+    <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>CZ75-Auto | Tuxedo (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
   </si>
   <si>
     <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
@@ -933,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.9</v>
+        <v>81.97</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -988,10 +988,10 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C6">
-        <v>165.31</v>
+        <v>160.76</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
@@ -1026,10 +1026,10 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>136.65</v>
+        <v>138.08</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -1041,7 +1041,7 @@
         <v>10605.51</v>
       </c>
       <c r="G7">
-        <v>9907.71</v>
+        <v>10011.51</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1064,22 +1064,22 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="C8">
-        <v>118.65</v>
+        <v>119.73</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>13507.7</v>
+        <v>14611.39</v>
       </c>
       <c r="F8">
         <v>8869.65</v>
       </c>
       <c r="G8">
-        <v>8783.14</v>
+        <v>8869.65</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1102,10 +1102,10 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C9">
-        <v>96.16</v>
+        <v>96.62</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
@@ -1114,10 +1114,10 @@
         <v>10635.04</v>
       </c>
       <c r="F9">
-        <v>7538.62</v>
+        <v>7600.91</v>
       </c>
       <c r="G9">
-        <v>7681.64</v>
+        <v>7324.09</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1140,22 +1140,22 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="C10">
-        <v>85.99</v>
+        <v>88.06</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>8653.27</v>
+        <v>9008.75</v>
       </c>
       <c r="F10">
-        <v>6205.29</v>
+        <v>6574.38</v>
       </c>
       <c r="G10">
-        <v>6430.21</v>
+        <v>6470.57</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1178,22 +1178,22 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>198</v>
+        <v>52</v>
       </c>
       <c r="C11">
-        <v>85.47</v>
+        <v>85.13</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>9194.1</v>
+        <v>8653.27</v>
       </c>
       <c r="F11">
-        <v>6574.38</v>
+        <v>6205.29</v>
       </c>
       <c r="G11">
-        <v>6562.85</v>
+        <v>6395.6</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1216,22 +1216,22 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="C12">
-        <v>80.92</v>
+        <v>80.84</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>8508.17</v>
+        <v>8189.72</v>
       </c>
       <c r="F12">
-        <v>5920.4</v>
+        <v>5913.25</v>
       </c>
       <c r="G12">
-        <v>5893.87</v>
+        <v>5905.41</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1254,10 +1254,10 @@
         <v>32</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>69.07</v>
+        <v>71.11</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
@@ -1292,22 +1292,22 @@
         <v>33</v>
       </c>
       <c r="B14">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C14">
-        <v>61.34</v>
+        <v>61.5</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>6620.17</v>
+        <v>6723.51</v>
       </c>
       <c r="F14">
-        <v>4596.18</v>
+        <v>4595.15</v>
       </c>
       <c r="G14">
-        <v>4565.16</v>
+        <v>4665.5</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1330,22 +1330,22 @@
         <v>34</v>
       </c>
       <c r="B15">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="C15">
-        <v>58.2</v>
+        <v>58.85</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>6306.45</v>
+        <v>6211.06</v>
       </c>
       <c r="F15">
-        <v>4319.48</v>
+        <v>4382.92</v>
       </c>
       <c r="G15">
-        <v>4232.98</v>
+        <v>4336.78</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1368,22 +1368,22 @@
         <v>35</v>
       </c>
       <c r="B16">
-        <v>301</v>
+        <v>221</v>
       </c>
       <c r="C16">
-        <v>58.18</v>
+        <v>58.19</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>6351.43</v>
+        <v>6338.74</v>
       </c>
       <c r="F16">
-        <v>4371.39</v>
+        <v>4244.51</v>
       </c>
       <c r="G16">
-        <v>4260.66</v>
+        <v>4221.44</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1395,10 +1395,10 @@
         <f>IF(D16=0,"",(H16-D16)/D16)</f>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1406,22 +1406,22 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="C17">
-        <v>57.14</v>
+        <v>58.08</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>6294.68</v>
+        <v>6338.74</v>
       </c>
       <c r="F17">
-        <v>4394.45</v>
+        <v>4348.32</v>
       </c>
       <c r="G17">
-        <v>4348.32</v>
+        <v>4261.81</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1433,10 +1433,10 @@
         <f>IF(D17=0,"",(H17-D17)/D17)</f>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1444,22 +1444,22 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C18">
-        <v>56.9</v>
+        <v>55.03</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>6345.89</v>
+        <v>6334.82</v>
       </c>
       <c r="F18">
-        <v>4241.05</v>
+        <v>4186.84</v>
       </c>
       <c r="G18">
-        <v>4150.86</v>
+        <v>4134.71</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1482,22 +1482,22 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="C19">
-        <v>53.57</v>
+        <v>53.81</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5686.84</v>
+        <v>5939.89</v>
       </c>
       <c r="F19">
         <v>4036.9</v>
       </c>
       <c r="G19">
-        <v>3990.76</v>
+        <v>4019.6</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1520,19 +1520,19 @@
         <v>39</v>
       </c>
       <c r="B20">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C20">
-        <v>51.97</v>
+        <v>51.99</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>6024.21</v>
+        <v>6117.29</v>
       </c>
       <c r="F20">
-        <v>4015.91</v>
+        <v>3977.96</v>
       </c>
       <c r="G20">
         <v>3965.39</v>
@@ -1558,22 +1558,22 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C21">
-        <v>49.97</v>
+        <v>49.48</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>5717.63</v>
+        <v>5531.59</v>
       </c>
       <c r="F21">
-        <v>3610.03</v>
+        <v>3662.05</v>
       </c>
       <c r="G21">
-        <v>3610.14</v>
+        <v>3933.09</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1585,7 +1585,7 @@
         <f>IF(D21=0,"",(H21-D21)/D21)</f>
       </c>
       <c r="K21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L21" t="s">
         <v>24</v>
@@ -1596,22 +1596,22 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C22">
-        <v>49.86</v>
+        <v>48.3</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>5863.42</v>
+        <v>5716.83</v>
       </c>
       <c r="F22">
-        <v>3662.05</v>
+        <v>3621.68</v>
       </c>
       <c r="G22">
-        <v>3794.69</v>
+        <v>3621.68</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1623,7 +1623,7 @@
         <f>IF(D22=0,"",(H22-D22)/D22)</f>
       </c>
       <c r="K22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L22" t="s">
         <v>24</v>
@@ -1634,22 +1634,22 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="C23">
-        <v>48.53</v>
+        <v>48.15</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>5214.64</v>
+        <v>5134.24</v>
       </c>
       <c r="F23">
-        <v>3679.35</v>
+        <v>3667.81</v>
       </c>
       <c r="G23">
-        <v>3552.47</v>
+        <v>3540.94</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1672,22 +1672,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C24">
-        <v>47.75</v>
+        <v>47.43</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>5384.88</v>
+        <v>5132.63</v>
       </c>
       <c r="F24">
-        <v>3460.2</v>
+        <v>3454.32</v>
       </c>
       <c r="G24">
-        <v>3569.66</v>
+        <v>3540.25</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1710,19 +1710,19 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C25">
-        <v>37.54</v>
+        <v>38.7</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>4142.55</v>
+        <v>4149.59</v>
       </c>
       <c r="F25">
-        <v>2835.98</v>
+        <v>2870.47</v>
       </c>
       <c r="G25">
         <v>2807.38</v>
@@ -1748,10 +1748,10 @@
         <v>45</v>
       </c>
       <c r="B26">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C26">
-        <v>36.75</v>
+        <v>36.82</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
@@ -1760,10 +1760,10 @@
         <v>4058.24</v>
       </c>
       <c r="F26">
-        <v>2652.82</v>
+        <v>2987.19</v>
       </c>
       <c r="G26">
-        <v>2923.41</v>
+        <v>2893.65</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1786,22 +1786,22 @@
         <v>46</v>
       </c>
       <c r="B27">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C27">
-        <v>34.67</v>
+        <v>35.43</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>4301.72</v>
+        <v>4229.29</v>
       </c>
       <c r="F27">
-        <v>2641.29</v>
+        <v>2617.18</v>
       </c>
       <c r="G27">
-        <v>2946.94</v>
+        <v>2704.61</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1824,22 +1824,22 @@
         <v>47</v>
       </c>
       <c r="B28">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C28">
-        <v>32.56</v>
+        <v>32.41</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>3705.07</v>
+        <v>3930.44</v>
       </c>
       <c r="F28">
-        <v>2462.51</v>
+        <v>2445.09</v>
       </c>
       <c r="G28">
-        <v>2450.98</v>
+        <v>2410.61</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1862,22 +1862,22 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C29">
-        <v>31.73</v>
+        <v>31.43</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>3507.95</v>
+        <v>3503.22</v>
       </c>
       <c r="F29">
-        <v>2520.06</v>
+        <v>2422.14</v>
       </c>
       <c r="G29">
-        <v>2421.68</v>
+        <v>2410.61</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1900,22 +1900,22 @@
         <v>49</v>
       </c>
       <c r="B30">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C30">
-        <v>29.27</v>
+        <v>29.88</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>3123.29</v>
+        <v>3074.39</v>
       </c>
       <c r="F30">
-        <v>2241.4</v>
+        <v>2283.62</v>
       </c>
       <c r="G30">
-        <v>2204.15</v>
+        <v>2265.28</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1938,22 +1938,22 @@
         <v>50</v>
       </c>
       <c r="B31">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="C31">
-        <v>25.32</v>
+        <v>25.07</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2617.99</v>
+        <v>2653.4</v>
       </c>
       <c r="F31">
-        <v>1894.69</v>
+        <v>1923.64</v>
       </c>
       <c r="G31">
-        <v>1903.11</v>
+        <v>1897.34</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1976,22 +1976,22 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>387</v>
+        <v>295</v>
       </c>
       <c r="C32">
-        <v>24.11</v>
+        <v>24.29</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2897.8</v>
+        <v>3010.49</v>
       </c>
       <c r="F32">
-        <v>1914.64</v>
+        <v>1926.18</v>
       </c>
       <c r="G32">
-        <v>1926.18</v>
+        <v>1906.57</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2014,22 +2014,22 @@
         <v>54</v>
       </c>
       <c r="B33">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C33">
-        <v>20.65</v>
+        <v>21.34</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>2420.06</v>
+        <v>2252.13</v>
       </c>
       <c r="F33">
-        <v>1649.25</v>
+        <v>1652.59</v>
       </c>
       <c r="G33">
-        <v>1574.39</v>
+        <v>1660.9</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2052,7 +2052,7 @@
         <v>55</v>
       </c>
       <c r="B34">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>19.8</v>
@@ -2061,13 +2061,13 @@
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>2307.38</v>
+        <v>2191.46</v>
       </c>
       <c r="F34">
-        <v>1473.58</v>
+        <v>1473.12</v>
       </c>
       <c r="G34">
-        <v>1491.35</v>
+        <v>1497.11</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2090,22 +2090,22 @@
         <v>56</v>
       </c>
       <c r="B35">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="C35">
-        <v>19.51</v>
+        <v>19.16</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>2388.58</v>
+        <v>2327.79</v>
       </c>
       <c r="F35">
-        <v>1480.85</v>
+        <v>1481.77</v>
       </c>
       <c r="G35">
-        <v>1435.87</v>
+        <v>1430.22</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2128,22 +2128,22 @@
         <v>57</v>
       </c>
       <c r="B36">
-        <v>35</v>
+        <v>803</v>
       </c>
       <c r="C36">
-        <v>18.95</v>
+        <v>19.14</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>2287.65</v>
+        <v>2288.46</v>
       </c>
       <c r="F36">
-        <v>1454.44</v>
+        <v>1493.65</v>
       </c>
       <c r="G36">
-        <v>1451.78</v>
+        <v>1479.81</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2155,33 +2155,33 @@
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
       <c r="K36" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37">
-        <v>1113</v>
+        <v>33</v>
       </c>
       <c r="C37">
-        <v>18.94</v>
+        <v>18.95</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2286.04</v>
+        <v>2250.63</v>
       </c>
       <c r="F37">
-        <v>1493.65</v>
+        <v>1441.75</v>
       </c>
       <c r="G37">
-        <v>1464.59</v>
+        <v>1416.26</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2193,10 +2193,10 @@
         <f>IF(D37=0,"",(H37-D37)/D37)</f>
       </c>
       <c r="K37" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L37" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2204,22 +2204,22 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C38">
-        <v>18.84</v>
+        <v>18.35</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>2049.59</v>
+        <v>2167.82</v>
       </c>
       <c r="F38">
-        <v>1444.75</v>
+        <v>1444.06</v>
       </c>
       <c r="G38">
-        <v>1394.46</v>
+        <v>1384.08</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2245,7 +2245,7 @@
         <v>74</v>
       </c>
       <c r="C39">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
@@ -2254,10 +2254,10 @@
         <v>1967.59</v>
       </c>
       <c r="F39">
-        <v>1244.52</v>
+        <v>1257.21</v>
       </c>
       <c r="G39">
-        <v>1251.44</v>
+        <v>1245.67</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2280,10 +2280,10 @@
         <v>62</v>
       </c>
       <c r="B40">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C40">
-        <v>15.68</v>
+        <v>14.98</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
@@ -2292,10 +2292,10 @@
         <v>1800.46</v>
       </c>
       <c r="F40">
-        <v>1187.89</v>
+        <v>1158.94</v>
       </c>
       <c r="G40">
-        <v>1197.58</v>
+        <v>1147.63</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2321,7 +2321,7 @@
         <v>26</v>
       </c>
       <c r="C41">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
@@ -2330,7 +2330,7 @@
         <v>1455.94</v>
       </c>
       <c r="F41">
-        <v>1068.86</v>
+        <v>1049.59</v>
       </c>
       <c r="G41">
         <v>1092.27</v>
@@ -2345,7 +2345,7 @@
         <f>IF(D41=0,"",(H41-D41)/D41)</f>
       </c>
       <c r="K41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L41" t="s">
         <v>21</v>
@@ -2356,22 +2356,22 @@
         <v>64</v>
       </c>
       <c r="B42">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C42">
-        <v>13.68</v>
+        <v>13.54</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1537.94</v>
+        <v>1536.33</v>
       </c>
       <c r="F42">
         <v>980.39</v>
       </c>
       <c r="G42">
-        <v>942.9</v>
+        <v>935.98</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2394,16 +2394,16 @@
         <v>67</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C43">
-        <v>13.42</v>
+        <v>13.44</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1450.4</v>
+        <v>1567.93</v>
       </c>
       <c r="F43">
         <v>975.78</v>
@@ -2432,22 +2432,22 @@
         <v>68</v>
       </c>
       <c r="B44">
-        <v>1757</v>
+        <v>1128</v>
       </c>
       <c r="C44">
-        <v>13.39</v>
+        <v>13.34</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1496.19</v>
+        <v>1546.59</v>
       </c>
       <c r="F44">
-        <v>1038.06</v>
+        <v>1049.59</v>
       </c>
       <c r="G44">
-        <v>1036.68</v>
+        <v>1070.82</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2470,22 +2470,22 @@
         <v>70</v>
       </c>
       <c r="B45">
-        <v>1424</v>
+        <v>1178</v>
       </c>
       <c r="C45">
-        <v>13.01</v>
+        <v>13.3</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1519.84</v>
+        <v>1531.6</v>
       </c>
       <c r="F45">
-        <v>1003.46</v>
+        <v>1026.53</v>
       </c>
       <c r="G45">
-        <v>996.42</v>
+        <v>1055.25</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2508,10 +2508,10 @@
         <v>71</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>12.62</v>
+        <v>12.51</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
@@ -2520,7 +2520,7 @@
         <v>1418.11</v>
       </c>
       <c r="F46">
-        <v>1031.83</v>
+        <v>1031.25</v>
       </c>
       <c r="G46">
         <v>977.28</v>
@@ -2546,22 +2546,22 @@
         <v>73</v>
       </c>
       <c r="B47">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C47">
-        <v>12.27</v>
+        <v>12.08</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1384.2</v>
+        <v>1372.43</v>
       </c>
       <c r="F47">
-        <v>938.87</v>
+        <v>922.72</v>
       </c>
       <c r="G47">
-        <v>939.91</v>
+        <v>926.18</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2584,10 +2584,10 @@
         <v>74</v>
       </c>
       <c r="B48">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C48">
-        <v>12.2</v>
+        <v>12.08</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
@@ -2596,10 +2596,10 @@
         <v>1330.56</v>
       </c>
       <c r="F48">
-        <v>978.78</v>
+        <v>978.66</v>
       </c>
       <c r="G48">
-        <v>930.68</v>
+        <v>934.25</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2622,22 +2622,22 @@
         <v>76</v>
       </c>
       <c r="B49">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="C49">
-        <v>11.64</v>
+        <v>11.49</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1252.59</v>
+        <v>1263.67</v>
       </c>
       <c r="F49">
-        <v>862.74</v>
+        <v>839.68</v>
       </c>
       <c r="G49">
-        <v>856.86</v>
+        <v>852.59</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2660,22 +2660,22 @@
         <v>77</v>
       </c>
       <c r="B50">
-        <v>1799</v>
+        <v>1479</v>
       </c>
       <c r="C50">
-        <v>11.06</v>
+        <v>10.9</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1260.44</v>
+        <v>1381.89</v>
       </c>
       <c r="F50">
-        <v>848.67</v>
+        <v>851.44</v>
       </c>
       <c r="G50">
-        <v>841.52</v>
+        <v>830.45</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2698,22 +2698,22 @@
         <v>78</v>
       </c>
       <c r="B51">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C51">
-        <v>10.85</v>
+        <v>10.62</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1080.74</v>
+        <v>1112.22</v>
       </c>
       <c r="F51">
-        <v>779.12</v>
+        <v>757.32</v>
       </c>
       <c r="G51">
-        <v>793.54</v>
+        <v>760.09</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2736,22 +2736,22 @@
         <v>79</v>
       </c>
       <c r="B52">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C52">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1182.47</v>
+        <v>1160.32</v>
       </c>
       <c r="F52">
         <v>782.01</v>
       </c>
       <c r="G52">
-        <v>749.71</v>
+        <v>761.24</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2774,22 +2774,22 @@
         <v>80</v>
       </c>
       <c r="B53">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="C53">
-        <v>10.39</v>
+        <v>10.14</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1080.74</v>
+        <v>1180.04</v>
       </c>
       <c r="F53">
-        <v>757.55</v>
+        <v>753.63</v>
       </c>
       <c r="G53">
-        <v>749.71</v>
+        <v>807.38</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2801,10 +2801,10 @@
         <f>IF(D53=0,"",(H53-D53)/D53)</f>
       </c>
       <c r="K53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2812,22 +2812,22 @@
         <v>81</v>
       </c>
       <c r="B54">
-        <v>183</v>
+        <v>472</v>
       </c>
       <c r="C54">
-        <v>10.18</v>
+        <v>10.06</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1153.28</v>
+        <v>1080.74</v>
       </c>
       <c r="F54">
-        <v>749.48</v>
+        <v>724.22</v>
       </c>
       <c r="G54">
-        <v>821.91</v>
+        <v>713.72</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2839,7 +2839,7 @@
         <f>IF(D54=0,"",(H54-D54)/D54)</f>
       </c>
       <c r="K54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L54" t="s">
         <v>21</v>
@@ -2850,22 +2850,22 @@
         <v>82</v>
       </c>
       <c r="B55">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="C55">
-        <v>10.1</v>
+        <v>9.96</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1129.64</v>
+        <v>1111.42</v>
       </c>
       <c r="F55">
-        <v>725.49</v>
+        <v>756.05</v>
       </c>
       <c r="G55">
-        <v>714.99</v>
+        <v>786.5</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2880,7 +2880,7 @@
         <v>23</v>
       </c>
       <c r="L55" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2888,22 +2888,22 @@
         <v>83</v>
       </c>
       <c r="B56">
-        <v>102</v>
+        <v>1062</v>
       </c>
       <c r="C56">
-        <v>10.06</v>
+        <v>9.66</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1097.23</v>
+        <v>1143.83</v>
       </c>
       <c r="F56">
-        <v>726.64</v>
+        <v>771.62</v>
       </c>
       <c r="G56">
-        <v>788.81</v>
+        <v>757.55</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2915,33 +2915,33 @@
         <f>IF(D56=0,"",(H56-D56)/D56)</f>
       </c>
       <c r="K56" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L56" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B57">
-        <v>1318</v>
+        <v>795</v>
       </c>
       <c r="C57">
-        <v>9.76</v>
+        <v>9.52</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1076.81</v>
+        <v>1228.95</v>
       </c>
       <c r="F57">
-        <v>737.02</v>
+        <v>748.56</v>
       </c>
       <c r="G57">
-        <v>764.7</v>
+        <v>725.49</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2956,30 +2956,30 @@
         <v>52</v>
       </c>
       <c r="L57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B58">
-        <v>988</v>
+        <v>70</v>
       </c>
       <c r="C58">
-        <v>9.62</v>
+        <v>9.47</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1182.47</v>
+        <v>1002.65</v>
       </c>
       <c r="F58">
-        <v>738.18</v>
+        <v>711.42</v>
       </c>
       <c r="G58">
-        <v>725.49</v>
+        <v>741.64</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2991,10 +2991,10 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L58" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3002,22 +3002,22 @@
         <v>88</v>
       </c>
       <c r="B59">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="C59">
-        <v>9.57</v>
+        <v>9.02</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>1016.84</v>
+        <v>997.11</v>
       </c>
       <c r="F59">
-        <v>711.42</v>
+        <v>714.99</v>
       </c>
       <c r="G59">
-        <v>743.94</v>
+        <v>754.78</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3029,10 +3029,10 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L59" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,22 +3040,22 @@
         <v>89</v>
       </c>
       <c r="B60">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C60">
-        <v>8.89</v>
+        <v>8.8</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>906.46</v>
+        <v>919.14</v>
       </c>
       <c r="F60">
-        <v>657.32</v>
+        <v>640.02</v>
       </c>
       <c r="G60">
-        <v>665.4</v>
+        <v>660.55</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3078,22 +3078,22 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>677</v>
+        <v>80</v>
       </c>
       <c r="C61">
-        <v>8.65</v>
+        <v>8.72</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>1008.19</v>
+        <v>1040.48</v>
       </c>
       <c r="F61">
-        <v>663.21</v>
+        <v>678.2</v>
       </c>
       <c r="G61">
-        <v>641.29</v>
+        <v>634.37</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3105,10 +3105,10 @@
         <f>IF(D61=0,"",(H61-D61)/D61)</f>
       </c>
       <c r="K61" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="L61" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3116,22 +3116,22 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>553</v>
+        <v>91</v>
       </c>
       <c r="C62">
-        <v>8.61</v>
+        <v>8.71</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>931.72</v>
+        <v>1065.74</v>
       </c>
       <c r="F62">
-        <v>668.63</v>
+        <v>746.48</v>
       </c>
       <c r="G62">
-        <v>647.63</v>
+        <v>750.75</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3143,10 +3143,10 @@
         <f>IF(D62=0,"",(H62-D62)/D62)</f>
       </c>
       <c r="K62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L62" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3154,22 +3154,22 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>25</v>
+        <v>377</v>
       </c>
       <c r="C63">
-        <v>8.25</v>
+        <v>8.54</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>930.1</v>
+        <v>985.35</v>
       </c>
       <c r="F63">
-        <v>607.84</v>
+        <v>687.43</v>
       </c>
       <c r="G63">
-        <v>629.3</v>
+        <v>647.75</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3181,10 +3181,10 @@
         <f>IF(D63=0,"",(H63-D63)/D63)</f>
       </c>
       <c r="K63" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="L63" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3192,22 +3192,22 @@
         <v>93</v>
       </c>
       <c r="B64">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="C64">
-        <v>8.22</v>
+        <v>8.54</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>893.08</v>
+        <v>927.79</v>
       </c>
       <c r="F64">
-        <v>622.84</v>
+        <v>605.54</v>
       </c>
       <c r="G64">
-        <v>628.6</v>
+        <v>621.68</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3230,22 +3230,22 @@
         <v>94</v>
       </c>
       <c r="B65">
-        <v>209</v>
+        <v>265</v>
       </c>
       <c r="C65">
-        <v>8.18</v>
+        <v>8.38</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>930.91</v>
+        <v>889.96</v>
       </c>
       <c r="F65">
-        <v>631.37</v>
+        <v>622.84</v>
       </c>
       <c r="G65">
-        <v>619.03</v>
+        <v>632.06</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3257,10 +3257,10 @@
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
       <c r="K65" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="L65" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3268,22 +3268,22 @@
         <v>95</v>
       </c>
       <c r="B66">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="C66">
-        <v>8.14</v>
+        <v>8.29</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>1008.99</v>
+        <v>900.23</v>
       </c>
       <c r="F66">
-        <v>678.2</v>
+        <v>631.37</v>
       </c>
       <c r="G66">
-        <v>630.91</v>
+        <v>619.03</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3295,10 +3295,10 @@
         <f>IF(D66=0,"",(H66-D66)/D66)</f>
       </c>
       <c r="K66" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="L66" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3306,22 +3306,22 @@
         <v>96</v>
       </c>
       <c r="B67">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C67">
-        <v>8.06</v>
+        <v>8.05</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>892.27</v>
+        <v>894.69</v>
       </c>
       <c r="F67">
-        <v>588.12</v>
+        <v>586.97</v>
       </c>
       <c r="G67">
-        <v>599.77</v>
+        <v>576.7</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3344,22 +3344,22 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>845</v>
+        <v>658</v>
       </c>
       <c r="C68">
-        <v>7.98</v>
+        <v>7.94</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>990.89</v>
+        <v>1002.65</v>
       </c>
       <c r="F68">
-        <v>596.31</v>
+        <v>599.65</v>
       </c>
       <c r="G68">
-        <v>590.54</v>
+        <v>599.77</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3374,7 +3374,7 @@
         <v>52</v>
       </c>
       <c r="L68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3382,22 +3382,22 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>826</v>
+        <v>687</v>
       </c>
       <c r="C69">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>906.46</v>
+        <v>924.68</v>
       </c>
       <c r="F69">
-        <v>599.77</v>
+        <v>610.15</v>
       </c>
       <c r="G69">
-        <v>592.73</v>
+        <v>609.57</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3420,7 +3420,7 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>1424</v>
+        <v>1069</v>
       </c>
       <c r="C70">
         <v>7.84</v>
@@ -3429,13 +3429,13 @@
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>900.23</v>
+        <v>922.26</v>
       </c>
       <c r="F70">
         <v>599.77</v>
       </c>
       <c r="G70">
-        <v>593.77</v>
+        <v>610.15</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3458,22 +3458,22 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>749</v>
+        <v>611</v>
       </c>
       <c r="C71">
-        <v>7.81</v>
+        <v>7.77</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>929.41</v>
+        <v>881.31</v>
       </c>
       <c r="F71">
-        <v>598.61</v>
+        <v>606.11</v>
       </c>
       <c r="G71">
-        <v>576.7</v>
+        <v>590.89</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3496,22 +3496,22 @@
         <v>101</v>
       </c>
       <c r="B72">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C72">
-        <v>7.54</v>
+        <v>7.62</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>847.4</v>
+        <v>768.51</v>
       </c>
       <c r="F72">
         <v>551.56</v>
       </c>
       <c r="G72">
-        <v>571.16</v>
+        <v>550.17</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3534,10 +3534,10 @@
         <v>102</v>
       </c>
       <c r="B73">
-        <v>1121</v>
+        <v>836</v>
       </c>
       <c r="C73">
-        <v>7.32</v>
+        <v>7.25</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
@@ -3546,10 +3546,10 @@
         <v>922.26</v>
       </c>
       <c r="F73">
-        <v>570.93</v>
+        <v>564.01</v>
       </c>
       <c r="G73">
-        <v>540.83</v>
+        <v>547.75</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3572,22 +3572,22 @@
         <v>103</v>
       </c>
       <c r="B74">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="C74">
-        <v>7.05</v>
+        <v>6.98</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>748.79</v>
+        <v>770.13</v>
       </c>
       <c r="F74">
-        <v>583.39</v>
+        <v>582.24</v>
       </c>
       <c r="G74">
-        <v>576.7</v>
+        <v>544.4</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3610,22 +3610,22 @@
         <v>104</v>
       </c>
       <c r="B75">
-        <v>8</v>
+        <v>356</v>
       </c>
       <c r="C75">
-        <v>6.91</v>
+        <v>6.82</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>838.75</v>
+        <v>752.02</v>
       </c>
       <c r="F75">
-        <v>516.38</v>
+        <v>491.35</v>
       </c>
       <c r="G75">
-        <v>515.34</v>
+        <v>474.05</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3637,30 +3637,30 @@
         <f>IF(D75=0,"",(H75-D75)/D75)</f>
       </c>
       <c r="K75" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L75" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B76">
-        <v>1337</v>
+        <v>963</v>
       </c>
       <c r="C76">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>765.4</v>
+        <v>725.14</v>
       </c>
       <c r="F76">
-        <v>507.5</v>
+        <v>524.8</v>
       </c>
       <c r="G76">
         <v>517.88</v>
@@ -3683,25 +3683,25 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B77">
-        <v>397</v>
+        <v>51</v>
       </c>
       <c r="C77">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>748.79</v>
+        <v>900.23</v>
       </c>
       <c r="F77">
-        <v>490.54</v>
+        <v>529.18</v>
       </c>
       <c r="G77">
-        <v>479.81</v>
+        <v>461.36</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3713,33 +3713,33 @@
         <f>IF(D77=0,"",(H77-D77)/D77)</f>
       </c>
       <c r="K77" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L77" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B78">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>6.73</v>
+        <v>6.53</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>802.42</v>
+        <v>834.72</v>
       </c>
       <c r="F78">
-        <v>530.33</v>
+        <v>514.76</v>
       </c>
       <c r="G78">
-        <v>461.36</v>
+        <v>518.91</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3754,7 +3754,7 @@
         <v>65</v>
       </c>
       <c r="L78" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3762,22 +3762,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>78</v>
+        <v>665</v>
       </c>
       <c r="C79">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>750.4</v>
+        <v>800.11</v>
       </c>
       <c r="F79">
-        <v>475.32</v>
+        <v>481.31</v>
       </c>
       <c r="G79">
-        <v>573.47</v>
+        <v>473.82</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3789,10 +3789,10 @@
         <f>IF(D79=0,"",(H79-D79)/D79)</f>
       </c>
       <c r="K79" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L79" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3800,22 +3800,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>960</v>
+        <v>922</v>
       </c>
       <c r="C80">
-        <v>6.38</v>
+        <v>6.39</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>749.59</v>
+        <v>792.96</v>
       </c>
       <c r="F80">
-        <v>482.7</v>
+        <v>488.23</v>
       </c>
       <c r="G80">
-        <v>473.93</v>
+        <v>484.43</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3830,7 +3830,7 @@
         <v>52</v>
       </c>
       <c r="L80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3838,22 +3838,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>1199</v>
+        <v>64</v>
       </c>
       <c r="C81">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>685.81</v>
+        <v>750.4</v>
       </c>
       <c r="F81">
-        <v>477.85</v>
+        <v>474.16</v>
       </c>
       <c r="G81">
-        <v>479.58</v>
+        <v>551.33</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3865,10 +3865,10 @@
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
       <c r="K81" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L81" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3876,22 +3876,22 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C82">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>673.12</v>
+        <v>681.89</v>
       </c>
       <c r="F82">
-        <v>474.85</v>
+        <v>458.94</v>
       </c>
       <c r="G82">
-        <v>502.77</v>
+        <v>472.78</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3903,7 +3903,7 @@
         <f>IF(D82=0,"",(H82-D82)/D82)</f>
       </c>
       <c r="K82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L82" t="s">
         <v>21</v>
@@ -3914,7 +3914,7 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="C83">
         <v>6.11</v>
@@ -3923,13 +3923,13 @@
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>681.89</v>
+        <v>629.76</v>
       </c>
       <c r="F83">
-        <v>461.59</v>
+        <v>505.07</v>
       </c>
       <c r="G83">
-        <v>453.17</v>
+        <v>480.62</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3944,7 +3944,7 @@
         <v>65</v>
       </c>
       <c r="L83" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3952,22 +3952,22 @@
         <v>114</v>
       </c>
       <c r="B84">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C84">
-        <v>6.03</v>
+        <v>6.05</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>466.67</v>
+        <v>684.2</v>
       </c>
       <c r="F84">
-        <v>334.49</v>
+        <v>461.82</v>
       </c>
       <c r="G84">
-        <v>336.22</v>
+        <v>450.4</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3990,22 +3990,22 @@
         <v>115</v>
       </c>
       <c r="B85">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C85">
-        <v>5.85</v>
+        <v>6.03</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>685</v>
+        <v>466.67</v>
       </c>
       <c r="F85">
-        <v>419.03</v>
+        <v>334.49</v>
       </c>
       <c r="G85">
-        <v>391</v>
+        <v>339.1</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4020,7 +4020,7 @@
         <v>65</v>
       </c>
       <c r="L85" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4028,22 +4028,22 @@
         <v>116</v>
       </c>
       <c r="B86">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="C86">
-        <v>5.79</v>
+        <v>5.92</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>698.38</v>
+        <v>692.04</v>
       </c>
       <c r="F86">
-        <v>449.6</v>
+        <v>420.41</v>
       </c>
       <c r="G86">
-        <v>432.87</v>
+        <v>420.99</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4066,22 +4066,22 @@
         <v>117</v>
       </c>
       <c r="B87">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C87">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>692.85</v>
+        <v>685</v>
       </c>
       <c r="F87">
-        <v>427.8</v>
+        <v>414.53</v>
       </c>
       <c r="G87">
-        <v>448.33</v>
+        <v>389.73</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4096,7 +4096,7 @@
         <v>65</v>
       </c>
       <c r="L87" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4104,22 +4104,22 @@
         <v>118</v>
       </c>
       <c r="B88">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="C88">
-        <v>5.59</v>
+        <v>5.79</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>620.3</v>
+        <v>630.56</v>
       </c>
       <c r="F88">
-        <v>454.67</v>
+        <v>483.27</v>
       </c>
       <c r="G88">
-        <v>406</v>
+        <v>434.02</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4134,7 +4134,7 @@
         <v>65</v>
       </c>
       <c r="L88" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4142,22 +4142,22 @@
         <v>119</v>
       </c>
       <c r="B89">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="C89">
-        <v>5.54</v>
+        <v>5.59</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>599.88</v>
+        <v>608.53</v>
       </c>
       <c r="F89">
-        <v>510.96</v>
+        <v>453.4</v>
       </c>
       <c r="G89">
-        <v>444.06</v>
+        <v>410.61</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4172,7 +4172,7 @@
         <v>65</v>
       </c>
       <c r="L89" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4180,22 +4180,22 @@
         <v>120</v>
       </c>
       <c r="B90">
-        <v>226</v>
+        <v>117</v>
       </c>
       <c r="C90">
-        <v>5.53</v>
+        <v>5.48</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>634.49</v>
+        <v>602.19</v>
       </c>
       <c r="F90">
-        <v>507.38</v>
+        <v>492.5</v>
       </c>
       <c r="G90">
-        <v>481.89</v>
+        <v>444.06</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4210,7 +4210,7 @@
         <v>65</v>
       </c>
       <c r="L90" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4218,22 +4218,22 @@
         <v>121</v>
       </c>
       <c r="B91">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="C91">
-        <v>5.52</v>
+        <v>5.43</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>572.2</v>
+        <v>583.27</v>
       </c>
       <c r="F91">
-        <v>415.22</v>
+        <v>403.69</v>
       </c>
       <c r="G91">
-        <v>428.95</v>
+        <v>420.99</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4256,22 +4256,22 @@
         <v>122</v>
       </c>
       <c r="B92">
-        <v>511</v>
+        <v>105</v>
       </c>
       <c r="C92">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>576.24</v>
+        <v>622.72</v>
       </c>
       <c r="F92">
-        <v>397.92</v>
+        <v>438.29</v>
       </c>
       <c r="G92">
-        <v>385.24</v>
+        <v>403.69</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4294,22 +4294,22 @@
         <v>123</v>
       </c>
       <c r="B93">
-        <v>123</v>
+        <v>693</v>
       </c>
       <c r="C93">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>600.69</v>
+        <v>629.76</v>
       </c>
       <c r="F93">
-        <v>445.21</v>
+        <v>423.3</v>
       </c>
       <c r="G93">
-        <v>402.54</v>
+        <v>417.42</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4321,10 +4321,10 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L93" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4332,7 +4332,7 @@
         <v>124</v>
       </c>
       <c r="B94">
-        <v>871</v>
+        <v>454</v>
       </c>
       <c r="C94">
         <v>5.32</v>
@@ -4341,13 +4341,13 @@
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>585.7</v>
+        <v>594.35</v>
       </c>
       <c r="F94">
-        <v>403.69</v>
+        <v>397.92</v>
       </c>
       <c r="G94">
-        <v>422.14</v>
+        <v>369.09</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4359,10 +4359,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L94" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4370,22 +4370,22 @@
         <v>125</v>
       </c>
       <c r="B95">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C95">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>577.74</v>
+        <v>580.16</v>
       </c>
       <c r="F95">
-        <v>401.15</v>
+        <v>369.09</v>
       </c>
       <c r="G95">
-        <v>411.19</v>
+        <v>401.38</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4408,22 +4408,22 @@
         <v>126</v>
       </c>
       <c r="B96">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C96">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>567.47</v>
+        <v>611.65</v>
       </c>
       <c r="F96">
-        <v>412.23</v>
+        <v>409.46</v>
       </c>
       <c r="G96">
-        <v>388.7</v>
+        <v>378.32</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4435,33 +4435,33 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="L96" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B97">
-        <v>504</v>
+        <v>66</v>
       </c>
       <c r="C97">
-        <v>5.08</v>
+        <v>5.2</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>563.55</v>
+        <v>567.47</v>
       </c>
       <c r="F97">
-        <v>363.32</v>
+        <v>412.23</v>
       </c>
       <c r="G97">
-        <v>391.93</v>
+        <v>386.39</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4473,10 +4473,10 @@
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
       <c r="K97" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L97" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4484,22 +4484,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>72</v>
+        <v>322</v>
       </c>
       <c r="C98">
-        <v>4.91</v>
+        <v>5.02</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>580.16</v>
+        <v>590.43</v>
       </c>
       <c r="F98">
-        <v>381.89</v>
+        <v>367.93</v>
       </c>
       <c r="G98">
-        <v>374.86</v>
+        <v>391.69</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4511,10 +4511,10 @@
         <f>IF(D98=0,"",(H98-D98)/D98)</f>
       </c>
       <c r="K98" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L98" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4522,22 +4522,22 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="C99">
-        <v>4.73</v>
+        <v>4.88</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>592.73</v>
+        <v>580.16</v>
       </c>
       <c r="F99">
-        <v>410.84</v>
+        <v>379.58</v>
       </c>
       <c r="G99">
-        <v>378.32</v>
+        <v>371.39</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4560,22 +4560,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>639</v>
+        <v>432</v>
       </c>
       <c r="C100">
-        <v>4.72</v>
+        <v>4.76</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>502.88</v>
+        <v>520.99</v>
       </c>
       <c r="F100">
-        <v>357.9</v>
+        <v>351.79</v>
       </c>
       <c r="G100">
-        <v>363.09</v>
+        <v>362.97</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4598,22 +4598,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="C101">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>535.18</v>
+        <v>580.16</v>
       </c>
       <c r="F101">
-        <v>333.33</v>
+        <v>369.09</v>
       </c>
       <c r="G101">
-        <v>373.47</v>
+        <v>382.7</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4625,10 +4625,10 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L101" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4636,22 +4636,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C102">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>518.68</v>
+        <v>521.8</v>
       </c>
       <c r="F102">
-        <v>372.43</v>
+        <v>332.18</v>
       </c>
       <c r="G102">
-        <v>380.62</v>
+        <v>372.32</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4663,10 +4663,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L102" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4674,10 +4674,10 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C103">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
@@ -4686,7 +4686,7 @@
         <v>521.8</v>
       </c>
       <c r="F103">
-        <v>359.17</v>
+        <v>368.97</v>
       </c>
       <c r="G103">
         <v>351.79</v>
@@ -4712,22 +4712,22 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="C104">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>565.97</v>
+        <v>477.62</v>
       </c>
       <c r="F104">
-        <v>343.6</v>
+        <v>333.1</v>
       </c>
       <c r="G104">
-        <v>336.79</v>
+        <v>342.33</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4742,7 +4742,7 @@
         <v>65</v>
       </c>
       <c r="L104" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4750,22 +4750,22 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="C105">
-        <v>4.42</v>
+        <v>4.54</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>487.08</v>
+        <v>565.17</v>
       </c>
       <c r="F105">
-        <v>321.57</v>
+        <v>344.75</v>
       </c>
       <c r="G105">
-        <v>291.58</v>
+        <v>333.33</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4788,7 +4788,7 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="C106">
         <v>4.41</v>
@@ -4797,13 +4797,13 @@
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>480.05</v>
+        <v>453.17</v>
       </c>
       <c r="F106">
-        <v>339.21</v>
+        <v>321.68</v>
       </c>
       <c r="G106">
-        <v>332.18</v>
+        <v>290.43</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4818,7 +4818,7 @@
         <v>65</v>
       </c>
       <c r="L106" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4826,10 +4826,10 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C107">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
@@ -4864,10 +4864,10 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C108">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
@@ -4876,10 +4876,10 @@
         <v>475.32</v>
       </c>
       <c r="F108">
-        <v>339.79</v>
+        <v>339.68</v>
       </c>
       <c r="G108">
-        <v>361.82</v>
+        <v>343.14</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4902,22 +4902,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>2449</v>
+        <v>1574</v>
       </c>
       <c r="C109">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>496.54</v>
+        <v>465.86</v>
       </c>
       <c r="F109">
         <v>334.49</v>
       </c>
       <c r="G109">
-        <v>322.95</v>
+        <v>327.33</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4940,7 +4940,7 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C110">
         <v>4.19</v>
@@ -4949,13 +4949,13 @@
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>530.45</v>
+        <v>525.72</v>
       </c>
       <c r="F110">
-        <v>303.34</v>
+        <v>305.65</v>
       </c>
       <c r="G110">
-        <v>303.34</v>
+        <v>303.23</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4978,22 +4978,22 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="C111">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>420.88</v>
+        <v>412.23</v>
       </c>
       <c r="F111">
-        <v>312.46</v>
+        <v>334.49</v>
       </c>
       <c r="G111">
-        <v>310.26</v>
+        <v>325.03</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -5016,7 +5016,7 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="C112">
         <v>3.86</v>
@@ -5025,13 +5025,13 @@
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>440.6</v>
+        <v>439.79</v>
       </c>
       <c r="F112">
-        <v>310.96</v>
+        <v>311.42</v>
       </c>
       <c r="G112">
-        <v>290.54</v>
+        <v>292.96</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5054,22 +5054,22 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C113">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>394.12</v>
+        <v>402.77</v>
       </c>
       <c r="F113">
-        <v>295.27</v>
+        <v>288.12</v>
       </c>
       <c r="G113">
-        <v>277.97</v>
+        <v>282.58</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5092,22 +5092,22 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>365</v>
+        <v>61</v>
       </c>
       <c r="C114">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>402.77</v>
+        <v>476.82</v>
       </c>
       <c r="F114">
-        <v>287.2</v>
+        <v>265.51</v>
       </c>
       <c r="G114">
-        <v>286.97</v>
+        <v>279.12</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5119,10 +5119,10 @@
         <f>IF(D114=0,"",(H114-D114)/D114)</f>
       </c>
       <c r="K114" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L114" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5130,22 +5130,22 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>74</v>
+        <v>300</v>
       </c>
       <c r="C115">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>486.39</v>
+        <v>401.15</v>
       </c>
       <c r="F115">
-        <v>269.9</v>
+        <v>283.74</v>
       </c>
       <c r="G115">
-        <v>288.35</v>
+        <v>276.82</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5157,10 +5157,10 @@
         <f>IF(D115=0,"",(H115-D115)/D115)</f>
       </c>
       <c r="K115" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L115" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5168,22 +5168,22 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C116">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>394.12</v>
+        <v>362.51</v>
       </c>
       <c r="F116">
-        <v>286.97</v>
+        <v>256.98</v>
       </c>
       <c r="G116">
-        <v>275.66</v>
+        <v>258.82</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5195,10 +5195,10 @@
         <f>IF(D116=0,"",(H116-D116)/D116)</f>
       </c>
       <c r="K116" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L116" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5206,22 +5206,22 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C117">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>464.24</v>
+        <v>393.31</v>
       </c>
       <c r="F117">
-        <v>259.52</v>
+        <v>283.51</v>
       </c>
       <c r="G117">
-        <v>266.44</v>
+        <v>281.43</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5233,10 +5233,10 @@
         <f>IF(D117=0,"",(H117-D117)/D117)</f>
       </c>
       <c r="K117" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L117" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5244,22 +5244,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C118">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>364.94</v>
+        <v>439.79</v>
       </c>
       <c r="F118">
-        <v>252.36</v>
+        <v>281.43</v>
       </c>
       <c r="G118">
-        <v>259.17</v>
+        <v>265.17</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5271,10 +5271,10 @@
         <f>IF(D118=0,"",(H118-D118)/D118)</f>
       </c>
       <c r="K118" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="L118" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5282,22 +5282,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C119">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>349.94</v>
+        <v>404.38</v>
       </c>
       <c r="F119">
-        <v>253.75</v>
+        <v>236.45</v>
       </c>
       <c r="G119">
-        <v>239.79</v>
+        <v>257.78</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5312,7 +5312,7 @@
         <v>23</v>
       </c>
       <c r="L119" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5320,22 +5320,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C120">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>382.24</v>
+        <v>375.2</v>
       </c>
       <c r="F120">
-        <v>254.79</v>
+        <v>253.63</v>
       </c>
       <c r="G120">
-        <v>246.83</v>
+        <v>242.21</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5358,7 +5358,7 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="C121">
         <v>3.24</v>
@@ -5367,13 +5367,13 @@
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>340.48</v>
+        <v>353.86</v>
       </c>
       <c r="F121">
-        <v>236.33</v>
+        <v>232.99</v>
       </c>
       <c r="G121">
-        <v>234.95</v>
+        <v>234.49</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5396,19 +5396,19 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>294</v>
+        <v>239</v>
       </c>
       <c r="C122">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>360.21</v>
+        <v>362.51</v>
       </c>
       <c r="F122">
-        <v>250.29</v>
+        <v>262.98</v>
       </c>
       <c r="G122">
         <v>242.21</v>
@@ -5434,22 +5434,22 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="C123">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>326.3</v>
+        <v>311.3</v>
       </c>
       <c r="F123">
-        <v>214.3</v>
+        <v>222.95</v>
       </c>
       <c r="G123">
-        <v>208.77</v>
+        <v>221.34</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5464,7 +5464,7 @@
         <v>23</v>
       </c>
       <c r="L123" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5472,22 +5472,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="C124">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>334.95</v>
+        <v>331.83</v>
       </c>
       <c r="F124">
-        <v>218.11</v>
+        <v>226.07</v>
       </c>
       <c r="G124">
-        <v>217.76</v>
+        <v>221.45</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5510,22 +5510,22 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="C125">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>297.12</v>
+        <v>323.99</v>
       </c>
       <c r="F125">
-        <v>226.07</v>
+        <v>212.23</v>
       </c>
       <c r="G125">
-        <v>222.61</v>
+        <v>206.92</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5540,7 +5540,7 @@
         <v>23</v>
       </c>
       <c r="L125" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5548,19 +5548,19 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C126">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>367.24</v>
+        <v>353.06</v>
       </c>
       <c r="F126">
-        <v>191.93</v>
+        <v>189.16</v>
       </c>
       <c r="G126">
         <v>191.46</v>
@@ -5575,7 +5575,7 @@
         <f>IF(D126=0,"",(H126-D126)/D126)</f>
       </c>
       <c r="K126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L126" t="s">
         <v>21</v>
@@ -5586,22 +5586,22 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C127">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>279.01</v>
+        <v>275.89</v>
       </c>
       <c r="F127">
         <v>173.01</v>
       </c>
       <c r="G127">
-        <v>169.43</v>
+        <v>171.74</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5624,7 +5624,7 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C128">
         <v>2.23</v>
@@ -5636,10 +5636,10 @@
         <v>287.66</v>
       </c>
       <c r="F128">
-        <v>177.51</v>
+        <v>175.09</v>
       </c>
       <c r="G128">
-        <v>183.39</v>
+        <v>175.32</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5662,10 +5662,10 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C129">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
@@ -5674,10 +5674,10 @@
         <v>249.83</v>
       </c>
       <c r="F129">
-        <v>183.39</v>
+        <v>178.78</v>
       </c>
       <c r="G129">
-        <v>188</v>
+        <v>186.85</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5700,22 +5700,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C130">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>230.91</v>
+        <v>215.11</v>
       </c>
       <c r="F130">
-        <v>174.28</v>
+        <v>169.9</v>
       </c>
       <c r="G130">
-        <v>174.16</v>
+        <v>171.86</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5738,22 +5738,22 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C131">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
       </c>
       <c r="E131">
-        <v>211.19</v>
+        <v>211.99</v>
       </c>
       <c r="F131">
-        <v>146.14</v>
+        <v>142.56</v>
       </c>
       <c r="G131">
-        <v>152.25</v>
+        <v>149.94</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5776,10 +5776,10 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="C132">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
@@ -5791,7 +5791,7 @@
         <v>133.45</v>
       </c>
       <c r="G132">
-        <v>143.02</v>
+        <v>137.25</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5814,22 +5814,22 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C133">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>171.74</v>
+        <v>175.78</v>
       </c>
       <c r="F133">
-        <v>125.72</v>
+        <v>126.87</v>
       </c>
       <c r="G133">
-        <v>139.56</v>
+        <v>137.25</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5852,22 +5852,22 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>298</v>
+        <v>191</v>
       </c>
       <c r="C134">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>163.09</v>
+        <v>164.71</v>
       </c>
       <c r="F134">
-        <v>120.88</v>
+        <v>114.99</v>
       </c>
       <c r="G134">
-        <v>122.61</v>
+        <v>116.49</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5890,22 +5890,22 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C135">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>166.32</v>
+        <v>167.82</v>
       </c>
       <c r="F135">
-        <v>115.92</v>
+        <v>114.42</v>
       </c>
       <c r="G135">
-        <v>123.3</v>
+        <v>115.22</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5928,10 +5928,10 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>1030</v>
+        <v>752</v>
       </c>
       <c r="C136">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="D136">
         <f>C136*$B$3</f>
@@ -5940,10 +5940,10 @@
         <v>155.25</v>
       </c>
       <c r="F136">
-        <v>107.04</v>
+        <v>105.77</v>
       </c>
       <c r="G136">
-        <v>104.5</v>
+        <v>103.69</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5966,10 +5966,10 @@
         <v>168</v>
       </c>
       <c r="B137">
-        <v>559</v>
+        <v>463</v>
       </c>
       <c r="C137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="D137">
         <f>C137*$B$3</f>
@@ -5978,10 +5978,10 @@
         <v>121.34</v>
       </c>
       <c r="F137">
-        <v>74.86</v>
+        <v>73.01</v>
       </c>
       <c r="G137">
-        <v>80.51</v>
+        <v>77.28</v>
       </c>
       <c r="H137">
         <f>MIN(E137:G137)</f>
@@ -6004,10 +6004,10 @@
         <v>169</v>
       </c>
       <c r="B138">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="C138">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D138">
         <f>C138*$B$3</f>
@@ -6016,10 +6016,10 @@
         <v>92.96</v>
       </c>
       <c r="F138">
-        <v>65.97</v>
+        <v>62.28</v>
       </c>
       <c r="G138">
-        <v>64.24</v>
+        <v>64.13</v>
       </c>
       <c r="H138">
         <f>MIN(E138:G138)</f>
@@ -6042,22 +6042,22 @@
         <v>170</v>
       </c>
       <c r="B139">
-        <v>346</v>
+        <v>268</v>
       </c>
       <c r="C139">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="D139">
         <f>C139*$B$3</f>
       </c>
       <c r="E139">
-        <v>81.08</v>
+        <v>81.89</v>
       </c>
       <c r="F139">
-        <v>50.06</v>
+        <v>47.17</v>
       </c>
       <c r="G139">
-        <v>50.52</v>
+        <v>49.37</v>
       </c>
       <c r="H139">
         <f>MIN(E139:G139)</f>
@@ -6080,22 +6080,22 @@
         <v>171</v>
       </c>
       <c r="B140">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C140">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="D140">
         <f>C140*$B$3</f>
       </c>
       <c r="E140">
-        <v>66.9</v>
+        <v>59.86</v>
       </c>
       <c r="F140">
+        <v>36.79</v>
+      </c>
+      <c r="G140">
         <v>34.26</v>
-      </c>
-      <c r="G140">
-        <v>35.64</v>
       </c>
       <c r="H140">
         <f>MIN(E140:G140)</f>
@@ -6107,7 +6107,7 @@
         <f>IF(D140=0,"",(H140-D140)/D140)</f>
       </c>
       <c r="K140" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L140" t="s">
         <v>19</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 19.07.2026 16:35</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 19.07.2026 20:16</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -118,12 +118,12 @@
     <t>USP-S | Orion (Minimal Wear)</t>
   </si>
   <si>
+    <t>MAC-10 | Fade (Factory New)</t>
+  </si>
+  <si>
     <t>USP-S | Whiteout (Field-Tested)</t>
   </si>
   <si>
-    <t>MAC-10 | Fade (Factory New)</t>
-  </si>
-  <si>
     <t>AWP | Neo-Noir (Factory New)</t>
   </si>
   <si>
@@ -139,12 +139,12 @@
     <t>MP9 | Hydra (Factory New)</t>
   </si>
   <si>
+    <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
+  </si>
+  <si>
     <t>Desert Eagle | Starcade (Field-Tested)</t>
   </si>
   <si>
-    <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
-  </si>
-  <si>
     <t>CZ75-Auto | Emerald (Factory New)</t>
   </si>
   <si>
@@ -181,12 +181,12 @@
     <t>FAMAS | Styx (Minimal Wear)</t>
   </si>
   <si>
+    <t>Safecracker Voltzmann | The Professionals</t>
+  </si>
+  <si>
     <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
-    <t>Safecracker Voltzmann | The Professionals</t>
-  </si>
-  <si>
     <t>Nova | Sobek's Bite (Factory New)</t>
   </si>
   <si>
@@ -205,6 +205,9 @@
     <t>Nova | Sobek's Bite (Minimal Wear)</t>
   </si>
   <si>
+    <t>Michael Syfers  | FBI Sniper</t>
+  </si>
+  <si>
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -223,9 +226,6 @@
     <t>Master</t>
   </si>
   <si>
-    <t>Michael Syfers  | FBI Sniper</t>
-  </si>
-  <si>
     <t>Sticker | Great Wave (Foil)</t>
   </si>
   <si>
@@ -247,12 +247,12 @@
     <t>The Elite Mr. Muhlik | Elite Crew</t>
   </si>
   <si>
+    <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>USP-S | Guardian (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>FAMAS | Styx (Field-Tested)</t>
   </si>
   <si>
@@ -268,6 +268,9 @@
     <t>Exceptional</t>
   </si>
   <si>
+    <t>Five-SeveN | Kami (Factory New)</t>
+  </si>
+  <si>
     <t>B Squadron Officer | SAS</t>
   </si>
   <si>
@@ -286,9 +289,6 @@
     <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Five-SeveN | Kami (Factory New)</t>
-  </si>
-  <si>
     <t>MP7 | Fade (Minimal Wear)</t>
   </si>
   <si>
@@ -301,21 +301,21 @@
     <t>MP7 | Fade (Field-Tested)</t>
   </si>
   <si>
+    <t>Slingshot | Phoenix</t>
+  </si>
+  <si>
     <t>SG 553 | Integrale (Field-Tested)</t>
   </si>
   <si>
-    <t>Slingshot | Phoenix</t>
+    <t>Rezan the Redshirt | Sabre</t>
+  </si>
+  <si>
+    <t>Rezan The Ready | Sabre</t>
   </si>
   <si>
     <t>Blackwolf | Sabre</t>
   </si>
   <si>
-    <t>Rezan The Ready | Sabre</t>
-  </si>
-  <si>
-    <t>Rezan the Redshirt | Sabre</t>
-  </si>
-  <si>
     <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
+  </si>
+  <si>
     <t>AK-47 | Crossfade (Factory New)</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -373,24 +373,24 @@
     <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
   </si>
   <si>
     <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+    <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
     <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>CZ75-Auto | Tacticat (Factory New)</t>
-  </si>
-  <si>
     <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -412,31 +412,31 @@
     <t>Sticker | Stone Scales (Foil)</t>
   </si>
   <si>
+    <t>Sticker | Gold Web (Foil)</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Gold Web (Foil)</t>
+    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AK-47 | Slate (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Slate (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | Team Liquid (Holo) | Stockholm 2021</t>
@@ -933,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.97</v>
+        <v>81.93</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -988,10 +988,10 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C6">
-        <v>160.76</v>
+        <v>165.76</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
@@ -1026,10 +1026,10 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>138.08</v>
+        <v>136.81</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -1041,7 +1041,7 @@
         <v>10605.51</v>
       </c>
       <c r="G7">
-        <v>10011.51</v>
+        <v>9919.24</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1064,22 +1064,22 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C8">
-        <v>119.73</v>
+        <v>118.36</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>14611.39</v>
+        <v>14587.74</v>
       </c>
       <c r="F8">
         <v>8869.65</v>
       </c>
       <c r="G8">
-        <v>8869.65</v>
+        <v>8835.04</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1102,10 +1102,10 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9">
-        <v>96.62</v>
+        <v>98.09</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
@@ -1114,10 +1114,10 @@
         <v>10635.04</v>
       </c>
       <c r="F9">
-        <v>7600.91</v>
+        <v>7589.37</v>
       </c>
       <c r="G9">
-        <v>7324.09</v>
+        <v>7312.56</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1140,10 +1140,10 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C10">
-        <v>88.06</v>
+        <v>85.72</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1152,10 +1152,10 @@
         <v>9008.75</v>
       </c>
       <c r="F10">
-        <v>6574.38</v>
+        <v>6578.99</v>
       </c>
       <c r="G10">
-        <v>6470.57</v>
+        <v>6215.44</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1178,22 +1178,22 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11">
-        <v>85.13</v>
+        <v>85.59</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>8653.27</v>
+        <v>9065.61</v>
       </c>
       <c r="F11">
         <v>6205.29</v>
       </c>
       <c r="G11">
-        <v>6395.6</v>
+        <v>6401.25</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1216,19 +1216,19 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="C12">
-        <v>80.84</v>
+        <v>81.24</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>8189.72</v>
+        <v>8788.91</v>
       </c>
       <c r="F12">
-        <v>5913.25</v>
+        <v>5913.02</v>
       </c>
       <c r="G12">
         <v>5905.41</v>
@@ -1292,22 +1292,22 @@
         <v>33</v>
       </c>
       <c r="B14">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C14">
-        <v>61.5</v>
+        <v>62.9</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>6723.51</v>
+        <v>6574.5</v>
       </c>
       <c r="F14">
-        <v>4595.15</v>
+        <v>4596.18</v>
       </c>
       <c r="G14">
-        <v>4665.5</v>
+        <v>4671.27</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1330,10 +1330,10 @@
         <v>34</v>
       </c>
       <c r="B15">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C15">
-        <v>58.85</v>
+        <v>58.84</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
@@ -1342,10 +1342,10 @@
         <v>6211.06</v>
       </c>
       <c r="F15">
-        <v>4382.92</v>
+        <v>4484.42</v>
       </c>
       <c r="G15">
-        <v>4336.78</v>
+        <v>4313.72</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1368,22 +1368,22 @@
         <v>35</v>
       </c>
       <c r="B16">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="C16">
-        <v>58.19</v>
+        <v>58.08</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>6338.74</v>
+        <v>6336.43</v>
       </c>
       <c r="F16">
-        <v>4244.51</v>
+        <v>4348.32</v>
       </c>
       <c r="G16">
-        <v>4221.44</v>
+        <v>4256.05</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1395,10 +1395,10 @@
         <f>IF(D16=0,"",(H16-D16)/D16)</f>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1406,10 +1406,10 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="C17">
-        <v>58.08</v>
+        <v>58.04</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
@@ -1418,10 +1418,10 @@
         <v>6338.74</v>
       </c>
       <c r="F17">
-        <v>4348.32</v>
+        <v>4238.75</v>
       </c>
       <c r="G17">
-        <v>4261.81</v>
+        <v>4214.52</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1433,10 +1433,10 @@
         <f>IF(D17=0,"",(H17-D17)/D17)</f>
       </c>
       <c r="K17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1444,10 +1444,10 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C18">
-        <v>55.03</v>
+        <v>56.43</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1456,10 +1456,10 @@
         <v>6334.82</v>
       </c>
       <c r="F18">
-        <v>4186.84</v>
+        <v>4238.28</v>
       </c>
       <c r="G18">
-        <v>4134.71</v>
+        <v>4192.49</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1485,19 +1485,19 @@
         <v>260</v>
       </c>
       <c r="C19">
-        <v>53.81</v>
+        <v>53.76</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5939.89</v>
+        <v>5902.06</v>
       </c>
       <c r="F19">
         <v>4036.9</v>
       </c>
       <c r="G19">
-        <v>4019.6</v>
+        <v>4002.3</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1520,7 +1520,7 @@
         <v>39</v>
       </c>
       <c r="B20">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>51.99</v>
@@ -1529,10 +1529,10 @@
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>6117.29</v>
+        <v>6114.87</v>
       </c>
       <c r="F20">
-        <v>3977.96</v>
+        <v>3978.08</v>
       </c>
       <c r="G20">
         <v>3965.39</v>
@@ -1558,10 +1558,10 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21">
-        <v>49.48</v>
+        <v>49.67</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
@@ -1573,7 +1573,7 @@
         <v>3662.05</v>
       </c>
       <c r="G21">
-        <v>3933.09</v>
+        <v>3932.98</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>48.3</v>
@@ -1611,7 +1611,7 @@
         <v>3621.68</v>
       </c>
       <c r="G22">
-        <v>3621.68</v>
+        <v>3575.54</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1634,22 +1634,22 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="C23">
-        <v>48.15</v>
+        <v>47.76</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>5134.24</v>
+        <v>5425.13</v>
       </c>
       <c r="F23">
-        <v>3667.81</v>
+        <v>3719.72</v>
       </c>
       <c r="G23">
-        <v>3540.94</v>
+        <v>3528.6</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1661,7 +1661,7 @@
         <f>IF(D23=0,"",(H23-D23)/D23)</f>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L23" t="s">
         <v>24</v>
@@ -1672,22 +1672,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="C24">
-        <v>47.43</v>
+        <v>47.54</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>5132.63</v>
+        <v>5016.02</v>
       </c>
       <c r="F24">
-        <v>3454.32</v>
+        <v>3633.21</v>
       </c>
       <c r="G24">
-        <v>3540.25</v>
+        <v>3569.77</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1699,7 +1699,7 @@
         <f>IF(D24=0,"",(H24-D24)/D24)</f>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L24" t="s">
         <v>24</v>
@@ -1710,7 +1710,7 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>38.7</v>
@@ -1722,7 +1722,7 @@
         <v>4149.59</v>
       </c>
       <c r="F25">
-        <v>2870.47</v>
+        <v>2911.18</v>
       </c>
       <c r="G25">
         <v>2807.38</v>
@@ -1763,7 +1763,7 @@
         <v>2987.19</v>
       </c>
       <c r="G26">
-        <v>2893.65</v>
+        <v>2768.16</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1801,7 +1801,7 @@
         <v>2617.18</v>
       </c>
       <c r="G27">
-        <v>2704.61</v>
+        <v>2704.15</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1824,7 +1824,7 @@
         <v>47</v>
       </c>
       <c r="B28">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C28">
         <v>32.41</v>
@@ -1836,10 +1836,10 @@
         <v>3930.44</v>
       </c>
       <c r="F28">
-        <v>2445.09</v>
+        <v>2444.4</v>
       </c>
       <c r="G28">
-        <v>2410.61</v>
+        <v>2408.3</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1862,7 +1862,7 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C29">
         <v>31.43</v>
@@ -1871,10 +1871,10 @@
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>3503.22</v>
+        <v>3489.84</v>
       </c>
       <c r="F29">
-        <v>2422.14</v>
+        <v>2513.26</v>
       </c>
       <c r="G29">
         <v>2410.61</v>
@@ -1900,10 +1900,10 @@
         <v>49</v>
       </c>
       <c r="B30">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C30">
-        <v>29.88</v>
+        <v>29.66</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
@@ -1912,10 +1912,10 @@
         <v>3074.39</v>
       </c>
       <c r="F30">
-        <v>2283.62</v>
+        <v>2237.48</v>
       </c>
       <c r="G30">
-        <v>2265.28</v>
+        <v>2162.63</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1938,7 +1938,7 @@
         <v>50</v>
       </c>
       <c r="B31">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C31">
         <v>25.07</v>
@@ -1947,13 +1947,13 @@
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2653.4</v>
+        <v>2708.64</v>
       </c>
       <c r="F31">
-        <v>1923.64</v>
+        <v>1914.53</v>
       </c>
       <c r="G31">
-        <v>1897.34</v>
+        <v>1880.04</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1976,10 +1976,10 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="C32">
-        <v>24.29</v>
+        <v>24.54</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
@@ -1988,10 +1988,10 @@
         <v>3010.49</v>
       </c>
       <c r="F32">
-        <v>1926.18</v>
+        <v>1908.88</v>
       </c>
       <c r="G32">
-        <v>1906.57</v>
+        <v>1916.95</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2014,7 +2014,7 @@
         <v>54</v>
       </c>
       <c r="B33">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C33">
         <v>21.34</v>
@@ -2023,13 +2023,13 @@
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>2252.13</v>
+        <v>2318.33</v>
       </c>
       <c r="F33">
-        <v>1652.59</v>
+        <v>1666.2</v>
       </c>
       <c r="G33">
-        <v>1660.9</v>
+        <v>1659.74</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2052,7 +2052,7 @@
         <v>55</v>
       </c>
       <c r="B34">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>19.8</v>
@@ -2061,13 +2061,13 @@
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>2191.46</v>
+        <v>2186.73</v>
       </c>
       <c r="F34">
-        <v>1473.12</v>
+        <v>1473.01</v>
       </c>
       <c r="G34">
-        <v>1497.11</v>
+        <v>1502.88</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2090,22 +2090,22 @@
         <v>56</v>
       </c>
       <c r="B35">
-        <v>146</v>
+        <v>758</v>
       </c>
       <c r="C35">
-        <v>19.16</v>
+        <v>19.49</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>2327.79</v>
+        <v>2297.11</v>
       </c>
       <c r="F35">
-        <v>1481.77</v>
+        <v>1510.95</v>
       </c>
       <c r="G35">
-        <v>1430.22</v>
+        <v>1493.65</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2117,10 +2117,10 @@
         <f>IF(D35=0,"",(H35-D35)/D35)</f>
       </c>
       <c r="K35" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2128,22 +2128,22 @@
         <v>57</v>
       </c>
       <c r="B36">
-        <v>803</v>
+        <v>133</v>
       </c>
       <c r="C36">
-        <v>19.14</v>
+        <v>19.16</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>2288.46</v>
+        <v>2327.79</v>
       </c>
       <c r="F36">
-        <v>1493.65</v>
+        <v>1481.77</v>
       </c>
       <c r="G36">
-        <v>1479.81</v>
+        <v>1430.22</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2155,10 +2155,10 @@
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
       <c r="K36" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L36" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2166,7 +2166,7 @@
         <v>58</v>
       </c>
       <c r="B37">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C37">
         <v>18.95</v>
@@ -2175,13 +2175,13 @@
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2250.63</v>
+        <v>2162.28</v>
       </c>
       <c r="F37">
-        <v>1441.75</v>
+        <v>1441.63</v>
       </c>
       <c r="G37">
-        <v>1416.26</v>
+        <v>1444.86</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2204,7 +2204,7 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C38">
         <v>18.35</v>
@@ -2213,13 +2213,13 @@
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>2167.82</v>
+        <v>2163.89</v>
       </c>
       <c r="F38">
-        <v>1444.06</v>
+        <v>1442.9</v>
       </c>
       <c r="G38">
-        <v>1384.08</v>
+        <v>1382.7</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2242,7 +2242,7 @@
         <v>61</v>
       </c>
       <c r="B39">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C39">
         <v>15.89</v>
@@ -2280,10 +2280,10 @@
         <v>62</v>
       </c>
       <c r="B40">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C40">
-        <v>14.98</v>
+        <v>14.84</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
@@ -2295,7 +2295,7 @@
         <v>1158.94</v>
       </c>
       <c r="G40">
-        <v>1147.63</v>
+        <v>1141.87</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2318,7 +2318,7 @@
         <v>63</v>
       </c>
       <c r="B41">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C41">
         <v>13.94</v>
@@ -2330,7 +2330,7 @@
         <v>1455.94</v>
       </c>
       <c r="F41">
-        <v>1049.59</v>
+        <v>1061.01</v>
       </c>
       <c r="G41">
         <v>1092.27</v>
@@ -2356,22 +2356,22 @@
         <v>64</v>
       </c>
       <c r="B42">
-        <v>66</v>
+        <v>1158</v>
       </c>
       <c r="C42">
-        <v>13.54</v>
+        <v>13.86</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1536.33</v>
+        <v>1455.13</v>
       </c>
       <c r="F42">
-        <v>980.39</v>
+        <v>1038.06</v>
       </c>
       <c r="G42">
-        <v>935.98</v>
+        <v>1033.22</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2383,33 +2383,33 @@
         <f>IF(D42=0,"",(H42-D42)/D42)</f>
       </c>
       <c r="K42" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L42" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B43">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C43">
-        <v>13.44</v>
+        <v>13.54</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1567.93</v>
+        <v>1536.33</v>
       </c>
       <c r="F43">
-        <v>975.78</v>
+        <v>980.39</v>
       </c>
       <c r="G43">
-        <v>1035.75</v>
+        <v>936.91</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2421,10 +2421,10 @@
         <f>IF(D43=0,"",(H43-D43)/D43)</f>
       </c>
       <c r="K43" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2432,22 +2432,22 @@
         <v>68</v>
       </c>
       <c r="B44">
-        <v>1128</v>
+        <v>51</v>
       </c>
       <c r="C44">
-        <v>13.34</v>
+        <v>13.44</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1546.59</v>
+        <v>1448.09</v>
       </c>
       <c r="F44">
-        <v>1049.59</v>
+        <v>975.78</v>
       </c>
       <c r="G44">
-        <v>1070.82</v>
+        <v>1035.75</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2459,33 +2459,33 @@
         <f>IF(D44=0,"",(H44-D44)/D44)</f>
       </c>
       <c r="K44" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B45">
-        <v>1178</v>
+        <v>1104</v>
       </c>
       <c r="C45">
-        <v>13.3</v>
+        <v>13.36</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1531.6</v>
+        <v>1546.59</v>
       </c>
       <c r="F45">
-        <v>1026.53</v>
+        <v>1083.85</v>
       </c>
       <c r="G45">
-        <v>1055.25</v>
+        <v>1066.78</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2500,7 +2500,7 @@
         <v>52</v>
       </c>
       <c r="L45" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2520,7 +2520,7 @@
         <v>1418.11</v>
       </c>
       <c r="F46">
-        <v>1031.25</v>
+        <v>1031.02</v>
       </c>
       <c r="G46">
         <v>977.28</v>
@@ -2535,7 +2535,7 @@
         <f>IF(D46=0,"",(H46-D46)/D46)</f>
       </c>
       <c r="K46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L46" t="s">
         <v>72</v>
@@ -2546,10 +2546,10 @@
         <v>73</v>
       </c>
       <c r="B47">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C47">
-        <v>12.08</v>
+        <v>12.11</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
@@ -2558,10 +2558,10 @@
         <v>1372.43</v>
       </c>
       <c r="F47">
-        <v>922.72</v>
+        <v>957.32</v>
       </c>
       <c r="G47">
-        <v>926.18</v>
+        <v>925.03</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2584,10 +2584,10 @@
         <v>74</v>
       </c>
       <c r="B48">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C48">
-        <v>12.08</v>
+        <v>11.94</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
@@ -2596,7 +2596,7 @@
         <v>1330.56</v>
       </c>
       <c r="F48">
-        <v>978.66</v>
+        <v>974.39</v>
       </c>
       <c r="G48">
         <v>934.25</v>
@@ -2622,16 +2622,16 @@
         <v>76</v>
       </c>
       <c r="B49">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C49">
-        <v>11.49</v>
+        <v>11.64</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1263.67</v>
+        <v>1252.59</v>
       </c>
       <c r="F49">
         <v>839.68</v>
@@ -2660,22 +2660,22 @@
         <v>77</v>
       </c>
       <c r="B50">
-        <v>1479</v>
+        <v>1376</v>
       </c>
       <c r="C50">
-        <v>10.9</v>
+        <v>11.04</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1381.89</v>
+        <v>1357.44</v>
       </c>
       <c r="F50">
-        <v>851.44</v>
+        <v>830.45</v>
       </c>
       <c r="G50">
-        <v>830.45</v>
+        <v>837.95</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2690,7 +2690,7 @@
         <v>52</v>
       </c>
       <c r="L50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2698,22 +2698,22 @@
         <v>78</v>
       </c>
       <c r="B51">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="C51">
-        <v>10.62</v>
+        <v>10.38</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1112.22</v>
+        <v>1160.32</v>
       </c>
       <c r="F51">
-        <v>757.32</v>
+        <v>781.77</v>
       </c>
       <c r="G51">
-        <v>760.09</v>
+        <v>755.48</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2725,10 +2725,10 @@
         <f>IF(D51=0,"",(H51-D51)/D51)</f>
       </c>
       <c r="K51" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2736,22 +2736,22 @@
         <v>79</v>
       </c>
       <c r="B52">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="C52">
-        <v>10.38</v>
+        <v>10.17</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1160.32</v>
+        <v>1112.22</v>
       </c>
       <c r="F52">
-        <v>782.01</v>
+        <v>699.65</v>
       </c>
       <c r="G52">
-        <v>761.24</v>
+        <v>738.06</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2763,10 +2763,10 @@
         <f>IF(D52=0,"",(H52-D52)/D52)</f>
       </c>
       <c r="K52" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L52" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2774,7 +2774,7 @@
         <v>80</v>
       </c>
       <c r="B53">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C53">
         <v>10.14</v>
@@ -2789,7 +2789,7 @@
         <v>753.63</v>
       </c>
       <c r="G53">
-        <v>807.38</v>
+        <v>820.64</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2812,10 +2812,10 @@
         <v>81</v>
       </c>
       <c r="B54">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C54">
-        <v>10.06</v>
+        <v>10.07</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
@@ -2824,10 +2824,10 @@
         <v>1080.74</v>
       </c>
       <c r="F54">
-        <v>724.22</v>
+        <v>724.1</v>
       </c>
       <c r="G54">
-        <v>713.72</v>
+        <v>703.57</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2850,7 +2850,7 @@
         <v>82</v>
       </c>
       <c r="B55">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>9.96</v>
@@ -2859,13 +2859,13 @@
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1111.42</v>
+        <v>1135.87</v>
       </c>
       <c r="F55">
         <v>756.05</v>
       </c>
       <c r="G55">
-        <v>786.5</v>
+        <v>785.12</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2888,22 +2888,22 @@
         <v>83</v>
       </c>
       <c r="B56">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C56">
-        <v>9.66</v>
+        <v>9.67</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1143.83</v>
+        <v>1073.58</v>
       </c>
       <c r="F56">
-        <v>771.62</v>
+        <v>749.71</v>
       </c>
       <c r="G56">
-        <v>757.55</v>
+        <v>763.55</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2926,22 +2926,22 @@
         <v>85</v>
       </c>
       <c r="B57">
-        <v>795</v>
+        <v>95</v>
       </c>
       <c r="C57">
-        <v>9.52</v>
+        <v>9.59</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1228.95</v>
+        <v>1065.74</v>
       </c>
       <c r="F57">
-        <v>748.56</v>
+        <v>741.52</v>
       </c>
       <c r="G57">
-        <v>725.49</v>
+        <v>749.59</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2953,33 +2953,33 @@
         <f>IF(D57=0,"",(H57-D57)/D57)</f>
       </c>
       <c r="K57" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="L57" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58">
-        <v>70</v>
+        <v>777</v>
       </c>
       <c r="C58">
-        <v>9.47</v>
+        <v>9.53</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1002.65</v>
+        <v>1217.88</v>
       </c>
       <c r="F58">
-        <v>711.42</v>
+        <v>715.11</v>
       </c>
       <c r="G58">
-        <v>741.64</v>
+        <v>726.64</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2991,10 +2991,10 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L58" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3002,22 +3002,22 @@
         <v>88</v>
       </c>
       <c r="B59">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C59">
-        <v>9.02</v>
+        <v>9.47</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>997.11</v>
+        <v>1002.65</v>
       </c>
       <c r="F59">
-        <v>714.99</v>
+        <v>711.42</v>
       </c>
       <c r="G59">
-        <v>754.78</v>
+        <v>739.33</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3029,10 +3029,10 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,22 +3040,22 @@
         <v>89</v>
       </c>
       <c r="B60">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="C60">
-        <v>8.8</v>
+        <v>9.17</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>919.14</v>
+        <v>1008.19</v>
       </c>
       <c r="F60">
-        <v>640.02</v>
+        <v>715.11</v>
       </c>
       <c r="G60">
-        <v>660.55</v>
+        <v>746.13</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3067,10 +3067,10 @@
         <f>IF(D60=0,"",(H60-D60)/D60)</f>
       </c>
       <c r="K60" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="L60" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3078,22 +3078,22 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="C61">
-        <v>8.72</v>
+        <v>8.8</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>1040.48</v>
+        <v>906.46</v>
       </c>
       <c r="F61">
-        <v>678.2</v>
+        <v>653.86</v>
       </c>
       <c r="G61">
-        <v>634.37</v>
+        <v>656.28</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3105,10 +3105,10 @@
         <f>IF(D61=0,"",(H61-D61)/D61)</f>
       </c>
       <c r="K61" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L61" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3116,22 +3116,22 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C62">
-        <v>8.71</v>
+        <v>8.72</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>1065.74</v>
+        <v>1040.48</v>
       </c>
       <c r="F62">
-        <v>746.48</v>
+        <v>678.2</v>
       </c>
       <c r="G62">
-        <v>750.75</v>
+        <v>632.06</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3143,10 +3143,10 @@
         <f>IF(D62=0,"",(H62-D62)/D62)</f>
       </c>
       <c r="K62" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L62" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3154,10 +3154,10 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C63">
-        <v>8.54</v>
+        <v>8.58</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
@@ -3166,10 +3166,10 @@
         <v>985.35</v>
       </c>
       <c r="F63">
-        <v>687.43</v>
+        <v>678.2</v>
       </c>
       <c r="G63">
-        <v>647.75</v>
+        <v>645.9</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3201,7 +3201,7 @@
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>927.79</v>
+        <v>906.46</v>
       </c>
       <c r="F64">
         <v>605.54</v>
@@ -3219,10 +3219,10 @@
         <f>IF(D64=0,"",(H64-D64)/D64)</f>
       </c>
       <c r="K64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L64" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3230,10 +3230,10 @@
         <v>94</v>
       </c>
       <c r="B65">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C65">
-        <v>8.38</v>
+        <v>8.37</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
@@ -3257,10 +3257,10 @@
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
       <c r="K65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3268,10 +3268,10 @@
         <v>95</v>
       </c>
       <c r="B66">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C66">
-        <v>8.29</v>
+        <v>8.3</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
@@ -3280,7 +3280,7 @@
         <v>900.23</v>
       </c>
       <c r="F66">
-        <v>631.37</v>
+        <v>621.68</v>
       </c>
       <c r="G66">
         <v>619.03</v>
@@ -3306,22 +3306,22 @@
         <v>96</v>
       </c>
       <c r="B67">
-        <v>126</v>
+        <v>635</v>
       </c>
       <c r="C67">
-        <v>8.05</v>
+        <v>8.06</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>894.69</v>
+        <v>946.71</v>
       </c>
       <c r="F67">
-        <v>586.97</v>
+        <v>601.15</v>
       </c>
       <c r="G67">
-        <v>576.7</v>
+        <v>588.23</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3333,10 +3333,10 @@
         <f>IF(D67=0,"",(H67-D67)/D67)</f>
       </c>
       <c r="K67" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L67" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3344,22 +3344,22 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>658</v>
+        <v>124</v>
       </c>
       <c r="C68">
-        <v>7.94</v>
+        <v>8.02</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>1002.65</v>
+        <v>890.77</v>
       </c>
       <c r="F68">
-        <v>599.65</v>
+        <v>586.97</v>
       </c>
       <c r="G68">
-        <v>599.77</v>
+        <v>611.3</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3371,10 +3371,10 @@
         <f>IF(D68=0,"",(H68-D68)/D68)</f>
       </c>
       <c r="K68" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L68" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3382,22 +3382,22 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>687</v>
+        <v>603</v>
       </c>
       <c r="C69">
-        <v>7.86</v>
+        <v>7.96</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>924.68</v>
+        <v>876.58</v>
       </c>
       <c r="F69">
-        <v>610.15</v>
+        <v>607.73</v>
       </c>
       <c r="G69">
-        <v>609.57</v>
+        <v>607.84</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3420,22 +3420,22 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>1069</v>
+        <v>1035</v>
       </c>
       <c r="C70">
-        <v>7.84</v>
+        <v>7.91</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>922.26</v>
+        <v>928.6</v>
       </c>
       <c r="F70">
         <v>599.77</v>
       </c>
       <c r="G70">
-        <v>610.15</v>
+        <v>628.6</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3458,22 +3458,22 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>611</v>
+        <v>669</v>
       </c>
       <c r="C71">
-        <v>7.77</v>
+        <v>7.9</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>881.31</v>
+        <v>962.51</v>
       </c>
       <c r="F71">
-        <v>606.11</v>
+        <v>620.53</v>
       </c>
       <c r="G71">
-        <v>590.89</v>
+        <v>611.07</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3496,7 +3496,7 @@
         <v>101</v>
       </c>
       <c r="B72">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C72">
         <v>7.62</v>
@@ -3508,7 +3508,7 @@
         <v>768.51</v>
       </c>
       <c r="F72">
-        <v>551.56</v>
+        <v>550.29</v>
       </c>
       <c r="G72">
         <v>550.17</v>
@@ -3523,10 +3523,10 @@
         <f>IF(D72=0,"",(H72-D72)/D72)</f>
       </c>
       <c r="K72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <v>102</v>
       </c>
       <c r="B73">
-        <v>836</v>
+        <v>809</v>
       </c>
       <c r="C73">
         <v>7.25</v>
@@ -3543,13 +3543,13 @@
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>922.26</v>
+        <v>818.22</v>
       </c>
       <c r="F73">
-        <v>564.01</v>
+        <v>552.48</v>
       </c>
       <c r="G73">
-        <v>547.75</v>
+        <v>548.44</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3584,7 +3584,7 @@
         <v>770.13</v>
       </c>
       <c r="F74">
-        <v>582.24</v>
+        <v>583.27</v>
       </c>
       <c r="G74">
         <v>544.4</v>
@@ -3599,7 +3599,7 @@
         <f>IF(D74=0,"",(H74-D74)/D74)</f>
       </c>
       <c r="K74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L74" t="s">
         <v>72</v>
@@ -3610,22 +3610,22 @@
         <v>104</v>
       </c>
       <c r="B75">
-        <v>356</v>
+        <v>915</v>
       </c>
       <c r="C75">
-        <v>6.82</v>
+        <v>6.85</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>752.02</v>
+        <v>725.14</v>
       </c>
       <c r="F75">
-        <v>491.35</v>
+        <v>508.53</v>
       </c>
       <c r="G75">
-        <v>474.05</v>
+        <v>522.49</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3640,7 +3640,7 @@
         <v>26</v>
       </c>
       <c r="L75" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3648,22 +3648,22 @@
         <v>105</v>
       </c>
       <c r="B76">
-        <v>963</v>
+        <v>349</v>
       </c>
       <c r="C76">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>725.14</v>
+        <v>752.82</v>
       </c>
       <c r="F76">
-        <v>524.8</v>
+        <v>480.97</v>
       </c>
       <c r="G76">
-        <v>517.88</v>
+        <v>474.05</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3678,7 +3678,7 @@
         <v>26</v>
       </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3695,7 +3695,7 @@
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>900.23</v>
+        <v>899.42</v>
       </c>
       <c r="F77">
         <v>529.18</v>
@@ -3713,10 +3713,10 @@
         <f>IF(D77=0,"",(H77-D77)/D77)</f>
       </c>
       <c r="K77" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L77" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3736,7 +3736,7 @@
         <v>834.72</v>
       </c>
       <c r="F78">
-        <v>514.76</v>
+        <v>512.46</v>
       </c>
       <c r="G78">
         <v>518.91</v>
@@ -3751,7 +3751,7 @@
         <f>IF(D78=0,"",(H78-D78)/D78)</f>
       </c>
       <c r="K78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L78" t="s">
         <v>108</v>
@@ -3762,22 +3762,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="C79">
-        <v>6.42</v>
+        <v>6.46</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>800.11</v>
+        <v>775.66</v>
       </c>
       <c r="F79">
-        <v>481.31</v>
+        <v>461.36</v>
       </c>
       <c r="G79">
-        <v>473.82</v>
+        <v>475.09</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3800,22 +3800,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>922</v>
+        <v>892</v>
       </c>
       <c r="C80">
-        <v>6.39</v>
+        <v>6.41</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>792.96</v>
+        <v>707.03</v>
       </c>
       <c r="F80">
         <v>488.23</v>
       </c>
       <c r="G80">
-        <v>484.43</v>
+        <v>490.2</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3838,7 +3838,7 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C81">
         <v>6.32</v>
@@ -3850,10 +3850,10 @@
         <v>750.4</v>
       </c>
       <c r="F81">
-        <v>474.16</v>
+        <v>473.01</v>
       </c>
       <c r="G81">
-        <v>551.33</v>
+        <v>551.21</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3876,10 +3876,10 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C82">
-        <v>6.26</v>
+        <v>6.29</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
@@ -3888,10 +3888,10 @@
         <v>681.89</v>
       </c>
       <c r="F82">
-        <v>458.94</v>
+        <v>455.59</v>
       </c>
       <c r="G82">
-        <v>472.78</v>
+        <v>471.63</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3914,7 +3914,7 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C83">
         <v>6.11</v>
@@ -3923,10 +3923,10 @@
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>629.76</v>
+        <v>592.73</v>
       </c>
       <c r="F83">
-        <v>505.07</v>
+        <v>502.77</v>
       </c>
       <c r="G83">
         <v>480.62</v>
@@ -3941,7 +3941,7 @@
         <f>IF(D83=0,"",(H83-D83)/D83)</f>
       </c>
       <c r="K83" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L83" t="s">
         <v>72</v>
@@ -3964,10 +3964,10 @@
         <v>684.2</v>
       </c>
       <c r="F84">
-        <v>461.82</v>
+        <v>461.71</v>
       </c>
       <c r="G84">
-        <v>450.4</v>
+        <v>449.25</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3979,10 +3979,10 @@
         <f>IF(D84=0,"",(H84-D84)/D84)</f>
       </c>
       <c r="K84" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L84" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>334.49</v>
       </c>
       <c r="G85">
-        <v>339.1</v>
+        <v>340.02</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4017,10 +4017,10 @@
         <f>IF(D85=0,"",(H85-D85)/D85)</f>
       </c>
       <c r="K85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4028,7 +4028,7 @@
         <v>116</v>
       </c>
       <c r="B86">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C86">
         <v>5.92</v>
@@ -4040,10 +4040,10 @@
         <v>692.04</v>
       </c>
       <c r="F86">
-        <v>420.41</v>
+        <v>420.3</v>
       </c>
       <c r="G86">
-        <v>420.99</v>
+        <v>420.88</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4055,10 +4055,10 @@
         <f>IF(D86=0,"",(H86-D86)/D86)</f>
       </c>
       <c r="K86" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L86" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4078,10 +4078,10 @@
         <v>685</v>
       </c>
       <c r="F87">
-        <v>414.53</v>
+        <v>414.07</v>
       </c>
       <c r="G87">
-        <v>389.73</v>
+        <v>389.27</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4093,7 +4093,7 @@
         <f>IF(D87=0,"",(H87-D87)/D87)</f>
       </c>
       <c r="K87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L87" t="s">
         <v>72</v>
@@ -4104,7 +4104,7 @@
         <v>118</v>
       </c>
       <c r="B88">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C88">
         <v>5.79</v>
@@ -4116,10 +4116,10 @@
         <v>630.56</v>
       </c>
       <c r="F88">
-        <v>483.27</v>
+        <v>481.78</v>
       </c>
       <c r="G88">
-        <v>434.02</v>
+        <v>434.6</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4131,10 +4131,10 @@
         <f>IF(D88=0,"",(H88-D88)/D88)</f>
       </c>
       <c r="K88" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L88" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4142,7 +4142,7 @@
         <v>119</v>
       </c>
       <c r="B89">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C89">
         <v>5.59</v>
@@ -4157,7 +4157,7 @@
         <v>453.4</v>
       </c>
       <c r="G89">
-        <v>410.61</v>
+        <v>434.72</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4169,7 +4169,7 @@
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
       <c r="K89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L89" t="s">
         <v>72</v>
@@ -4180,22 +4180,22 @@
         <v>120</v>
       </c>
       <c r="B90">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C90">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>602.19</v>
+        <v>558.82</v>
       </c>
       <c r="F90">
-        <v>492.5</v>
+        <v>438.18</v>
       </c>
       <c r="G90">
-        <v>444.06</v>
+        <v>424.34</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4207,10 +4207,10 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L90" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4218,22 +4218,22 @@
         <v>121</v>
       </c>
       <c r="B91">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C91">
-        <v>5.43</v>
+        <v>5.48</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>583.27</v>
+        <v>600.69</v>
       </c>
       <c r="F91">
-        <v>403.69</v>
+        <v>490.43</v>
       </c>
       <c r="G91">
-        <v>420.99</v>
+        <v>443.94</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4245,10 +4245,10 @@
         <f>IF(D91=0,"",(H91-D91)/D91)</f>
       </c>
       <c r="K91" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L91" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4256,22 +4256,22 @@
         <v>122</v>
       </c>
       <c r="B92">
-        <v>105</v>
+        <v>673</v>
       </c>
       <c r="C92">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>622.72</v>
+        <v>630.56</v>
       </c>
       <c r="F92">
-        <v>438.29</v>
+        <v>415.22</v>
       </c>
       <c r="G92">
-        <v>403.69</v>
+        <v>418.57</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4283,10 +4283,10 @@
         <f>IF(D92=0,"",(H92-D92)/D92)</f>
       </c>
       <c r="K92" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L92" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4294,22 +4294,22 @@
         <v>123</v>
       </c>
       <c r="B93">
-        <v>693</v>
+        <v>97</v>
       </c>
       <c r="C93">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>629.76</v>
+        <v>681.08</v>
       </c>
       <c r="F93">
-        <v>423.3</v>
+        <v>432.53</v>
       </c>
       <c r="G93">
-        <v>417.42</v>
+        <v>403.69</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4321,10 +4321,10 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="L93" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4332,22 +4332,22 @@
         <v>124</v>
       </c>
       <c r="B94">
-        <v>454</v>
+        <v>26</v>
       </c>
       <c r="C94">
-        <v>5.32</v>
+        <v>5.27</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>594.35</v>
+        <v>577.05</v>
       </c>
       <c r="F94">
-        <v>397.92</v>
+        <v>386.27</v>
       </c>
       <c r="G94">
-        <v>369.09</v>
+        <v>392.16</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4359,10 +4359,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4370,22 +4370,22 @@
         <v>125</v>
       </c>
       <c r="B95">
-        <v>24</v>
+        <v>438</v>
       </c>
       <c r="C95">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>580.16</v>
+        <v>590.43</v>
       </c>
       <c r="F95">
-        <v>369.09</v>
+        <v>397.81</v>
       </c>
       <c r="G95">
-        <v>401.38</v>
+        <v>379.47</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4397,10 +4397,10 @@
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
       <c r="K95" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L95" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4423,7 +4423,7 @@
         <v>409.46</v>
       </c>
       <c r="G96">
-        <v>378.32</v>
+        <v>369.09</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4435,7 +4435,7 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L96" t="s">
         <v>72</v>
@@ -4458,7 +4458,7 @@
         <v>567.47</v>
       </c>
       <c r="F97">
-        <v>412.23</v>
+        <v>413.26</v>
       </c>
       <c r="G97">
         <v>386.39</v>
@@ -4484,22 +4484,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C98">
-        <v>5.02</v>
+        <v>4.94</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>590.43</v>
+        <v>564.36</v>
       </c>
       <c r="F98">
-        <v>367.93</v>
+        <v>368.97</v>
       </c>
       <c r="G98">
-        <v>391.69</v>
+        <v>391.46</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4534,10 +4534,10 @@
         <v>580.16</v>
       </c>
       <c r="F99">
-        <v>379.58</v>
+        <v>378.43</v>
       </c>
       <c r="G99">
-        <v>371.39</v>
+        <v>370.24</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4549,7 +4549,7 @@
         <f>IF(D99=0,"",(H99-D99)/D99)</f>
       </c>
       <c r="K99" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L99" t="s">
         <v>72</v>
@@ -4560,22 +4560,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C100">
-        <v>4.76</v>
+        <v>4.81</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>520.99</v>
+        <v>510.03</v>
       </c>
       <c r="F100">
-        <v>351.79</v>
+        <v>342.56</v>
       </c>
       <c r="G100">
-        <v>362.97</v>
+        <v>360.67</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4610,10 +4610,10 @@
         <v>580.16</v>
       </c>
       <c r="F101">
-        <v>369.09</v>
+        <v>367.93</v>
       </c>
       <c r="G101">
-        <v>382.7</v>
+        <v>381.54</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4625,7 +4625,7 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L101" t="s">
         <v>72</v>
@@ -4636,22 +4636,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C102">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>521.8</v>
+        <v>565.17</v>
       </c>
       <c r="F102">
+        <v>343.48</v>
+      </c>
+      <c r="G102">
         <v>332.18</v>
-      </c>
-      <c r="G102">
-        <v>372.32</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4663,10 +4663,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L102" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4674,22 +4674,22 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C103">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>521.8</v>
+        <v>527.33</v>
       </c>
       <c r="F103">
-        <v>368.97</v>
+        <v>332.06</v>
       </c>
       <c r="G103">
-        <v>351.79</v>
+        <v>372.2</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4701,10 +4701,10 @@
         <f>IF(D103=0,"",(H103-D103)/D103)</f>
       </c>
       <c r="K103" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L103" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4712,7 +4712,7 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C104">
         <v>4.6</v>
@@ -4724,7 +4724,7 @@
         <v>477.62</v>
       </c>
       <c r="F104">
-        <v>333.1</v>
+        <v>332.76</v>
       </c>
       <c r="G104">
         <v>342.33</v>
@@ -4739,10 +4739,10 @@
         <f>IF(D104=0,"",(H104-D104)/D104)</f>
       </c>
       <c r="K104" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L104" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4750,22 +4750,22 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="C105">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>565.17</v>
+        <v>521.8</v>
       </c>
       <c r="F105">
-        <v>344.75</v>
+        <v>368.97</v>
       </c>
       <c r="G105">
-        <v>333.33</v>
+        <v>351.79</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4777,10 +4777,10 @@
         <f>IF(D105=0,"",(H105-D105)/D105)</f>
       </c>
       <c r="K105" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L105" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4788,22 +4788,22 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C106">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>453.17</v>
+        <v>446.94</v>
       </c>
       <c r="F106">
-        <v>321.68</v>
+        <v>353.98</v>
       </c>
       <c r="G106">
-        <v>290.43</v>
+        <v>312.69</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4815,7 +4815,7 @@
         <f>IF(D106=0,"",(H106-D106)/D106)</f>
       </c>
       <c r="K106" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L106" t="s">
         <v>72</v>
@@ -4826,22 +4826,22 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="C107">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>446.94</v>
+        <v>475.32</v>
       </c>
       <c r="F107">
-        <v>353.98</v>
+        <v>339.68</v>
       </c>
       <c r="G107">
-        <v>312.69</v>
+        <v>341.87</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4853,10 +4853,10 @@
         <f>IF(D107=0,"",(H107-D107)/D107)</f>
       </c>
       <c r="K107" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L107" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4864,7 +4864,7 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>94</v>
+        <v>1542</v>
       </c>
       <c r="C108">
         <v>4.3</v>
@@ -4873,13 +4873,13 @@
         <f>C108*$B$3</f>
       </c>
       <c r="E108">
-        <v>475.32</v>
+        <v>465.86</v>
       </c>
       <c r="F108">
-        <v>339.68</v>
+        <v>326.41</v>
       </c>
       <c r="G108">
-        <v>343.14</v>
+        <v>331.03</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4891,10 +4891,10 @@
         <f>IF(D108=0,"",(H108-D108)/D108)</f>
       </c>
       <c r="K108" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L108" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4902,22 +4902,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>1574</v>
+        <v>50</v>
       </c>
       <c r="C109">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>465.86</v>
+        <v>525.72</v>
       </c>
       <c r="F109">
-        <v>334.49</v>
+        <v>305.65</v>
       </c>
       <c r="G109">
-        <v>327.33</v>
+        <v>302.08</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4929,10 +4929,10 @@
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
       <c r="K109" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="L109" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4940,22 +4940,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C110">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>525.72</v>
+        <v>453.17</v>
       </c>
       <c r="F110">
-        <v>305.65</v>
+        <v>321.68</v>
       </c>
       <c r="G110">
-        <v>303.23</v>
+        <v>291.58</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4967,7 +4967,7 @@
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
       <c r="K110" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L110" t="s">
         <v>72</v>
@@ -4978,7 +4978,7 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C111">
         <v>4.06</v>
@@ -4990,10 +4990,10 @@
         <v>412.23</v>
       </c>
       <c r="F111">
-        <v>334.49</v>
+        <v>338.52</v>
       </c>
       <c r="G111">
-        <v>325.03</v>
+        <v>334.26</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -5005,10 +5005,10 @@
         <f>IF(D111=0,"",(H111-D111)/D111)</f>
       </c>
       <c r="K111" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L111" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5016,7 +5016,7 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C112">
         <v>3.86</v>
@@ -5025,13 +5025,13 @@
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>439.79</v>
+        <v>424.11</v>
       </c>
       <c r="F112">
         <v>311.42</v>
       </c>
       <c r="G112">
-        <v>292.96</v>
+        <v>292.39</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5054,7 +5054,7 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C113">
         <v>3.82</v>
@@ -5069,7 +5069,7 @@
         <v>288.12</v>
       </c>
       <c r="G113">
-        <v>282.58</v>
+        <v>281.43</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5081,7 +5081,7 @@
         <f>IF(D113=0,"",(H113-D113)/D113)</f>
       </c>
       <c r="K113" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L113" t="s">
         <v>72</v>
@@ -5104,10 +5104,10 @@
         <v>476.82</v>
       </c>
       <c r="F114">
-        <v>265.51</v>
+        <v>265.17</v>
       </c>
       <c r="G114">
-        <v>279.12</v>
+        <v>276.7</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5119,10 +5119,10 @@
         <f>IF(D114=0,"",(H114-D114)/D114)</f>
       </c>
       <c r="K114" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L114" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5130,22 +5130,22 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C115">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>401.15</v>
+        <v>400.46</v>
       </c>
       <c r="F115">
-        <v>283.74</v>
+        <v>280.16</v>
       </c>
       <c r="G115">
-        <v>276.82</v>
+        <v>274.51</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5168,10 +5168,10 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C116">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
@@ -5180,10 +5180,10 @@
         <v>362.51</v>
       </c>
       <c r="F116">
-        <v>256.98</v>
+        <v>258.13</v>
       </c>
       <c r="G116">
-        <v>258.82</v>
+        <v>253.63</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5206,7 +5206,7 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C117">
         <v>3.5</v>
@@ -5221,7 +5221,7 @@
         <v>283.51</v>
       </c>
       <c r="G117">
-        <v>281.43</v>
+        <v>280.05</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5233,10 +5233,10 @@
         <f>IF(D117=0,"",(H117-D117)/D117)</f>
       </c>
       <c r="K117" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L117" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5256,10 +5256,10 @@
         <v>439.79</v>
       </c>
       <c r="F118">
-        <v>281.43</v>
+        <v>281.31</v>
       </c>
       <c r="G118">
-        <v>265.17</v>
+        <v>265.05</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5282,10 +5282,10 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C119">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
@@ -5294,10 +5294,10 @@
         <v>404.38</v>
       </c>
       <c r="F119">
-        <v>236.45</v>
+        <v>238.52</v>
       </c>
       <c r="G119">
-        <v>257.78</v>
+        <v>257.67</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5323,7 +5323,7 @@
         <v>225</v>
       </c>
       <c r="C120">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
@@ -5332,7 +5332,7 @@
         <v>375.2</v>
       </c>
       <c r="F120">
-        <v>253.63</v>
+        <v>252.48</v>
       </c>
       <c r="G120">
         <v>242.21</v>
@@ -5347,10 +5347,10 @@
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
       <c r="K120" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L120" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5358,22 +5358,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C121">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>353.86</v>
+        <v>351.56</v>
       </c>
       <c r="F121">
-        <v>232.99</v>
+        <v>231.37</v>
       </c>
       <c r="G121">
-        <v>234.49</v>
+        <v>233.22</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5396,7 +5396,7 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C122">
         <v>3.18</v>
@@ -5405,10 +5405,10 @@
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>362.51</v>
+        <v>364.94</v>
       </c>
       <c r="F122">
-        <v>262.98</v>
+        <v>261.82</v>
       </c>
       <c r="G122">
         <v>242.21</v>
@@ -5434,7 +5434,7 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C123">
         <v>2.98</v>
@@ -5443,13 +5443,13 @@
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>311.3</v>
+        <v>310.5</v>
       </c>
       <c r="F123">
-        <v>222.95</v>
+        <v>226.07</v>
       </c>
       <c r="G123">
-        <v>221.34</v>
+        <v>222.03</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5472,10 +5472,10 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C124">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
@@ -5487,7 +5487,7 @@
         <v>226.07</v>
       </c>
       <c r="G124">
-        <v>221.45</v>
+        <v>217.99</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5499,10 +5499,10 @@
         <f>IF(D124=0,"",(H124-D124)/D124)</f>
       </c>
       <c r="K124" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L124" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5510,10 +5510,10 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C125">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
@@ -5548,10 +5548,10 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C126">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
@@ -5563,7 +5563,7 @@
         <v>189.16</v>
       </c>
       <c r="G126">
-        <v>191.46</v>
+        <v>191.23</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5595,10 +5595,10 @@
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>275.89</v>
+        <v>266.44</v>
       </c>
       <c r="F127">
-        <v>173.01</v>
+        <v>171.74</v>
       </c>
       <c r="G127">
         <v>171.74</v>
@@ -5624,7 +5624,7 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C128">
         <v>2.23</v>
@@ -5633,10 +5633,10 @@
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>287.66</v>
+        <v>290.89</v>
       </c>
       <c r="F128">
-        <v>175.09</v>
+        <v>176.24</v>
       </c>
       <c r="G128">
         <v>175.32</v>
@@ -5651,10 +5651,10 @@
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
       <c r="K128" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L128" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5689,7 +5689,7 @@
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
       <c r="K129" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L129" t="s">
         <v>72</v>
@@ -5700,7 +5700,7 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C130">
         <v>2.08</v>
@@ -5712,7 +5712,7 @@
         <v>215.11</v>
       </c>
       <c r="F130">
-        <v>169.9</v>
+        <v>169.2</v>
       </c>
       <c r="G130">
         <v>171.86</v>
@@ -5727,7 +5727,7 @@
         <f>IF(D130=0,"",(H130-D130)/D130)</f>
       </c>
       <c r="K130" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L130" t="s">
         <v>72</v>
@@ -5750,7 +5750,7 @@
         <v>211.99</v>
       </c>
       <c r="F131">
-        <v>142.56</v>
+        <v>142.44</v>
       </c>
       <c r="G131">
         <v>149.94</v>
@@ -5765,7 +5765,7 @@
         <f>IF(D131=0,"",(H131-D131)/D131)</f>
       </c>
       <c r="K131" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L131" t="s">
         <v>72</v>
@@ -5776,7 +5776,7 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C132">
         <v>1.75</v>
@@ -5791,7 +5791,7 @@
         <v>133.45</v>
       </c>
       <c r="G132">
-        <v>137.25</v>
+        <v>136.1</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5803,10 +5803,10 @@
         <f>IF(D132=0,"",(H132-D132)/D132)</f>
       </c>
       <c r="K132" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L132" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C133">
         <v>1.66</v>
@@ -5823,13 +5823,13 @@
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>175.78</v>
+        <v>173.36</v>
       </c>
       <c r="F133">
         <v>126.87</v>
       </c>
       <c r="G133">
-        <v>137.25</v>
+        <v>133.79</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5841,10 +5841,10 @@
         <f>IF(D133=0,"",(H133-D133)/D133)</f>
       </c>
       <c r="K133" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L133" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5852,10 +5852,10 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C134">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
@@ -5867,7 +5867,7 @@
         <v>114.99</v>
       </c>
       <c r="G134">
-        <v>116.49</v>
+        <v>115.34</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5879,10 +5879,10 @@
         <f>IF(D134=0,"",(H134-D134)/D134)</f>
       </c>
       <c r="K134" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L134" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5890,10 +5890,10 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C135">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
@@ -5905,7 +5905,7 @@
         <v>114.42</v>
       </c>
       <c r="G135">
-        <v>115.22</v>
+        <v>114.19</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5928,7 +5928,7 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>752</v>
+        <v>713</v>
       </c>
       <c r="C136">
         <v>1.49</v>
@@ -5940,7 +5940,7 @@
         <v>155.25</v>
       </c>
       <c r="F136">
-        <v>105.77</v>
+        <v>103.69</v>
       </c>
       <c r="G136">
         <v>103.69</v>
@@ -5955,10 +5955,10 @@
         <f>IF(D136=0,"",(H136-D136)/D136)</f>
       </c>
       <c r="K136" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L136" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5966,7 +5966,7 @@
         <v>168</v>
       </c>
       <c r="B137">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C137">
         <v>1.03</v>
@@ -5978,7 +5978,7 @@
         <v>121.34</v>
       </c>
       <c r="F137">
-        <v>73.01</v>
+        <v>75.55</v>
       </c>
       <c r="G137">
         <v>77.28</v>
@@ -6004,7 +6004,7 @@
         <v>169</v>
       </c>
       <c r="B138">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C138">
         <v>0.86</v>
@@ -6016,10 +6016,10 @@
         <v>92.96</v>
       </c>
       <c r="F138">
+        <v>62.17</v>
+      </c>
+      <c r="G138">
         <v>62.28</v>
-      </c>
-      <c r="G138">
-        <v>64.13</v>
       </c>
       <c r="H138">
         <f>MIN(E138:G138)</f>
@@ -6042,7 +6042,7 @@
         <v>170</v>
       </c>
       <c r="B139">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C139">
         <v>0.74</v>
@@ -6054,10 +6054,10 @@
         <v>81.89</v>
       </c>
       <c r="F139">
-        <v>47.17</v>
+        <v>48.21</v>
       </c>
       <c r="G139">
-        <v>49.37</v>
+        <v>49.02</v>
       </c>
       <c r="H139">
         <f>MIN(E139:G139)</f>
@@ -6080,7 +6080,7 @@
         <v>171</v>
       </c>
       <c r="B140">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C140">
         <v>0.5</v>
@@ -6089,13 +6089,13 @@
         <f>C140*$B$3</f>
       </c>
       <c r="E140">
-        <v>59.86</v>
+        <v>63.78</v>
       </c>
       <c r="F140">
-        <v>36.79</v>
+        <v>34.49</v>
       </c>
       <c r="G140">
-        <v>34.26</v>
+        <v>34.14</v>
       </c>
       <c r="H140">
         <f>MIN(E140:G140)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="172">
-  <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 19.07.2026 20:16</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="168">
+  <si>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 26.07.2026 17:12</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -64,7 +64,25 @@
     <t>Редкость</t>
   </si>
   <si>
-    <t>MP9 | Pandora's Box (Factory New)</t>
+    <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Rifle</t>
+  </si>
+  <si>
+    <t>Classified</t>
+  </si>
+  <si>
+    <t>AWP | Containment Breach (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sniper Rifle</t>
+  </si>
+  <si>
+    <t>Covert</t>
+  </si>
+  <si>
+    <t>MP9 | Dark Age (Factory New)</t>
   </si>
   <si>
     <t>SMG</t>
@@ -73,90 +91,57 @@
     <t>Mil-Spec Grade</t>
   </si>
   <si>
-    <t>MP9 | Stained Glass (Factory New)</t>
+    <t>AK-47 | Legion of Anubis (Factory New)</t>
+  </si>
+  <si>
+    <t>USP-S | Orion (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Pistol</t>
+  </si>
+  <si>
+    <t>USP-S | Whiteout (Field-Tested)</t>
+  </si>
+  <si>
+    <t>MAC-10 | Fade (Factory New)</t>
+  </si>
+  <si>
+    <t>AWP | Neo-Noir (Factory New)</t>
+  </si>
+  <si>
+    <t>M4A1-S | Vaporwave (Field-Tested)</t>
+  </si>
+  <si>
+    <t>AWP | Containment Breach (Well-Worn)</t>
+  </si>
+  <si>
+    <t>MP9 | Hydra (Factory New)</t>
+  </si>
+  <si>
+    <t>Desert Eagle | Starcade (Field-Tested)</t>
+  </si>
+  <si>
+    <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
+  </si>
+  <si>
+    <t>P250 | Apep's Curse (Field-Tested)</t>
+  </si>
+  <si>
+    <t>CZ75-Auto | Emerald (Factory New)</t>
+  </si>
+  <si>
+    <t>Dual Berettas | Emerald (Factory New)</t>
+  </si>
+  <si>
+    <t>SCAR-20 | Cyrex (Factory New)</t>
+  </si>
+  <si>
+    <t>M4A4 | Polysoup (Factory New)</t>
   </si>
   <si>
     <t>Restricted</t>
   </si>
   <si>
-    <t>USP-S | Whiteout (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Pistol</t>
-  </si>
-  <si>
-    <t>Classified</t>
-  </si>
-  <si>
-    <t>M4A4 | Desolate Space (Factory New)</t>
-  </si>
-  <si>
-    <t>Rifle</t>
-  </si>
-  <si>
-    <t>AK-47 | Point Disarray (Factory New)</t>
-  </si>
-  <si>
-    <t>FAMAS | Waters of Nephthys (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>AWP | Containment Breach (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sniper Rifle</t>
-  </si>
-  <si>
-    <t>Covert</t>
-  </si>
-  <si>
-    <t>MP9 | Dark Age (Factory New)</t>
-  </si>
-  <si>
-    <t>AK-47 | Legion of Anubis (Factory New)</t>
-  </si>
-  <si>
-    <t>USP-S | Orion (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>MAC-10 | Fade (Factory New)</t>
-  </si>
-  <si>
-    <t>USP-S | Whiteout (Field-Tested)</t>
-  </si>
-  <si>
-    <t>AWP | Neo-Noir (Factory New)</t>
-  </si>
-  <si>
-    <t>M4A1-S | Vaporwave (Field-Tested)</t>
-  </si>
-  <si>
-    <t>AWP | Containment Breach (Well-Worn)</t>
-  </si>
-  <si>
-    <t>P250 | Apep's Curse (Field-Tested)</t>
-  </si>
-  <si>
-    <t>MP9 | Hydra (Factory New)</t>
-  </si>
-  <si>
-    <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Desert Eagle | Starcade (Field-Tested)</t>
-  </si>
-  <si>
-    <t>CZ75-Auto | Emerald (Factory New)</t>
-  </si>
-  <si>
-    <t>Dual Berettas | Emerald (Factory New)</t>
-  </si>
-  <si>
-    <t>SCAR-20 | Cyrex (Factory New)</t>
-  </si>
-  <si>
-    <t>M4A4 | Polysoup (Factory New)</t>
-  </si>
-  <si>
     <t>Galil AR | Cerberus (Field-Tested)</t>
   </si>
   <si>
@@ -175,66 +160,69 @@
     <t>Superior</t>
   </si>
   <si>
+    <t>Galil AR | Amber Fade (Factory New)</t>
+  </si>
+  <si>
     <t>SG 553 | Integrale (Minimal Wear)</t>
   </si>
   <si>
+    <t>Safecracker Voltzmann | The Professionals</t>
+  </si>
+  <si>
     <t>FAMAS | Styx (Minimal Wear)</t>
   </si>
   <si>
-    <t>Safecracker Voltzmann | The Professionals</t>
+    <t>Nova | Sobek's Bite (Factory New)</t>
+  </si>
+  <si>
+    <t>Shotgun</t>
   </si>
   <si>
     <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
-    <t>Nova | Sobek's Bite (Factory New)</t>
-  </si>
-  <si>
-    <t>Shotgun</t>
-  </si>
-  <si>
     <t>M4A4 | Polysoup (Minimal Wear)</t>
   </si>
   <si>
+    <t>MP9 | Music Box (Factory New)</t>
+  </si>
+  <si>
     <t>Tec-9 | Brass (Minimal Wear)</t>
   </si>
   <si>
-    <t>MP9 | Music Box (Factory New)</t>
-  </si>
-  <si>
     <t>Nova | Sobek's Bite (Minimal Wear)</t>
   </si>
   <si>
+    <t>'The Doctor' Romanov | Sabre</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Great Wave (Foil)</t>
+  </si>
+  <si>
+    <t>Sticker</t>
+  </si>
+  <si>
+    <t>Exotic</t>
+  </si>
+  <si>
     <t>Michael Syfers  | FBI Sniper</t>
   </si>
   <si>
+    <t>M4A4 | Evil Daimyo (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Movistar Riders (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker</t>
-  </si>
-  <si>
     <t>Remarkable</t>
   </si>
   <si>
-    <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>'The Doctor' Romanov | Sabre</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Sticker | Great Wave (Foil)</t>
-  </si>
-  <si>
-    <t>Exotic</t>
-  </si>
-  <si>
-    <t>M4A4 | Evil Daimyo (Factory New)</t>
-  </si>
-  <si>
     <t>SG 553 | Candy Apple (Factory New)</t>
   </si>
   <si>
@@ -250,231 +238,231 @@
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>P250 | Epicenter (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Osiris | Elite Crew</t>
+  </si>
+  <si>
+    <t>Exceptional</t>
+  </si>
+  <si>
+    <t>FAMAS | Styx (Field-Tested)</t>
+  </si>
+  <si>
+    <t>B Squadron Officer | SAS</t>
+  </si>
+  <si>
+    <t>Distinguished</t>
+  </si>
+  <si>
+    <t>Markus Delrow | FBI HRT</t>
+  </si>
+  <si>
+    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
+  </si>
+  <si>
     <t>USP-S | Guardian (Factory New)</t>
   </si>
   <si>
-    <t>FAMAS | Styx (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Osiris | Elite Crew</t>
-  </si>
-  <si>
-    <t>Exceptional</t>
+    <t>AUG | Carved Jade (Minimal Wear)</t>
   </si>
   <si>
     <t>Five-SeveN | Kami (Factory New)</t>
   </si>
   <si>
-    <t>B Squadron Officer | SAS</t>
-  </si>
-  <si>
-    <t>Distinguished</t>
-  </si>
-  <si>
-    <t>AUG | Carved Jade (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Markus Delrow | FBI HRT</t>
+    <t>MP7 | Fade (Minimal Wear)</t>
   </si>
   <si>
     <t>SSG 08 | Rapid Transit (Factory New)</t>
   </si>
   <si>
+    <t>Sticker | Great Wave (Holo)</t>
+  </si>
+  <si>
+    <t>MP7 | Fade (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
+    <t>Slingshot | Phoenix</t>
+  </si>
+  <si>
     <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>MP7 | Fade (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Great Wave (Holo)</t>
+    <t>SG 553 | Integrale (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Rezan the Redshirt | Sabre</t>
+  </si>
+  <si>
+    <t>Rezan The Ready | Sabre</t>
   </si>
   <si>
     <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>MP7 | Fade (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Slingshot | Phoenix</t>
-  </si>
-  <si>
-    <t>SG 553 | Integrale (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Rezan the Redshirt | Sabre</t>
-  </si>
-  <si>
-    <t>Rezan The Ready | Sabre</t>
-  </si>
-  <si>
-    <t>Blackwolf | Sabre</t>
+    <t>Prof. Shahmat | Elite Crew</t>
+  </si>
+  <si>
+    <t>AK-47 | Slate (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Prof. Shahmat | Elite Crew</t>
+    <t>AK-47 | Crossfade (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Liquid Fire</t>
+  </si>
+  <si>
+    <t>High Grade</t>
   </si>
   <si>
     <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>AK-47 | Slate (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>AK-47 | Crossfade (Factory New)</t>
+    <t>Maximus | Sabre</t>
+  </si>
+  <si>
+    <t>Dragomir | Sabre</t>
   </si>
   <si>
     <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Liquid Fire</t>
-  </si>
-  <si>
-    <t>High Grade</t>
-  </si>
-  <si>
-    <t>Dragomir | Sabre</t>
-  </si>
-  <si>
-    <t>Maximus | Sabre</t>
+    <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>XM1014 | Black Tie (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>MAC-10 | Strats (Factory New)</t>
+  </si>
+  <si>
+    <t>Consumer Grade</t>
+  </si>
+  <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
     <t>Tec-9 | Brass (Field-Tested)</t>
   </si>
   <si>
-    <t>XM1014 | Black Tie (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
+    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AWP | Black Nile (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | Stone Scales (Foil)</t>
+  </si>
+  <si>
+    <t>Sticker | Gold Web (Foil)</t>
+  </si>
+  <si>
+    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
+    <t>P250 | Epicenter (Field-Tested)</t>
+  </si>
+  <si>
+    <t>R8 Revolver | Blaze (Factory New)</t>
+  </si>
+  <si>
+    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AK-47 | Slate (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>Sticker | Gambit Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
-    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>CZ75-Auto | Tacticat (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>MAC-10 | Strats (Factory New)</t>
-  </si>
-  <si>
-    <t>Consumer Grade</t>
-  </si>
-  <si>
-    <t>AWP | Black Nile (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>R8 Revolver | Blaze (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Stone Scales (Foil)</t>
-  </si>
-  <si>
-    <t>Sticker | Gold Web (Foil)</t>
-  </si>
-  <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
+    <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Team Liquid (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>M4A4 | Turbine (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Slate (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | Complexity Gaming (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | G2 Esports (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Team Liquid (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>M4A4 | Turbine (Minimal Wear)</t>
+    <t>Galil AR | Tuxedo (Factory New)</t>
   </si>
   <si>
     <t>Sticker | Perfect World (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>XM1014 | Seasons (Factory New)</t>
+  </si>
+  <si>
+    <t>AK-47 | Crossfade (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Five-SeveN | Kami (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Galil AR | Tuxedo (Factory New)</t>
+    <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>P2000 | Amber Fade (Factory New)</t>
   </si>
   <si>
     <t>Five-SeveN | Retrobution (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>XM1014 | Seasons (Factory New)</t>
-  </si>
-  <si>
-    <t>Five-SeveN | Kami (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>P2000 | Amber Fade (Factory New)</t>
-  </si>
-  <si>
-    <t>AK-47 | Crossfade (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Dual Berettas | Hydro Strike (Minimal Wear)</t>
   </si>
   <si>
@@ -487,19 +475,19 @@
     <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>SSG 08 | Ghost Crusader (Minimal Wear)</t>
   </si>
   <si>
     <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
-    <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
+    <t>Sticker | Ancient Beast (Foil)</t>
   </si>
   <si>
     <t>Sticker | BIG (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Sticker | Ancient Beast (Foil)</t>
   </si>
   <si>
     <t>Sticker | Coiled Strike (Holo)</t>
@@ -911,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -933,7 +921,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.93</v>
+        <v>81.55</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -942,7 +930,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>11.534</v>
+        <v>11.5607</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -988,22 +976,22 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>165.76</v>
+        <v>83.47</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>18760.28</v>
+        <v>9460.24</v>
       </c>
       <c r="F6">
-        <v>12053.03</v>
+        <v>6358.39</v>
       </c>
       <c r="G6">
-        <v>12099.17</v>
+        <v>6289.02</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -1026,22 +1014,22 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>55</v>
+        <v>295</v>
       </c>
       <c r="C7">
-        <v>136.81</v>
+        <v>79.48</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>18259.71</v>
+        <v>8426.02</v>
       </c>
       <c r="F7">
-        <v>10605.51</v>
+        <v>5942.2</v>
       </c>
       <c r="G7">
-        <v>9919.24</v>
+        <v>5919.08</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1053,33 +1041,33 @@
         <f>IF(D7=0,"",(H7-D7)/D7)</f>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>332</v>
+        <v>28</v>
       </c>
       <c r="C8">
-        <v>118.36</v>
+        <v>70.99</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>14587.74</v>
+        <v>7320.58</v>
       </c>
       <c r="F8">
-        <v>8869.65</v>
+        <v>5306.36</v>
       </c>
       <c r="G8">
-        <v>8835.04</v>
+        <v>5156.07</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1091,33 +1079,33 @@
         <f>IF(D8=0,"",(H8-D8)/D8)</f>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C9">
-        <v>98.09</v>
+        <v>60.69</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>10635.04</v>
+        <v>6635.49</v>
       </c>
       <c r="F9">
-        <v>7589.37</v>
+        <v>4733.99</v>
       </c>
       <c r="G9">
-        <v>7312.56</v>
+        <v>4658.96</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1129,10 +1117,10 @@
         <f>IF(D9=0,"",(H9-D9)/D9)</f>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1140,22 +1128,22 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="C10">
-        <v>85.72</v>
+        <v>57.53</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>9008.75</v>
+        <v>6029.48</v>
       </c>
       <c r="F10">
-        <v>6578.99</v>
+        <v>4485.55</v>
       </c>
       <c r="G10">
-        <v>6215.44</v>
+        <v>4358.38</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1167,33 +1155,33 @@
         <f>IF(D10=0,"",(H10-D10)/D10)</f>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
-        <v>50</v>
+        <v>271</v>
       </c>
       <c r="C11">
-        <v>85.59</v>
+        <v>55.91</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>9065.61</v>
+        <v>6336.07</v>
       </c>
       <c r="F11">
-        <v>6205.29</v>
+        <v>4203.7</v>
       </c>
       <c r="G11">
-        <v>6401.25</v>
+        <v>4150.29</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1205,33 +1193,33 @@
         <f>IF(D11=0,"",(H11-D11)/D11)</f>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12">
-        <v>211</v>
+        <v>326</v>
       </c>
       <c r="C12">
-        <v>81.24</v>
+        <v>55.61</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>8788.91</v>
+        <v>5924.4</v>
       </c>
       <c r="F12">
-        <v>5913.02</v>
+        <v>4161.85</v>
       </c>
       <c r="G12">
-        <v>5905.41</v>
+        <v>4144.51</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1243,33 +1231,33 @@
         <f>IF(D12=0,"",(H12-D12)/D12)</f>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13">
-        <v>29</v>
+        <v>245</v>
       </c>
       <c r="C13">
-        <v>71.11</v>
+        <v>54.68</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>7374.61</v>
+        <v>6003.47</v>
       </c>
       <c r="F13">
-        <v>5755.47</v>
+        <v>4231.22</v>
       </c>
       <c r="G13">
-        <v>5155.7</v>
+        <v>4235.84</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1281,33 +1269,33 @@
         <f>IF(D13=0,"",(H13-D13)/D13)</f>
       </c>
       <c r="K13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14">
-        <v>125</v>
+        <v>368</v>
       </c>
       <c r="C14">
-        <v>62.9</v>
+        <v>52.57</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>6574.5</v>
+        <v>5853.3</v>
       </c>
       <c r="F14">
-        <v>4596.18</v>
+        <v>4046.25</v>
       </c>
       <c r="G14">
-        <v>4671.27</v>
+        <v>3930.64</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1319,33 +1307,33 @@
         <f>IF(D14=0,"",(H14-D14)/D14)</f>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L14" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="C15">
-        <v>58.84</v>
+        <v>51.9</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>6211.06</v>
+        <v>5819.31</v>
       </c>
       <c r="F15">
-        <v>4484.42</v>
+        <v>3786.13</v>
       </c>
       <c r="G15">
-        <v>4313.72</v>
+        <v>3858.96</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1357,33 +1345,33 @@
         <f>IF(D15=0,"",(H15-D15)/D15)</f>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="C16">
-        <v>58.08</v>
+        <v>48.51</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>6336.43</v>
+        <v>5729.25</v>
       </c>
       <c r="F16">
-        <v>4348.32</v>
+        <v>3802.08</v>
       </c>
       <c r="G16">
-        <v>4256.05</v>
+        <v>3630.06</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1395,7 +1383,7 @@
         <f>IF(D16=0,"",(H16-D16)/D16)</f>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L16" t="s">
         <v>19</v>
@@ -1403,25 +1391,25 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C17">
-        <v>58.04</v>
+        <v>47.09</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>6338.74</v>
+        <v>5373.64</v>
       </c>
       <c r="F17">
-        <v>4238.75</v>
+        <v>3618.5</v>
       </c>
       <c r="G17">
-        <v>4214.52</v>
+        <v>3514.45</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1433,33 +1421,33 @@
         <f>IF(D17=0,"",(H17-D17)/D17)</f>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18">
-        <v>237</v>
+        <v>123</v>
       </c>
       <c r="C18">
-        <v>56.43</v>
+        <v>45.79</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>6334.82</v>
+        <v>5361.04</v>
       </c>
       <c r="F18">
-        <v>4238.28</v>
+        <v>3485.09</v>
       </c>
       <c r="G18">
-        <v>4192.49</v>
+        <v>3391.33</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1471,33 +1459,33 @@
         <f>IF(D18=0,"",(H18-D18)/D18)</f>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="C19">
-        <v>53.76</v>
+        <v>44.97</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5902.06</v>
+        <v>5152.49</v>
       </c>
       <c r="F19">
-        <v>4036.9</v>
+        <v>3658.96</v>
       </c>
       <c r="G19">
-        <v>4002.3</v>
+        <v>3377.34</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1509,33 +1497,33 @@
         <f>IF(D19=0,"",(H19-D19)/D19)</f>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L19" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>64</v>
       </c>
       <c r="C20">
-        <v>51.99</v>
+        <v>36.43</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>6114.87</v>
+        <v>4139.42</v>
       </c>
       <c r="F20">
-        <v>3978.08</v>
+        <v>2895.96</v>
       </c>
       <c r="G20">
-        <v>3965.39</v>
+        <v>2953.76</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1547,33 +1535,33 @@
         <f>IF(D20=0,"",(H20-D20)/D20)</f>
       </c>
       <c r="K20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L20" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C21">
-        <v>49.67</v>
+        <v>36.3</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>5531.59</v>
+        <v>4029.6</v>
       </c>
       <c r="F21">
-        <v>3662.05</v>
+        <v>3179.19</v>
       </c>
       <c r="G21">
-        <v>3932.98</v>
+        <v>2685.55</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1585,33 +1573,33 @@
         <f>IF(D21=0,"",(H21-D21)/D21)</f>
       </c>
       <c r="K21" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C22">
-        <v>48.3</v>
+        <v>35.45</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>5716.83</v>
+        <v>4285.67</v>
       </c>
       <c r="F22">
-        <v>3621.68</v>
+        <v>2709.94</v>
       </c>
       <c r="G22">
-        <v>3575.54</v>
+        <v>2687.17</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1623,33 +1611,33 @@
         <f>IF(D22=0,"",(H22-D22)/D22)</f>
       </c>
       <c r="K22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="C23">
-        <v>47.76</v>
+        <v>31.84</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>5425.13</v>
+        <v>3548.44</v>
       </c>
       <c r="F23">
-        <v>3719.72</v>
+        <v>2456.65</v>
       </c>
       <c r="G23">
-        <v>3528.6</v>
+        <v>2419.65</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1661,10 +1649,10 @@
         <f>IF(D23=0,"",(H23-D23)/D23)</f>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L23" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1672,22 +1660,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C24">
-        <v>47.54</v>
+        <v>30.79</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>5016.02</v>
+        <v>3545.32</v>
       </c>
       <c r="F24">
-        <v>3633.21</v>
+        <v>2346.48</v>
       </c>
       <c r="G24">
-        <v>3569.77</v>
+        <v>2254.34</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1699,10 +1687,10 @@
         <f>IF(D24=0,"",(H24-D24)/D24)</f>
       </c>
       <c r="K24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L24" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1710,22 +1698,22 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>45</v>
+        <v>237</v>
       </c>
       <c r="C25">
-        <v>38.7</v>
+        <v>28.02</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>4149.59</v>
+        <v>3045.09</v>
       </c>
       <c r="F25">
-        <v>2911.18</v>
+        <v>2091.33</v>
       </c>
       <c r="G25">
-        <v>2807.38</v>
+        <v>2056.53</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1737,7 +1725,7 @@
         <f>IF(D25=0,"",(H25-D25)/D25)</f>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
         <v>19</v>
@@ -1748,22 +1736,22 @@
         <v>45</v>
       </c>
       <c r="B26">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="C26">
-        <v>36.82</v>
+        <v>23.84</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>4058.24</v>
+        <v>2904.51</v>
       </c>
       <c r="F26">
-        <v>2987.19</v>
+        <v>1815.03</v>
       </c>
       <c r="G26">
-        <v>2768.16</v>
+        <v>1901.74</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1775,10 +1763,10 @@
         <f>IF(D26=0,"",(H26-D26)/D26)</f>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1786,22 +1774,22 @@
         <v>46</v>
       </c>
       <c r="B27">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="C27">
-        <v>35.43</v>
+        <v>23.32</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>4229.29</v>
+        <v>2986.71</v>
       </c>
       <c r="F27">
-        <v>2617.18</v>
+        <v>1734.11</v>
       </c>
       <c r="G27">
-        <v>2704.15</v>
+        <v>1699.42</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1813,33 +1801,33 @@
         <f>IF(D27=0,"",(H27-D27)/D27)</f>
       </c>
       <c r="K27" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="L27" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B28">
-        <v>238</v>
+        <v>70</v>
       </c>
       <c r="C28">
-        <v>32.41</v>
+        <v>22.82</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>3930.44</v>
+        <v>2626.36</v>
       </c>
       <c r="F28">
-        <v>2444.4</v>
+        <v>1838.04</v>
       </c>
       <c r="G28">
-        <v>2408.3</v>
+        <v>1818.84</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1851,33 +1839,33 @@
         <f>IF(D28=0,"",(H28-D28)/D28)</f>
       </c>
       <c r="K28" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B29">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="C29">
-        <v>31.43</v>
+        <v>21.01</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>3489.84</v>
+        <v>2425.67</v>
       </c>
       <c r="F29">
-        <v>2513.26</v>
+        <v>1656.65</v>
       </c>
       <c r="G29">
-        <v>2410.61</v>
+        <v>1560.58</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1889,33 +1877,33 @@
         <f>IF(D29=0,"",(H29-D29)/D29)</f>
       </c>
       <c r="K29" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30">
-        <v>186</v>
+        <v>1186</v>
       </c>
       <c r="C30">
-        <v>29.66</v>
+        <v>19.45</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>3074.39</v>
+        <v>2228.09</v>
       </c>
       <c r="F30">
-        <v>2237.48</v>
+        <v>1468.21</v>
       </c>
       <c r="G30">
-        <v>2162.63</v>
+        <v>1421.97</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1927,33 +1915,33 @@
         <f>IF(D30=0,"",(H30-D30)/D30)</f>
       </c>
       <c r="K30" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="L30" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B31">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="C31">
-        <v>25.07</v>
+        <v>19.44</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2708.64</v>
+        <v>2133.3</v>
       </c>
       <c r="F31">
-        <v>1914.53</v>
+        <v>1434.91</v>
       </c>
       <c r="G31">
-        <v>1880.04</v>
+        <v>1450.87</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1968,30 +1956,30 @@
         <v>18</v>
       </c>
       <c r="L31" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B32">
-        <v>263</v>
+        <v>29</v>
       </c>
       <c r="C32">
-        <v>24.54</v>
+        <v>18.95</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>3010.49</v>
+        <v>2321.39</v>
       </c>
       <c r="F32">
-        <v>1908.88</v>
+        <v>1419.65</v>
       </c>
       <c r="G32">
-        <v>1916.95</v>
+        <v>1395.38</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2003,33 +1991,33 @@
         <f>IF(D32=0,"",(H32-D32)/D32)</f>
       </c>
       <c r="K32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L32" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C33">
-        <v>21.34</v>
+        <v>18.83</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>2318.33</v>
+        <v>2072.49</v>
       </c>
       <c r="F33">
-        <v>1666.2</v>
+        <v>1398.84</v>
       </c>
       <c r="G33">
-        <v>1659.74</v>
+        <v>1356.07</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2041,33 +2029,33 @@
         <f>IF(D33=0,"",(H33-D33)/D33)</f>
       </c>
       <c r="K33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="C34">
-        <v>19.8</v>
+        <v>18.35</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>2186.73</v>
+        <v>2022.66</v>
       </c>
       <c r="F34">
-        <v>1473.01</v>
+        <v>1368.79</v>
       </c>
       <c r="G34">
-        <v>1502.88</v>
+        <v>1327.17</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2079,33 +2067,33 @@
         <f>IF(D34=0,"",(H34-D34)/D34)</f>
       </c>
       <c r="K34" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35">
-        <v>758</v>
+        <v>44</v>
       </c>
       <c r="C35">
-        <v>19.49</v>
+        <v>16.25</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>2297.11</v>
+        <v>1746.94</v>
       </c>
       <c r="F35">
-        <v>1510.95</v>
+        <v>1218.5</v>
       </c>
       <c r="G35">
-        <v>1493.65</v>
+        <v>1212.49</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2117,33 +2105,33 @@
         <f>IF(D35=0,"",(H35-D35)/D35)</f>
       </c>
       <c r="K35" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="L35" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="C36">
-        <v>19.16</v>
+        <v>15.86</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>2327.79</v>
+        <v>1785.67</v>
       </c>
       <c r="F36">
-        <v>1481.77</v>
+        <v>1275.03</v>
       </c>
       <c r="G36">
-        <v>1430.22</v>
+        <v>1226.01</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2155,33 +2143,33 @@
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
       <c r="K36" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37">
-        <v>18.95</v>
+        <v>13.82</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>2162.28</v>
+        <v>1415.03</v>
       </c>
       <c r="F37">
-        <v>1441.63</v>
+        <v>1141.97</v>
       </c>
       <c r="G37">
-        <v>1444.86</v>
+        <v>1039.08</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2193,10 +2181,10 @@
         <f>IF(D37=0,"",(H37-D37)/D37)</f>
       </c>
       <c r="K37" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L37" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2204,22 +2192,22 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>123</v>
+        <v>1797</v>
       </c>
       <c r="C38">
-        <v>18.35</v>
+        <v>13.11</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>2163.89</v>
+        <v>1527.28</v>
       </c>
       <c r="F38">
-        <v>1442.9</v>
+        <v>989.6</v>
       </c>
       <c r="G38">
-        <v>1382.7</v>
+        <v>966.36</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2231,33 +2219,33 @@
         <f>IF(D38=0,"",(H38-D38)/D38)</f>
       </c>
       <c r="K38" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B39">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39">
-        <v>15.89</v>
+        <v>13.01</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1967.59</v>
+        <v>1547.05</v>
       </c>
       <c r="F39">
-        <v>1257.21</v>
+        <v>1014.8</v>
       </c>
       <c r="G39">
-        <v>1245.67</v>
+        <v>976.76</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2269,33 +2257,33 @@
         <f>IF(D39=0,"",(H39-D39)/D39)</f>
       </c>
       <c r="K39" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B40">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C40">
-        <v>14.84</v>
+        <v>12.62</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1800.46</v>
+        <v>1456.19</v>
       </c>
       <c r="F40">
-        <v>1158.94</v>
+        <v>981.97</v>
       </c>
       <c r="G40">
-        <v>1141.87</v>
+        <v>951.33</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2307,33 +2295,33 @@
         <f>IF(D40=0,"",(H40-D40)/D40)</f>
       </c>
       <c r="K40" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="L40" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B41">
-        <v>23</v>
+        <v>1478</v>
       </c>
       <c r="C41">
-        <v>13.94</v>
+        <v>12.41</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1455.94</v>
+        <v>1450.64</v>
       </c>
       <c r="F41">
-        <v>1061.01</v>
+        <v>955.84</v>
       </c>
       <c r="G41">
-        <v>1092.27</v>
+        <v>906.24</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2345,33 +2333,33 @@
         <f>IF(D41=0,"",(H41-D41)/D41)</f>
       </c>
       <c r="K41" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L41" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B42">
-        <v>1158</v>
+        <v>540</v>
       </c>
       <c r="C42">
-        <v>13.86</v>
+        <v>12.11</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1455.13</v>
+        <v>1278.38</v>
       </c>
       <c r="F42">
-        <v>1038.06</v>
+        <v>913.06</v>
       </c>
       <c r="G42">
-        <v>1033.22</v>
+        <v>913.87</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2383,33 +2371,33 @@
         <f>IF(D42=0,"",(H42-D42)/D42)</f>
       </c>
       <c r="K42" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="L42" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B43">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="C43">
-        <v>13.54</v>
+        <v>11.82</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1536.33</v>
+        <v>1412.72</v>
       </c>
       <c r="F43">
-        <v>980.39</v>
+        <v>843.93</v>
       </c>
       <c r="G43">
-        <v>936.91</v>
+        <v>842.78</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2421,33 +2409,33 @@
         <f>IF(D43=0,"",(H43-D43)/D43)</f>
       </c>
       <c r="K43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L43" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B44">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C44">
-        <v>13.44</v>
+        <v>11.63</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1448.09</v>
+        <v>1578.61</v>
       </c>
       <c r="F44">
-        <v>975.78</v>
+        <v>929.83</v>
       </c>
       <c r="G44">
-        <v>1035.75</v>
+        <v>884.16</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2459,33 +2447,33 @@
         <f>IF(D44=0,"",(H44-D44)/D44)</f>
       </c>
       <c r="K44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B45">
-        <v>1104</v>
+        <v>166</v>
       </c>
       <c r="C45">
-        <v>13.36</v>
+        <v>11.08</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1546.59</v>
+        <v>1242.78</v>
       </c>
       <c r="F45">
-        <v>1083.85</v>
+        <v>820.81</v>
       </c>
       <c r="G45">
-        <v>1066.78</v>
+        <v>832.25</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2497,33 +2485,33 @@
         <f>IF(D45=0,"",(H45-D45)/D45)</f>
       </c>
       <c r="K45" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="L45" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>1680</v>
       </c>
       <c r="C46">
-        <v>12.51</v>
+        <v>10.71</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1418.11</v>
+        <v>1336.88</v>
       </c>
       <c r="F46">
-        <v>1031.02</v>
+        <v>819.65</v>
       </c>
       <c r="G46">
-        <v>977.28</v>
+        <v>805.78</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2535,33 +2523,33 @@
         <f>IF(D46=0,"",(H46-D46)/D46)</f>
       </c>
       <c r="K46" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L46" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B47">
-        <v>370</v>
+        <v>233</v>
       </c>
       <c r="C47">
-        <v>12.11</v>
+        <v>10.47</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1372.43</v>
+        <v>1313.18</v>
       </c>
       <c r="F47">
-        <v>957.32</v>
+        <v>797.11</v>
       </c>
       <c r="G47">
-        <v>925.03</v>
+        <v>805.2</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2573,33 +2561,33 @@
         <f>IF(D47=0,"",(H47-D47)/D47)</f>
       </c>
       <c r="K47" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L47" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B48">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C48">
-        <v>11.94</v>
+        <v>10.01</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1330.56</v>
+        <v>1091.91</v>
       </c>
       <c r="F48">
-        <v>974.39</v>
+        <v>716.65</v>
       </c>
       <c r="G48">
-        <v>934.25</v>
+        <v>714.22</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2611,10 +2599,10 @@
         <f>IF(D48=0,"",(H48-D48)/D48)</f>
       </c>
       <c r="K48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2622,22 +2610,22 @@
         <v>76</v>
       </c>
       <c r="B49">
-        <v>129</v>
+        <v>1404</v>
       </c>
       <c r="C49">
-        <v>11.64</v>
+        <v>9.99</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1252.59</v>
+        <v>1068.21</v>
       </c>
       <c r="F49">
-        <v>839.68</v>
+        <v>727.17</v>
       </c>
       <c r="G49">
-        <v>852.59</v>
+        <v>728.32</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2649,33 +2637,33 @@
         <f>IF(D49=0,"",(H49-D49)/D49)</f>
       </c>
       <c r="K49" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="L49" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B50">
-        <v>1376</v>
+        <v>161</v>
       </c>
       <c r="C50">
-        <v>11.04</v>
+        <v>9.84</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1357.44</v>
+        <v>1147.98</v>
       </c>
       <c r="F50">
-        <v>830.45</v>
+        <v>785.67</v>
       </c>
       <c r="G50">
-        <v>837.95</v>
+        <v>745.55</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2687,33 +2675,33 @@
         <f>IF(D50=0,"",(H50-D50)/D50)</f>
       </c>
       <c r="K50" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="L50" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B51">
-        <v>196</v>
+        <v>1030</v>
       </c>
       <c r="C51">
-        <v>10.38</v>
+        <v>9.84</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1160.32</v>
+        <v>1142.43</v>
       </c>
       <c r="F51">
-        <v>781.77</v>
+        <v>716.76</v>
       </c>
       <c r="G51">
-        <v>755.48</v>
+        <v>719.08</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2725,33 +2713,33 @@
         <f>IF(D51=0,"",(H51-D51)/D51)</f>
       </c>
       <c r="K51" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L51" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B52">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="C52">
-        <v>10.17</v>
+        <v>9.71</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1112.22</v>
+        <v>1091.1</v>
       </c>
       <c r="F52">
-        <v>699.65</v>
+        <v>715.61</v>
       </c>
       <c r="G52">
-        <v>738.06</v>
+        <v>739.88</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2763,33 +2751,33 @@
         <f>IF(D52=0,"",(H52-D52)/D52)</f>
       </c>
       <c r="K52" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="L52" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B53">
-        <v>131</v>
+        <v>448</v>
       </c>
       <c r="C53">
-        <v>10.14</v>
+        <v>9.58</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1180.04</v>
+        <v>1050.87</v>
       </c>
       <c r="F53">
-        <v>753.63</v>
+        <v>717.92</v>
       </c>
       <c r="G53">
-        <v>820.64</v>
+        <v>700.35</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2801,33 +2789,33 @@
         <f>IF(D53=0,"",(H53-D53)/D53)</f>
       </c>
       <c r="K53" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B54">
-        <v>470</v>
+        <v>215</v>
       </c>
       <c r="C54">
-        <v>10.07</v>
+        <v>9.29</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1080.74</v>
+        <v>1077.69</v>
       </c>
       <c r="F54">
-        <v>724.1</v>
+        <v>704.28</v>
       </c>
       <c r="G54">
-        <v>703.57</v>
+        <v>728.32</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2839,33 +2827,33 @@
         <f>IF(D54=0,"",(H54-D54)/D54)</f>
       </c>
       <c r="K54" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L54" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B55">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C55">
-        <v>9.96</v>
+        <v>8.69</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1135.87</v>
+        <v>949.71</v>
       </c>
       <c r="F55">
-        <v>756.05</v>
+        <v>658.61</v>
       </c>
       <c r="G55">
-        <v>785.12</v>
+        <v>676.3</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2877,33 +2865,33 @@
         <f>IF(D55=0,"",(H55-D55)/D55)</f>
       </c>
       <c r="K55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B56">
-        <v>1063</v>
+        <v>134</v>
       </c>
       <c r="C56">
-        <v>9.67</v>
+        <v>8.62</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>1073.58</v>
+        <v>985.2</v>
       </c>
       <c r="F56">
-        <v>749.71</v>
+        <v>658.73</v>
       </c>
       <c r="G56">
-        <v>763.55</v>
+        <v>618.5</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2915,33 +2903,33 @@
         <f>IF(D56=0,"",(H56-D56)/D56)</f>
       </c>
       <c r="K56" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="L56" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B57">
-        <v>95</v>
+        <v>646</v>
       </c>
       <c r="C57">
-        <v>9.59</v>
+        <v>8.53</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1065.74</v>
+        <v>999.42</v>
       </c>
       <c r="F57">
-        <v>741.52</v>
+        <v>647.4</v>
       </c>
       <c r="G57">
-        <v>749.59</v>
+        <v>624.28</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2953,33 +2941,33 @@
         <f>IF(D57=0,"",(H57-D57)/D57)</f>
       </c>
       <c r="K57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L57" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B58">
-        <v>777</v>
+        <v>215</v>
       </c>
       <c r="C58">
-        <v>9.53</v>
+        <v>8.37</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>1217.88</v>
+        <v>895.95</v>
       </c>
       <c r="F58">
-        <v>715.11</v>
+        <v>611.56</v>
       </c>
       <c r="G58">
-        <v>726.64</v>
+        <v>604.39</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2991,10 +2979,10 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="L58" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3002,22 +2990,22 @@
         <v>88</v>
       </c>
       <c r="B59">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C59">
-        <v>9.47</v>
+        <v>8.2</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>1002.65</v>
+        <v>903.12</v>
       </c>
       <c r="F59">
-        <v>711.42</v>
+        <v>584.39</v>
       </c>
       <c r="G59">
-        <v>739.33</v>
+        <v>593.64</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3029,10 +3017,10 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L59" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,22 +3028,22 @@
         <v>89</v>
       </c>
       <c r="B60">
-        <v>244</v>
+        <v>361</v>
       </c>
       <c r="C60">
-        <v>9.17</v>
+        <v>8.15</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>1008.19</v>
+        <v>888.09</v>
       </c>
       <c r="F60">
-        <v>715.11</v>
+        <v>599.88</v>
       </c>
       <c r="G60">
-        <v>746.13</v>
+        <v>612.72</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3067,10 +3055,10 @@
         <f>IF(D60=0,"",(H60-D60)/D60)</f>
       </c>
       <c r="K60" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="L60" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3078,22 +3066,22 @@
         <v>90</v>
       </c>
       <c r="B61">
-        <v>170</v>
+        <v>797</v>
       </c>
       <c r="C61">
-        <v>8.8</v>
+        <v>8.12</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>906.46</v>
+        <v>854.91</v>
       </c>
       <c r="F61">
-        <v>653.86</v>
+        <v>589.6</v>
       </c>
       <c r="G61">
-        <v>656.28</v>
+        <v>588.44</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3105,10 +3093,10 @@
         <f>IF(D61=0,"",(H61-D61)/D61)</f>
       </c>
       <c r="K61" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="L61" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3116,22 +3104,22 @@
         <v>91</v>
       </c>
       <c r="B62">
-        <v>77</v>
+        <v>855</v>
       </c>
       <c r="C62">
-        <v>8.72</v>
+        <v>8.1</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>1040.48</v>
+        <v>982.89</v>
       </c>
       <c r="F62">
-        <v>678.2</v>
+        <v>600.81</v>
       </c>
       <c r="G62">
-        <v>632.06</v>
+        <v>578.38</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3143,10 +3131,10 @@
         <f>IF(D62=0,"",(H62-D62)/D62)</f>
       </c>
       <c r="K62" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L62" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3154,22 +3142,22 @@
         <v>92</v>
       </c>
       <c r="B63">
-        <v>366</v>
+        <v>124</v>
       </c>
       <c r="C63">
-        <v>8.58</v>
+        <v>8.05</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>985.35</v>
+        <v>995.49</v>
       </c>
       <c r="F63">
-        <v>678.2</v>
+        <v>595.95</v>
       </c>
       <c r="G63">
-        <v>645.9</v>
+        <v>589.48</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3181,10 +3169,10 @@
         <f>IF(D63=0,"",(H63-D63)/D63)</f>
       </c>
       <c r="K63" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="L63" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3192,22 +3180,22 @@
         <v>93</v>
       </c>
       <c r="B64">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="C64">
-        <v>8.54</v>
+        <v>7.88</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>906.46</v>
+        <v>893.64</v>
       </c>
       <c r="F64">
-        <v>605.54</v>
+        <v>566.36</v>
       </c>
       <c r="G64">
-        <v>621.68</v>
+        <v>584.51</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3219,10 +3207,10 @@
         <f>IF(D64=0,"",(H64-D64)/D64)</f>
       </c>
       <c r="K64" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L64" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3230,22 +3218,22 @@
         <v>94</v>
       </c>
       <c r="B65">
-        <v>263</v>
+        <v>778</v>
       </c>
       <c r="C65">
-        <v>8.37</v>
+        <v>7.72</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>889.96</v>
+        <v>905.43</v>
       </c>
       <c r="F65">
-        <v>622.84</v>
+        <v>575.72</v>
       </c>
       <c r="G65">
-        <v>632.06</v>
+        <v>553.76</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3257,10 +3245,10 @@
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
       <c r="K65" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L65" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3268,22 +3256,22 @@
         <v>95</v>
       </c>
       <c r="B66">
-        <v>157</v>
+        <v>1368</v>
       </c>
       <c r="C66">
-        <v>8.3</v>
+        <v>7.69</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>900.23</v>
+        <v>966.24</v>
       </c>
       <c r="F66">
-        <v>621.68</v>
+        <v>588.44</v>
       </c>
       <c r="G66">
-        <v>619.03</v>
+        <v>558.96</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3295,10 +3283,10 @@
         <f>IF(D66=0,"",(H66-D66)/D66)</f>
       </c>
       <c r="K66" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="L66" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3306,22 +3294,22 @@
         <v>96</v>
       </c>
       <c r="B67">
-        <v>635</v>
+        <v>285</v>
       </c>
       <c r="C67">
-        <v>8.06</v>
+        <v>7.57</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>946.71</v>
+        <v>876.99</v>
       </c>
       <c r="F67">
-        <v>601.15</v>
+        <v>583.58</v>
       </c>
       <c r="G67">
-        <v>588.23</v>
+        <v>554.91</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3333,10 +3321,10 @@
         <f>IF(D67=0,"",(H67-D67)/D67)</f>
       </c>
       <c r="K67" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L67" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3344,22 +3332,22 @@
         <v>97</v>
       </c>
       <c r="B68">
-        <v>124</v>
+        <v>1002</v>
       </c>
       <c r="C68">
-        <v>8.02</v>
+        <v>7.46</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>890.77</v>
+        <v>837.46</v>
       </c>
       <c r="F68">
-        <v>586.97</v>
+        <v>564.16</v>
       </c>
       <c r="G68">
-        <v>611.3</v>
+        <v>545.67</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3371,10 +3359,10 @@
         <f>IF(D68=0,"",(H68-D68)/D68)</f>
       </c>
       <c r="K68" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L68" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3382,22 +3370,22 @@
         <v>98</v>
       </c>
       <c r="B69">
-        <v>603</v>
+        <v>1461</v>
       </c>
       <c r="C69">
-        <v>7.96</v>
+        <v>6.91</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>876.58</v>
+        <v>737.92</v>
       </c>
       <c r="F69">
-        <v>607.73</v>
+        <v>516.65</v>
       </c>
       <c r="G69">
-        <v>607.84</v>
+        <v>531.56</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3409,10 +3397,10 @@
         <f>IF(D69=0,"",(H69-D69)/D69)</f>
       </c>
       <c r="K69" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="L69" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3420,22 +3408,22 @@
         <v>99</v>
       </c>
       <c r="B70">
-        <v>1035</v>
+        <v>138</v>
       </c>
       <c r="C70">
-        <v>7.91</v>
+        <v>6.86</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>928.6</v>
+        <v>778.27</v>
       </c>
       <c r="F70">
-        <v>599.77</v>
+        <v>532.25</v>
       </c>
       <c r="G70">
-        <v>628.6</v>
+        <v>509.83</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3447,10 +3435,10 @@
         <f>IF(D70=0,"",(H70-D70)/D70)</f>
       </c>
       <c r="K70" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L70" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3458,22 +3446,22 @@
         <v>100</v>
       </c>
       <c r="B71">
-        <v>669</v>
+        <v>576</v>
       </c>
       <c r="C71">
-        <v>7.9</v>
+        <v>6.49</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>962.51</v>
+        <v>669.13</v>
       </c>
       <c r="F71">
-        <v>620.53</v>
+        <v>470.29</v>
       </c>
       <c r="G71">
-        <v>611.07</v>
+        <v>475.72</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3485,10 +3473,10 @@
         <f>IF(D71=0,"",(H71-D71)/D71)</f>
       </c>
       <c r="K71" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="L71" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3496,22 +3484,22 @@
         <v>101</v>
       </c>
       <c r="B72">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>7.62</v>
+        <v>6.49</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>768.51</v>
+        <v>628.9</v>
       </c>
       <c r="F72">
-        <v>550.29</v>
+        <v>466.47</v>
       </c>
       <c r="G72">
-        <v>550.17</v>
+        <v>462.43</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3523,33 +3511,33 @@
         <f>IF(D72=0,"",(H72-D72)/D72)</f>
       </c>
       <c r="K72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L72" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B73">
-        <v>809</v>
+        <v>209</v>
       </c>
       <c r="C73">
-        <v>7.25</v>
+        <v>6.45</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>818.22</v>
+        <v>749.02</v>
       </c>
       <c r="F73">
-        <v>552.48</v>
+        <v>526.82</v>
       </c>
       <c r="G73">
-        <v>548.44</v>
+        <v>508.67</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3561,33 +3549,33 @@
         <f>IF(D73=0,"",(H73-D73)/D73)</f>
       </c>
       <c r="K73" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L73" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B74">
-        <v>178</v>
+        <v>1123</v>
       </c>
       <c r="C74">
-        <v>6.98</v>
+        <v>6.41</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>770.13</v>
+        <v>667.63</v>
       </c>
       <c r="F74">
-        <v>583.27</v>
+        <v>473.99</v>
       </c>
       <c r="G74">
-        <v>544.4</v>
+        <v>471.68</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3599,33 +3587,33 @@
         <f>IF(D74=0,"",(H74-D74)/D74)</f>
       </c>
       <c r="K74" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L74" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B75">
-        <v>915</v>
+        <v>986</v>
       </c>
       <c r="C75">
-        <v>6.85</v>
+        <v>6.38</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>725.14</v>
+        <v>784.51</v>
       </c>
       <c r="F75">
-        <v>508.53</v>
+        <v>483.24</v>
       </c>
       <c r="G75">
-        <v>522.49</v>
+        <v>471.56</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3637,33 +3625,33 @@
         <f>IF(D75=0,"",(H75-D75)/D75)</f>
       </c>
       <c r="K75" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L75" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B76">
-        <v>349</v>
+        <v>58</v>
       </c>
       <c r="C76">
-        <v>6.76</v>
+        <v>6.36</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>752.82</v>
+        <v>851.68</v>
       </c>
       <c r="F76">
-        <v>480.97</v>
+        <v>508.56</v>
       </c>
       <c r="G76">
-        <v>474.05</v>
+        <v>477.46</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3675,33 +3663,33 @@
         <f>IF(D76=0,"",(H76-D76)/D76)</f>
       </c>
       <c r="K76" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L76" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B77">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="C77">
-        <v>6.73</v>
+        <v>5.97</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>899.42</v>
+        <v>674.68</v>
       </c>
       <c r="F77">
-        <v>529.18</v>
+        <v>445.32</v>
       </c>
       <c r="G77">
-        <v>461.36</v>
+        <v>449.13</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3713,33 +3701,33 @@
         <f>IF(D77=0,"",(H77-D77)/D77)</f>
       </c>
       <c r="K77" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L77" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="C78">
-        <v>6.53</v>
+        <v>5.89</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>834.72</v>
+        <v>615.49</v>
       </c>
       <c r="F78">
-        <v>512.46</v>
+        <v>421.73</v>
       </c>
       <c r="G78">
-        <v>518.91</v>
+        <v>436.88</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3751,10 +3739,10 @@
         <f>IF(D78=0,"",(H78-D78)/D78)</f>
       </c>
       <c r="K78" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="L78" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3762,22 +3750,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>645</v>
+        <v>127</v>
       </c>
       <c r="C79">
-        <v>6.46</v>
+        <v>5.71</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>775.66</v>
+        <v>632.02</v>
       </c>
       <c r="F79">
-        <v>461.36</v>
+        <v>449.71</v>
       </c>
       <c r="G79">
-        <v>475.09</v>
+        <v>405.78</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3789,10 +3777,10 @@
         <f>IF(D79=0,"",(H79-D79)/D79)</f>
       </c>
       <c r="K79" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L79" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3800,22 +3788,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>892</v>
+        <v>101</v>
       </c>
       <c r="C80">
-        <v>6.41</v>
+        <v>5.7</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>707.03</v>
+        <v>615.49</v>
       </c>
       <c r="F80">
-        <v>488.23</v>
+        <v>434.22</v>
       </c>
       <c r="G80">
-        <v>490.2</v>
+        <v>433.53</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3827,10 +3815,10 @@
         <f>IF(D80=0,"",(H80-D80)/D80)</f>
       </c>
       <c r="K80" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L80" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3838,22 +3826,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C81">
-        <v>6.32</v>
+        <v>5.54</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>750.4</v>
+        <v>597.34</v>
       </c>
       <c r="F81">
-        <v>473.01</v>
+        <v>404.62</v>
       </c>
       <c r="G81">
-        <v>551.21</v>
+        <v>412.6</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3865,33 +3853,33 @@
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
       <c r="K81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L81" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B82">
-        <v>47</v>
+        <v>705</v>
       </c>
       <c r="C82">
-        <v>6.29</v>
+        <v>5.52</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>681.89</v>
+        <v>584.62</v>
       </c>
       <c r="F82">
-        <v>455.59</v>
+        <v>418.27</v>
       </c>
       <c r="G82">
-        <v>471.63</v>
+        <v>413.87</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3903,33 +3891,33 @@
         <f>IF(D82=0,"",(H82-D82)/D82)</f>
       </c>
       <c r="K82" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L82" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B83">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C83">
-        <v>6.11</v>
+        <v>5.49</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>592.73</v>
+        <v>633.64</v>
       </c>
       <c r="F83">
-        <v>502.77</v>
+        <v>440.46</v>
       </c>
       <c r="G83">
-        <v>480.62</v>
+        <v>403.47</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3941,33 +3929,33 @@
         <f>IF(D83=0,"",(H83-D83)/D83)</f>
       </c>
       <c r="K83" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L83" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B84">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="C84">
-        <v>6.05</v>
+        <v>5.42</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>684.2</v>
+        <v>627.28</v>
       </c>
       <c r="F84">
-        <v>461.71</v>
+        <v>412.72</v>
       </c>
       <c r="G84">
-        <v>449.25</v>
+        <v>410.4</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3979,33 +3967,33 @@
         <f>IF(D84=0,"",(H84-D84)/D84)</f>
       </c>
       <c r="K84" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L84" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B85">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="C85">
-        <v>6.03</v>
+        <v>5.36</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>466.67</v>
+        <v>556.99</v>
       </c>
       <c r="F85">
-        <v>334.49</v>
+        <v>402.08</v>
       </c>
       <c r="G85">
-        <v>340.02</v>
+        <v>390.75</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4017,33 +4005,33 @@
         <f>IF(D85=0,"",(H85-D85)/D85)</f>
       </c>
       <c r="K85" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L85" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B86">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="C86">
-        <v>5.92</v>
+        <v>5.19</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>692.04</v>
+        <v>602.08</v>
       </c>
       <c r="F86">
-        <v>420.3</v>
+        <v>411.56</v>
       </c>
       <c r="G86">
-        <v>420.88</v>
+        <v>409.25</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4055,33 +4043,33 @@
         <f>IF(D86=0,"",(H86-D86)/D86)</f>
       </c>
       <c r="K86" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L86" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B87">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="C87">
-        <v>5.82</v>
+        <v>5.17</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>685</v>
+        <v>568.09</v>
       </c>
       <c r="F87">
-        <v>414.07</v>
+        <v>392.95</v>
       </c>
       <c r="G87">
-        <v>389.27</v>
+        <v>393.18</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4093,33 +4081,33 @@
         <f>IF(D87=0,"",(H87-D87)/D87)</f>
       </c>
       <c r="K87" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L87" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B88">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C88">
-        <v>5.79</v>
+        <v>5.15</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>630.56</v>
+        <v>575.95</v>
       </c>
       <c r="F88">
-        <v>481.78</v>
+        <v>442.89</v>
       </c>
       <c r="G88">
-        <v>434.6</v>
+        <v>377.92</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4131,33 +4119,33 @@
         <f>IF(D88=0,"",(H88-D88)/D88)</f>
       </c>
       <c r="K88" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L88" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B89">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="C89">
-        <v>5.59</v>
+        <v>5.08</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>608.53</v>
+        <v>568.09</v>
       </c>
       <c r="F89">
-        <v>453.4</v>
+        <v>390.17</v>
       </c>
       <c r="G89">
-        <v>434.72</v>
+        <v>376.88</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4169,33 +4157,33 @@
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
       <c r="K89" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L89" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B90">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="C90">
-        <v>5.53</v>
+        <v>4.82</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>558.82</v>
+        <v>600.46</v>
       </c>
       <c r="F90">
-        <v>438.18</v>
+        <v>375.61</v>
       </c>
       <c r="G90">
-        <v>424.34</v>
+        <v>364.16</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4207,33 +4195,33 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B91">
-        <v>117</v>
+        <v>603</v>
       </c>
       <c r="C91">
-        <v>5.48</v>
+        <v>4.72</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>600.69</v>
+        <v>534.1</v>
       </c>
       <c r="F91">
-        <v>490.43</v>
+        <v>368.79</v>
       </c>
       <c r="G91">
-        <v>443.94</v>
+        <v>344.51</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4245,33 +4233,33 @@
         <f>IF(D91=0,"",(H91-D91)/D91)</f>
       </c>
       <c r="K91" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="L91" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B92">
-        <v>673</v>
+        <v>64</v>
       </c>
       <c r="C92">
-        <v>5.42</v>
+        <v>4.64</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>630.56</v>
+        <v>602.77</v>
       </c>
       <c r="F92">
-        <v>415.22</v>
+        <v>346.82</v>
       </c>
       <c r="G92">
-        <v>418.57</v>
+        <v>345.66</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4283,33 +4271,33 @@
         <f>IF(D92=0,"",(H92-D92)/D92)</f>
       </c>
       <c r="K92" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L92" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B93">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C93">
-        <v>5.36</v>
+        <v>4.59</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>681.08</v>
+        <v>538.03</v>
       </c>
       <c r="F93">
-        <v>432.53</v>
+        <v>364.16</v>
       </c>
       <c r="G93">
-        <v>403.69</v>
+        <v>327.05</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4321,33 +4309,33 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L93" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B94">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="C94">
-        <v>5.27</v>
+        <v>4.58</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>577.05</v>
+        <v>560.12</v>
       </c>
       <c r="F94">
-        <v>386.27</v>
+        <v>393.06</v>
       </c>
       <c r="G94">
-        <v>392.16</v>
+        <v>376.88</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4359,33 +4347,33 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L94" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B95">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="C95">
-        <v>5.26</v>
+        <v>4.58</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>590.43</v>
+        <v>556.99</v>
       </c>
       <c r="F95">
-        <v>397.81</v>
+        <v>401.73</v>
       </c>
       <c r="G95">
-        <v>379.47</v>
+        <v>343.35</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4397,33 +4385,33 @@
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
       <c r="K95" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L95" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>127</v>
+      </c>
+      <c r="B96">
         <v>126</v>
       </c>
-      <c r="B96">
-        <v>116</v>
-      </c>
       <c r="C96">
-        <v>5.24</v>
+        <v>4.53</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>611.65</v>
+        <v>602.08</v>
       </c>
       <c r="F96">
-        <v>409.46</v>
+        <v>392.95</v>
       </c>
       <c r="G96">
-        <v>369.09</v>
+        <v>335.26</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4435,33 +4423,33 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L96" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B97">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C97">
-        <v>5.2</v>
+        <v>4.53</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>567.47</v>
+        <v>504.86</v>
       </c>
       <c r="F97">
-        <v>413.26</v>
+        <v>330.4</v>
       </c>
       <c r="G97">
-        <v>386.39</v>
+        <v>333.87</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4473,10 +4461,10 @@
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
       <c r="K97" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L97" t="s">
-        <v>128</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4484,22 +4472,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>312</v>
+        <v>648</v>
       </c>
       <c r="C98">
-        <v>4.94</v>
+        <v>4.49</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>564.36</v>
+        <v>485.09</v>
       </c>
       <c r="F98">
-        <v>368.97</v>
+        <v>355.84</v>
       </c>
       <c r="G98">
-        <v>391.46</v>
+        <v>346.82</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4511,10 +4499,10 @@
         <f>IF(D98=0,"",(H98-D98)/D98)</f>
       </c>
       <c r="K98" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L98" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4522,22 +4510,22 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C99">
-        <v>4.88</v>
+        <v>4.38</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>580.16</v>
+        <v>513.53</v>
       </c>
       <c r="F99">
-        <v>378.43</v>
+        <v>391.79</v>
       </c>
       <c r="G99">
-        <v>370.24</v>
+        <v>321.39</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4549,10 +4537,10 @@
         <f>IF(D99=0,"",(H99-D99)/D99)</f>
       </c>
       <c r="K99" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L99" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4560,22 +4548,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>424</v>
+        <v>111</v>
       </c>
       <c r="C100">
-        <v>4.81</v>
+        <v>4.38</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>510.03</v>
+        <v>481.16</v>
       </c>
       <c r="F100">
-        <v>342.56</v>
+        <v>330.4</v>
       </c>
       <c r="G100">
-        <v>360.67</v>
+        <v>328.32</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4587,10 +4575,10 @@
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
       <c r="K100" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L100" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4598,22 +4586,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>51</v>
+        <v>2810</v>
       </c>
       <c r="C101">
-        <v>4.71</v>
+        <v>4.34</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>580.16</v>
+        <v>483.47</v>
       </c>
       <c r="F101">
-        <v>367.93</v>
+        <v>323.7</v>
       </c>
       <c r="G101">
-        <v>381.54</v>
+        <v>331.33</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4625,10 +4613,10 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L101" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4636,22 +4624,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="C102">
-        <v>4.67</v>
+        <v>4.1</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>565.17</v>
+        <v>438.5</v>
       </c>
       <c r="F102">
-        <v>343.48</v>
+        <v>375.72</v>
       </c>
       <c r="G102">
-        <v>332.18</v>
+        <v>337.57</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4663,10 +4651,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L102" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4674,22 +4662,22 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C103">
-        <v>4.64</v>
+        <v>4.05</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>527.33</v>
+        <v>477.23</v>
       </c>
       <c r="F103">
-        <v>332.06</v>
+        <v>301.73</v>
       </c>
       <c r="G103">
-        <v>372.2</v>
+        <v>308.67</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4701,10 +4689,10 @@
         <f>IF(D103=0,"",(H103-D103)/D103)</f>
       </c>
       <c r="K103" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L103" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4712,22 +4700,22 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C104">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>477.62</v>
+        <v>472.49</v>
       </c>
       <c r="F104">
-        <v>332.76</v>
+        <v>322.31</v>
       </c>
       <c r="G104">
-        <v>342.33</v>
+        <v>289.02</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4739,10 +4727,10 @@
         <f>IF(D104=0,"",(H104-D104)/D104)</f>
       </c>
       <c r="K104" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L104" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4750,22 +4738,22 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C105">
-        <v>4.6</v>
+        <v>3.89</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>521.8</v>
+        <v>473.99</v>
       </c>
       <c r="F105">
-        <v>368.97</v>
+        <v>323.7</v>
       </c>
       <c r="G105">
-        <v>351.79</v>
+        <v>329.48</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4777,10 +4765,10 @@
         <f>IF(D105=0,"",(H105-D105)/D105)</f>
       </c>
       <c r="K105" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L105" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4788,22 +4776,22 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="C106">
-        <v>4.33</v>
+        <v>3.87</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>446.94</v>
+        <v>457.46</v>
       </c>
       <c r="F106">
-        <v>353.98</v>
+        <v>322.08</v>
       </c>
       <c r="G106">
-        <v>312.69</v>
+        <v>279.77</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4815,10 +4803,10 @@
         <f>IF(D106=0,"",(H106-D106)/D106)</f>
       </c>
       <c r="K106" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L106" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4826,22 +4814,22 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>97</v>
+        <v>262</v>
       </c>
       <c r="C107">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>475.32</v>
+        <v>425.09</v>
       </c>
       <c r="F107">
-        <v>339.68</v>
+        <v>304.74</v>
       </c>
       <c r="G107">
-        <v>341.87</v>
+        <v>322.31</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4853,10 +4841,10 @@
         <f>IF(D107=0,"",(H107-D107)/D107)</f>
       </c>
       <c r="K107" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L107" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4864,22 +4852,22 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>1542</v>
+        <v>42</v>
       </c>
       <c r="C108">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
       </c>
       <c r="E108">
-        <v>465.86</v>
+        <v>515.14</v>
       </c>
       <c r="F108">
-        <v>326.41</v>
+        <v>343.93</v>
       </c>
       <c r="G108">
-        <v>331.03</v>
+        <v>277.34</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4891,10 +4879,10 @@
         <f>IF(D108=0,"",(H108-D108)/D108)</f>
       </c>
       <c r="K108" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L108" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4902,22 +4890,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>50</v>
+        <v>383</v>
       </c>
       <c r="C109">
-        <v>4.19</v>
+        <v>3.59</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>525.72</v>
+        <v>392.6</v>
       </c>
       <c r="F109">
-        <v>305.65</v>
+        <v>273.87</v>
       </c>
       <c r="G109">
-        <v>302.08</v>
+        <v>273.87</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4929,10 +4917,10 @@
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
       <c r="K109" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L109" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4940,22 +4928,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>26</v>
+        <v>385</v>
       </c>
       <c r="C110">
-        <v>4.09</v>
+        <v>3.54</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>453.17</v>
+        <v>385.55</v>
       </c>
       <c r="F110">
-        <v>321.68</v>
+        <v>277.46</v>
       </c>
       <c r="G110">
-        <v>291.58</v>
+        <v>294.45</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4967,10 +4955,10 @@
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
       <c r="K110" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L110" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4978,22 +4966,22 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C111">
-        <v>4.06</v>
+        <v>3.39</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>412.23</v>
+        <v>372.14</v>
       </c>
       <c r="F111">
-        <v>338.52</v>
+        <v>260.12</v>
       </c>
       <c r="G111">
-        <v>334.26</v>
+        <v>261.27</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -5005,10 +4993,10 @@
         <f>IF(D111=0,"",(H111-D111)/D111)</f>
       </c>
       <c r="K111" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L111" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5016,22 +5004,22 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="C112">
-        <v>3.86</v>
+        <v>3.36</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>424.11</v>
+        <v>429.02</v>
       </c>
       <c r="F112">
-        <v>311.42</v>
+        <v>256.65</v>
       </c>
       <c r="G112">
-        <v>292.39</v>
+        <v>255.38</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5043,10 +5031,10 @@
         <f>IF(D112=0,"",(H112-D112)/D112)</f>
       </c>
       <c r="K112" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="L112" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -5054,22 +5042,22 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="C113">
-        <v>3.82</v>
+        <v>3.21</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>402.77</v>
+        <v>353.87</v>
       </c>
       <c r="F113">
-        <v>288.12</v>
+        <v>248.56</v>
       </c>
       <c r="G113">
-        <v>281.43</v>
+        <v>241.62</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5081,10 +5069,10 @@
         <f>IF(D113=0,"",(H113-D113)/D113)</f>
       </c>
       <c r="K113" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L113" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5092,22 +5080,22 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C114">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>476.82</v>
+        <v>351.56</v>
       </c>
       <c r="F114">
-        <v>265.17</v>
+        <v>233.87</v>
       </c>
       <c r="G114">
-        <v>276.7</v>
+        <v>241.85</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5119,10 +5107,10 @@
         <f>IF(D114=0,"",(H114-D114)/D114)</f>
       </c>
       <c r="K114" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L114" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5130,22 +5118,22 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>293</v>
+        <v>66</v>
       </c>
       <c r="C115">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>400.46</v>
+        <v>414.8</v>
       </c>
       <c r="F115">
-        <v>280.16</v>
+        <v>269.48</v>
       </c>
       <c r="G115">
-        <v>274.51</v>
+        <v>265.9</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5157,10 +5145,10 @@
         <f>IF(D115=0,"",(H115-D115)/D115)</f>
       </c>
       <c r="K115" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L115" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5168,22 +5156,22 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>46</v>
+        <v>269</v>
       </c>
       <c r="C116">
-        <v>3.51</v>
+        <v>3.14</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>362.51</v>
+        <v>392.6</v>
       </c>
       <c r="F116">
-        <v>258.13</v>
+        <v>253.18</v>
       </c>
       <c r="G116">
-        <v>253.63</v>
+        <v>242.77</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5195,10 +5183,10 @@
         <f>IF(D116=0,"",(H116-D116)/D116)</f>
       </c>
       <c r="K116" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L116" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5206,22 +5194,22 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="C117">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>393.31</v>
+        <v>353.87</v>
       </c>
       <c r="F117">
-        <v>283.51</v>
+        <v>229.94</v>
       </c>
       <c r="G117">
-        <v>280.05</v>
+        <v>227.05</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5233,10 +5221,10 @@
         <f>IF(D117=0,"",(H117-D117)/D117)</f>
       </c>
       <c r="K117" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L117" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5244,22 +5232,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C118">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>439.79</v>
+        <v>338.96</v>
       </c>
       <c r="F118">
-        <v>281.31</v>
+        <v>229.6</v>
       </c>
       <c r="G118">
-        <v>265.05</v>
+        <v>214.8</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5271,10 +5259,10 @@
         <f>IF(D118=0,"",(H118-D118)/D118)</f>
       </c>
       <c r="K118" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="L118" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5282,22 +5270,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C119">
-        <v>3.31</v>
+        <v>2.87</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>404.38</v>
+        <v>310.52</v>
       </c>
       <c r="F119">
-        <v>238.52</v>
+        <v>223.7</v>
       </c>
       <c r="G119">
-        <v>257.67</v>
+        <v>214.91</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5309,10 +5297,10 @@
         <f>IF(D119=0,"",(H119-D119)/D119)</f>
       </c>
       <c r="K119" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L119" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5320,22 +5308,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C120">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>375.2</v>
+        <v>304.97</v>
       </c>
       <c r="F120">
-        <v>252.48</v>
+        <v>231.21</v>
       </c>
       <c r="G120">
-        <v>242.21</v>
+        <v>202.31</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5347,10 +5335,10 @@
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
       <c r="K120" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L120" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5358,22 +5346,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="C121">
-        <v>3.21</v>
+        <v>2.77</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>351.56</v>
+        <v>308.9</v>
       </c>
       <c r="F121">
-        <v>231.37</v>
+        <v>206.82</v>
       </c>
       <c r="G121">
-        <v>233.22</v>
+        <v>197.92</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5385,10 +5373,10 @@
         <f>IF(D121=0,"",(H121-D121)/D121)</f>
       </c>
       <c r="K121" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L121" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5396,22 +5384,22 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>237</v>
+        <v>31</v>
       </c>
       <c r="C122">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>364.94</v>
+        <v>315.95</v>
       </c>
       <c r="F122">
-        <v>261.82</v>
+        <v>182.66</v>
       </c>
       <c r="G122">
-        <v>242.21</v>
+        <v>195.26</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -5423,10 +5411,10 @@
         <f>IF(D122=0,"",(H122-D122)/D122)</f>
       </c>
       <c r="K122" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="L122" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5434,22 +5422,22 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C123">
-        <v>2.98</v>
+        <v>2.29</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>310.5</v>
+        <v>248.09</v>
       </c>
       <c r="F123">
-        <v>226.07</v>
+        <v>179.19</v>
       </c>
       <c r="G123">
-        <v>222.03</v>
+        <v>176.53</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5461,10 +5449,10 @@
         <f>IF(D123=0,"",(H123-D123)/D123)</f>
       </c>
       <c r="K123" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L123" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5472,22 +5460,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="C124">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>331.83</v>
+        <v>252.02</v>
       </c>
       <c r="F124">
-        <v>226.07</v>
+        <v>164.05</v>
       </c>
       <c r="G124">
-        <v>217.99</v>
+        <v>161.85</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5499,10 +5487,10 @@
         <f>IF(D124=0,"",(H124-D124)/D124)</f>
       </c>
       <c r="K124" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="L124" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5510,22 +5498,22 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C125">
-        <v>2.77</v>
+        <v>2.21</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>323.99</v>
+        <v>275.72</v>
       </c>
       <c r="F125">
-        <v>212.23</v>
+        <v>172.25</v>
       </c>
       <c r="G125">
-        <v>206.92</v>
+        <v>183.12</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5537,10 +5525,10 @@
         <f>IF(D125=0,"",(H125-D125)/D125)</f>
       </c>
       <c r="K125" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L125" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5548,22 +5536,22 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C126">
-        <v>2.59</v>
+        <v>1.89</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>353.06</v>
+        <v>201.39</v>
       </c>
       <c r="F126">
-        <v>189.16</v>
+        <v>138.27</v>
       </c>
       <c r="G126">
-        <v>191.23</v>
+        <v>138.5</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5575,10 +5563,10 @@
         <f>IF(D126=0,"",(H126-D126)/D126)</f>
       </c>
       <c r="K126" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L126" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5586,22 +5574,22 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C127">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>266.44</v>
+        <v>197.46</v>
       </c>
       <c r="F127">
-        <v>171.74</v>
+        <v>160.46</v>
       </c>
       <c r="G127">
-        <v>171.74</v>
+        <v>138.73</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5613,10 +5601,10 @@
         <f>IF(D127=0,"",(H127-D127)/D127)</f>
       </c>
       <c r="K127" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="L127" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5624,22 +5612,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>100</v>
+        <v>263</v>
       </c>
       <c r="C128">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>290.89</v>
+        <v>184.05</v>
       </c>
       <c r="F128">
-        <v>176.24</v>
+        <v>134.8</v>
       </c>
       <c r="G128">
-        <v>175.32</v>
+        <v>117.92</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5651,10 +5639,10 @@
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
       <c r="K128" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L128" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5662,22 +5650,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>14</v>
+        <v>266</v>
       </c>
       <c r="C129">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>249.83</v>
+        <v>172.14</v>
       </c>
       <c r="F129">
-        <v>178.78</v>
+        <v>118.38</v>
       </c>
       <c r="G129">
-        <v>186.85</v>
+        <v>135.84</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5689,10 +5677,10 @@
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
       <c r="K129" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L129" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5700,22 +5688,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>70</v>
+        <v>314</v>
       </c>
       <c r="C130">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>215.11</v>
+        <v>154.8</v>
       </c>
       <c r="F130">
-        <v>169.2</v>
+        <v>113.18</v>
       </c>
       <c r="G130">
-        <v>171.86</v>
+        <v>114.91</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5727,10 +5715,10 @@
         <f>IF(D130=0,"",(H130-D130)/D130)</f>
       </c>
       <c r="K130" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L130" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5738,22 +5726,22 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="C131">
-        <v>1.99</v>
+        <v>1.37</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
       </c>
       <c r="E131">
-        <v>211.99</v>
+        <v>172.14</v>
       </c>
       <c r="F131">
-        <v>142.44</v>
+        <v>103.12</v>
       </c>
       <c r="G131">
-        <v>149.94</v>
+        <v>103.7</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5765,10 +5753,10 @@
         <f>IF(D131=0,"",(H131-D131)/D131)</f>
       </c>
       <c r="K131" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L131" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5776,22 +5764,22 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>205</v>
+        <v>1037</v>
       </c>
       <c r="C132">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>206.46</v>
+        <v>147.75</v>
       </c>
       <c r="F132">
-        <v>133.45</v>
+        <v>99.65</v>
       </c>
       <c r="G132">
-        <v>136.1</v>
+        <v>102.43</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5803,10 +5791,10 @@
         <f>IF(D132=0,"",(H132-D132)/D132)</f>
       </c>
       <c r="K132" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L132" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5814,22 +5802,22 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>255</v>
+        <v>616</v>
       </c>
       <c r="C133">
-        <v>1.66</v>
+        <v>0.93</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>173.36</v>
+        <v>112.14</v>
       </c>
       <c r="F133">
-        <v>126.87</v>
+        <v>72.02</v>
       </c>
       <c r="G133">
-        <v>133.79</v>
+        <v>72.14</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5841,10 +5829,10 @@
         <f>IF(D133=0,"",(H133-D133)/D133)</f>
       </c>
       <c r="K133" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L133" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5852,22 +5840,22 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>195</v>
+        <v>391</v>
       </c>
       <c r="C134">
-        <v>1.53</v>
+        <v>0.82</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>164.71</v>
+        <v>100.35</v>
       </c>
       <c r="F134">
-        <v>114.99</v>
+        <v>61.16</v>
       </c>
       <c r="G134">
-        <v>115.34</v>
+        <v>64.51</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5879,10 +5867,10 @@
         <f>IF(D134=0,"",(H134-D134)/D134)</f>
       </c>
       <c r="K134" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L134" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5890,22 +5878,22 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>54</v>
+        <v>362</v>
       </c>
       <c r="C135">
-        <v>1.52</v>
+        <v>0.72</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>167.82</v>
+        <v>78.96</v>
       </c>
       <c r="F135">
-        <v>114.42</v>
+        <v>43.35</v>
       </c>
       <c r="G135">
-        <v>114.19</v>
+        <v>47.17</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5917,10 +5905,10 @@
         <f>IF(D135=0,"",(H135-D135)/D135)</f>
       </c>
       <c r="K135" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L135" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5928,22 +5916,22 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>713</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>1.49</v>
+        <v>0.47</v>
       </c>
       <c r="D136">
         <f>C136*$B$3</f>
       </c>
       <c r="E136">
-        <v>155.25</v>
+        <v>64.74</v>
       </c>
       <c r="F136">
-        <v>103.69</v>
+        <v>36.3</v>
       </c>
       <c r="G136">
-        <v>103.69</v>
+        <v>33.87</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5955,162 +5943,10 @@
         <f>IF(D136=0,"",(H136-D136)/D136)</f>
       </c>
       <c r="K136" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="L136" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>168</v>
-      </c>
-      <c r="B137">
-        <v>455</v>
-      </c>
-      <c r="C137">
-        <v>1.03</v>
-      </c>
-      <c r="D137">
-        <f>C137*$B$3</f>
-      </c>
-      <c r="E137">
-        <v>121.34</v>
-      </c>
-      <c r="F137">
-        <v>75.55</v>
-      </c>
-      <c r="G137">
-        <v>77.28</v>
-      </c>
-      <c r="H137">
-        <f>MIN(E137:G137)</f>
-      </c>
-      <c r="I137">
-        <f>H137-D137</f>
-      </c>
-      <c r="J137" s="2">
-        <f>IF(D137=0,"",(H137-D137)/D137)</f>
-      </c>
-      <c r="K137" t="s">
-        <v>23</v>
-      </c>
-      <c r="L137" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>169</v>
-      </c>
-      <c r="B138">
-        <v>197</v>
-      </c>
-      <c r="C138">
-        <v>0.86</v>
-      </c>
-      <c r="D138">
-        <f>C138*$B$3</f>
-      </c>
-      <c r="E138">
-        <v>92.96</v>
-      </c>
-      <c r="F138">
-        <v>62.17</v>
-      </c>
-      <c r="G138">
-        <v>62.28</v>
-      </c>
-      <c r="H138">
-        <f>MIN(E138:G138)</f>
-      </c>
-      <c r="I138">
-        <f>H138-D138</f>
-      </c>
-      <c r="J138" s="2">
-        <f>IF(D138=0,"",(H138-D138)/D138)</f>
-      </c>
-      <c r="K138" t="s">
-        <v>23</v>
-      </c>
-      <c r="L138" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>170</v>
-      </c>
-      <c r="B139">
-        <v>262</v>
-      </c>
-      <c r="C139">
-        <v>0.74</v>
-      </c>
-      <c r="D139">
-        <f>C139*$B$3</f>
-      </c>
-      <c r="E139">
-        <v>81.89</v>
-      </c>
-      <c r="F139">
-        <v>48.21</v>
-      </c>
-      <c r="G139">
-        <v>49.02</v>
-      </c>
-      <c r="H139">
-        <f>MIN(E139:G139)</f>
-      </c>
-      <c r="I139">
-        <f>H139-D139</f>
-      </c>
-      <c r="J139" s="2">
-        <f>IF(D139=0,"",(H139-D139)/D139)</f>
-      </c>
-      <c r="K139" t="s">
-        <v>26</v>
-      </c>
-      <c r="L139" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>171</v>
-      </c>
-      <c r="B140">
-        <v>39</v>
-      </c>
-      <c r="C140">
-        <v>0.5</v>
-      </c>
-      <c r="D140">
-        <f>C140*$B$3</f>
-      </c>
-      <c r="E140">
-        <v>63.78</v>
-      </c>
-      <c r="F140">
-        <v>34.49</v>
-      </c>
-      <c r="G140">
-        <v>34.14</v>
-      </c>
-      <c r="H140">
-        <f>MIN(E140:G140)</f>
-      </c>
-      <c r="I140">
-        <f>H140-D140</f>
-      </c>
-      <c r="J140" s="2">
-        <f>IF(D140=0,"",(H140-D140)/D140)</f>
-      </c>
-      <c r="K140" t="s">
-        <v>59</v>
-      </c>
-      <c r="L140" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="168">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 26.07.2026 17:12</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 27.07.2026 16:47</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -121,10 +121,13 @@
     <t>Desert Eagle | Starcade (Field-Tested)</t>
   </si>
   <si>
+    <t>P250 | Apep's Curse (Field-Tested)</t>
+  </si>
+  <si>
     <t>FAMAS | Waters of Nephthys (Field-Tested)</t>
   </si>
   <si>
-    <t>P250 | Apep's Curse (Field-Tested)</t>
+    <t>SCAR-20 | Cyrex (Factory New)</t>
   </si>
   <si>
     <t>CZ75-Auto | Emerald (Factory New)</t>
@@ -133,15 +136,21 @@
     <t>Dual Berettas | Emerald (Factory New)</t>
   </si>
   <si>
-    <t>SCAR-20 | Cyrex (Factory New)</t>
-  </si>
-  <si>
     <t>M4A4 | Polysoup (Factory New)</t>
   </si>
   <si>
     <t>Restricted</t>
   </si>
   <si>
+    <t>Sticker | Liquid Fire</t>
+  </si>
+  <si>
+    <t>Sticker</t>
+  </si>
+  <si>
+    <t>High Grade</t>
+  </si>
+  <si>
     <t>Galil AR | Cerberus (Field-Tested)</t>
   </si>
   <si>
@@ -166,10 +175,16 @@
     <t>SG 553 | Integrale (Minimal Wear)</t>
   </si>
   <si>
+    <t>FAMAS | Styx (Minimal Wear)</t>
+  </si>
+  <si>
     <t>Safecracker Voltzmann | The Professionals</t>
   </si>
   <si>
-    <t>FAMAS | Styx (Minimal Wear)</t>
+    <t>M4A4 | Polysoup (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
   </si>
   <si>
     <t>Nova | Sobek's Bite (Factory New)</t>
@@ -178,12 +193,6 @@
     <t>Shotgun</t>
   </si>
   <si>
-    <t>Glock-18 | Ramese's Reach (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>M4A4 | Polysoup (Minimal Wear)</t>
-  </si>
-  <si>
     <t>MP9 | Music Box (Factory New)</t>
   </si>
   <si>
@@ -193,21 +202,18 @@
     <t>Nova | Sobek's Bite (Minimal Wear)</t>
   </si>
   <si>
+    <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
+  </si>
+  <si>
     <t>'The Doctor' Romanov | Sabre</t>
   </si>
   <si>
     <t>Master</t>
   </si>
   <si>
-    <t>Five-SeveN | Copper Galaxy (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | Great Wave (Foil)</t>
   </si>
   <si>
-    <t>Sticker</t>
-  </si>
-  <si>
     <t>Exotic</t>
   </si>
   <si>
@@ -229,121 +235,121 @@
     <t>Industrial Grade</t>
   </si>
   <si>
+    <t>The Elite Mr. Muhlik | Elite Crew</t>
+  </si>
+  <si>
     <t>AWP | Exoskeleton (Minimal Wear)</t>
   </si>
   <si>
-    <t>The Elite Mr. Muhlik | Elite Crew</t>
-  </si>
-  <si>
     <t>Sticker | Cloud9 (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Osiris | Elite Crew</t>
+  </si>
+  <si>
+    <t>Exceptional</t>
+  </si>
+  <si>
     <t>P250 | Epicenter (Minimal Wear)</t>
   </si>
   <si>
-    <t>Osiris | Elite Crew</t>
-  </si>
-  <si>
-    <t>Exceptional</t>
-  </si>
-  <si>
     <t>FAMAS | Styx (Field-Tested)</t>
   </si>
   <si>
+    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
+  </si>
+  <si>
     <t>B Squadron Officer | SAS</t>
   </si>
   <si>
     <t>Distinguished</t>
   </si>
   <si>
+    <t>USP-S | Guardian (Factory New)</t>
+  </si>
+  <si>
     <t>Markus Delrow | FBI HRT</t>
   </si>
   <si>
-    <t>Glock-18 | Ramese's Reach (Field-Tested)</t>
-  </si>
-  <si>
-    <t>USP-S | Guardian (Factory New)</t>
-  </si>
-  <si>
     <t>AUG | Carved Jade (Minimal Wear)</t>
   </si>
   <si>
+    <t>MP7 | Fade (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Great Wave (Holo)</t>
+  </si>
+  <si>
+    <t>SSG 08 | Rapid Transit (Factory New)</t>
+  </si>
+  <si>
+    <t>MP7 | Fade (Field-Tested)</t>
+  </si>
+  <si>
+    <t>Slingshot | Phoenix</t>
+  </si>
+  <si>
+    <t>Blackwolf | Sabre</t>
+  </si>
+  <si>
     <t>Five-SeveN | Kami (Factory New)</t>
   </si>
   <si>
-    <t>MP7 | Fade (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>SSG 08 | Rapid Transit (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Great Wave (Holo)</t>
-  </si>
-  <si>
-    <t>MP7 | Fade (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Blackwolf | Sabre</t>
-  </si>
-  <si>
-    <t>Slingshot | Phoenix</t>
-  </si>
-  <si>
-    <t>Sticker | 9z Team (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
     <t>SG 553 | Integrale (Field-Tested)</t>
   </si>
   <si>
+    <t>Rezan The Ready | Sabre</t>
+  </si>
+  <si>
+    <t>Prof. Shahmat | Elite Crew</t>
+  </si>
+  <si>
     <t>Rezan the Redshirt | Sabre</t>
   </si>
   <si>
-    <t>Rezan The Ready | Sabre</t>
-  </si>
-  <si>
     <t>Sticker | Copenhagen Flames (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Prof. Shahmat | Elite Crew</t>
+    <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
   </si>
   <si>
     <t>AK-47 | Slate (Minimal Wear)</t>
   </si>
   <si>
-    <t>Sticker | Entropiq (Holo) | Stockholm 2021</t>
+    <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Maximus | Sabre</t>
+  </si>
+  <si>
+    <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Dragomir | Sabre</t>
   </si>
   <si>
     <t>AK-47 | Crossfade (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Liquid Fire</t>
-  </si>
-  <si>
-    <t>High Grade</t>
-  </si>
-  <si>
-    <t>Sticker | Outsiders (Holo) | Antwerp 2022</t>
-  </si>
-  <si>
-    <t>Maximus | Sabre</t>
-  </si>
-  <si>
-    <t>Dragomir | Sabre</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>Sticker | Sharks Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>XM1014 | Black Tie (Factory New)</t>
   </si>
   <si>
     <t>Sticker | Virtus.Pro (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | BIG (Holo) | Stockholm 2021</t>
+    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
+  </si>
+  <si>
+    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
   </si>
   <si>
     <t>MAC-10 | Strats (Factory New)</t>
@@ -352,66 +358,60 @@
     <t>Consumer Grade</t>
   </si>
   <si>
-    <t>AK-47 | Phantom Disruptor (Field-Tested)</t>
+    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
   </si>
   <si>
     <t>Sticker | Copenhagen Flames (Holo) | Antwerp 2022</t>
   </si>
   <si>
-    <t>Five-SeveN | Boost Protocol (Minimal Wear)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
     <t>Sticker | FURIA (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Tec-9 | Brass (Field-Tested)</t>
+  </si>
+  <si>
     <t>CZ75-Auto | Tacticat (Factory New)</t>
   </si>
   <si>
-    <t>Tec-9 | Brass (Field-Tested)</t>
-  </si>
-  <si>
-    <t>Sticker | GODSENT (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Evil Geniuses (Holo) | Stockholm 2021</t>
+    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
+    <t>Sticker | Gold Web (Foil)</t>
   </si>
   <si>
     <t>AWP | Black Nile (Minimal Wear)</t>
   </si>
   <si>
+    <t>R8 Revolver | Blaze (Factory New)</t>
+  </si>
+  <si>
     <t>Sticker | Stone Scales (Foil)</t>
   </si>
   <si>
-    <t>Sticker | Gold Web (Foil)</t>
-  </si>
-  <si>
-    <t>Sticker | Team Spirit (Holo) | Antwerp 2022</t>
+    <t>P250 | Epicenter (Field-Tested)</t>
   </si>
   <si>
     <t>Sticker | Imperial Esports (Holo) | Antwerp 2022</t>
   </si>
   <si>
+    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
+    <t>AK-47 | Slate (Field-Tested)</t>
+  </si>
+  <si>
     <t>Sticker | Wildcard (Holo) | Shanghai 2024</t>
   </si>
   <si>
-    <t>P250 | Epicenter (Field-Tested)</t>
-  </si>
-  <si>
-    <t>R8 Revolver | Blaze (Factory New)</t>
-  </si>
-  <si>
-    <t>Sticker | Astralis (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>Sticker | Renegades (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
-    <t>AK-47 | Slate (Field-Tested)</t>
-  </si>
-  <si>
     <t>Sticker | paiN Gaming (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -433,12 +433,12 @@
     <t>Sticker | Fnatic (Holo) | Shanghai 2024</t>
   </si>
   <si>
+    <t>Sticker | Perfect World (Holo) | Shanghai 2024</t>
+  </si>
+  <si>
     <t>Galil AR | Tuxedo (Factory New)</t>
   </si>
   <si>
-    <t>Sticker | Perfect World (Holo) | Shanghai 2024</t>
-  </si>
-  <si>
     <t>Sticker | G2 Esports (Holo) | Stockholm 2021</t>
   </si>
   <si>
@@ -451,12 +451,12 @@
     <t>Five-SeveN | Kami (Minimal Wear)</t>
   </si>
   <si>
+    <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
+  </si>
+  <si>
     <t>Sticker | Heroic (Holo) | Stockholm 2021</t>
   </si>
   <si>
-    <t>Sticker | Vitality (Holo) | Stockholm 2021</t>
-  </si>
-  <si>
     <t>P2000 | Amber Fade (Factory New)</t>
   </si>
   <si>
@@ -469,12 +469,12 @@
     <t>Sticker | Natus Vincere (Holo) | Stockholm 2021</t>
   </si>
   <si>
+    <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
+  </si>
+  <si>
     <t>CZ75-Auto | Tuxedo (Factory New)</t>
   </si>
   <si>
-    <t>MAG-7 | BI83 Spectrum (Minimal Wear)</t>
-  </si>
-  <si>
     <t>Sticker | forZe eSports (Holo) | Antwerp 2022</t>
   </si>
   <si>
@@ -484,10 +484,10 @@
     <t>Sticker | Broken Fang (Holo)</t>
   </si>
   <si>
+    <t>Sticker | BIG (Holo) | Antwerp 2022</t>
+  </si>
+  <si>
     <t>Sticker | Ancient Beast (Foil)</t>
-  </si>
-  <si>
-    <t>Sticker | BIG (Holo) | Antwerp 2022</t>
   </si>
   <si>
     <t>Sticker | Coiled Strike (Holo)</t>
@@ -921,7 +921,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.55</v>
+        <v>81.48</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -979,19 +979,19 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>83.47</v>
+        <v>83.24</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>9460.24</v>
+        <v>9341.74</v>
       </c>
       <c r="F6">
-        <v>6358.39</v>
+        <v>6352.6</v>
       </c>
       <c r="G6">
-        <v>6289.02</v>
+        <v>6225.44</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -1014,22 +1014,22 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C7">
-        <v>79.48</v>
+        <v>78.66</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>8426.02</v>
+        <v>9431.8</v>
       </c>
       <c r="F7">
-        <v>5942.2</v>
+        <v>5918.96</v>
       </c>
       <c r="G7">
-        <v>5919.08</v>
+        <v>5826.48</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1064,7 +1064,7 @@
         <v>7320.58</v>
       </c>
       <c r="F8">
-        <v>5306.36</v>
+        <v>6228.91</v>
       </c>
       <c r="G8">
         <v>5156.07</v>
@@ -1090,22 +1090,22 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C9">
-        <v>60.69</v>
+        <v>60.35</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>6635.49</v>
+        <v>6558.15</v>
       </c>
       <c r="F9">
-        <v>4733.99</v>
+        <v>4635.84</v>
       </c>
       <c r="G9">
-        <v>4658.96</v>
+        <v>4531.79</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1128,22 +1128,22 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10">
-        <v>57.53</v>
+        <v>58.54</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>6029.48</v>
+        <v>6360.58</v>
       </c>
       <c r="F10">
-        <v>4485.55</v>
+        <v>4462.43</v>
       </c>
       <c r="G10">
-        <v>4358.38</v>
+        <v>4300.58</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1169,7 +1169,7 @@
         <v>271</v>
       </c>
       <c r="C11">
-        <v>55.91</v>
+        <v>56.64</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
@@ -1178,10 +1178,10 @@
         <v>6336.07</v>
       </c>
       <c r="F11">
-        <v>4203.7</v>
+        <v>4188.56</v>
       </c>
       <c r="G11">
-        <v>4150.29</v>
+        <v>4138.73</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1204,22 +1204,22 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C12">
-        <v>55.61</v>
+        <v>55.91</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>5924.4</v>
+        <v>5926.01</v>
       </c>
       <c r="F12">
-        <v>4161.85</v>
+        <v>4167.63</v>
       </c>
       <c r="G12">
-        <v>4144.51</v>
+        <v>4150.29</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1242,7 +1242,7 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C13">
         <v>54.68</v>
@@ -1251,13 +1251,13 @@
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>6003.47</v>
+        <v>5927.52</v>
       </c>
       <c r="F13">
-        <v>4231.22</v>
+        <v>4161.85</v>
       </c>
       <c r="G13">
-        <v>4235.84</v>
+        <v>4173.41</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1280,7 +1280,7 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="C14">
         <v>52.57</v>
@@ -1289,13 +1289,13 @@
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>5853.3</v>
+        <v>5869.83</v>
       </c>
       <c r="F14">
-        <v>4046.25</v>
+        <v>3982.66</v>
       </c>
       <c r="G14">
-        <v>3930.64</v>
+        <v>3924.86</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1318,22 +1318,22 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C15">
-        <v>51.9</v>
+        <v>51.48</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>5819.31</v>
+        <v>5752.14</v>
       </c>
       <c r="F15">
-        <v>3786.13</v>
+        <v>3757.23</v>
       </c>
       <c r="G15">
-        <v>3858.96</v>
+        <v>3965.32</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1356,7 +1356,7 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>48.51</v>
@@ -1371,7 +1371,7 @@
         <v>3802.08</v>
       </c>
       <c r="G16">
-        <v>3630.06</v>
+        <v>3617.11</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1394,19 +1394,19 @@
         <v>35</v>
       </c>
       <c r="B17">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C17">
-        <v>47.09</v>
+        <v>46.94</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>5373.64</v>
+        <v>5433.76</v>
       </c>
       <c r="F17">
-        <v>3618.5</v>
+        <v>3684.51</v>
       </c>
       <c r="G17">
         <v>3514.45</v>
@@ -1432,22 +1432,22 @@
         <v>36</v>
       </c>
       <c r="B18">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="C18">
-        <v>45.79</v>
+        <v>44.86</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>5361.04</v>
+        <v>5229.83</v>
       </c>
       <c r="F18">
-        <v>3485.09</v>
+        <v>3494.57</v>
       </c>
       <c r="G18">
-        <v>3391.33</v>
+        <v>3265.9</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1459,7 +1459,7 @@
         <f>IF(D18=0,"",(H18-D18)/D18)</f>
       </c>
       <c r="K18" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L18" t="s">
         <v>19</v>
@@ -1470,22 +1470,22 @@
         <v>37</v>
       </c>
       <c r="B19">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C19">
-        <v>44.97</v>
+        <v>44.04</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5152.49</v>
+        <v>5361.04</v>
       </c>
       <c r="F19">
-        <v>3658.96</v>
+        <v>3455.26</v>
       </c>
       <c r="G19">
-        <v>3377.34</v>
+        <v>3288.9</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1497,7 +1497,7 @@
         <f>IF(D19=0,"",(H19-D19)/D19)</f>
       </c>
       <c r="K19" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
@@ -1508,22 +1508,22 @@
         <v>38</v>
       </c>
       <c r="B20">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C20">
-        <v>36.43</v>
+        <v>36.53</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>4139.42</v>
+        <v>4285.67</v>
       </c>
       <c r="F20">
-        <v>2895.96</v>
+        <v>2709.94</v>
       </c>
       <c r="G20">
-        <v>2953.76</v>
+        <v>2653.18</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1535,10 +1535,10 @@
         <f>IF(D20=0,"",(H20-D20)/D20)</f>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1546,22 +1546,22 @@
         <v>39</v>
       </c>
       <c r="B21">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>36.3</v>
+        <v>36.43</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>4029.6</v>
+        <v>4139.42</v>
       </c>
       <c r="F21">
         <v>3179.19</v>
       </c>
       <c r="G21">
-        <v>2685.55</v>
+        <v>2947.98</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1584,22 +1584,22 @@
         <v>40</v>
       </c>
       <c r="B22">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C22">
-        <v>35.45</v>
+        <v>36.33</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>4285.67</v>
+        <v>4029.6</v>
       </c>
       <c r="F22">
-        <v>2709.94</v>
+        <v>3150.29</v>
       </c>
       <c r="G22">
-        <v>2687.17</v>
+        <v>2685.55</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1611,10 +1611,10 @@
         <f>IF(D22=0,"",(H22-D22)/D22)</f>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1622,22 +1622,22 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C23">
-        <v>31.84</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>3548.44</v>
+        <v>3565.9</v>
       </c>
       <c r="F23">
-        <v>2456.65</v>
+        <v>2439.31</v>
       </c>
       <c r="G23">
-        <v>2419.65</v>
+        <v>2368.79</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1660,22 +1660,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>30.79</v>
+        <v>31.95</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>3545.32</v>
+        <v>661.27</v>
       </c>
       <c r="F24">
-        <v>2346.48</v>
+        <v>460.35</v>
       </c>
       <c r="G24">
-        <v>2254.34</v>
+        <v>462.43</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1687,33 +1687,33 @@
         <f>IF(D24=0,"",(H24-D24)/D24)</f>
       </c>
       <c r="K24" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="L24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B25">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="C25">
-        <v>28.02</v>
+        <v>30.18</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>3045.09</v>
+        <v>3234.8</v>
       </c>
       <c r="F25">
-        <v>2091.33</v>
+        <v>2346.13</v>
       </c>
       <c r="G25">
-        <v>2056.53</v>
+        <v>2279.77</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1725,33 +1725,33 @@
         <f>IF(D25=0,"",(H25-D25)/D25)</f>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B26">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="C26">
-        <v>23.84</v>
+        <v>27.47</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>2904.51</v>
+        <v>3074.34</v>
       </c>
       <c r="F26">
-        <v>1815.03</v>
+        <v>2057.8</v>
       </c>
       <c r="G26">
-        <v>1901.74</v>
+        <v>2062.43</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1763,33 +1763,33 @@
         <f>IF(D26=0,"",(H26-D26)/D26)</f>
       </c>
       <c r="K26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B27">
-        <v>415</v>
+        <v>241</v>
       </c>
       <c r="C27">
-        <v>23.32</v>
+        <v>23.89</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>2986.71</v>
+        <v>2844.39</v>
       </c>
       <c r="F27">
-        <v>1734.11</v>
+        <v>1803.47</v>
       </c>
       <c r="G27">
-        <v>1699.42</v>
+        <v>1801.85</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1801,10 +1801,10 @@
         <f>IF(D27=0,"",(H27-D27)/D27)</f>
       </c>
       <c r="K27" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L27" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1812,22 +1812,22 @@
         <v>49</v>
       </c>
       <c r="B28">
-        <v>70</v>
+        <v>431</v>
       </c>
       <c r="C28">
-        <v>22.82</v>
+        <v>23.24</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>2626.36</v>
+        <v>3090.18</v>
       </c>
       <c r="F28">
-        <v>1838.04</v>
+        <v>1802.31</v>
       </c>
       <c r="G28">
-        <v>1818.84</v>
+        <v>1728.21</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1839,33 +1839,33 @@
         <f>IF(D28=0,"",(H28-D28)/D28)</f>
       </c>
       <c r="K28" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="L28" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B29">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="C29">
-        <v>21.01</v>
+        <v>22.38</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>2425.67</v>
+        <v>2484.97</v>
       </c>
       <c r="F29">
-        <v>1656.65</v>
+        <v>1843.58</v>
       </c>
       <c r="G29">
-        <v>1560.58</v>
+        <v>1878.5</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1880,30 +1880,30 @@
         <v>18</v>
       </c>
       <c r="L29" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B30">
-        <v>1186</v>
+        <v>165</v>
       </c>
       <c r="C30">
-        <v>19.45</v>
+        <v>21.27</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>2228.09</v>
+        <v>2613.76</v>
       </c>
       <c r="F30">
-        <v>1468.21</v>
+        <v>1618.5</v>
       </c>
       <c r="G30">
-        <v>1421.97</v>
+        <v>1549.02</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1915,21 +1915,21 @@
         <f>IF(D30=0,"",(H30-D30)/D30)</f>
       </c>
       <c r="K30" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="L30" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B31">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C31">
-        <v>19.44</v>
+        <v>19.76</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
@@ -1938,7 +1938,7 @@
         <v>2133.3</v>
       </c>
       <c r="F31">
-        <v>1434.91</v>
+        <v>1429.02</v>
       </c>
       <c r="G31">
         <v>1450.87</v>
@@ -1961,25 +1961,25 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B32">
-        <v>29</v>
+        <v>1214</v>
       </c>
       <c r="C32">
-        <v>18.95</v>
+        <v>19.38</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2321.39</v>
+        <v>2266.01</v>
       </c>
       <c r="F32">
-        <v>1419.65</v>
+        <v>1443.93</v>
       </c>
       <c r="G32">
-        <v>1395.38</v>
+        <v>1439.31</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -1991,33 +1991,33 @@
         <f>IF(D32=0,"",(H32-D32)/D32)</f>
       </c>
       <c r="K32" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L32" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="C33">
-        <v>18.83</v>
+        <v>18.77</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>2072.49</v>
+        <v>1965.78</v>
       </c>
       <c r="F33">
-        <v>1398.84</v>
+        <v>1329.25</v>
       </c>
       <c r="G33">
-        <v>1356.07</v>
+        <v>1309.6</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2029,7 +2029,7 @@
         <f>IF(D33=0,"",(H33-D33)/D33)</f>
       </c>
       <c r="K33" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L33" t="s">
         <v>42</v>
@@ -2037,25 +2037,25 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B34">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="C34">
-        <v>18.35</v>
+        <v>18.68</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>2022.66</v>
+        <v>2323.7</v>
       </c>
       <c r="F34">
-        <v>1368.79</v>
+        <v>1410.41</v>
       </c>
       <c r="G34">
-        <v>1327.17</v>
+        <v>1352.6</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2067,7 +2067,7 @@
         <f>IF(D34=0,"",(H34-D34)/D34)</f>
       </c>
       <c r="K34" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L34" t="s">
         <v>42</v>
@@ -2075,25 +2075,25 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C35">
-        <v>16.25</v>
+        <v>18.39</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>1746.94</v>
+        <v>2315.03</v>
       </c>
       <c r="F35">
-        <v>1218.5</v>
+        <v>1410.41</v>
       </c>
       <c r="G35">
-        <v>1212.49</v>
+        <v>1368.79</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2105,33 +2105,33 @@
         <f>IF(D35=0,"",(H35-D35)/D35)</f>
       </c>
       <c r="K35" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L35" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C36">
-        <v>15.86</v>
+        <v>17.35</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>1785.67</v>
+        <v>1859.19</v>
       </c>
       <c r="F36">
-        <v>1275.03</v>
+        <v>1277.34</v>
       </c>
       <c r="G36">
-        <v>1226.01</v>
+        <v>1277.46</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2143,7 +2143,7 @@
         <f>IF(D36=0,"",(H36-D36)/D36)</f>
       </c>
       <c r="K36" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L36" t="s">
         <v>25</v>
@@ -2151,25 +2151,25 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B37">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="C37">
-        <v>13.82</v>
+        <v>15.84</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>1415.03</v>
+        <v>1738.27</v>
       </c>
       <c r="F37">
-        <v>1141.97</v>
+        <v>1255.84</v>
       </c>
       <c r="G37">
-        <v>1039.08</v>
+        <v>1225.67</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2181,33 +2181,33 @@
         <f>IF(D37=0,"",(H37-D37)/D37)</f>
       </c>
       <c r="K37" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="L37" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B38">
-        <v>1797</v>
+        <v>39</v>
       </c>
       <c r="C38">
-        <v>13.11</v>
+        <v>13.82</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1527.28</v>
+        <v>1460.12</v>
       </c>
       <c r="F38">
-        <v>989.6</v>
+        <v>1141.97</v>
       </c>
       <c r="G38">
-        <v>966.36</v>
+        <v>1098.15</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2219,33 +2219,33 @@
         <f>IF(D38=0,"",(H38-D38)/D38)</f>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L38" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B39">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C39">
-        <v>13.01</v>
+        <v>12.96</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1547.05</v>
+        <v>1548.67</v>
       </c>
       <c r="F39">
-        <v>1014.8</v>
+        <v>994.22</v>
       </c>
       <c r="G39">
-        <v>976.76</v>
+        <v>1002.54</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2265,25 +2265,25 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B40">
-        <v>108</v>
+        <v>1748</v>
       </c>
       <c r="C40">
-        <v>12.62</v>
+        <v>12.89</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1456.19</v>
+        <v>1501.16</v>
       </c>
       <c r="F40">
-        <v>981.97</v>
+        <v>987.17</v>
       </c>
       <c r="G40">
-        <v>951.33</v>
+        <v>981.27</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2295,7 +2295,7 @@
         <f>IF(D40=0,"",(H40-D40)/D40)</f>
       </c>
       <c r="K40" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L40" t="s">
         <v>65</v>
@@ -2306,22 +2306,22 @@
         <v>66</v>
       </c>
       <c r="B41">
-        <v>1478</v>
+        <v>112</v>
       </c>
       <c r="C41">
-        <v>12.41</v>
+        <v>12.39</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1450.64</v>
+        <v>1493.3</v>
       </c>
       <c r="F41">
-        <v>955.84</v>
+        <v>922.66</v>
       </c>
       <c r="G41">
-        <v>906.24</v>
+        <v>949.02</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2333,33 +2333,33 @@
         <f>IF(D41=0,"",(H41-D41)/D41)</f>
       </c>
       <c r="K41" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L41" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B42">
-        <v>540</v>
+        <v>1480</v>
       </c>
       <c r="C42">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1278.38</v>
+        <v>1517.8</v>
       </c>
       <c r="F42">
-        <v>913.06</v>
+        <v>946.71</v>
       </c>
       <c r="G42">
-        <v>913.87</v>
+        <v>913.3</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2371,33 +2371,33 @@
         <f>IF(D42=0,"",(H42-D42)/D42)</f>
       </c>
       <c r="K42" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="L42" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B43">
-        <v>123</v>
+        <v>544</v>
       </c>
       <c r="C43">
-        <v>11.82</v>
+        <v>11.9</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1412.72</v>
+        <v>1290.29</v>
       </c>
       <c r="F43">
-        <v>843.93</v>
+        <v>896.42</v>
       </c>
       <c r="G43">
-        <v>842.78</v>
+        <v>906.36</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2409,10 +2409,10 @@
         <f>IF(D43=0,"",(H43-D43)/D43)</f>
       </c>
       <c r="K43" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="L43" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2420,22 +2420,22 @@
         <v>70</v>
       </c>
       <c r="B44">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C44">
-        <v>11.63</v>
+        <v>11.82</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1578.61</v>
+        <v>1303.7</v>
       </c>
       <c r="F44">
-        <v>929.83</v>
+        <v>842.54</v>
       </c>
       <c r="G44">
-        <v>884.16</v>
+        <v>831.21</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2447,7 +2447,7 @@
         <f>IF(D44=0,"",(H44-D44)/D44)</f>
       </c>
       <c r="K44" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="L44" t="s">
         <v>71</v>
@@ -2458,22 +2458,22 @@
         <v>72</v>
       </c>
       <c r="B45">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="C45">
-        <v>11.08</v>
+        <v>11.76</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1242.78</v>
+        <v>1512.26</v>
       </c>
       <c r="F45">
-        <v>820.81</v>
+        <v>881.27</v>
       </c>
       <c r="G45">
-        <v>832.25</v>
+        <v>877.34</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2485,33 +2485,33 @@
         <f>IF(D45=0,"",(H45-D45)/D45)</f>
       </c>
       <c r="K45" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L45" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B46">
-        <v>1680</v>
+        <v>1670</v>
       </c>
       <c r="C46">
-        <v>10.71</v>
+        <v>11.04</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1336.88</v>
+        <v>1279.19</v>
       </c>
       <c r="F46">
-        <v>819.65</v>
+        <v>824.28</v>
       </c>
       <c r="G46">
-        <v>805.78</v>
+        <v>804.51</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2523,33 +2523,33 @@
         <f>IF(D46=0,"",(H46-D46)/D46)</f>
       </c>
       <c r="K46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L46" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B47">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="C47">
-        <v>10.47</v>
+        <v>11.04</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1313.18</v>
+        <v>1266.59</v>
       </c>
       <c r="F47">
-        <v>797.11</v>
+        <v>806.94</v>
       </c>
       <c r="G47">
-        <v>805.2</v>
+        <v>830.98</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2561,33 +2561,33 @@
         <f>IF(D47=0,"",(H47-D47)/D47)</f>
       </c>
       <c r="K47" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="L47" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B48">
-        <v>89</v>
+        <v>233</v>
       </c>
       <c r="C48">
-        <v>10.01</v>
+        <v>10.42</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1091.91</v>
+        <v>1313.99</v>
       </c>
       <c r="F48">
-        <v>716.65</v>
+        <v>796.53</v>
       </c>
       <c r="G48">
-        <v>714.22</v>
+        <v>771.1</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2599,33 +2599,33 @@
         <f>IF(D48=0,"",(H48-D48)/D48)</f>
       </c>
       <c r="K48" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L48" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B49">
-        <v>1404</v>
+        <v>1469</v>
       </c>
       <c r="C49">
-        <v>9.99</v>
+        <v>10.1</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1068.21</v>
+        <v>1142.43</v>
       </c>
       <c r="F49">
-        <v>727.17</v>
+        <v>745.67</v>
       </c>
       <c r="G49">
-        <v>728.32</v>
+        <v>735.26</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2637,33 +2637,33 @@
         <f>IF(D49=0,"",(H49-D49)/D49)</f>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B50">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="C50">
-        <v>9.84</v>
+        <v>10.01</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1147.98</v>
+        <v>1196.19</v>
       </c>
       <c r="F50">
-        <v>785.67</v>
+        <v>711.45</v>
       </c>
       <c r="G50">
-        <v>745.55</v>
+        <v>710.17</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2675,33 +2675,33 @@
         <f>IF(D50=0,"",(H50-D50)/D50)</f>
       </c>
       <c r="K50" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L50" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B51">
-        <v>1030</v>
+        <v>172</v>
       </c>
       <c r="C51">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1142.43</v>
+        <v>1144.86</v>
       </c>
       <c r="F51">
-        <v>716.76</v>
+        <v>781.5</v>
       </c>
       <c r="G51">
-        <v>719.08</v>
+        <v>728.21</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2713,10 +2713,10 @@
         <f>IF(D51=0,"",(H51-D51)/D51)</f>
       </c>
       <c r="K51" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="L51" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2724,22 +2724,22 @@
         <v>81</v>
       </c>
       <c r="B52">
-        <v>302</v>
+        <v>452</v>
       </c>
       <c r="C52">
-        <v>9.71</v>
+        <v>9.82</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1091.1</v>
+        <v>1077.69</v>
       </c>
       <c r="F52">
-        <v>715.61</v>
+        <v>706.36</v>
       </c>
       <c r="G52">
-        <v>739.88</v>
+        <v>682.08</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2751,10 +2751,10 @@
         <f>IF(D52=0,"",(H52-D52)/D52)</f>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="L52" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2762,19 +2762,19 @@
         <v>82</v>
       </c>
       <c r="B53">
-        <v>448</v>
+        <v>1048</v>
       </c>
       <c r="C53">
-        <v>9.58</v>
+        <v>9.78</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1050.87</v>
+        <v>1183.58</v>
       </c>
       <c r="F53">
-        <v>717.92</v>
+        <v>728.32</v>
       </c>
       <c r="G53">
         <v>700.35</v>
@@ -2789,33 +2789,33 @@
         <f>IF(D53=0,"",(H53-D53)/D53)</f>
       </c>
       <c r="K53" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="L53" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B54">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="C54">
-        <v>9.29</v>
+        <v>9.37</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1077.69</v>
+        <v>1011.33</v>
       </c>
       <c r="F54">
-        <v>704.28</v>
+        <v>674.57</v>
       </c>
       <c r="G54">
-        <v>728.32</v>
+        <v>693.64</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2835,25 +2835,25 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B55">
-        <v>95</v>
+        <v>332</v>
       </c>
       <c r="C55">
-        <v>8.69</v>
+        <v>9.15</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>949.71</v>
+        <v>1092.72</v>
       </c>
       <c r="F55">
-        <v>658.61</v>
+        <v>682.08</v>
       </c>
       <c r="G55">
-        <v>676.3</v>
+        <v>707.28</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2865,33 +2865,33 @@
         <f>IF(D55=0,"",(H55-D55)/D55)</f>
       </c>
       <c r="K55" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="L55" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B56">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="C56">
-        <v>8.62</v>
+        <v>8.96</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>985.2</v>
+        <v>949.71</v>
       </c>
       <c r="F56">
-        <v>658.73</v>
+        <v>658.96</v>
       </c>
       <c r="G56">
-        <v>618.5</v>
+        <v>669.36</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2903,7 +2903,7 @@
         <f>IF(D56=0,"",(H56-D56)/D56)</f>
       </c>
       <c r="K56" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L56" t="s">
         <v>25</v>
@@ -2911,25 +2911,25 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B57">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="C57">
-        <v>8.53</v>
+        <v>8.65</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>999.42</v>
+        <v>1011.33</v>
       </c>
       <c r="F57">
-        <v>647.4</v>
+        <v>621.97</v>
       </c>
       <c r="G57">
-        <v>624.28</v>
+        <v>635.84</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2949,25 +2949,25 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B58">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="C58">
-        <v>8.37</v>
+        <v>8.24</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>895.95</v>
+        <v>920.46</v>
       </c>
       <c r="F58">
-        <v>611.56</v>
+        <v>594.8</v>
       </c>
       <c r="G58">
-        <v>604.39</v>
+        <v>584.86</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2979,18 +2979,18 @@
         <f>IF(D58=0,"",(H58-D58)/D58)</f>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L58" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B59">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C59">
         <v>8.2</v>
@@ -3002,10 +3002,10 @@
         <v>903.12</v>
       </c>
       <c r="F59">
-        <v>584.39</v>
+        <v>580.93</v>
       </c>
       <c r="G59">
-        <v>593.64</v>
+        <v>577.92</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3017,33 +3017,33 @@
         <f>IF(D59=0,"",(H59-D59)/D59)</f>
       </c>
       <c r="K59" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L59" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B60">
-        <v>361</v>
+        <v>215</v>
       </c>
       <c r="C60">
-        <v>8.15</v>
+        <v>8.19</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>888.09</v>
+        <v>897.57</v>
       </c>
       <c r="F60">
-        <v>599.88</v>
+        <v>595.38</v>
       </c>
       <c r="G60">
-        <v>612.72</v>
+        <v>593.87</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3055,7 +3055,7 @@
         <f>IF(D60=0,"",(H60-D60)/D60)</f>
       </c>
       <c r="K60" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L60" t="s">
         <v>42</v>
@@ -3063,25 +3063,25 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B61">
-        <v>797</v>
+        <v>394</v>
       </c>
       <c r="C61">
-        <v>8.12</v>
+        <v>8.15</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>854.91</v>
+        <v>868.32</v>
       </c>
       <c r="F61">
-        <v>589.6</v>
+        <v>576.65</v>
       </c>
       <c r="G61">
-        <v>588.44</v>
+        <v>619.65</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3093,18 +3093,18 @@
         <f>IF(D61=0,"",(H61-D61)/D61)</f>
       </c>
       <c r="K61" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L61" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B62">
-        <v>855</v>
+        <v>828</v>
       </c>
       <c r="C62">
         <v>8.1</v>
@@ -3113,13 +3113,13 @@
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>982.89</v>
+        <v>942.54</v>
       </c>
       <c r="F62">
-        <v>600.81</v>
+        <v>596.99</v>
       </c>
       <c r="G62">
-        <v>578.38</v>
+        <v>573.99</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3131,33 +3131,33 @@
         <f>IF(D62=0,"",(H62-D62)/D62)</f>
       </c>
       <c r="K62" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B63">
-        <v>124</v>
+        <v>788</v>
       </c>
       <c r="C63">
-        <v>8.05</v>
+        <v>8.1</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>995.49</v>
+        <v>897.57</v>
       </c>
       <c r="F63">
-        <v>595.95</v>
+        <v>600</v>
       </c>
       <c r="G63">
-        <v>589.48</v>
+        <v>580.23</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3169,33 +3169,33 @@
         <f>IF(D63=0,"",(H63-D63)/D63)</f>
       </c>
       <c r="K63" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L63" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B64">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C64">
-        <v>7.88</v>
+        <v>7.97</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>893.64</v>
+        <v>892.83</v>
       </c>
       <c r="F64">
-        <v>566.36</v>
+        <v>581.27</v>
       </c>
       <c r="G64">
-        <v>584.51</v>
+        <v>609.48</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3207,33 +3207,33 @@
         <f>IF(D64=0,"",(H64-D64)/D64)</f>
       </c>
       <c r="K64" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L64" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B65">
-        <v>778</v>
+        <v>143</v>
       </c>
       <c r="C65">
-        <v>7.72</v>
+        <v>7.94</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>905.43</v>
+        <v>884.86</v>
       </c>
       <c r="F65">
-        <v>575.72</v>
+        <v>561.27</v>
       </c>
       <c r="G65">
-        <v>553.76</v>
+        <v>587.05</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3245,33 +3245,33 @@
         <f>IF(D65=0,"",(H65-D65)/D65)</f>
       </c>
       <c r="K65" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="L65" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B66">
-        <v>1368</v>
+        <v>1379</v>
       </c>
       <c r="C66">
-        <v>7.69</v>
+        <v>7.79</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>966.24</v>
+        <v>869.13</v>
       </c>
       <c r="F66">
-        <v>588.44</v>
+        <v>566.47</v>
       </c>
       <c r="G66">
-        <v>558.96</v>
+        <v>574.22</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3283,33 +3283,33 @@
         <f>IF(D66=0,"",(H66-D66)/D66)</f>
       </c>
       <c r="K66" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L66" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B67">
-        <v>285</v>
+        <v>1011</v>
       </c>
       <c r="C67">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>876.99</v>
+        <v>904.62</v>
       </c>
       <c r="F67">
-        <v>583.58</v>
+        <v>553.18</v>
       </c>
       <c r="G67">
-        <v>554.91</v>
+        <v>541.04</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3321,33 +3321,33 @@
         <f>IF(D67=0,"",(H67-D67)/D67)</f>
       </c>
       <c r="K67" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L67" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B68">
-        <v>1002</v>
+        <v>821</v>
       </c>
       <c r="C68">
-        <v>7.46</v>
+        <v>7.57</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>837.46</v>
+        <v>914.91</v>
       </c>
       <c r="F68">
-        <v>564.16</v>
+        <v>578.04</v>
       </c>
       <c r="G68">
-        <v>545.67</v>
+        <v>550.29</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3359,33 +3359,33 @@
         <f>IF(D68=0,"",(H68-D68)/D68)</f>
       </c>
       <c r="K68" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L68" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B69">
-        <v>1461</v>
+        <v>286</v>
       </c>
       <c r="C69">
-        <v>6.91</v>
+        <v>7.54</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>737.92</v>
+        <v>854.91</v>
       </c>
       <c r="F69">
-        <v>516.65</v>
+        <v>582.2</v>
       </c>
       <c r="G69">
-        <v>531.56</v>
+        <v>547.98</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3397,33 +3397,33 @@
         <f>IF(D69=0,"",(H69-D69)/D69)</f>
       </c>
       <c r="K69" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="L69" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B70">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C70">
-        <v>6.86</v>
+        <v>7.11</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>778.27</v>
+        <v>790.06</v>
       </c>
       <c r="F70">
-        <v>532.25</v>
+        <v>535.84</v>
       </c>
       <c r="G70">
-        <v>509.83</v>
+        <v>519.08</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3435,33 +3435,33 @@
         <f>IF(D70=0,"",(H70-D70)/D70)</f>
       </c>
       <c r="K70" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L70" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B71">
-        <v>576</v>
+        <v>1513</v>
       </c>
       <c r="C71">
-        <v>6.49</v>
+        <v>6.83</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>669.13</v>
+        <v>724.51</v>
       </c>
       <c r="F71">
-        <v>470.29</v>
+        <v>524.86</v>
       </c>
       <c r="G71">
-        <v>475.72</v>
+        <v>518.84</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3476,30 +3476,30 @@
         <v>18</v>
       </c>
       <c r="L71" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C72">
-        <v>6.49</v>
+        <v>6.73</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>628.9</v>
+        <v>844.62</v>
       </c>
       <c r="F72">
-        <v>466.47</v>
+        <v>462.31</v>
       </c>
       <c r="G72">
-        <v>462.43</v>
+        <v>469.83</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3511,10 +3511,10 @@
         <f>IF(D72=0,"",(H72-D72)/D72)</f>
       </c>
       <c r="K72" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L72" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3522,22 +3522,22 @@
         <v>103</v>
       </c>
       <c r="B73">
-        <v>209</v>
+        <v>1138</v>
       </c>
       <c r="C73">
-        <v>6.45</v>
+        <v>6.48</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>749.02</v>
+        <v>740.35</v>
       </c>
       <c r="F73">
-        <v>526.82</v>
+        <v>473.99</v>
       </c>
       <c r="G73">
-        <v>508.67</v>
+        <v>460.12</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3549,10 +3549,10 @@
         <f>IF(D73=0,"",(H73-D73)/D73)</f>
       </c>
       <c r="K73" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L73" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3560,22 +3560,22 @@
         <v>104</v>
       </c>
       <c r="B74">
-        <v>1123</v>
+        <v>212</v>
       </c>
       <c r="C74">
-        <v>6.41</v>
+        <v>6.45</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>667.63</v>
+        <v>748.21</v>
       </c>
       <c r="F74">
-        <v>473.99</v>
+        <v>525.32</v>
       </c>
       <c r="G74">
-        <v>471.68</v>
+        <v>508.67</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3587,10 +3587,10 @@
         <f>IF(D74=0,"",(H74-D74)/D74)</f>
       </c>
       <c r="K74" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L74" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3598,22 +3598,22 @@
         <v>105</v>
       </c>
       <c r="B75">
-        <v>986</v>
+        <v>1017</v>
       </c>
       <c r="C75">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>784.51</v>
+        <v>774.34</v>
       </c>
       <c r="F75">
-        <v>483.24</v>
+        <v>473.99</v>
       </c>
       <c r="G75">
-        <v>471.56</v>
+        <v>464.62</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3625,10 +3625,10 @@
         <f>IF(D75=0,"",(H75-D75)/D75)</f>
       </c>
       <c r="K75" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3636,22 +3636,22 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>58</v>
+        <v>588</v>
       </c>
       <c r="C76">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>851.68</v>
+        <v>681.85</v>
       </c>
       <c r="F76">
-        <v>508.56</v>
+        <v>466.82</v>
       </c>
       <c r="G76">
-        <v>477.46</v>
+        <v>471.45</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3663,10 +3663,10 @@
         <f>IF(D76=0,"",(H76-D76)/D76)</f>
       </c>
       <c r="K76" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="L76" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3674,10 +3674,10 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C77">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
@@ -3686,10 +3686,10 @@
         <v>674.68</v>
       </c>
       <c r="F77">
-        <v>445.32</v>
+        <v>443.93</v>
       </c>
       <c r="G77">
-        <v>449.13</v>
+        <v>445.09</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3701,10 +3701,10 @@
         <f>IF(D77=0,"",(H77-D77)/D77)</f>
       </c>
       <c r="K77" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L77" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3712,22 +3712,22 @@
         <v>108</v>
       </c>
       <c r="B78">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C78">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>615.49</v>
+        <v>641.5</v>
       </c>
       <c r="F78">
-        <v>421.73</v>
+        <v>431.1</v>
       </c>
       <c r="G78">
-        <v>436.88</v>
+        <v>425.43</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3739,10 +3739,10 @@
         <f>IF(D78=0,"",(H78-D78)/D78)</f>
       </c>
       <c r="K78" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L78" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3750,22 +3750,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C79">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>632.02</v>
+        <v>628.09</v>
       </c>
       <c r="F79">
-        <v>449.71</v>
+        <v>409.83</v>
       </c>
       <c r="G79">
-        <v>405.78</v>
+        <v>432.95</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3777,10 +3777,10 @@
         <f>IF(D79=0,"",(H79-D79)/D79)</f>
       </c>
       <c r="K79" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L79" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3788,22 +3788,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C80">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>615.49</v>
+        <v>630.52</v>
       </c>
       <c r="F80">
-        <v>434.22</v>
+        <v>442.77</v>
       </c>
       <c r="G80">
-        <v>433.53</v>
+        <v>404.62</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3815,10 +3815,10 @@
         <f>IF(D80=0,"",(H80-D80)/D80)</f>
       </c>
       <c r="K80" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L80" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3826,22 +3826,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="C81">
-        <v>5.54</v>
+        <v>5.6</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>597.34</v>
+        <v>619.42</v>
       </c>
       <c r="F81">
-        <v>404.62</v>
+        <v>413.76</v>
       </c>
       <c r="G81">
-        <v>412.6</v>
+        <v>402.89</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3853,33 +3853,33 @@
         <f>IF(D81=0,"",(H81-D81)/D81)</f>
       </c>
       <c r="K81" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L81" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B82">
-        <v>705</v>
+        <v>760</v>
       </c>
       <c r="C82">
-        <v>5.52</v>
+        <v>5.56</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>584.62</v>
+        <v>575.95</v>
       </c>
       <c r="F82">
-        <v>418.27</v>
+        <v>413.87</v>
       </c>
       <c r="G82">
-        <v>413.87</v>
+        <v>419.54</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3899,25 +3899,25 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B83">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="C83">
-        <v>5.49</v>
+        <v>5.54</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>633.64</v>
+        <v>597.34</v>
       </c>
       <c r="F83">
-        <v>440.46</v>
+        <v>449.48</v>
       </c>
       <c r="G83">
-        <v>403.47</v>
+        <v>402.77</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3929,10 +3929,10 @@
         <f>IF(D83=0,"",(H83-D83)/D83)</f>
       </c>
       <c r="K83" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="L83" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3940,22 +3940,22 @@
         <v>115</v>
       </c>
       <c r="B84">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C84">
-        <v>5.42</v>
+        <v>5.36</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>627.28</v>
+        <v>620.23</v>
       </c>
       <c r="F84">
-        <v>412.72</v>
+        <v>400.81</v>
       </c>
       <c r="G84">
-        <v>410.4</v>
+        <v>397.69</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3967,10 +3967,10 @@
         <f>IF(D84=0,"",(H84-D84)/D84)</f>
       </c>
       <c r="K84" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L84" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3978,22 +3978,22 @@
         <v>116</v>
       </c>
       <c r="B85">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="C85">
-        <v>5.36</v>
+        <v>5.2</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>556.99</v>
+        <v>626.47</v>
       </c>
       <c r="F85">
-        <v>402.08</v>
+        <v>425.2</v>
       </c>
       <c r="G85">
-        <v>390.75</v>
+        <v>386.13</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4005,10 +4005,10 @@
         <f>IF(D85=0,"",(H85-D85)/D85)</f>
       </c>
       <c r="K85" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L85" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4016,7 +4016,7 @@
         <v>117</v>
       </c>
       <c r="B86">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C86">
         <v>5.19</v>
@@ -4025,13 +4025,13 @@
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>602.08</v>
+        <v>628.9</v>
       </c>
       <c r="F86">
-        <v>411.56</v>
+        <v>404.62</v>
       </c>
       <c r="G86">
-        <v>409.25</v>
+        <v>412.49</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4043,10 +4043,10 @@
         <f>IF(D86=0,"",(H86-D86)/D86)</f>
       </c>
       <c r="K86" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L86" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4054,22 +4054,22 @@
         <v>118</v>
       </c>
       <c r="B87">
-        <v>45</v>
+        <v>451</v>
       </c>
       <c r="C87">
-        <v>5.17</v>
+        <v>5.05</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>568.09</v>
+        <v>606.01</v>
       </c>
       <c r="F87">
-        <v>392.95</v>
+        <v>369.71</v>
       </c>
       <c r="G87">
-        <v>393.18</v>
+        <v>367.63</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4081,10 +4081,10 @@
         <f>IF(D87=0,"",(H87-D87)/D87)</f>
       </c>
       <c r="K87" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L87" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4092,22 +4092,22 @@
         <v>119</v>
       </c>
       <c r="B88">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C88">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>575.95</v>
+        <v>638.38</v>
       </c>
       <c r="F88">
-        <v>442.89</v>
+        <v>381.5</v>
       </c>
       <c r="G88">
-        <v>377.92</v>
+        <v>364.16</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4119,10 +4119,10 @@
         <f>IF(D88=0,"",(H88-D88)/D88)</f>
       </c>
       <c r="K88" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L88" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4130,22 +4130,22 @@
         <v>120</v>
       </c>
       <c r="B89">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="C89">
-        <v>5.08</v>
+        <v>5.03</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>568.09</v>
+        <v>575.95</v>
       </c>
       <c r="F89">
-        <v>390.17</v>
+        <v>440.58</v>
       </c>
       <c r="G89">
-        <v>376.88</v>
+        <v>373.3</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4157,10 +4157,10 @@
         <f>IF(D89=0,"",(H89-D89)/D89)</f>
       </c>
       <c r="K89" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="L89" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4168,22 +4168,22 @@
         <v>121</v>
       </c>
       <c r="B90">
-        <v>460</v>
+        <v>50</v>
       </c>
       <c r="C90">
-        <v>4.82</v>
+        <v>4.98</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>600.46</v>
+        <v>556.19</v>
       </c>
       <c r="F90">
-        <v>375.61</v>
+        <v>378.73</v>
       </c>
       <c r="G90">
-        <v>364.16</v>
+        <v>360.69</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4195,10 +4195,10 @@
         <f>IF(D90=0,"",(H90-D90)/D90)</f>
       </c>
       <c r="K90" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="L90" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4206,22 +4206,22 @@
         <v>122</v>
       </c>
       <c r="B91">
-        <v>603</v>
+        <v>59</v>
       </c>
       <c r="C91">
-        <v>4.72</v>
+        <v>4.9</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>534.1</v>
+        <v>572.83</v>
       </c>
       <c r="F91">
-        <v>368.79</v>
+        <v>381.5</v>
       </c>
       <c r="G91">
-        <v>344.51</v>
+        <v>355.84</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4233,10 +4233,10 @@
         <f>IF(D91=0,"",(H91-D91)/D91)</f>
       </c>
       <c r="K91" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L91" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4244,22 +4244,22 @@
         <v>123</v>
       </c>
       <c r="B92">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C92">
-        <v>4.64</v>
+        <v>4.86</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>602.77</v>
+        <v>592.6</v>
       </c>
       <c r="F92">
-        <v>346.82</v>
+        <v>363.93</v>
       </c>
       <c r="G92">
-        <v>345.66</v>
+        <v>326.01</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4271,10 +4271,10 @@
         <f>IF(D92=0,"",(H92-D92)/D92)</f>
       </c>
       <c r="K92" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L92" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4282,22 +4282,22 @@
         <v>124</v>
       </c>
       <c r="B93">
-        <v>141</v>
+        <v>614</v>
       </c>
       <c r="C93">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>538.03</v>
+        <v>535.61</v>
       </c>
       <c r="F93">
-        <v>364.16</v>
+        <v>369.71</v>
       </c>
       <c r="G93">
-        <v>327.05</v>
+        <v>346.71</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4309,10 +4309,10 @@
         <f>IF(D93=0,"",(H93-D93)/D93)</f>
       </c>
       <c r="K93" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="L93" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4320,22 +4320,22 @@
         <v>125</v>
       </c>
       <c r="B94">
-        <v>61</v>
+        <v>595</v>
       </c>
       <c r="C94">
-        <v>4.58</v>
+        <v>4.59</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>560.12</v>
+        <v>495.38</v>
       </c>
       <c r="F94">
-        <v>393.06</v>
+        <v>339.88</v>
       </c>
       <c r="G94">
-        <v>376.88</v>
+        <v>335.26</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4347,10 +4347,10 @@
         <f>IF(D94=0,"",(H94-D94)/D94)</f>
       </c>
       <c r="K94" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="L94" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4358,22 +4358,22 @@
         <v>126</v>
       </c>
       <c r="B95">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C95">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>556.99</v>
+        <v>659.65</v>
       </c>
       <c r="F95">
-        <v>401.73</v>
+        <v>344.51</v>
       </c>
       <c r="G95">
-        <v>343.35</v>
+        <v>345.55</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4385,10 +4385,10 @@
         <f>IF(D95=0,"",(H95-D95)/D95)</f>
       </c>
       <c r="K95" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L95" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4396,22 +4396,22 @@
         <v>127</v>
       </c>
       <c r="B96">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="C96">
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>602.08</v>
+        <v>487.51</v>
       </c>
       <c r="F96">
-        <v>392.95</v>
+        <v>327.98</v>
       </c>
       <c r="G96">
-        <v>335.26</v>
+        <v>330.29</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4423,10 +4423,10 @@
         <f>IF(D96=0,"",(H96-D96)/D96)</f>
       </c>
       <c r="K96" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="L96" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4434,22 +4434,22 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="C97">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>504.86</v>
+        <v>537.23</v>
       </c>
       <c r="F97">
-        <v>330.4</v>
+        <v>392.83</v>
       </c>
       <c r="G97">
-        <v>333.87</v>
+        <v>339.88</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4461,10 +4461,10 @@
         <f>IF(D97=0,"",(H97-D97)/D97)</f>
       </c>
       <c r="K97" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L97" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4472,22 +4472,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>648</v>
+        <v>114</v>
       </c>
       <c r="C98">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>485.09</v>
+        <v>479.54</v>
       </c>
       <c r="F98">
-        <v>355.84</v>
+        <v>330.4</v>
       </c>
       <c r="G98">
-        <v>346.82</v>
+        <v>324.28</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4499,10 +4499,10 @@
         <f>IF(D98=0,"",(H98-D98)/D98)</f>
       </c>
       <c r="K98" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L98" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4510,7 +4510,7 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C99">
         <v>4.38</v>
@@ -4519,13 +4519,13 @@
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>513.53</v>
+        <v>511.21</v>
       </c>
       <c r="F99">
-        <v>391.79</v>
+        <v>354.57</v>
       </c>
       <c r="G99">
-        <v>321.39</v>
+        <v>316.19</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4537,10 +4537,10 @@
         <f>IF(D99=0,"",(H99-D99)/D99)</f>
       </c>
       <c r="K99" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L99" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4548,22 +4548,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>111</v>
+        <v>2885</v>
       </c>
       <c r="C100">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>481.16</v>
+        <v>464.51</v>
       </c>
       <c r="F100">
-        <v>330.4</v>
+        <v>328.32</v>
       </c>
       <c r="G100">
-        <v>328.32</v>
+        <v>330.64</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4575,10 +4575,10 @@
         <f>IF(D100=0,"",(H100-D100)/D100)</f>
       </c>
       <c r="K100" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="L100" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4586,22 +4586,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>2810</v>
+        <v>127</v>
       </c>
       <c r="C101">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>483.47</v>
+        <v>558.61</v>
       </c>
       <c r="F101">
-        <v>323.7</v>
+        <v>380</v>
       </c>
       <c r="G101">
-        <v>331.33</v>
+        <v>329.48</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4613,10 +4613,10 @@
         <f>IF(D101=0,"",(H101-D101)/D101)</f>
       </c>
       <c r="K101" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="L101" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4624,7 +4624,7 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C102">
         <v>4.1</v>
@@ -4636,10 +4636,10 @@
         <v>438.5</v>
       </c>
       <c r="F102">
-        <v>375.72</v>
+        <v>375.61</v>
       </c>
       <c r="G102">
-        <v>337.57</v>
+        <v>332.95</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4651,10 +4651,10 @@
         <f>IF(D102=0,"",(H102-D102)/D102)</f>
       </c>
       <c r="K102" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L102" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4662,7 +4662,7 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C103">
         <v>4.05</v>
@@ -4671,13 +4671,13 @@
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>477.23</v>
+        <v>448.79</v>
       </c>
       <c r="F103">
-        <v>301.73</v>
+        <v>297.8</v>
       </c>
       <c r="G103">
-        <v>308.67</v>
+        <v>300.58</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4689,10 +4689,10 @@
         <f>IF(D103=0,"",(H103-D103)/D103)</f>
       </c>
       <c r="K103" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L103" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4700,7 +4700,7 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C104">
         <v>4.05</v>
@@ -4709,13 +4709,13 @@
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>472.49</v>
+        <v>449.48</v>
       </c>
       <c r="F104">
         <v>322.31</v>
       </c>
       <c r="G104">
-        <v>289.02</v>
+        <v>280.23</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4727,10 +4727,10 @@
         <f>IF(D104=0,"",(H104-D104)/D104)</f>
       </c>
       <c r="K104" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L104" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4738,22 +4738,22 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C105">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>473.99</v>
+        <v>513.53</v>
       </c>
       <c r="F105">
-        <v>323.7</v>
+        <v>312.14</v>
       </c>
       <c r="G105">
-        <v>329.48</v>
+        <v>324.86</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4765,10 +4765,10 @@
         <f>IF(D105=0,"",(H105-D105)/D105)</f>
       </c>
       <c r="K105" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L105" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4776,22 +4776,22 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C106">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>457.46</v>
+        <v>429.83</v>
       </c>
       <c r="F106">
-        <v>322.08</v>
+        <v>317.57</v>
       </c>
       <c r="G106">
-        <v>279.77</v>
+        <v>300.58</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4803,10 +4803,10 @@
         <f>IF(D106=0,"",(H106-D106)/D106)</f>
       </c>
       <c r="K106" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L106" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4814,7 +4814,7 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C107">
         <v>3.85</v>
@@ -4823,13 +4823,13 @@
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>425.09</v>
+        <v>433.76</v>
       </c>
       <c r="F107">
         <v>304.74</v>
       </c>
       <c r="G107">
-        <v>322.31</v>
+        <v>306.36</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4852,7 +4852,7 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C108">
         <v>3.7</v>
@@ -4864,10 +4864,10 @@
         <v>515.14</v>
       </c>
       <c r="F108">
-        <v>343.93</v>
+        <v>289.02</v>
       </c>
       <c r="G108">
-        <v>277.34</v>
+        <v>265.78</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4879,10 +4879,10 @@
         <f>IF(D108=0,"",(H108-D108)/D108)</f>
       </c>
       <c r="K108" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L108" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4890,10 +4890,10 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C109">
-        <v>3.59</v>
+        <v>3.68</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
@@ -4902,10 +4902,10 @@
         <v>392.6</v>
       </c>
       <c r="F109">
-        <v>273.87</v>
+        <v>287.63</v>
       </c>
       <c r="G109">
-        <v>273.87</v>
+        <v>287.63</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4917,10 +4917,10 @@
         <f>IF(D109=0,"",(H109-D109)/D109)</f>
       </c>
       <c r="K109" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="L109" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4928,22 +4928,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="C110">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>385.55</v>
+        <v>383.93</v>
       </c>
       <c r="F110">
-        <v>277.46</v>
+        <v>263.35</v>
       </c>
       <c r="G110">
-        <v>294.45</v>
+        <v>264.74</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4955,10 +4955,10 @@
         <f>IF(D110=0,"",(H110-D110)/D110)</f>
       </c>
       <c r="K110" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="L110" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4966,7 +4966,7 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C111">
         <v>3.39</v>
@@ -4975,13 +4975,13 @@
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>372.14</v>
+        <v>382.31</v>
       </c>
       <c r="F111">
-        <v>260.12</v>
+        <v>252.95</v>
       </c>
       <c r="G111">
-        <v>261.27</v>
+        <v>253.41</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -4993,10 +4993,10 @@
         <f>IF(D111=0,"",(H111-D111)/D111)</f>
       </c>
       <c r="K111" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L111" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5007,19 +5007,19 @@
         <v>79</v>
       </c>
       <c r="C112">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>429.02</v>
+        <v>395.03</v>
       </c>
       <c r="F112">
-        <v>256.65</v>
+        <v>252.95</v>
       </c>
       <c r="G112">
-        <v>255.38</v>
+        <v>250.29</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5031,7 +5031,7 @@
         <f>IF(D112=0,"",(H112-D112)/D112)</f>
       </c>
       <c r="K112" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L112" t="s">
         <v>42</v>
@@ -5042,7 +5042,7 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C113">
         <v>3.21</v>
@@ -5051,13 +5051,13 @@
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>353.87</v>
+        <v>336.53</v>
       </c>
       <c r="F113">
-        <v>248.56</v>
+        <v>244.74</v>
       </c>
       <c r="G113">
-        <v>241.62</v>
+        <v>242.77</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5080,22 +5080,22 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C114">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>351.56</v>
+        <v>383.12</v>
       </c>
       <c r="F114">
-        <v>233.87</v>
+        <v>245.09</v>
       </c>
       <c r="G114">
-        <v>241.85</v>
+        <v>235.61</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5118,7 +5118,7 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>66</v>
+        <v>268</v>
       </c>
       <c r="C115">
         <v>3.15</v>
@@ -5127,13 +5127,13 @@
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>414.8</v>
+        <v>382.31</v>
       </c>
       <c r="F115">
-        <v>269.48</v>
+        <v>241.62</v>
       </c>
       <c r="G115">
-        <v>265.9</v>
+        <v>238.84</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5145,10 +5145,10 @@
         <f>IF(D115=0,"",(H115-D115)/D115)</f>
       </c>
       <c r="K115" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L115" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5156,22 +5156,22 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>269</v>
+        <v>69</v>
       </c>
       <c r="C116">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>392.6</v>
+        <v>455.03</v>
       </c>
       <c r="F116">
-        <v>253.18</v>
+        <v>269.48</v>
       </c>
       <c r="G116">
-        <v>242.77</v>
+        <v>265.78</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5183,10 +5183,10 @@
         <f>IF(D116=0,"",(H116-D116)/D116)</f>
       </c>
       <c r="K116" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L116" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5194,22 +5194,22 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="C117">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>353.87</v>
+        <v>363.35</v>
       </c>
       <c r="F117">
-        <v>229.94</v>
+        <v>224.28</v>
       </c>
       <c r="G117">
-        <v>227.05</v>
+        <v>223.24</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5232,7 +5232,7 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C118">
         <v>3</v>
@@ -5241,13 +5241,13 @@
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>338.96</v>
+        <v>376.07</v>
       </c>
       <c r="F118">
-        <v>229.6</v>
+        <v>231.21</v>
       </c>
       <c r="G118">
-        <v>214.8</v>
+        <v>217.57</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5270,7 +5270,7 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C119">
         <v>2.87</v>
@@ -5282,10 +5282,10 @@
         <v>310.52</v>
       </c>
       <c r="F119">
-        <v>223.7</v>
+        <v>215.03</v>
       </c>
       <c r="G119">
-        <v>214.91</v>
+        <v>208.09</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5308,22 +5308,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C120">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>304.97</v>
+        <v>363.35</v>
       </c>
       <c r="F120">
-        <v>231.21</v>
+        <v>231.1</v>
       </c>
       <c r="G120">
-        <v>202.31</v>
+        <v>218.5</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5335,10 +5335,10 @@
         <f>IF(D120=0,"",(H120-D120)/D120)</f>
       </c>
       <c r="K120" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L120" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5346,22 +5346,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="C121">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>308.9</v>
+        <v>301.04</v>
       </c>
       <c r="F121">
-        <v>206.82</v>
+        <v>191.79</v>
       </c>
       <c r="G121">
-        <v>197.92</v>
+        <v>195.26</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5373,10 +5373,10 @@
         <f>IF(D121=0,"",(H121-D121)/D121)</f>
       </c>
       <c r="K121" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="L121" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5384,22 +5384,22 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="C122">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>315.95</v>
+        <v>290.75</v>
       </c>
       <c r="F122">
-        <v>182.66</v>
+        <v>205.66</v>
       </c>
       <c r="G122">
-        <v>195.26</v>
+        <v>197.8</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -5411,10 +5411,10 @@
         <f>IF(D122=0,"",(H122-D122)/D122)</f>
       </c>
       <c r="K122" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="L122" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5434,10 +5434,10 @@
         <v>248.09</v>
       </c>
       <c r="F123">
-        <v>179.19</v>
+        <v>179.08</v>
       </c>
       <c r="G123">
-        <v>176.53</v>
+        <v>174.34</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5449,10 +5449,10 @@
         <f>IF(D123=0,"",(H123-D123)/D123)</f>
       </c>
       <c r="K123" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L123" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5460,22 +5460,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C124">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>252.02</v>
+        <v>259.08</v>
       </c>
       <c r="F124">
-        <v>164.05</v>
+        <v>167.51</v>
       </c>
       <c r="G124">
-        <v>161.85</v>
+        <v>159.42</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5498,7 +5498,7 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C125">
         <v>2.21</v>
@@ -5507,13 +5507,13 @@
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>275.72</v>
+        <v>266.24</v>
       </c>
       <c r="F125">
-        <v>172.25</v>
+        <v>172.72</v>
       </c>
       <c r="G125">
-        <v>183.12</v>
+        <v>175.03</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5525,10 +5525,10 @@
         <f>IF(D125=0,"",(H125-D125)/D125)</f>
       </c>
       <c r="K125" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L125" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5536,22 +5536,22 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="C126">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>201.39</v>
+        <v>196.65</v>
       </c>
       <c r="F126">
-        <v>138.27</v>
+        <v>138.5</v>
       </c>
       <c r="G126">
-        <v>138.5</v>
+        <v>138.61</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5563,10 +5563,10 @@
         <f>IF(D126=0,"",(H126-D126)/D126)</f>
       </c>
       <c r="K126" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L126" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5574,22 +5574,22 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C127">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>197.46</v>
+        <v>196.65</v>
       </c>
       <c r="F127">
-        <v>160.46</v>
+        <v>125.32</v>
       </c>
       <c r="G127">
-        <v>138.73</v>
+        <v>125.2</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5601,10 +5601,10 @@
         <f>IF(D127=0,"",(H127-D127)/D127)</f>
       </c>
       <c r="K127" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L127" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5612,22 +5612,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C128">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>184.05</v>
+        <v>183.24</v>
       </c>
       <c r="F128">
-        <v>134.8</v>
+        <v>130.64</v>
       </c>
       <c r="G128">
-        <v>117.92</v>
+        <v>124.62</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5639,10 +5639,10 @@
         <f>IF(D128=0,"",(H128-D128)/D128)</f>
       </c>
       <c r="K128" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L128" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5650,7 +5650,7 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C129">
         <v>1.54</v>
@@ -5659,13 +5659,13 @@
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>172.14</v>
+        <v>176.88</v>
       </c>
       <c r="F129">
-        <v>118.38</v>
+        <v>119.31</v>
       </c>
       <c r="G129">
-        <v>135.84</v>
+        <v>132.95</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5677,10 +5677,10 @@
         <f>IF(D129=0,"",(H129-D129)/D129)</f>
       </c>
       <c r="K129" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L129" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5688,22 +5688,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C130">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>154.8</v>
+        <v>157.23</v>
       </c>
       <c r="F130">
-        <v>113.18</v>
+        <v>109.48</v>
       </c>
       <c r="G130">
-        <v>114.91</v>
+        <v>115.49</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5715,10 +5715,10 @@
         <f>IF(D130=0,"",(H130-D130)/D130)</f>
       </c>
       <c r="K130" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L130" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5726,10 +5726,10 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C131">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
@@ -5738,10 +5738,10 @@
         <v>172.14</v>
       </c>
       <c r="F131">
-        <v>103.12</v>
+        <v>101.85</v>
       </c>
       <c r="G131">
-        <v>103.7</v>
+        <v>102.31</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5764,7 +5764,7 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C132">
         <v>1.35</v>
@@ -5773,13 +5773,13 @@
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>147.75</v>
+        <v>149.25</v>
       </c>
       <c r="F132">
-        <v>99.65</v>
+        <v>99.31</v>
       </c>
       <c r="G132">
-        <v>102.43</v>
+        <v>101.39</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5791,10 +5791,10 @@
         <f>IF(D132=0,"",(H132-D132)/D132)</f>
       </c>
       <c r="K132" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L132" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5802,7 +5802,7 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="C133">
         <v>0.93</v>
@@ -5811,13 +5811,13 @@
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>112.14</v>
+        <v>110.52</v>
       </c>
       <c r="F133">
-        <v>72.02</v>
+        <v>71.91</v>
       </c>
       <c r="G133">
-        <v>72.14</v>
+        <v>71.1</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5840,7 +5840,7 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>391</v>
+        <v>344</v>
       </c>
       <c r="C134">
         <v>0.82</v>
@@ -5849,13 +5849,13 @@
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>100.35</v>
+        <v>93.18</v>
       </c>
       <c r="F134">
-        <v>61.16</v>
+        <v>60.81</v>
       </c>
       <c r="G134">
-        <v>64.51</v>
+        <v>64.16</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5878,22 +5878,22 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="C135">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>78.96</v>
+        <v>81.27</v>
       </c>
       <c r="F135">
-        <v>43.35</v>
+        <v>43.01</v>
       </c>
       <c r="G135">
-        <v>47.17</v>
+        <v>46.13</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5908,7 +5908,7 @@
         <v>18</v>
       </c>
       <c r="L135" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5916,7 +5916,7 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C136">
         <v>0.47</v>
@@ -5925,13 +5925,13 @@
         <f>C136*$B$3</f>
       </c>
       <c r="E136">
-        <v>64.74</v>
+        <v>60.81</v>
       </c>
       <c r="F136">
-        <v>36.3</v>
+        <v>34.68</v>
       </c>
       <c r="G136">
-        <v>33.87</v>
+        <v>34.34</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>
@@ -5943,7 +5943,7 @@
         <f>IF(D136=0,"",(H136-D136)/D136)</f>
       </c>
       <c r="K136" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L136" t="s">
         <v>25</v>
